--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1163,27 +1163,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6133161.9322233526</v>
+        <v>7384820.0516374568</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6426890.2879607258</v>
+        <v>7794403.2465877896</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>4.7891831160390197E-2</v>
+        <v>5.5462853811788504E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>8.6309523809523725E-2</v>
+        <v>5.3097345132743445E-2</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1211,15 +1211,15 @@
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>4.7961630695443569E-2</v>
+        <v>1.674641148325362E-2</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1243,27 +1243,27 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7408856.1091459207</v>
+        <v>8808432.9749075994</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6694035.2704439107</v>
+        <v>8190359.7394492216</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-9.648194379421049E-2</v>
+        <v>-7.0168353124678395E-2</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>0</v>
+        <v>4.0404040404040442E-2</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1279,27 +1279,27 @@
       </c>
       <c r="O3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="12">
         <f t="shared" ref="Q3:Q66" si="3">IFERROR(P3/O3-1,0)</f>
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-0.10971786833855801</v>
+        <v>-0.14175654853620956</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1323,27 +1323,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7914319.7785731563</v>
+        <v>10477595.383566588</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10142443.009948455</v>
+        <v>11063906.54678895</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>0.28153060448828593</v>
+        <v>5.5958561268929286E-2</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>582</v>
+        <v>295</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>-0.17211948790896159</v>
+        <v>-0.57246376811594202</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1359,27 +1359,27 @@
       </c>
       <c r="O4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="3"/>
-        <v>-0.25</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>6.675749318801083E-2</v>
+        <v>6.1391541609822742E-2</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15676332.964186031</v>
+        <v>19011434.547334105</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16412847.693510678</v>
+        <v>19871487.575189549</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>4.6982590316707373E-2</v>
+        <v>4.523872334379142E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-6.2196307094266268E-2</v>
+        <v>-5.1909892262487767E-2</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1439,27 +1439,27 @@
       </c>
       <c r="O5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>2.0695364238410674E-2</v>
+        <v>9.0534979423868567E-3</v>
       </c>
       <c r="U5">
         <v>1</v>
@@ -1483,27 +1483,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6756366.5511118118</v>
+        <v>8381329.5959949316</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7361194.2484042142</v>
+        <v>8985930.6731321104</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>8.9519668999141766E-2</v>
+        <v>7.2136654478555551E-2</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1235955056179803E-2</v>
+        <v>3.8567493112947604E-2</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1531,15 +1531,15 @@
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>-3.1784841075794601E-2</v>
+        <v>-3.2098765432098775E-2</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1563,27 +1563,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5974812.4305151608</v>
+        <v>7145519.7571021039</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4574358.0257645678</v>
+        <v>5498928.2696352452</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>-0.23439303259095667</v>
+        <v>-0.23043690920177951</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>-0.13058419243986252</v>
+        <v>-7.7738515901060068E-2</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1603,23 +1603,23 @@
       </c>
       <c r="P7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>2.6385224274405594E-3</v>
+        <v>2.6109660574411553E-3</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -1643,31 +1643,31 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6850963.5922380947</v>
+        <v>8340069.6906619277</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7142647.5146417981</v>
+        <v>8715775.2807155531</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>4.2575605384061799E-2</v>
+        <v>4.5048255468930876E-2</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>461</v>
+        <v>489</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>-9.9609375E-2</v>
+        <v>-2.39520958083832E-2</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="O8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>7.7834179357022082E-2</v>
+        <v>5.8043117744610351E-2</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1723,27 +1723,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3088581.578316391</v>
+        <v>3747444.9194353758</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3323110.0629795291</v>
+        <v>3950550.299179432</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>7.5934042445134686E-2</v>
+        <v>5.419836291407254E-2</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>-0.13013698630136983</v>
+        <v>-3.8167938931297662E-2</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1771,15 +1771,15 @@
       </c>
       <c r="R9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>8.3333333333333259E-2</v>
+        <v>6.5868263473053856E-2</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1803,27 +1803,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>268469.072030415</v>
+        <v>586599.09295351198</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3241022.5148599562</v>
+        <v>3899890.5906057432</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>11.072237931722649</v>
+        <v>5.6483065477818766</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>178</v>
+        <v>0.34615384615384626</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1851,15 +1851,15 @@
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>0.1166666666666667</v>
+        <v>0.12021857923497259</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1883,27 +1883,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6790088.2390767578</v>
+        <v>7940043.156108438</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5541699.3345496301</v>
+        <v>6730366.9863225957</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>-0.18385459224854939</v>
+        <v>-0.15235133436966442</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>509</v>
+        <v>329</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>-0.30451866404715122</v>
+        <v>9.1185410334346573E-2</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1923,23 +1923,23 @@
       </c>
       <c r="P11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>-5.2219321148825104E-2</v>
+        <v>-2.7100271002710064E-2</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2950606.2866052231</v>
+        <v>3605945.15739296</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2806071.7254887219</v>
+        <v>3309685.3118176642</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>-4.8984699101550899E-2</v>
+        <v>-8.2158721956128389E-2</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>-0.23443223443223449</v>
+        <v>-0.17786561264822132</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>0.16915422885572129</v>
+        <v>0.14634146341463405</v>
       </c>
       <c r="U12">
         <v>2</v>
@@ -2043,31 +2043,31 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3308609.7061486649</v>
+        <v>3977027.8671158012</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3322773.159289625</v>
+        <v>4053726.7902464792</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>4.2807869162200252E-3</v>
+        <v>1.928548798082752E-2</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>219</v>
+        <v>1029</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>-4.1095890410958957E-2</v>
+        <v>-0.78620019436345967</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="O13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2087,11 +2087,11 @@
       </c>
       <c r="Q13" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6528925619834656E-2</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2123,27 +2123,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9953290.1160668265</v>
+        <v>13399000.366042772</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18811440.518050212</v>
+        <v>22834765.983763617</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>0.88997208949876372</v>
+        <v>0.70421414732057208</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>867</v>
+        <v>1622</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1283</v>
+        <v>1328</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>0.4798154555940024</v>
+        <v>-0.18125770653514184</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2163,23 +2163,23 @@
       </c>
       <c r="P14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>-1.5427769985974726E-2</v>
+        <v>-1.4685314685314643E-2</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2203,27 +2203,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21779025.984482516</v>
+        <v>26643248.081871454</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27426455.115565561</v>
+        <v>33008994.284924474</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>0.25930586313211701</v>
+        <v>0.23892530608474827</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>896</v>
+        <v>881</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>5.5803571428571397E-2</v>
+        <v>7.1509648127128234E-2</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2251,15 +2251,15 @@
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>1.3776337115072979E-2</v>
+        <v>1.4574898785425061E-2</v>
       </c>
       <c r="U15">
         <v>3</v>
@@ -2283,27 +2283,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12905524.417407267</v>
+        <v>15828242.32627888</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13166622.355437858</v>
+        <v>15843798.763286391</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>2.0231486112909591E-2</v>
+        <v>9.8282782679426361E-4</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>907</v>
+        <v>961</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.8176033934252396E-2</v>
+        <v>-5.1759834368529933E-3</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2331,15 +2331,15 @@
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>-1.851851851851849E-2</v>
+        <v>-1.3592233009708687E-2</v>
       </c>
       <c r="U16">
         <v>3</v>
@@ -2363,27 +2363,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8546617.3825953603</v>
+        <v>10913566.119168691</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12639179.227718508</v>
+        <v>14999077.867172075</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>0.47885165111724648</v>
+        <v>0.37435167418169146</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>726</v>
+        <v>657</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>703</v>
+        <v>649</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.1680440771349905E-2</v>
+        <v>-1.2176560121765601E-2</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2411,15 +2411,15 @@
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>-4.362050163576936E-3</v>
+        <v>-6.5861690450055299E-3</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2443,27 +2443,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>48912893.789661609</v>
+        <v>58775003.547264457</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>44334164.274636917</v>
+        <v>53555984.147053935</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>-9.3609867670361946E-2</v>
+        <v>-8.8796581628678206E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2900</v>
+        <v>2097</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2455</v>
+        <v>2243</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>-0.15344827586206899</v>
+        <v>6.9623271340009563E-2</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2479,27 +2479,27 @@
       </c>
       <c r="O18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>-0.60119047619047616</v>
+        <v>-0.39766081871345027</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2942</v>
+        <v>2902</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2775</v>
+        <v>2812</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>-5.6764106050305907E-2</v>
+        <v>-3.1013094417642995E-2</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2523,27 +2523,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8067116.1734909713</v>
+        <v>11584685.638031436</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23636147.164518557</v>
+        <v>28439991.090680379</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>1.9299376203591017</v>
+        <v>1.4549644227992307</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>9</v>
+        <v>1135</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1243</v>
+        <v>1190</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>137.11111111111111</v>
+        <v>4.8458149779735615E-2</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2559,27 +2559,27 @@
       </c>
       <c r="O19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1358</v>
+        <v>1368</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>-6.5837600585223477E-3</v>
+        <v>0</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2603,27 +2603,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>47589497.746377259</v>
+        <v>57592953.799537219</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38442880.37404453</v>
+        <v>48206739.535607196</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>-0.19219823291850169</v>
+        <v>-0.16297504546477082</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2214</v>
+        <v>2229</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1710</v>
+        <v>2139</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-0.22764227642276424</v>
+        <v>-4.037685060565277E-2</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2639,27 +2639,27 @@
       </c>
       <c r="O20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>-0.7</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2962</v>
+        <v>2969</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2783</v>
+        <v>2775</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-6.0432140445644822E-2</v>
+        <v>-6.5341865948130629E-2</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2683,27 +2683,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7103110.1359766154</v>
+        <v>9055980.6224311255</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6614407.9173041824</v>
+        <v>7894030.6329214247</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>-6.8801160240666959E-2</v>
+        <v>-0.12830747303407652</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9417475728155331E-2</v>
+        <v>-2.9940119760479056E-2</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2731,15 +2731,15 @@
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-3.7523452157598447E-3</v>
+        <v>-1.8382352941176516E-2</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2763,27 +2763,27 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19250463.316177037</v>
+        <v>23687070.811500505</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17836490.49011419</v>
+        <v>21540252.204000156</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>-7.3451365966585414E-2</v>
+        <v>-9.0632506846647698E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1334</v>
+        <v>1298</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1505</v>
+        <v>1446</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>0.12818590704647681</v>
+        <v>0.11402157164869031</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2799,19 +2799,19 @@
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>0.375</v>
+        <v>9.0909090909090828E-2</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1732</v>
+        <v>1739</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>-2.3094688221708681E-3</v>
+        <v>-6.3254744105808447E-3</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2843,27 +2843,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7823262.2443494322</v>
+        <v>9478921.5549611673</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7264698.4773071362</v>
+        <v>9013330.2175357286</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>-7.1397806898999772E-2</v>
+        <v>-4.9118598009892045E-2</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>766</v>
+        <v>740</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>789</v>
+        <v>824</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>3.0026109660574507E-2</v>
+        <v>0.11351351351351346</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2879,27 +2879,27 @@
       </c>
       <c r="O23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5714285714285714</v>
+        <v>-0.5</v>
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>-5.4176072234762951E-2</v>
+        <v>-5.1252847380410027E-2</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2923,27 +2923,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9933707.18830988</v>
+        <v>12129368.103966432</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9164224.2770352941</v>
+        <v>11323368.874365836</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>-7.7461807227429014E-2</v>
+        <v>-6.6450224174252281E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>757</v>
+        <v>837</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>669</v>
+        <v>769</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>-0.11624834874504619</v>
+        <v>-8.1242532855436034E-2</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="O24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2967,19 +2967,19 @@
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="3"/>
-        <v>-0.75</v>
+        <v>-0.8</v>
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>-1.4772727272727271E-2</v>
+        <v>-1.9144144144144115E-2</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -3003,27 +3003,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2051568.491111354</v>
+        <v>2536402.8153050868</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2229968.7390251779</v>
+        <v>2808535.7045010701</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>8.6957978096642963E-2</v>
+        <v>0.10729087964809336</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>0.10273972602739723</v>
+        <v>0.33522727272727271</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3051,15 +3051,15 @@
       </c>
       <c r="R25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="S25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="4"/>
-        <v>-7.2340425531914887E-2</v>
+        <v>-5.1948051948051965E-2</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -3083,27 +3083,27 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18618927.923217751</v>
+        <v>22511788.425732885</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19277893.993381854</v>
+        <v>22367217.405995153</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>3.5392267099459307E-2</v>
+        <v>-6.422013969022311E-3</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1398</v>
+        <v>1297</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>6.2947067238912746E-2</v>
+        <v>0.14494988434849643</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3111,11 +3111,11 @@
       </c>
       <c r="M26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.16666666666666663</v>
       </c>
       <c r="O26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3131,15 +3131,15 @@
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1646</v>
+        <v>1639</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>-9.0307043949428012E-3</v>
+        <v>-1.4431749849669218E-2</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -3163,27 +3163,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14506889.258832024</v>
+        <v>18118545.915352695</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16063145.378722521</v>
+        <v>20204926.878771558</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>0.10727703866237359</v>
+        <v>0.11515167790870984</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>0.11831442463533226</v>
+        <v>0.10416666666666674</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3203,23 +3203,23 @@
       </c>
       <c r="P27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>3.2444959443800769E-2</v>
+        <v>3.3333333333333437E-2</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -3243,27 +3243,27 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14387241.825953936</v>
+        <v>17752317.438190568</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15559954.107234888</v>
+        <v>19114856.538799368</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>8.1510569952708556E-2</v>
+        <v>7.6752745400866296E-2</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>664</v>
+        <v>911</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>-0.19612590799031482</v>
+        <v>0.10157194679564685</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3287,19 +3287,19 @@
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-3.9399624765478425E-2</v>
+        <v>-5.070422535211272E-2</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -3323,27 +3323,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19992124.091455083</v>
+        <v>24186906.744684663</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21918944.083954044</v>
+        <v>25226309.632355992</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>9.6378953216007313E-2</v>
+        <v>4.2973783239138141E-2</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>864</v>
+        <v>832</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>936</v>
+        <v>812</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>8.3333333333333259E-2</v>
+        <v>-2.4038461538461564E-2</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3371,15 +3371,15 @@
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>2.6881720430107503E-2</v>
+        <v>2.5067144136078801E-2</v>
       </c>
       <c r="U29">
         <v>0</v>
@@ -3403,27 +3403,27 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28204861.723208327</v>
+        <v>34394456.147691317</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30169389.89326692</v>
+        <v>35006468.816651084</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>6.9652111374901127E-2</v>
+        <v>1.7793933601733869E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1146</v>
+        <v>1185</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1204</v>
+        <v>1169</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>5.0610820244328059E-2</v>
+        <v>-1.3502109704641385E-2</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="O30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3447,19 +3447,19 @@
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="3"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.5</v>
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1478</v>
+        <v>1459</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>-2.3680649526387043E-2</v>
+        <v>-7.5394105551748192E-3</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3483,27 +3483,27 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11521977.507242309</v>
+        <v>14133878.193473892</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10852281.281489624</v>
+        <v>13924727.038236933</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>-5.8123375551786816E-2</v>
+        <v>-1.4797860316465128E-2</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>679</v>
+        <v>612</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>0.2859848484848484</v>
+        <v>0.17692307692307696</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="P31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="3"/>
@@ -3531,15 +3531,15 @@
       </c>
       <c r="R31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>5.8997050147493457E-3</v>
+        <v>1.0309278350515427E-2</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3563,27 +3563,27 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35178724.13029144</v>
+        <v>43001448.166093811</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19349044.074072417</v>
+        <v>26036926.729291752</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-0.44997879961736642</v>
+        <v>-0.39451046790973909</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1579</v>
+        <v>1571</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1669</v>
+        <v>1707</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>5.6998100063331281E-2</v>
+        <v>8.6569064290261011E-2</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1937</v>
+        <v>1943</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-4.2333505420753759E-2</v>
+        <v>-4.52907874420998E-2</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3643,27 +3643,27 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11496843.696313253</v>
+        <v>14132076.933236703</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12468667.542720955</v>
+        <v>14724372.928554051</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>8.452962152728416E-2</v>
+        <v>4.1911461288775431E-2</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>696</v>
+        <v>887</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>644</v>
+        <v>670</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>-7.4712643678160884E-2</v>
+        <v>-0.24464487034949267</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3671,11 +3671,11 @@
       </c>
       <c r="M33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3691,15 +3691,15 @@
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>2.0262216924910703E-2</v>
+        <v>1.3095238095238049E-2</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3723,27 +3723,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11081479.212508269</v>
+        <v>13627139.337142861</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10864601.777345827</v>
+        <v>13006674.485248519</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>-1.957116292901051E-2</v>
+        <v>-4.553155556303512E-2</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>557</v>
+        <v>746</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>1.4362657091562037E-2</v>
+        <v>-0.20375335120643434</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3771,15 +3771,15 @@
       </c>
       <c r="R34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>732</v>
+        <v>745</v>
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>9.5628415300545999E-3</v>
+        <v>-1.7449664429530221E-2</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3803,27 +3803,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17141886.430531561</v>
+        <v>20545921.86789586</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19206431.863842171</v>
+        <v>22932126.399725944</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>0.12043863676715483</v>
+        <v>0.11614005675543138</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>836</v>
+        <v>465</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>817</v>
+        <v>908</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2727272727272707E-2</v>
+        <v>0.95268817204301071</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="O35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3847,19 +3847,19 @@
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="3"/>
-        <v>-0.16666666666666663</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>6.8027210884353817E-3</v>
+        <v>2.3195876288659711E-2</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3883,27 +3883,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15596539.676497009</v>
+        <v>19120041.93568055</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17745440.702579733</v>
+        <v>21141554.628010023</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>0.13778062766839105</v>
+        <v>0.10572741938170438</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>769</v>
+        <v>811</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1028</v>
+        <v>858</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>0.33680104031209357</v>
+        <v>5.7953144266337908E-2</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3923,23 +3923,23 @@
       </c>
       <c r="P36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>233</v>
+        <v>317</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="3"/>
-        <v>0.94166666666666665</v>
+        <v>1.6416666666666666</v>
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1365</v>
+        <v>1335</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1381</v>
+        <v>1452</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>1.172161172161168E-2</v>
+        <v>8.764044943820215E-2</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3963,27 +3963,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28549586.631023839</v>
+        <v>34901512.498659305</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29255931.280371618</v>
+        <v>35002790.497653201</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>2.4740976409802773E-2</v>
+        <v>2.9018226358465959E-3</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1439</v>
+        <v>1575</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1714</v>
+        <v>1484</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>0.19110493398193196</v>
+        <v>-5.7777777777777817E-2</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3999,27 +3999,27 @@
       </c>
       <c r="O37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>118</v>
+        <v>235</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="3"/>
-        <v>0.73529411764705888</v>
+        <v>2.4057971014492754</v>
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2469</v>
+        <v>2418</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2195</v>
+        <v>2265</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>-0.11097610368570276</v>
+        <v>-6.3275434243176165E-2</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4043,27 +4043,27 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10313879.042900581</v>
+        <v>12522131.034147704</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10916359.854945768</v>
+        <v>12972219.559267271</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>5.8414570263929599E-2</v>
+        <v>3.5943444761293408E-2</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>-5.7939914163090078E-2</v>
+        <v>3.3557046979865834E-2</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4079,27 +4079,27 @@
       </c>
       <c r="O38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q38" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>-4.166666666666663E-2</v>
+        <v>-4.0257648953301084E-2</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4123,27 +4123,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34467171.240222543</v>
+        <v>41927511.893101111</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33435528.542818047</v>
+        <v>40159357.461528517</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>-2.9931168131389629E-2</v>
+        <v>-4.2171699481731717E-2</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1934</v>
+        <v>1950</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1987</v>
+        <v>1850</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>2.7404343329886283E-2</v>
+        <v>-5.1282051282051322E-2</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4171,15 +4171,15 @@
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2049</v>
+        <v>2064</v>
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2047</v>
+        <v>2040</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>-9.7608589555875369E-4</v>
+        <v>-1.1627906976744207E-2</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4203,27 +4203,27 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22237665.004112385</v>
+        <v>27163671.010994777</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26120332.746377055</v>
+        <v>31332334.071481273</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>0.17459871535732963</v>
+        <v>0.15346464249251079</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>1.8820577164366359E-2</v>
+        <v>1.9925280199252882E-2</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4231,15 +4231,15 @@
       </c>
       <c r="M40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N40" s="12">
         <f t="shared" si="2"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4247,19 +4247,19 @@
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="R40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>3.3370411568409253E-2</v>
+        <v>3.44444444444445E-2</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10362877.114542577</v>
+        <v>14178492.832121568</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18743763.672474202</v>
+        <v>22149087.91487515</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>0.80874128538786216</v>
+        <v>0.5621609558313625</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1019</v>
+        <v>944</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>0.10162162162162169</v>
+        <v>2.7203482045701888E-2</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
@@ -4331,15 +4331,15 @@
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1043</v>
+        <v>1052</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-3.8709677419354827E-2</v>
+        <v>-2.7726432532347522E-2</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4363,27 +4363,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17698698.547770157</v>
+        <v>21673565.670844473</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18394155.295887496</v>
+        <v>22463428.205046136</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>3.929423094247575E-2</v>
+        <v>3.6443589679578947E-2</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>788</v>
+        <v>635</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>0.22170542635658919</v>
+        <v>-2.457757296466978E-2</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4411,15 +4411,15 @@
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>2.8083028083027983E-2</v>
+        <v>1.2121212121212199E-2</v>
       </c>
       <c r="U42">
         <v>1</v>
@@ -4443,27 +4443,27 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11326902.340657758</v>
+        <v>13895483.106158944</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11180304.84275686</v>
+        <v>13423472.227419101</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>-1.2942417396386352E-2</v>
+        <v>-3.3968655507244039E-2</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>708</v>
+        <v>560</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>595</v>
+        <v>563</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>-0.15960451977401124</v>
+        <v>5.3571428571428381E-3</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="O43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4491,15 +4491,15 @@
       </c>
       <c r="R43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>692</v>
+        <v>707</v>
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>4.1907514450867156E-2</v>
+        <v>1.1315417256011262E-2</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4523,27 +4523,27 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9749315.3487538137</v>
+        <v>12161003.483174358</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10329690.532225767</v>
+        <v>12527683.802709805</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>5.9529840066783635E-2</v>
+        <v>3.0152143286758859E-2</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>744</v>
+        <v>713</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>4.5698924731182755E-2</v>
+        <v>7.7138849929873743E-2</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4551,11 +4551,11 @@
       </c>
       <c r="M44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4575,11 +4575,11 @@
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>2.6162790697674465E-2</v>
+        <v>2.1802325581395277E-2</v>
       </c>
       <c r="U44">
         <v>2</v>
@@ -4603,27 +4603,27 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30643816.421466332</v>
+        <v>37273755.084821194</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34833280.631897286</v>
+        <v>41936647.835470937</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>0.13671483188680722</v>
+        <v>0.1250985509787983</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1127</v>
+        <v>1078</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>6.5661047027506747E-2</v>
+        <v>0.10946196660482377</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="P45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="3"/>
@@ -4651,15 +4651,15 @@
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>2.8157683024939706E-2</v>
+        <v>3.1400966183574797E-2</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4683,31 +4683,31 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14694364.793953007</v>
+        <v>17874087.659617409</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14864008.548044087</v>
+        <v>17870643.858846333</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>1.1544817109814254E-2</v>
+        <v>-1.926700168790596E-4</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>3212</v>
+        <v>881</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>925</v>
+        <v>899</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>-0.71201743462017442</v>
+        <v>2.0431328036322416E-2</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="N46" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="O46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4735,11 +4735,11 @@
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>-3.0634573304157531E-2</v>
+        <v>-3.8293216630196913E-2</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4763,27 +4763,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26326685.795884985</v>
+        <v>32056870.004816383</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26740693.628350247</v>
+        <v>32663997.039998908</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>1.5725786210810222E-2</v>
+        <v>1.8939061583096217E-2</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1033</v>
+        <v>1045</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1050</v>
+        <v>1014</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>1.6456921587608919E-2</v>
+        <v>-2.966507177033495E-2</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4791,11 +4791,11 @@
       </c>
       <c r="M47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N47" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-8.333333333333337E-2</v>
       </c>
       <c r="O47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4811,15 +4811,15 @@
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1402</v>
+        <v>1417</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>2.8613352898019029E-2</v>
+        <v>4.4985250737463067E-2</v>
       </c>
       <c r="U47">
         <v>5</v>
@@ -4843,27 +4843,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13634364.861858128</v>
+        <v>16539048.45741608</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12304766.659372153</v>
+        <v>15061140.755258827</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>-9.7518162082159021E-2</v>
+        <v>-8.9358689888508147E-2</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>385</v>
+        <v>514</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>3.2171581769437019E-2</v>
+        <v>0.42777777777777781</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4871,15 +4871,15 @@
       </c>
       <c r="M48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N48" s="12">
         <f t="shared" si="2"/>
-        <v>0.16666666666666674</v>
+        <v>0</v>
       </c>
       <c r="O48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -4895,11 +4895,11 @@
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>1.2422360248447228E-2</v>
+        <v>1.6563146997929712E-2</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4923,27 +4923,27 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10085942.515286084</v>
+        <v>12081136.709517296</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10771677.970238339</v>
+        <v>13095908.736033432</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>6.7989228960304571E-2</v>
+        <v>8.3996402897809963E-2</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>8.9743589743589647E-2</v>
+        <v>0.26229508196721318</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4971,15 +4971,15 @@
       </c>
       <c r="R49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>4.405286343612369E-3</v>
+        <v>2.1929824561404132E-3</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -5003,31 +5003,31 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8794364.8169755638</v>
+        <v>10520584.106780592</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5287043.4016682496</v>
+        <v>5501887.3312636809</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-0.39881463736155354</v>
+        <v>-0.4770359444474499</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>319</v>
+        <v>5</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-7.80346820809249E-2</v>
+        <v>-0.98493975903614461</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="N50" s="12">
         <f t="shared" si="2"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.5</v>
       </c>
       <c r="O50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5051,15 +5051,15 @@
       </c>
       <c r="R50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="S50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="4"/>
-        <v>-6.2937062937062915E-2</v>
+        <v>-6.9605568445475607E-2</v>
       </c>
       <c r="U50">
         <v>4</v>
@@ -5083,27 +5083,27 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20589581.956771232</v>
+        <v>24723580.217376906</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21708708.646214969</v>
+        <v>26527780.340592857</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>5.4354026798280497E-2</v>
+        <v>7.2974872868447838E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>940</v>
+        <v>962</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>9.6670247046186653E-3</v>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="O51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5127,19 +5127,19 @@
       </c>
       <c r="Q51" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-2.7247956403270157E-3</v>
+        <v>-4.5289855072463414E-3</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5163,27 +5163,27 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18172569.992024127</v>
+        <v>23331162.81574592</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21711269.083108783</v>
+        <v>26543308.271027669</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>0.19472749823705593</v>
+        <v>0.13767618359398326</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>805</v>
+        <v>960</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>-9.6520763187429859E-2</v>
+        <v>7.9865016872890937E-2</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5199,27 +5199,27 @@
       </c>
       <c r="O52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q52" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="R52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>973</v>
+        <v>995</v>
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>-4.213771839671121E-2</v>
+        <v>-5.8291457286432147E-2</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5243,27 +5243,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>39084951.029873677</v>
+        <v>46692177.299890816</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>40331079.886328921</v>
+        <v>48360579.666022353</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>3.1882574331557834E-2</v>
+        <v>3.5731946176248197E-2</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1631</v>
+        <v>1445</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1802</v>
+        <v>1627</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>0.1048436541998774</v>
+        <v>0.12595155709342554</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5283,23 +5283,23 @@
       </c>
       <c r="P53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q53" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2110</v>
+        <v>2103</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>1.6867469879518149E-2</v>
+        <v>1.3005780346820872E-2</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5323,27 +5323,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8843951.5906833</v>
+        <v>11101958.599655284</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10725083.805626824</v>
+        <v>12869337.990031293</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>0.2127026811097894</v>
+        <v>0.15919527842869874</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>0.10192307692307701</v>
+        <v>9.7378277153558068E-2</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="O54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5367,19 +5367,19 @@
       </c>
       <c r="Q54" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>-4.2584434654919234E-2</v>
+        <v>-4.1055718475073277E-2</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5403,27 +5403,27 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15871422.260580655</v>
+        <v>19744310.44305547</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18384833.519360822</v>
+        <v>22427850.574070819</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>0.15836080834561672</v>
+        <v>0.13591460379206155</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>758</v>
+        <v>695</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>856</v>
+        <v>807</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>0.12928759894459096</v>
+        <v>0.16115107913669058</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5431,11 +5431,11 @@
       </c>
       <c r="M55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N55" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="O55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5443,11 +5443,11 @@
       </c>
       <c r="P55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q55" s="12">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -5455,11 +5455,11 @@
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>3.2295271049596286E-2</v>
+        <v>4.2675893886966465E-2</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5483,27 +5483,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9791521.9231825955</v>
+        <v>12108515.79752842</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10484385.024936249</v>
+        <v>12081050.832576821</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>7.0761533006755251E-2</v>
+        <v>-2.2682354642676872E-3</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>562</v>
+        <v>632</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12050078247261342</v>
+        <v>-6.2893081761006275E-3</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="O56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5531,15 +5531,15 @@
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-8.2210242587601123E-2</v>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="U56">
         <v>2</v>
@@ -5563,27 +5563,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21348622.992430314</v>
+        <v>25953478.849800728</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23099376.1903781</v>
+        <v>28241591.85484669</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>8.2007780950019926E-2</v>
+        <v>8.816209257679275E-2</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>999</v>
+        <v>986</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1147</v>
+        <v>1112</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>0.14814814814814814</v>
+        <v>0.12778904665314395</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="M57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" s="12">
         <f t="shared" si="2"/>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>5.4397098821397094E-3</v>
+        <v>4.5289855072463414E-3</v>
       </c>
       <c r="U57">
         <v>2</v>
@@ -5643,27 +5643,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24991750.938691661</v>
+        <v>31393322.515753064</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31747644.601805378</v>
+        <v>38769776.034656703</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>0.2703249436058679</v>
+        <v>0.23496887005834322</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1429</v>
+        <v>1510</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1600</v>
+        <v>1633</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>0.11966410076976897</v>
+        <v>8.1456953642384144E-2</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5679,27 +5679,27 @@
       </c>
       <c r="O58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q58" s="12">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1399</v>
+        <v>1425</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>0.13867047891350959</v>
+        <v>0.12070175438596498</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5723,31 +5723,31 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14329352.807133865</v>
+        <v>17452043.978152473</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12337857.407070264</v>
+        <v>15455780.272549629</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>-0.13898013586992808</v>
+        <v>-0.11438566783935955</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>769</v>
+        <v>812</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>0.11773255813953498</v>
+        <v>0.18540145985401457</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="N59" s="12">
         <f t="shared" si="2"/>
-        <v>0.66666666666666674</v>
+        <v>0.25</v>
       </c>
       <c r="O59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5763,23 +5763,23 @@
       </c>
       <c r="P59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q59" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>2.8460543337645472E-2</v>
+        <v>4.1504539559014342E-2</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5803,27 +5803,27 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15913750.060137004</v>
+        <v>19453163.939775139</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16570255.383356037</v>
+        <v>20408682.048246805</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>4.1253967213142229E-2</v>
+        <v>4.9118904843954647E-2</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>1.4644351464435212E-2</v>
+        <v>4.366812227074246E-2</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="O60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5847,19 +5847,19 @@
       </c>
       <c r="Q60" s="12">
         <f t="shared" si="3"/>
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="R60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>-1.6975308641975273E-2</v>
+        <v>-1.5360983102918557E-2</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5883,63 +5883,63 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>51156826.689083554</v>
+        <v>62712300.78279233</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>53725402.89775309</v>
+        <v>65608445.879055992</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>5.0209842457207055E-2</v>
+        <v>4.6181451806315055E-2</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1633</v>
+        <v>1606</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1785</v>
+        <v>1794</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>9.3080220453153784E-2</v>
+        <v>0.11706102117061024</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N61" s="12">
         <f t="shared" si="2"/>
-        <v>9.0909090909090828E-2</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2000</v>
+        <v>1970</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1984</v>
+        <v>1971</v>
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>-8.0000000000000071E-3</v>
+        <v>5.0761421319789335E-4</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5963,27 +5963,27 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36192720.881001942</v>
+        <v>45460845.578881703</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38409566.627921052</v>
+        <v>46716196.328422241</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>6.1251149207816713E-2</v>
+        <v>2.761388912932361E-2</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1195</v>
+        <v>1219</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1313</v>
+        <v>1265</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>9.8744769874477001E-2</v>
+        <v>3.7735849056603765E-2</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5999,15 +5999,15 @@
       </c>
       <c r="O62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q62" s="12">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -6015,11 +6015,11 @@
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>1.1385199240986799E-2</v>
+        <v>1.5812776723592714E-2</v>
       </c>
       <c r="U62">
         <v>9</v>
@@ -6043,27 +6043,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24480721.503467716</v>
+        <v>30167393.236838799</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26258051.197483271</v>
+        <v>31840007.43950006</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>7.260119738561599E-2</v>
+        <v>5.5444439283496072E-2</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5572005383580065E-2</v>
+        <v>-2.6027397260273921E-2</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6083,15 +6083,15 @@
       </c>
       <c r="P63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>9.0293453724605843E-3</v>
+        <v>1.2457531143827749E-2</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6123,27 +6123,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36777108.621974111</v>
+        <v>45486578.400095366</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34416120.328050949</v>
+        <v>41636311.204481982</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>-6.4197224371044914E-2</v>
+        <v>-8.464622600862215E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1387</v>
+        <v>1437</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1470</v>
+        <v>1292</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>5.9841384282624421E-2</v>
+        <v>-0.10090466249130137</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6159,27 +6159,27 @@
       </c>
       <c r="O64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>108</v>
+        <v>366</v>
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>2.2870370370370372</v>
+        <v>1.6393442622950838E-2</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2104</v>
+        <v>2335</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2362</v>
+        <v>2338</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>0.12262357414448677</v>
+        <v>1.2847965738758127E-3</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6203,31 +6203,31 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>622601.72598268196</v>
+        <v>1088870.296364038</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2808305.1556609101</v>
+        <v>3332193.916553128</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>3.5105964832147363</v>
+        <v>2.0602303393526382</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>254</v>
+        <v>415</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5748031496062964E-2</v>
+        <v>-0.36144578313253017</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="N65" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="R65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>-2.4096385542168641E-2</v>
+        <v>-1.619433198380571E-2</v>
       </c>
       <c r="U65">
         <v>2</v>
@@ -6283,51 +6283,51 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26797354.943077229</v>
+        <v>32343585.173141804</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26291966.492786366</v>
+        <v>31714020.902646456</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-1.8859639369796177E-2</v>
+        <v>-1.9464888234410727E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1623</v>
+        <v>1542</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1558</v>
+        <v>1458</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>-4.0049291435613088E-2</v>
+        <v>-5.4474708171206254E-2</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N66" s="12">
         <f t="shared" si="2"/>
-        <v>0.39999999999999991</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="O66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q66" s="12">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>1.3333333333333335</v>
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -6335,11 +6335,11 @@
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1607</v>
+        <v>1625</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>-4.0023894862604492E-2</v>
+        <v>-2.9271206690561491E-2</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6363,27 +6363,27 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12442434.197569257</v>
+        <v>15328774.192921566</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12151901.567606615</v>
+        <v>14576827.875886289</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>-2.335014397901336E-2</v>
+        <v>-4.9054562848378724E-2</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>582</v>
+        <v>614</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>2.5773195876288568E-2</v>
+        <v>-1.9543973941368087E-2</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6403,23 +6403,23 @@
       </c>
       <c r="P67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q67" s="12">
         <f t="shared" ref="Q67:Q85" si="8">IFERROR(P67/O67-1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>8.46047156726768E-2</v>
+        <v>7.5136612021857951E-2</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6443,27 +6443,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17684885.685970344</v>
+        <v>21872709.188291144</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19240732.411861435</v>
+        <v>23086254.829625059</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>8.7976069142780222E-2</v>
+        <v>5.5482182425922177E-2</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>946</v>
+        <v>859</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>842</v>
+        <v>889</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>-0.10993657505285415</v>
+        <v>3.4924330616996402E-2</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6491,15 +6491,15 @@
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1515</v>
+        <v>1477</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>0.10989010989010994</v>
+        <v>7.8889700511322047E-2</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6523,27 +6523,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12901963.149557795</v>
+        <v>14513828.217951603</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15409388.827121716</v>
+        <v>18591108.258868024</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>0.19434450776972345</v>
+        <v>0.28092381828478485</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1218</v>
+        <v>597</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1426</v>
+        <v>1361</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>0.17077175697865354</v>
+        <v>1.2797319932998326</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6559,11 +6559,11 @@
       </c>
       <c r="O69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q69" s="12">
         <f t="shared" si="8"/>
@@ -6571,15 +6571,15 @@
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1296</v>
+        <v>1287</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1293</v>
+        <v>1314</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>-2.3148148148147696E-3</v>
+        <v>2.0979020979021046E-2</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6603,27 +6603,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32750863.538609803</v>
+        <v>39840425.618532181</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33955011.525192656</v>
+        <v>41382219.443157539</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>3.6766907998114107E-2</v>
+        <v>3.8699230760932846E-2</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1175</v>
+        <v>1229</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1330</v>
+        <v>1266</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>0.13191489361702136</v>
+        <v>3.0105777054515892E-2</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6639,11 +6639,11 @@
       </c>
       <c r="O70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q70" s="12">
         <f t="shared" si="8"/>
@@ -6651,15 +6651,15 @@
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1728</v>
+        <v>1737</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>3.067129629629628E-2</v>
+        <v>2.3028209556706924E-2</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6683,27 +6683,27 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6739342.6329431906</v>
+        <v>8058967.8740208512</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6439608.1652408363</v>
+        <v>7736582.7318614321</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-4.4475327050029323E-2</v>
+        <v>-4.0003279228680189E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>473</v>
+        <v>433</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>433</v>
+        <v>473</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>-8.456659619450313E-2</v>
+        <v>9.2378752886836057E-2</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6723,23 +6723,23 @@
       </c>
       <c r="P71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q71" s="12">
         <f t="shared" si="8"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>-4.4921875E-2</v>
+        <v>-5.6092843326885911E-2</v>
       </c>
       <c r="U71">
         <v>1</v>
@@ -6763,27 +6763,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10301292.77501234</v>
+        <v>12600460.760555159</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12293560.868492804</v>
+        <v>15138195.546056001</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>0.1933998127218628</v>
+        <v>0.20140015779780351</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>879</v>
+        <v>999</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>780</v>
+        <v>812</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>-0.11262798634812288</v>
+        <v>-0.18718718718718719</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6811,15 +6811,15 @@
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>-8.9485458612975632E-3</v>
+        <v>5.6179775280897903E-3</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6843,27 +6843,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9995696.629863428</v>
+        <v>12247960.588351307</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10923169.481146952</v>
+        <v>13531617.314519268</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>9.2787214901318693E-2</v>
+        <v>0.10480575250942681</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>465</v>
+        <v>513</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>6.4073226544622441E-2</v>
+        <v>4.0567951318458473E-2</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6891,15 +6891,15 @@
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-4.4274809160305351E-2</v>
+        <v>-3.9755351681957207E-2</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6923,27 +6923,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8664072.1058999225</v>
+        <v>10279087.37903594</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6517199.5900564799</v>
+        <v>8513336.6178804133</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>-0.24779024107861469</v>
+        <v>-0.17178088832640448</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>710</v>
+        <v>732</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>778</v>
+        <v>1095</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>9.5774647887324038E-2</v>
+        <v>0.49590163934426235</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="O74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6967,19 +6967,19 @@
       </c>
       <c r="Q74" s="12">
         <f t="shared" si="8"/>
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>-3.3955857385399302E-3</v>
+        <v>1.1686143572620988E-2</v>
       </c>
       <c r="U74">
         <v>1</v>
@@ -7003,27 +7003,27 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9280196.177744668</v>
+        <v>11214438.848868918</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7529202.7045356091</v>
+        <v>9194851.3412616476</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>-0.18868065283018576</v>
+        <v>-0.18008814661385975</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>-5.7522123893805288E-2</v>
+        <v>-3.5416666666666652E-2</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="P75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="12">
         <f t="shared" si="8"/>
@@ -7051,15 +7051,15 @@
       </c>
       <c r="R75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>2.2727272727272041E-3</v>
+        <v>-2.8953229398663738E-2</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -7083,27 +7083,27 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23425680.163103808</v>
+        <v>29020876.322520785</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19142013.66925722</v>
+        <v>22449998.135948103</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>-0.18286199009040938</v>
+        <v>-0.22641901345596338</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>-0.28514056224899598</v>
+        <v>-0.28609271523178803</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7111,11 +7111,11 @@
       </c>
       <c r="M76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N76" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="O76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7123,23 +7123,23 @@
       </c>
       <c r="P76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q76" s="12">
         <f t="shared" si="8"/>
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-0.11578947368421055</v>
+        <v>-0.11227701993704098</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7163,27 +7163,27 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14576040.191355832</v>
+        <v>17509810.325102132</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14255558.120859461</v>
+        <v>17291531.897691596</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>-2.1986909084295014E-2</v>
+        <v>-1.2466064643636421E-2</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>750</v>
+        <v>705</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>2.1798365122615904E-2</v>
+        <v>-2.2191400832177521E-2</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7211,15 +7211,15 @@
       </c>
       <c r="R77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>5.1480051480050637E-3</v>
+        <v>2.5906735751295429E-3</v>
       </c>
       <c r="U77">
         <v>2</v>
@@ -7243,27 +7243,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12932652.057971435</v>
+        <v>14022555.382335631</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12141154.944297301</v>
+        <v>14540962.879546613</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>-6.1201454282245993E-2</v>
+        <v>3.6969545355764799E-2</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1182</v>
+        <v>791</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>884</v>
+        <v>924</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>-0.25211505922165822</v>
+        <v>0.16814159292035402</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7291,15 +7291,15 @@
       </c>
       <c r="R78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>-1.0298661174047319E-2</v>
+        <v>-1.1410788381742698E-2</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7323,31 +7323,31 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9981637.0205054078</v>
+        <v>13097969.624595124</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14297155.155265316</v>
+        <v>17335025.564646862</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>0.43234572905170587</v>
+        <v>0.3234895225360328</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>844</v>
+        <v>891</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>838</v>
+        <v>905</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>-7.1090047393365108E-3</v>
+        <v>1.5712682379348974E-2</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -7355,11 +7355,11 @@
       </c>
       <c r="N79" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="O79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7367,11 +7367,11 @@
       </c>
       <c r="Q79" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-2.8798411122144985E-2</v>
+        <v>-2.1021021021020991E-2</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7403,27 +7403,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14505794.519231632</v>
+        <v>18310243.092242092</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16606259.866167733</v>
+        <v>20062269.907639056</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>0.14480181310657092</v>
+        <v>9.5685611958875816E-2</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>711</v>
+        <v>769</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>-5.9523809523809534E-2</v>
+        <v>2.6702269692923997E-2</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7443,23 +7443,23 @@
       </c>
       <c r="P80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="12">
         <f t="shared" si="8"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>3.6241610738255048E-2</v>
+        <v>2.9490616621983934E-2</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7483,27 +7483,27 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7293208.2181321681</v>
+        <v>8670745.7737258058</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6774648.0106049767</v>
+        <v>8159419.8209574521</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>-7.1101796632922376E-2</v>
+        <v>-5.8971392555157043E-2</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>599</v>
+        <v>540</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>-0.13689482470784642</v>
+        <v>-3.3333333333333326E-2</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7511,11 +7511,11 @@
       </c>
       <c r="M81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="12">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7523,23 +7523,23 @@
       </c>
       <c r="P81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q81" s="12">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>-2.4475524475524479E-2</v>
+        <v>-4.0492957746478875E-2</v>
       </c>
       <c r="U81">
         <v>0</v>
@@ -7563,27 +7563,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28428762.025288314</v>
+        <v>35310344.073664188</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35222545.764984086</v>
+        <v>42702965.826996572</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>0.23897571528624706</v>
+        <v>0.20936136271880978</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1277</v>
+        <v>1290</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>8.3007047768206776E-2</v>
+        <v>7.5968992248061973E-2</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7611,15 +7611,15 @@
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1750</v>
+        <v>1754</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1782</v>
+        <v>1778</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>1.8285714285714239E-2</v>
+        <v>1.36830102622576E-2</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7643,27 +7643,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5928454.9220199343</v>
+        <v>7539509.8299834495</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7643312.6360125961</v>
+        <v>8983939.4270911943</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>0.2892587928134871</v>
+        <v>0.19158136665111503</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>692</v>
+        <v>872</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>701</v>
+        <v>628</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>1.3005780346820872E-2</v>
+        <v>-0.27981651376146788</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>9.9650349650349579E-2</v>
+        <v>0.1212121212121211</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7723,27 +7723,27 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13656288.42308018</v>
+        <v>16488973.74900602</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14040647.878120376</v>
+        <v>17466134.791588984</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>2.8145235596415796E-2</v>
+        <v>5.9261483307405216E-2</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>548</v>
+        <v>580</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>607</v>
+        <v>816</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>0.10766423357664223</v>
+        <v>0.40689655172413786</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7759,27 +7759,27 @@
       </c>
       <c r="O84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q84" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="S84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="T84" s="12">
         <f t="shared" si="9"/>
-        <v>3.6277602523659302E-2</v>
+        <v>5.5467511885895382E-2</v>
       </c>
       <c r="U84">
         <v>7</v>
@@ -7803,27 +7803,27 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3441098.5518438071</v>
+        <v>4056251.955859642</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3736480.5201603561</v>
+        <v>4177272.1257785661</v>
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>8.5839438733388729E-2</v>
+        <v>2.9835466641587427E-2</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>348</v>
+        <v>68</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>5.4545454545454453E-2</v>
+        <v>-0.7799352750809061</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="O85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7847,19 +7847,19 @@
       </c>
       <c r="Q85" s="12">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>4.1551246537396169E-2</v>
+        <v>3.8251366120218622E-2</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7898,31 +7898,31 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>84646</v>
+        <v>84861</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>652</v>
+        <v>963</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>71621</v>
+        <v>70217</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>1348656223.5730584</v>
+        <v>1652684078.2688403</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84547</v>
+        <v>84687</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>971</v>
+        <v>1272</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
@@ -7930,11 +7930,11 @@
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>71605</v>
+        <v>71131</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>1417866992.8139043</v>
+        <v>1715218317.2305956</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7994,7 +7994,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
@@ -8003,13 +8003,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F6" s="10">
-        <v>6133161.9322233526</v>
+        <v>7384820.0516374568</v>
       </c>
       <c r="G6" s="10">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="H6" s="10">
         <v>1</v>
@@ -8018,10 +8018,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="K6" s="10">
-        <v>6426890.2879607258</v>
+        <v>7794403.2465877896</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -8029,34 +8029,34 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="C7" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="10">
         <v>2</v>
       </c>
       <c r="E7" s="10">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="F7" s="10">
-        <v>7408856.1091459207</v>
+        <v>8808432.9749075994</v>
       </c>
       <c r="G7" s="10">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="H7" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="10">
         <v>3</v>
       </c>
       <c r="J7" s="10">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="K7" s="10">
-        <v>6694035.2704439107</v>
+        <v>8190359.7394492216</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8064,34 +8064,34 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C8" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="10">
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="F8" s="10">
-        <v>7914319.7785731563</v>
+        <v>10477595.383566588</v>
       </c>
       <c r="G8" s="10">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="H8" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>582</v>
+        <v>295</v>
       </c>
       <c r="K8" s="10">
-        <v>10142443.009948455</v>
+        <v>11063906.54678895</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8099,34 +8099,34 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="C9" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" s="10">
         <v>3</v>
       </c>
       <c r="E9" s="10">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="F9" s="10">
-        <v>15676332.964186031</v>
+        <v>19011434.547334105</v>
       </c>
       <c r="G9" s="10">
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="H9" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="10">
         <v>2</v>
       </c>
       <c r="J9" s="10">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="K9" s="10">
-        <v>16412847.693510678</v>
+        <v>19871487.575189549</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8134,7 +8134,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -8143,13 +8143,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F10" s="10">
-        <v>6756366.5511118118</v>
+        <v>8381329.5959949316</v>
       </c>
       <c r="G10" s="10">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="H10" s="10">
         <v>3</v>
@@ -8158,10 +8158,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="K10" s="10">
-        <v>7361194.2484042142</v>
+        <v>8985930.6731321104</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8169,7 +8169,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C11" s="10">
         <v>2</v>
@@ -8178,25 +8178,25 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F11" s="10">
-        <v>5974812.4305151608</v>
+        <v>7145519.7571021039</v>
       </c>
       <c r="G11" s="10">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H11" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="10">
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="K11" s="10">
-        <v>4574358.0257645678</v>
+        <v>5498928.2696352452</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8204,34 +8204,34 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C12" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="10">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="F12" s="10">
-        <v>6850963.5922380947</v>
+        <v>8340069.6906619277</v>
       </c>
       <c r="G12" s="10">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H12" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="10">
         <v>0</v>
       </c>
       <c r="J12" s="10">
-        <v>461</v>
+        <v>489</v>
       </c>
       <c r="K12" s="10">
-        <v>7142647.5146417981</v>
+        <v>8715775.2807155531</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8239,7 +8239,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="10">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -8248,13 +8248,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="F13" s="10">
-        <v>3088581.578316391</v>
+        <v>3747444.9194353758</v>
       </c>
       <c r="G13" s="10">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
@@ -8263,10 +8263,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K13" s="10">
-        <v>3323110.0629795291</v>
+        <v>3950550.299179432</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8274,7 +8274,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C14" s="10">
         <v>0</v>
@@ -8283,13 +8283,13 @@
         <v>1</v>
       </c>
       <c r="E14" s="10">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="F14" s="10">
-        <v>268469.072030415</v>
+        <v>586599.09295351198</v>
       </c>
       <c r="G14" s="10">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H14" s="10">
         <v>0</v>
@@ -8298,10 +8298,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K14" s="10">
-        <v>3241022.5148599562</v>
+        <v>3899890.5906057432</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8309,7 +8309,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="C15" s="10">
         <v>1</v>
@@ -8318,25 +8318,25 @@
         <v>1</v>
       </c>
       <c r="E15" s="10">
-        <v>509</v>
+        <v>329</v>
       </c>
       <c r="F15" s="10">
-        <v>6790088.2390767578</v>
+        <v>7940043.156108438</v>
       </c>
       <c r="G15" s="10">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H15" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="10">
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="K15" s="10">
-        <v>5541699.3345496301</v>
+        <v>6730366.9863225957</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8344,7 +8344,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -8353,10 +8353,10 @@
         <v>2</v>
       </c>
       <c r="E16" s="10">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="F16" s="10">
-        <v>2950606.2866052231</v>
+        <v>3605945.15739296</v>
       </c>
       <c r="G16" s="10">
         <v>235</v>
@@ -8368,10 +8368,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K16" s="10">
-        <v>2806071.7254887219</v>
+        <v>3309685.3118176642</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8379,19 +8379,19 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C17" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="10">
-        <v>219</v>
+        <v>1029</v>
       </c>
       <c r="F17" s="10">
-        <v>3308609.7061486649</v>
+        <v>3977027.8671158012</v>
       </c>
       <c r="G17" s="10">
         <v>246</v>
@@ -8403,10 +8403,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="10">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="K17" s="10">
-        <v>3322773.159289625</v>
+        <v>4053726.7902464792</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8414,7 +8414,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="C18" s="10">
         <v>2</v>
@@ -8423,25 +8423,25 @@
         <v>3</v>
       </c>
       <c r="E18" s="10">
-        <v>867</v>
+        <v>1622</v>
       </c>
       <c r="F18" s="10">
-        <v>9953290.1160668265</v>
+        <v>13399000.366042772</v>
       </c>
       <c r="G18" s="10">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="H18" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I18" s="10">
         <v>5</v>
       </c>
       <c r="J18" s="10">
-        <v>1283</v>
+        <v>1328</v>
       </c>
       <c r="K18" s="10">
-        <v>18811440.518050212</v>
+        <v>22834765.983763617</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8449,7 +8449,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
@@ -8458,13 +8458,13 @@
         <v>3</v>
       </c>
       <c r="E19" s="10">
-        <v>896</v>
+        <v>881</v>
       </c>
       <c r="F19" s="10">
-        <v>21779025.984482516</v>
+        <v>26643248.081871454</v>
       </c>
       <c r="G19" s="10">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="H19" s="10">
         <v>0</v>
@@ -8473,10 +8473,10 @@
         <v>2</v>
       </c>
       <c r="J19" s="10">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="K19" s="10">
-        <v>27426455.115565561</v>
+        <v>33008994.284924474</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8484,7 +8484,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="C20" s="10">
         <v>2</v>
@@ -8493,13 +8493,13 @@
         <v>5</v>
       </c>
       <c r="E20" s="10">
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="F20" s="10">
-        <v>12905524.417407267</v>
+        <v>15828242.32627888</v>
       </c>
       <c r="G20" s="10">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="H20" s="10">
         <v>4</v>
@@ -8508,10 +8508,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>907</v>
+        <v>961</v>
       </c>
       <c r="K20" s="10">
-        <v>13166622.355437858</v>
+        <v>15843798.763286391</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8519,7 +8519,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C21" s="10">
         <v>3</v>
@@ -8528,13 +8528,13 @@
         <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>726</v>
+        <v>657</v>
       </c>
       <c r="F21" s="10">
-        <v>8546617.3825953603</v>
+        <v>10913566.119168691</v>
       </c>
       <c r="G21" s="10">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="H21" s="10">
         <v>0</v>
@@ -8543,10 +8543,10 @@
         <v>3</v>
       </c>
       <c r="J21" s="10">
-        <v>703</v>
+        <v>649</v>
       </c>
       <c r="K21" s="10">
-        <v>12639179.227718508</v>
+        <v>14999077.867172075</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8554,34 +8554,34 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2942</v>
+        <v>2902</v>
       </c>
       <c r="C22" s="10">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2900</v>
+        <v>2097</v>
       </c>
       <c r="F22" s="10">
-        <v>48912893.789661609</v>
+        <v>58775003.547264457</v>
       </c>
       <c r="G22" s="10">
-        <v>2775</v>
+        <v>2812</v>
       </c>
       <c r="H22" s="10">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="I22" s="10">
         <v>12</v>
       </c>
       <c r="J22" s="10">
-        <v>2455</v>
+        <v>2243</v>
       </c>
       <c r="K22" s="10">
-        <v>44334164.274636917</v>
+        <v>53555984.147053935</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8589,34 +8589,34 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="C23" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="10">
         <v>1</v>
       </c>
       <c r="E23" s="10">
-        <v>9</v>
+        <v>1135</v>
       </c>
       <c r="F23" s="10">
-        <v>8067116.1734909713</v>
+        <v>11584685.638031436</v>
       </c>
       <c r="G23" s="10">
-        <v>1358</v>
+        <v>1368</v>
       </c>
       <c r="H23" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="10">
         <v>2</v>
       </c>
       <c r="J23" s="10">
-        <v>1243</v>
+        <v>1190</v>
       </c>
       <c r="K23" s="10">
-        <v>23636147.164518557</v>
+        <v>28439991.090680379</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8624,34 +8624,34 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>2962</v>
+        <v>2969</v>
       </c>
       <c r="C24" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D24" s="10">
         <v>10</v>
       </c>
       <c r="E24" s="10">
-        <v>2214</v>
+        <v>2229</v>
       </c>
       <c r="F24" s="10">
-        <v>47589497.746377259</v>
+        <v>57592953.799537219</v>
       </c>
       <c r="G24" s="10">
-        <v>2783</v>
+        <v>2775</v>
       </c>
       <c r="H24" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>1710</v>
+        <v>2139</v>
       </c>
       <c r="K24" s="10">
-        <v>38442880.37404453</v>
+        <v>48206739.535607196</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8659,7 +8659,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="C25" s="10">
         <v>4</v>
@@ -8668,13 +8668,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="F25" s="10">
-        <v>7103110.1359766154</v>
+        <v>9055980.6224311255</v>
       </c>
       <c r="G25" s="10">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="H25" s="10">
         <v>2</v>
@@ -8683,10 +8683,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="K25" s="10">
-        <v>6614407.9173041824</v>
+        <v>7894030.6329214247</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8694,34 +8694,34 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1732</v>
+        <v>1739</v>
       </c>
       <c r="C26" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" s="10">
         <v>2</v>
       </c>
       <c r="E26" s="10">
-        <v>1334</v>
+        <v>1298</v>
       </c>
       <c r="F26" s="10">
-        <v>19250463.316177037</v>
+        <v>23687070.811500505</v>
       </c>
       <c r="G26" s="10">
         <v>1728</v>
       </c>
       <c r="H26" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" s="10">
         <v>1</v>
       </c>
       <c r="J26" s="10">
-        <v>1505</v>
+        <v>1446</v>
       </c>
       <c r="K26" s="10">
-        <v>17836490.49011419</v>
+        <v>21540252.204000156</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8729,34 +8729,34 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="C27" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" s="10">
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>766</v>
+        <v>740</v>
       </c>
       <c r="F27" s="10">
-        <v>7823262.2443494322</v>
+        <v>9478921.5549611673</v>
       </c>
       <c r="G27" s="10">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="H27" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="10">
         <v>0</v>
       </c>
       <c r="J27" s="10">
-        <v>789</v>
+        <v>824</v>
       </c>
       <c r="K27" s="10">
-        <v>7264698.4773071362</v>
+        <v>9013330.2175357286</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8764,22 +8764,22 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="C28" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="10">
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>757</v>
+        <v>837</v>
       </c>
       <c r="F28" s="10">
-        <v>9933707.18830988</v>
+        <v>12129368.103966432</v>
       </c>
       <c r="G28" s="10">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="H28" s="10">
         <v>1</v>
@@ -8788,10 +8788,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="10">
-        <v>669</v>
+        <v>769</v>
       </c>
       <c r="K28" s="10">
-        <v>9164224.2770352941</v>
+        <v>11323368.874365836</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8799,34 +8799,34 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
+        <v>231</v>
+      </c>
+      <c r="C29" s="10">
+        <v>1</v>
+      </c>
+      <c r="D29" s="10">
+        <v>2</v>
+      </c>
+      <c r="E29" s="10">
+        <v>176</v>
+      </c>
+      <c r="F29" s="10">
+        <v>2536402.8153050868</v>
+      </c>
+      <c r="G29" s="10">
+        <v>219</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0</v>
+      </c>
+      <c r="I29" s="10">
+        <v>0</v>
+      </c>
+      <c r="J29" s="10">
         <v>235</v>
       </c>
-      <c r="C29" s="10">
-        <v>1</v>
-      </c>
-      <c r="D29" s="10">
-        <v>2</v>
-      </c>
-      <c r="E29" s="10">
-        <v>146</v>
-      </c>
-      <c r="F29" s="10">
-        <v>2051568.491111354</v>
-      </c>
-      <c r="G29" s="10">
-        <v>218</v>
-      </c>
-      <c r="H29" s="10">
-        <v>0</v>
-      </c>
-      <c r="I29" s="10">
-        <v>0</v>
-      </c>
-      <c r="J29" s="10">
-        <v>161</v>
-      </c>
       <c r="K29" s="10">
-        <v>2229968.7390251779</v>
+        <v>2808535.7045010701</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8834,7 +8834,7 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="C30" s="10">
         <v>9</v>
@@ -8843,25 +8843,25 @@
         <v>6</v>
       </c>
       <c r="E30" s="10">
-        <v>1398</v>
+        <v>1297</v>
       </c>
       <c r="F30" s="10">
-        <v>18618927.923217751</v>
+        <v>22511788.425732885</v>
       </c>
       <c r="G30" s="10">
-        <v>1646</v>
+        <v>1639</v>
       </c>
       <c r="H30" s="10">
         <v>2</v>
       </c>
       <c r="I30" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J30" s="10">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K30" s="10">
-        <v>19277893.993381854</v>
+        <v>22367217.405995153</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8869,7 +8869,7 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
@@ -8878,25 +8878,25 @@
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="F31" s="10">
-        <v>14506889.258832024</v>
+        <v>18118545.915352695</v>
       </c>
       <c r="G31" s="10">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="H31" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="10">
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K31" s="10">
-        <v>16063145.378722521</v>
+        <v>20204926.878771558</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8904,22 +8904,22 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C32" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="10">
         <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F32" s="10">
-        <v>14387241.825953936</v>
+        <v>17752317.438190568</v>
       </c>
       <c r="G32" s="10">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="H32" s="10">
         <v>1</v>
@@ -8928,10 +8928,10 @@
         <v>2</v>
       </c>
       <c r="J32" s="10">
-        <v>664</v>
+        <v>911</v>
       </c>
       <c r="K32" s="10">
-        <v>15559954.107234888</v>
+        <v>19114856.538799368</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8939,7 +8939,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C33" s="10">
         <v>2</v>
@@ -8948,13 +8948,13 @@
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>864</v>
+        <v>832</v>
       </c>
       <c r="F33" s="10">
-        <v>19992124.091455083</v>
+        <v>24186906.744684663</v>
       </c>
       <c r="G33" s="10">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H33" s="10">
         <v>1</v>
@@ -8963,10 +8963,10 @@
         <v>3</v>
       </c>
       <c r="J33" s="10">
-        <v>936</v>
+        <v>812</v>
       </c>
       <c r="K33" s="10">
-        <v>21918944.083954044</v>
+        <v>25226309.632355992</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8974,22 +8974,22 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1478</v>
+        <v>1459</v>
       </c>
       <c r="C34" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="10">
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1146</v>
+        <v>1185</v>
       </c>
       <c r="F34" s="10">
-        <v>28204861.723208327</v>
+        <v>34394456.147691317</v>
       </c>
       <c r="G34" s="10">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="H34" s="10">
         <v>2</v>
@@ -8998,10 +8998,10 @@
         <v>2</v>
       </c>
       <c r="J34" s="10">
-        <v>1204</v>
+        <v>1169</v>
       </c>
       <c r="K34" s="10">
-        <v>30169389.89326692</v>
+        <v>35006468.816651084</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -9009,7 +9009,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C35" s="10">
         <v>0</v>
@@ -9018,25 +9018,25 @@
         <v>5</v>
       </c>
       <c r="E35" s="10">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="F35" s="10">
-        <v>11521977.507242309</v>
+        <v>14133878.193473892</v>
       </c>
       <c r="G35" s="10">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="H35" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" s="10">
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>679</v>
+        <v>612</v>
       </c>
       <c r="K35" s="10">
-        <v>10852281.281489624</v>
+        <v>13924727.038236933</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9044,7 +9044,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1937</v>
+        <v>1943</v>
       </c>
       <c r="C36" s="10">
         <v>6</v>
@@ -9053,10 +9053,10 @@
         <v>11</v>
       </c>
       <c r="E36" s="10">
-        <v>1579</v>
+        <v>1571</v>
       </c>
       <c r="F36" s="10">
-        <v>35178724.13029144</v>
+        <v>43001448.166093811</v>
       </c>
       <c r="G36" s="10">
         <v>1855</v>
@@ -9068,10 +9068,10 @@
         <v>6</v>
       </c>
       <c r="J36" s="10">
-        <v>1669</v>
+        <v>1707</v>
       </c>
       <c r="K36" s="10">
-        <v>19349044.074072417</v>
+        <v>26036926.729291752</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9079,7 +9079,7 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C37" s="10">
         <v>1</v>
@@ -9088,25 +9088,25 @@
         <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>696</v>
+        <v>887</v>
       </c>
       <c r="F37" s="10">
-        <v>11496843.696313253</v>
+        <v>14132076.933236703</v>
       </c>
       <c r="G37" s="10">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="H37" s="10">
         <v>2</v>
       </c>
       <c r="I37" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J37" s="10">
-        <v>644</v>
+        <v>670</v>
       </c>
       <c r="K37" s="10">
-        <v>12468667.542720955</v>
+        <v>14724372.928554051</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9114,23 +9114,23 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
+        <v>745</v>
+      </c>
+      <c r="C38" s="10">
+        <v>1</v>
+      </c>
+      <c r="D38" s="10">
+        <v>1</v>
+      </c>
+      <c r="E38" s="10">
+        <v>746</v>
+      </c>
+      <c r="F38" s="10">
+        <v>13627139.337142861</v>
+      </c>
+      <c r="G38" s="10">
         <v>732</v>
       </c>
-      <c r="C38" s="10">
-        <v>0</v>
-      </c>
-      <c r="D38" s="10">
-        <v>1</v>
-      </c>
-      <c r="E38" s="10">
-        <v>557</v>
-      </c>
-      <c r="F38" s="10">
-        <v>11081479.212508269</v>
-      </c>
-      <c r="G38" s="10">
-        <v>739</v>
-      </c>
       <c r="H38" s="10">
         <v>1</v>
       </c>
@@ -9138,10 +9138,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="K38" s="10">
-        <v>10864601.777345827</v>
+        <v>13006674.485248519</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9149,22 +9149,22 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="C39" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" s="10">
         <v>1</v>
       </c>
       <c r="E39" s="10">
-        <v>836</v>
+        <v>465</v>
       </c>
       <c r="F39" s="10">
-        <v>17141886.430531561</v>
+        <v>20545921.86789586</v>
       </c>
       <c r="G39" s="10">
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="H39" s="10">
         <v>5</v>
@@ -9173,10 +9173,10 @@
         <v>2</v>
       </c>
       <c r="J39" s="10">
-        <v>817</v>
+        <v>908</v>
       </c>
       <c r="K39" s="10">
-        <v>19206431.863842171</v>
+        <v>22932126.399725944</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9184,7 +9184,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1365</v>
+        <v>1335</v>
       </c>
       <c r="C40" s="10">
         <v>120</v>
@@ -9193,25 +9193,25 @@
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>769</v>
+        <v>811</v>
       </c>
       <c r="F40" s="10">
-        <v>15596539.676497009</v>
+        <v>19120041.93568055</v>
       </c>
       <c r="G40" s="10">
-        <v>1381</v>
+        <v>1452</v>
       </c>
       <c r="H40" s="10">
-        <v>233</v>
+        <v>317</v>
       </c>
       <c r="I40" s="10">
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>1028</v>
+        <v>858</v>
       </c>
       <c r="K40" s="10">
-        <v>17745440.702579733</v>
+        <v>21141554.628010023</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9219,34 +9219,34 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>2469</v>
+        <v>2418</v>
       </c>
       <c r="C41" s="10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D41" s="10">
         <v>5</v>
       </c>
       <c r="E41" s="10">
-        <v>1439</v>
+        <v>1575</v>
       </c>
       <c r="F41" s="10">
-        <v>28549586.631023839</v>
+        <v>34901512.498659305</v>
       </c>
       <c r="G41" s="10">
-        <v>2195</v>
+        <v>2265</v>
       </c>
       <c r="H41" s="10">
-        <v>118</v>
+        <v>235</v>
       </c>
       <c r="I41" s="10">
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1714</v>
+        <v>1484</v>
       </c>
       <c r="K41" s="10">
-        <v>29255931.280371618</v>
+        <v>35002790.497653201</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9254,34 +9254,34 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C42" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="10">
         <v>6</v>
       </c>
       <c r="E42" s="10">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="F42" s="10">
-        <v>10313879.042900581</v>
+        <v>12522131.034147704</v>
       </c>
       <c r="G42" s="10">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H42" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" s="10">
         <v>7</v>
       </c>
       <c r="J42" s="10">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="K42" s="10">
-        <v>10916359.854945768</v>
+        <v>12972219.559267271</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9289,7 +9289,7 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>2049</v>
+        <v>2064</v>
       </c>
       <c r="C43" s="10">
         <v>2</v>
@@ -9298,13 +9298,13 @@
         <v>6</v>
       </c>
       <c r="E43" s="10">
-        <v>1934</v>
+        <v>1950</v>
       </c>
       <c r="F43" s="10">
-        <v>34467171.240222543</v>
+        <v>41927511.893101111</v>
       </c>
       <c r="G43" s="10">
-        <v>2047</v>
+        <v>2040</v>
       </c>
       <c r="H43" s="10">
         <v>4</v>
@@ -9313,10 +9313,10 @@
         <v>5</v>
       </c>
       <c r="J43" s="10">
-        <v>1987</v>
+        <v>1850</v>
       </c>
       <c r="K43" s="10">
-        <v>33435528.542818047</v>
+        <v>40159357.461528517</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9324,34 +9324,34 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C44" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" s="10">
         <v>2</v>
       </c>
       <c r="E44" s="10">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="F44" s="10">
-        <v>22237665.004112385</v>
+        <v>27163671.010994777</v>
       </c>
       <c r="G44" s="10">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="H44" s="10">
         <v>5</v>
       </c>
       <c r="I44" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J44" s="10">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="K44" s="10">
-        <v>26120332.746377055</v>
+        <v>31332334.071481273</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9359,7 +9359,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="C45" s="10">
         <v>0</v>
@@ -9368,25 +9368,25 @@
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="F45" s="10">
-        <v>10362877.114542577</v>
+        <v>14178492.832121568</v>
       </c>
       <c r="G45" s="10">
-        <v>1043</v>
+        <v>1052</v>
       </c>
       <c r="H45" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" s="10">
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>1019</v>
+        <v>944</v>
       </c>
       <c r="K45" s="10">
-        <v>18743763.672474202</v>
+        <v>22149087.91487515</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9394,7 +9394,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="C46" s="10">
         <v>3</v>
@@ -9403,13 +9403,13 @@
         <v>4</v>
       </c>
       <c r="E46" s="10">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="F46" s="10">
-        <v>17698698.547770157</v>
+        <v>21673565.670844473</v>
       </c>
       <c r="G46" s="10">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="H46" s="10">
         <v>2</v>
@@ -9418,10 +9418,10 @@
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>788</v>
+        <v>635</v>
       </c>
       <c r="K46" s="10">
-        <v>18394155.295887496</v>
+        <v>22463428.205046136</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9429,22 +9429,22 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>692</v>
+        <v>707</v>
       </c>
       <c r="C47" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="10">
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>708</v>
+        <v>560</v>
       </c>
       <c r="F47" s="10">
-        <v>11326902.340657758</v>
+        <v>13895483.106158944</v>
       </c>
       <c r="G47" s="10">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="H47" s="10">
         <v>0</v>
@@ -9453,10 +9453,10 @@
         <v>9</v>
       </c>
       <c r="J47" s="10">
-        <v>595</v>
+        <v>563</v>
       </c>
       <c r="K47" s="10">
-        <v>11180304.84275686</v>
+        <v>13423472.227419101</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9473,25 +9473,25 @@
         <v>2</v>
       </c>
       <c r="E48" s="10">
-        <v>744</v>
+        <v>713</v>
       </c>
       <c r="F48" s="10">
-        <v>9749315.3487538137</v>
+        <v>12161003.483174358</v>
       </c>
       <c r="G48" s="10">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
       </c>
       <c r="I48" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" s="10">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="K48" s="10">
-        <v>10329690.532225767</v>
+        <v>12527683.802709805</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9499,7 +9499,7 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C49" s="10">
         <v>0</v>
@@ -9508,25 +9508,25 @@
         <v>4</v>
       </c>
       <c r="E49" s="10">
-        <v>1127</v>
+        <v>1078</v>
       </c>
       <c r="F49" s="10">
-        <v>30643816.421466332</v>
+        <v>37273755.084821194</v>
       </c>
       <c r="G49" s="10">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="H49" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="10">
         <v>6</v>
       </c>
       <c r="J49" s="10">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="K49" s="10">
-        <v>34833280.631897286</v>
+        <v>41936647.835470937</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9534,7 +9534,7 @@
         <v>201</v>
       </c>
       <c r="B50" s="10">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C50" s="10">
         <v>0</v>
@@ -9543,13 +9543,13 @@
         <v>1</v>
       </c>
       <c r="E50" s="10">
-        <v>429</v>
+        <v>484</v>
       </c>
       <c r="F50" s="10">
-        <v>5110675.4936231552</v>
+        <v>6162776.9085115492</v>
       </c>
       <c r="G50" s="10">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H50" s="10">
         <v>1</v>
@@ -9558,10 +9558,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="K50" s="10">
-        <v>5328430.7744395826</v>
+        <v>6384247.944338074</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9575,16 +9575,16 @@
         <v>2</v>
       </c>
       <c r="D51" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E51" s="10">
-        <v>3212</v>
+        <v>881</v>
       </c>
       <c r="F51" s="10">
-        <v>14694364.793953007</v>
+        <v>17874087.659617409</v>
       </c>
       <c r="G51" s="10">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="H51" s="10">
         <v>1</v>
@@ -9593,10 +9593,10 @@
         <v>4</v>
       </c>
       <c r="J51" s="10">
-        <v>925</v>
+        <v>899</v>
       </c>
       <c r="K51" s="10">
-        <v>14864008.548044087</v>
+        <v>17870643.858846333</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9604,7 +9604,7 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="C52" s="10">
         <v>3</v>
@@ -9613,25 +9613,25 @@
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>1033</v>
+        <v>1045</v>
       </c>
       <c r="F52" s="10">
-        <v>26326685.795884985</v>
+        <v>32056870.004816383</v>
       </c>
       <c r="G52" s="10">
-        <v>1402</v>
+        <v>1417</v>
       </c>
       <c r="H52" s="10">
         <v>1</v>
       </c>
       <c r="I52" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J52" s="10">
-        <v>1050</v>
+        <v>1014</v>
       </c>
       <c r="K52" s="10">
-        <v>26740693.628350247</v>
+        <v>32663997.039998908</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9642,31 +9642,31 @@
         <v>483</v>
       </c>
       <c r="C53" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" s="10">
         <v>6</v>
       </c>
       <c r="E53" s="10">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="F53" s="10">
-        <v>13634364.861858128</v>
+        <v>16539048.45741608</v>
       </c>
       <c r="G53" s="10">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H53" s="10">
         <v>3</v>
       </c>
       <c r="I53" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>385</v>
+        <v>514</v>
       </c>
       <c r="K53" s="10">
-        <v>12304766.659372153</v>
+        <v>15061140.755258827</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9674,7 +9674,7 @@
         <v>81</v>
       </c>
       <c r="B54" s="10">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C54" s="10">
         <v>0</v>
@@ -9683,13 +9683,13 @@
         <v>4</v>
       </c>
       <c r="E54" s="10">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F54" s="10">
-        <v>10085942.515286084</v>
+        <v>12081136.709517296</v>
       </c>
       <c r="G54" s="10">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H54" s="10">
         <v>1</v>
@@ -9698,10 +9698,10 @@
         <v>3</v>
       </c>
       <c r="J54" s="10">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="K54" s="10">
-        <v>10771677.970238339</v>
+        <v>13095908.736033432</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9709,22 +9709,22 @@
         <v>87</v>
       </c>
       <c r="B55" s="10">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C55" s="10">
         <v>1</v>
       </c>
       <c r="D55" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E55" s="10">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="F55" s="10">
-        <v>8794364.8169755638</v>
+        <v>10520584.106780592</v>
       </c>
       <c r="G55" s="10">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H55" s="10">
         <v>0</v>
@@ -9733,10 +9733,10 @@
         <v>2</v>
       </c>
       <c r="J55" s="10">
-        <v>319</v>
+        <v>5</v>
       </c>
       <c r="K55" s="10">
-        <v>5287043.4016682496</v>
+        <v>5501887.3312636809</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9744,22 +9744,22 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="C56" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" s="10">
         <v>0</v>
       </c>
       <c r="E56" s="10">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="F56" s="10">
-        <v>20589581.956771232</v>
+        <v>24723580.217376906</v>
       </c>
       <c r="G56" s="10">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H56" s="10">
         <v>2</v>
@@ -9768,10 +9768,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>940</v>
+        <v>962</v>
       </c>
       <c r="K56" s="10">
-        <v>21708708.646214969</v>
+        <v>26527780.340592857</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9779,34 +9779,34 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>973</v>
+        <v>995</v>
       </c>
       <c r="C57" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D57" s="10">
         <v>1</v>
       </c>
       <c r="E57" s="10">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="F57" s="10">
-        <v>18172569.992024127</v>
+        <v>23331162.81574592</v>
       </c>
       <c r="G57" s="10">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="H57" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I57" s="10">
         <v>2</v>
       </c>
       <c r="J57" s="10">
-        <v>805</v>
+        <v>960</v>
       </c>
       <c r="K57" s="10">
-        <v>21711269.083108783</v>
+        <v>26543308.271027669</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9814,7 +9814,7 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="C58" s="10">
         <v>6</v>
@@ -9823,25 +9823,25 @@
         <v>8</v>
       </c>
       <c r="E58" s="10">
-        <v>1631</v>
+        <v>1445</v>
       </c>
       <c r="F58" s="10">
-        <v>39084951.029873677</v>
+        <v>46692177.299890816</v>
       </c>
       <c r="G58" s="10">
-        <v>2110</v>
+        <v>2103</v>
       </c>
       <c r="H58" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I58" s="10">
         <v>9</v>
       </c>
       <c r="J58" s="10">
-        <v>1802</v>
+        <v>1627</v>
       </c>
       <c r="K58" s="10">
-        <v>40331079.886328921</v>
+        <v>48360579.666022353</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9849,22 +9849,22 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C59" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D59" s="10">
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="F59" s="10">
-        <v>8843951.5906833</v>
+        <v>11101958.599655284</v>
       </c>
       <c r="G59" s="10">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H59" s="10">
         <v>2</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="K59" s="10">
-        <v>10725083.805626824</v>
+        <v>12869337.990031293</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9893,25 +9893,25 @@
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>758</v>
+        <v>695</v>
       </c>
       <c r="F60" s="10">
-        <v>15871422.260580655</v>
+        <v>19744310.44305547</v>
       </c>
       <c r="G60" s="10">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="H60" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I60" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J60" s="10">
-        <v>856</v>
+        <v>807</v>
       </c>
       <c r="K60" s="10">
-        <v>18384833.519360822</v>
+        <v>22427850.574070819</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9919,22 +9919,22 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="C61" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" s="10">
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F61" s="10">
-        <v>9791521.9231825955</v>
+        <v>12108515.79752842</v>
       </c>
       <c r="G61" s="10">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="H61" s="10">
         <v>0</v>
@@ -9943,10 +9943,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="10">
-        <v>562</v>
+        <v>632</v>
       </c>
       <c r="K61" s="10">
-        <v>10484385.024936249</v>
+        <v>12081050.832576821</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9954,7 +9954,7 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C62" s="10">
         <v>4</v>
@@ -9963,10 +9963,10 @@
         <v>0</v>
       </c>
       <c r="E62" s="10">
-        <v>999</v>
+        <v>986</v>
       </c>
       <c r="F62" s="10">
-        <v>21348622.992430314</v>
+        <v>25953478.849800728</v>
       </c>
       <c r="G62" s="10">
         <v>1109</v>
@@ -9975,13 +9975,13 @@
         <v>4</v>
       </c>
       <c r="I62" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="10">
-        <v>1147</v>
+        <v>1112</v>
       </c>
       <c r="K62" s="10">
-        <v>23099376.1903781</v>
+        <v>28241591.85484669</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9989,34 +9989,34 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1399</v>
+        <v>1425</v>
       </c>
       <c r="C63" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63" s="10">
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1429</v>
+        <v>1510</v>
       </c>
       <c r="F63" s="10">
-        <v>24991750.938691661</v>
+        <v>31393322.515753064</v>
       </c>
       <c r="G63" s="10">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="H63" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I63" s="10">
         <v>5</v>
       </c>
       <c r="J63" s="10">
-        <v>1600</v>
+        <v>1633</v>
       </c>
       <c r="K63" s="10">
-        <v>31747644.601805378</v>
+        <v>38769776.034656703</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -10024,34 +10024,34 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C64" s="10">
         <v>1</v>
       </c>
       <c r="D64" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E64" s="10">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F64" s="10">
-        <v>14329352.807133865</v>
+        <v>17452043.978152473</v>
       </c>
       <c r="G64" s="10">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="H64" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I64" s="10">
         <v>5</v>
       </c>
       <c r="J64" s="10">
-        <v>769</v>
+        <v>812</v>
       </c>
       <c r="K64" s="10">
-        <v>12337857.407070264</v>
+        <v>15455780.272549629</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10059,22 +10059,22 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C65" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D65" s="10">
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="F65" s="10">
-        <v>15913750.060137004</v>
+        <v>19453163.939775139</v>
       </c>
       <c r="G65" s="10">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="H65" s="10">
         <v>3</v>
@@ -10083,10 +10083,10 @@
         <v>7</v>
       </c>
       <c r="J65" s="10">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="K65" s="10">
-        <v>16570255.383356037</v>
+        <v>20408682.048246805</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10094,34 +10094,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>2000</v>
+        <v>1970</v>
       </c>
       <c r="C66" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D66" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E66" s="10">
-        <v>1633</v>
+        <v>1606</v>
       </c>
       <c r="F66" s="10">
-        <v>51156826.689083554</v>
+        <v>62712300.78279233</v>
       </c>
       <c r="G66" s="10">
-        <v>1984</v>
+        <v>1971</v>
       </c>
       <c r="H66" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I66" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J66" s="10">
-        <v>1785</v>
+        <v>1794</v>
       </c>
       <c r="K66" s="10">
-        <v>53725402.89775309</v>
+        <v>65608445.879055992</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10132,31 +10132,31 @@
         <v>1581</v>
       </c>
       <c r="C67" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D67" s="10">
         <v>6</v>
       </c>
       <c r="E67" s="10">
-        <v>1195</v>
+        <v>1219</v>
       </c>
       <c r="F67" s="10">
-        <v>36192720.881001942</v>
+        <v>45460845.578881703</v>
       </c>
       <c r="G67" s="10">
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="H67" s="10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I67" s="10">
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1313</v>
+        <v>1265</v>
       </c>
       <c r="K67" s="10">
-        <v>38409566.627921052</v>
+        <v>46716196.328422241</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10164,7 +10164,7 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C68" s="10">
         <v>3</v>
@@ -10173,25 +10173,25 @@
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="F68" s="10">
-        <v>24480721.503467716</v>
+        <v>30167393.236838799</v>
       </c>
       <c r="G68" s="10">
         <v>894</v>
       </c>
       <c r="H68" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="10">
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="K68" s="10">
-        <v>26258051.197483271</v>
+        <v>31840007.43950006</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10199,34 +10199,34 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>2104</v>
+        <v>2335</v>
       </c>
       <c r="C69" s="10">
-        <v>108</v>
+        <v>366</v>
       </c>
       <c r="D69" s="10">
         <v>12</v>
       </c>
       <c r="E69" s="10">
-        <v>1387</v>
+        <v>1437</v>
       </c>
       <c r="F69" s="10">
-        <v>36777108.621974111</v>
+        <v>45486578.400095366</v>
       </c>
       <c r="G69" s="10">
-        <v>2362</v>
+        <v>2338</v>
       </c>
       <c r="H69" s="10">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="I69" s="10">
         <v>13</v>
       </c>
       <c r="J69" s="10">
-        <v>1470</v>
+        <v>1292</v>
       </c>
       <c r="K69" s="10">
-        <v>34416120.328050949</v>
+        <v>41636311.204481982</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10234,19 +10234,19 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C70" s="10">
         <v>0</v>
       </c>
       <c r="D70" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>254</v>
+        <v>415</v>
       </c>
       <c r="F70" s="10">
-        <v>622601.72598268196</v>
+        <v>1088870.296364038</v>
       </c>
       <c r="G70" s="10">
         <v>243</v>
@@ -10258,10 +10258,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="10">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="K70" s="10">
-        <v>2808305.1556609101</v>
+        <v>3332193.916553128</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10272,31 +10272,31 @@
         <v>1674</v>
       </c>
       <c r="C71" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D71" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E71" s="10">
-        <v>1623</v>
+        <v>1542</v>
       </c>
       <c r="F71" s="10">
-        <v>26797354.943077229</v>
+        <v>32343585.173141804</v>
       </c>
       <c r="G71" s="10">
-        <v>1607</v>
+        <v>1625</v>
       </c>
       <c r="H71" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I71" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J71" s="10">
-        <v>1558</v>
+        <v>1458</v>
       </c>
       <c r="K71" s="10">
-        <v>26291966.492786366</v>
+        <v>31714020.902646456</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10304,7 +10304,7 @@
         <v>12</v>
       </c>
       <c r="B72" s="10">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="C72" s="10">
         <v>1</v>
@@ -10313,25 +10313,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="10">
-        <v>582</v>
+        <v>614</v>
       </c>
       <c r="F72" s="10">
-        <v>12442434.197569257</v>
+        <v>15328774.192921566</v>
       </c>
       <c r="G72" s="10">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="H72" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" s="10">
         <v>4</v>
       </c>
       <c r="J72" s="10">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="K72" s="10">
-        <v>12151901.567606615</v>
+        <v>14576827.875886289</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10339,7 +10339,7 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="C73" s="10">
         <v>19</v>
@@ -10348,13 +10348,13 @@
         <v>4</v>
       </c>
       <c r="E73" s="10">
-        <v>946</v>
+        <v>859</v>
       </c>
       <c r="F73" s="10">
-        <v>17684885.685970344</v>
+        <v>21872709.188291144</v>
       </c>
       <c r="G73" s="10">
-        <v>1515</v>
+        <v>1477</v>
       </c>
       <c r="H73" s="10">
         <v>1</v>
@@ -10363,10 +10363,10 @@
         <v>5</v>
       </c>
       <c r="J73" s="10">
-        <v>842</v>
+        <v>889</v>
       </c>
       <c r="K73" s="10">
-        <v>19240732.411861435</v>
+        <v>23086254.829625059</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10374,34 +10374,34 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1296</v>
+        <v>1287</v>
       </c>
       <c r="C74" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" s="10">
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>1218</v>
+        <v>597</v>
       </c>
       <c r="F74" s="10">
-        <v>12901963.149557795</v>
+        <v>14513828.217951603</v>
       </c>
       <c r="G74" s="10">
-        <v>1293</v>
+        <v>1314</v>
       </c>
       <c r="H74" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74" s="10">
         <v>4</v>
       </c>
       <c r="J74" s="10">
-        <v>1426</v>
+        <v>1361</v>
       </c>
       <c r="K74" s="10">
-        <v>15409388.827121716</v>
+        <v>18591108.258868024</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10409,34 +10409,34 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1728</v>
+        <v>1737</v>
       </c>
       <c r="C75" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D75" s="10">
         <v>4</v>
       </c>
       <c r="E75" s="10">
-        <v>1175</v>
+        <v>1229</v>
       </c>
       <c r="F75" s="10">
-        <v>32750863.538609803</v>
+        <v>39840425.618532181</v>
       </c>
       <c r="G75" s="10">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="H75" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I75" s="10">
         <v>7</v>
       </c>
       <c r="J75" s="10">
-        <v>1330</v>
+        <v>1266</v>
       </c>
       <c r="K75" s="10">
-        <v>33955011.525192656</v>
+        <v>41382219.443157539</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10444,7 +10444,7 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C76" s="10">
         <v>2</v>
@@ -10453,25 +10453,25 @@
         <v>1</v>
       </c>
       <c r="E76" s="10">
+        <v>433</v>
+      </c>
+      <c r="F76" s="10">
+        <v>8058967.8740208512</v>
+      </c>
+      <c r="G76" s="10">
+        <v>488</v>
+      </c>
+      <c r="H76" s="10">
+        <v>2</v>
+      </c>
+      <c r="I76" s="10">
+        <v>1</v>
+      </c>
+      <c r="J76" s="10">
         <v>473</v>
       </c>
-      <c r="F76" s="10">
-        <v>6739342.6329431906</v>
-      </c>
-      <c r="G76" s="10">
-        <v>489</v>
-      </c>
-      <c r="H76" s="10">
-        <v>1</v>
-      </c>
-      <c r="I76" s="10">
-        <v>1</v>
-      </c>
-      <c r="J76" s="10">
-        <v>433</v>
-      </c>
       <c r="K76" s="10">
-        <v>6439608.1652408363</v>
+        <v>7736582.7318614321</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10479,7 +10479,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C77" s="10">
         <v>3</v>
@@ -10488,13 +10488,13 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>879</v>
+        <v>999</v>
       </c>
       <c r="F77" s="10">
-        <v>10301292.77501234</v>
+        <v>12600460.760555159</v>
       </c>
       <c r="G77" s="10">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="H77" s="10">
         <v>1</v>
@@ -10503,10 +10503,10 @@
         <v>0</v>
       </c>
       <c r="J77" s="10">
-        <v>780</v>
+        <v>812</v>
       </c>
       <c r="K77" s="10">
-        <v>12293560.868492804</v>
+        <v>15138195.546056001</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10514,7 +10514,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C78" s="10">
         <v>0</v>
@@ -10523,13 +10523,13 @@
         <v>3</v>
       </c>
       <c r="E78" s="10">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="F78" s="10">
-        <v>9995696.629863428</v>
+        <v>12247960.588351307</v>
       </c>
       <c r="G78" s="10">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H78" s="10">
         <v>2</v>
@@ -10538,10 +10538,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>465</v>
+        <v>513</v>
       </c>
       <c r="K78" s="10">
-        <v>10923169.481146952</v>
+        <v>13531617.314519268</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10549,22 +10549,22 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="C79" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D79" s="10">
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>710</v>
+        <v>732</v>
       </c>
       <c r="F79" s="10">
-        <v>8664072.1058999225</v>
+        <v>10279087.37903594</v>
       </c>
       <c r="G79" s="10">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="H79" s="10">
         <v>2</v>
@@ -10573,10 +10573,10 @@
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>778</v>
+        <v>1095</v>
       </c>
       <c r="K79" s="10">
-        <v>6517199.5900564799</v>
+        <v>8513336.6178804133</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10584,7 +10584,7 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="C80" s="10">
         <v>0</v>
@@ -10593,25 +10593,25 @@
         <v>7</v>
       </c>
       <c r="E80" s="10">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="F80" s="10">
-        <v>9280196.177744668</v>
+        <v>11214438.848868918</v>
       </c>
       <c r="G80" s="10">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="H80" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" s="10">
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="K80" s="10">
-        <v>7529202.7045356091</v>
+        <v>9194851.3412616476</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10619,7 +10619,7 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C81" s="10">
         <v>4</v>
@@ -10628,25 +10628,25 @@
         <v>3</v>
       </c>
       <c r="E81" s="10">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="F81" s="10">
-        <v>23425680.163103808</v>
+        <v>29020876.322520785</v>
       </c>
       <c r="G81" s="10">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="H81" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I81" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J81" s="10">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K81" s="10">
-        <v>19142013.66925722</v>
+        <v>22449998.135948103</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10654,7 +10654,7 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="C82" s="10">
         <v>2</v>
@@ -10663,13 +10663,13 @@
         <v>10</v>
       </c>
       <c r="E82" s="10">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="F82" s="10">
-        <v>14576040.191355832</v>
+        <v>17509810.325102132</v>
       </c>
       <c r="G82" s="10">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="H82" s="10">
         <v>3</v>
@@ -10678,10 +10678,10 @@
         <v>9</v>
       </c>
       <c r="J82" s="10">
-        <v>750</v>
+        <v>705</v>
       </c>
       <c r="K82" s="10">
-        <v>14255558.120859461</v>
+        <v>17291531.897691596</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10689,7 +10689,7 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="C83" s="10">
         <v>1</v>
@@ -10698,13 +10698,13 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>1182</v>
+        <v>791</v>
       </c>
       <c r="F83" s="10">
-        <v>12932652.057971435</v>
+        <v>14022555.382335631</v>
       </c>
       <c r="G83" s="10">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="H83" s="10">
         <v>2</v>
@@ -10713,10 +10713,10 @@
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>884</v>
+        <v>924</v>
       </c>
       <c r="K83" s="10">
-        <v>12141154.944297301</v>
+        <v>14540962.879546613</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10724,19 +10724,19 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="C84" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E84" s="10">
-        <v>844</v>
+        <v>891</v>
       </c>
       <c r="F84" s="10">
-        <v>9981637.0205054078</v>
+        <v>13097969.624595124</v>
       </c>
       <c r="G84" s="10">
         <v>978</v>
@@ -10748,10 +10748,10 @@
         <v>4</v>
       </c>
       <c r="J84" s="10">
-        <v>838</v>
+        <v>905</v>
       </c>
       <c r="K84" s="10">
-        <v>14297155.155265316</v>
+        <v>17335025.564646862</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10759,7 +10759,7 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C85" s="10">
         <v>2</v>
@@ -10768,25 +10768,25 @@
         <v>6</v>
       </c>
       <c r="E85" s="10">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="F85" s="10">
-        <v>14505794.519231632</v>
+        <v>18310243.092242092</v>
       </c>
       <c r="G85" s="10">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="H85" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85" s="10">
         <v>7</v>
       </c>
       <c r="J85" s="10">
-        <v>711</v>
+        <v>769</v>
       </c>
       <c r="K85" s="10">
-        <v>16606259.866167733</v>
+        <v>20062269.907639056</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10794,7 +10794,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C86" s="10">
         <v>1</v>
@@ -10803,25 +10803,25 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>599</v>
+        <v>540</v>
       </c>
       <c r="F86" s="10">
-        <v>7293208.2181321681</v>
+        <v>8670745.7737258058</v>
       </c>
       <c r="G86" s="10">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="H86" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I86" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="K86" s="10">
-        <v>6774648.0106049767</v>
+        <v>8159419.8209574521</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10829,7 +10829,7 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1750</v>
+        <v>1754</v>
       </c>
       <c r="C87" s="10">
         <v>0</v>
@@ -10838,13 +10838,13 @@
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1277</v>
+        <v>1290</v>
       </c>
       <c r="F87" s="10">
-        <v>28428762.025288314</v>
+        <v>35310344.073664188</v>
       </c>
       <c r="G87" s="10">
-        <v>1782</v>
+        <v>1778</v>
       </c>
       <c r="H87" s="10">
         <v>2</v>
@@ -10853,10 +10853,10 @@
         <v>9</v>
       </c>
       <c r="J87" s="10">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="K87" s="10">
-        <v>35222545.764984086</v>
+        <v>42702965.826996572</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10864,7 +10864,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="C88" s="10">
         <v>0</v>
@@ -10873,10 +10873,10 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>692</v>
+        <v>872</v>
       </c>
       <c r="F88" s="10">
-        <v>5928454.9220199343</v>
+        <v>7539509.8299834495</v>
       </c>
       <c r="G88" s="10">
         <v>629</v>
@@ -10888,10 +10888,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>701</v>
+        <v>628</v>
       </c>
       <c r="K88" s="10">
-        <v>7643312.6360125961</v>
+        <v>8983939.4270911943</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10899,34 +10899,34 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C89" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89" s="10">
         <v>7</v>
       </c>
       <c r="E89" s="10">
-        <v>548</v>
+        <v>580</v>
       </c>
       <c r="F89" s="10">
-        <v>13656288.42308018</v>
+        <v>16488973.74900602</v>
       </c>
       <c r="G89" s="10">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="H89" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I89" s="10">
         <v>8</v>
       </c>
       <c r="J89" s="10">
-        <v>607</v>
+        <v>816</v>
       </c>
       <c r="K89" s="10">
-        <v>14040647.878120376</v>
+        <v>17466134.791588984</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10934,22 +10934,22 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C90" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" s="10">
         <v>0</v>
       </c>
       <c r="E90" s="10">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="F90" s="10">
-        <v>3441098.5518438071</v>
+        <v>4056251.955859642</v>
       </c>
       <c r="G90" s="10">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -10958,10 +10958,10 @@
         <v>1</v>
       </c>
       <c r="J90" s="10">
-        <v>348</v>
+        <v>68</v>
       </c>
       <c r="K90" s="10">
-        <v>3736480.5201603561</v>
+        <v>4177272.1257785661</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.35">
@@ -10969,34 +10969,34 @@
         <v>203</v>
       </c>
       <c r="B91" s="13">
-        <v>84646</v>
+        <v>84861</v>
       </c>
       <c r="C91" s="13">
-        <v>652</v>
+        <v>963</v>
       </c>
       <c r="D91" s="13">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E91" s="13">
-        <v>71621</v>
+        <v>70217</v>
       </c>
       <c r="F91" s="13">
-        <v>1348656223.5730584</v>
+        <v>1652684078.2688403</v>
       </c>
       <c r="G91" s="13">
-        <v>84547</v>
+        <v>84687</v>
       </c>
       <c r="H91" s="13">
-        <v>971</v>
+        <v>1272</v>
       </c>
       <c r="I91" s="13">
         <v>313</v>
       </c>
       <c r="J91" s="13">
-        <v>71605</v>
+        <v>71131</v>
       </c>
       <c r="K91" s="13">
-        <v>1417866992.8139043</v>
+        <v>1715218317.2305956</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -1163,27 +1163,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7384820.0516374568</v>
+        <v>8011855.9913176866</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7794403.2465877896</v>
+        <v>8539462.2923211604</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>5.5462853811788504E-2</v>
+        <v>6.585319326448591E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>5.3097345132743445E-2</v>
+        <v>1.9943019943019946E-2</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1211,15 +1211,15 @@
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>1.674641148325362E-2</v>
+        <v>2.857142857142847E-2</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1243,27 +1243,27 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8808432.9749075994</v>
+        <v>9589962.4832898322</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8190359.7394492216</v>
+        <v>8996481.4656081535</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-7.0168353124678395E-2</v>
+        <v>-6.1885645404327505E-2</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>515</v>
+        <v>634</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>4.0404040404040442E-2</v>
+        <v>0.28600405679513186</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="O3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1287,19 +1287,19 @@
       </c>
       <c r="Q3" s="12">
         <f t="shared" ref="Q3:Q66" si="3">IFERROR(P3/O3-1,0)</f>
-        <v>1.5</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-0.14175654853620956</v>
+        <v>-0.14525993883792054</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1323,27 +1323,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10477595.383566588</v>
+        <v>11693170.217475448</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11063906.54678895</v>
+        <v>11439196.74842638</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>5.5958561268929286E-2</v>
+        <v>-2.1719812875853339E-2</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>690</v>
+        <v>724</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>-0.57246376811594202</v>
+        <v>-0.51657458563535918</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="O4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1367,19 +1367,19 @@
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="3"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>6.1391541609822742E-2</v>
+        <v>3.5087719298245723E-2</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1403,31 +1403,31 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19011434.547334105</v>
+        <v>20529286.348929532</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19871487.575189549</v>
+        <v>21858809.479129504</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>4.523872334379142E-2</v>
+        <v>6.4762267309369959E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1021</v>
+        <v>2035</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>968</v>
+        <v>1007</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1909892262487767E-2</v>
+        <v>-0.50515970515970521</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="N5" s="12">
         <f t="shared" si="2"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.5</v>
       </c>
       <c r="O5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1451,15 +1451,15 @@
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1215</v>
+        <v>1208</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>9.0534979423868567E-3</v>
+        <v>1.655629139072845E-2</v>
       </c>
       <c r="U5">
         <v>1</v>
@@ -1483,27 +1483,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8381329.5959949316</v>
+        <v>9136539.7726296578</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8985930.6731321104</v>
+        <v>9958782.7049773205</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>7.2136654478555551E-2</v>
+        <v>8.9995003886575997E-2</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>3.8567493112947604E-2</v>
+        <v>5.5696202531645644E-2</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>-3.2098765432098775E-2</v>
+        <v>-2.4875621890547261E-2</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1563,27 +1563,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7145519.7571021039</v>
+        <v>7743516.6435261397</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5498928.2696352452</v>
+        <v>6081677.9457779359</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>-0.23043690920177951</v>
+        <v>-0.2146103345871363</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>-7.7738515901060068E-2</v>
+        <v>1.4981273408239737E-2</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="O7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -1615,11 +1615,11 @@
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>2.6109660574411553E-3</v>
+        <v>-1.0443864229765065E-2</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -1643,27 +1643,27 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8340069.6906619277</v>
+        <v>9125846.8320685625</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8715775.2807155531</v>
+        <v>9528640.5381818991</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>4.5048255468930876E-2</v>
+        <v>4.413767988061168E-2</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>-2.39520958083832E-2</v>
+        <v>1.8145161290322509E-2</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1683,23 +1683,23 @@
       </c>
       <c r="P8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>5.8043117744610351E-2</v>
+        <v>6.2184873949579833E-2</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1723,27 +1723,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3747444.9194353758</v>
+        <v>4059495.7912112302</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3950550.299179432</v>
+        <v>4278470.8679645592</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>5.419836291407254E-2</v>
+        <v>5.394144692240066E-2</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>-3.8167938931297662E-2</v>
+        <v>8.2089552238805874E-2</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="R9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>6.5868263473053856E-2</v>
+        <v>5.9523809523809534E-2</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1803,27 +1803,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>586599.09295351198</v>
+        <v>832225.483727457</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3899890.5906057432</v>
+        <v>4260676.8748711916</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>5.6483065477818766</v>
+        <v>4.1196183704781957</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>0.34615384615384626</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1847,19 +1847,19 @@
       </c>
       <c r="Q10" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>0.12021857923497259</v>
+        <v>0.11229946524064172</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1883,27 +1883,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7940043.156108438</v>
+        <v>8440011.6415319797</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6730366.9863225957</v>
+        <v>7427057.5940592606</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>-0.15235133436966442</v>
+        <v>-0.1200180865258681</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>9.1185410334346573E-2</v>
+        <v>8.3333333333333037E-3</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>-2.7100271002710064E-2</v>
+        <v>-2.4456521739130488E-2</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3605945.15739296</v>
+        <v>3926643.4736452131</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3309685.3118176642</v>
+        <v>3647125.4913574592</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>-8.2158721956128389E-2</v>
+        <v>-7.1184966031120123E-2</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>-0.17786561264822132</v>
+        <v>-0.18250950570342206</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2011,15 +2011,15 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>0.14634146341463405</v>
+        <v>0.12918660287081329</v>
       </c>
       <c r="U12">
         <v>2</v>
@@ -2043,19 +2043,19 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3977027.8671158012</v>
+        <v>4329889.7318454506</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4053726.7902464792</v>
+        <v>4468512.0865646908</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>1.928548798082752E-2</v>
+        <v>3.2015215930258245E-2</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1029</v>
+        <v>232</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>-0.78620019436345967</v>
+        <v>-5.1724137931034475E-2</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2091,15 +2091,15 @@
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>1.6528925619834656E-2</v>
+        <v>-8.1967213114754189E-3</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2123,27 +2123,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13399000.366042772</v>
+        <v>15542536.569016691</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22834765.983763617</v>
+        <v>24968411.489844091</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>0.70421414732057208</v>
+        <v>0.60645666677197552</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1622</v>
+        <v>1327</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1328</v>
+        <v>1269</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>-0.18125770653514184</v>
+        <v>-4.3707611152976611E-2</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="O14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2167,19 +2167,19 @@
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>-1.4685314685314643E-2</v>
+        <v>-2.023726448011165E-2</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2203,27 +2203,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26643248.081871454</v>
+        <v>29238120.41858248</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33008994.284924474</v>
+        <v>35824755.92923595</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>0.23892530608474827</v>
+        <v>0.22527561335534041</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>881</v>
+        <v>907</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>944</v>
+        <v>889</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>7.1509648127128234E-2</v>
+        <v>-1.9845644983461974E-2</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2283,27 +2283,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15828242.32627888</v>
+        <v>17096402.744824786</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15843798.763286391</v>
+        <v>17290212.931036513</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>9.8282782679426361E-4</v>
+        <v>1.1336313790946129E-2</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>966</v>
+        <v>922</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>961</v>
+        <v>907</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1759834368529933E-3</v>
+        <v>-1.6268980477223471E-2</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2331,15 +2331,15 @@
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>-1.3592233009708687E-2</v>
+        <v>-5.859375E-3</v>
       </c>
       <c r="U16">
         <v>3</v>
@@ -2363,27 +2363,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10913566.119168691</v>
+        <v>12161015.921806771</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14999077.867172075</v>
+        <v>16203096.619572133</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>0.37435167418169146</v>
+        <v>0.33238018301721173</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>657</v>
+        <v>681</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>-1.2176560121765601E-2</v>
+        <v>-6.607929515418498E-2</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="M17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="O17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2411,15 +2411,15 @@
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>-6.5861690450055299E-3</v>
+        <v>3.3222591362125353E-3</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2443,27 +2443,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>58775003.547264457</v>
+        <v>63455337.242055319</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>53555984.147053935</v>
+        <v>58431495.578616232</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>-8.8796581628678206E-2</v>
+        <v>-7.9171301923355197E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2097</v>
+        <v>2091</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2243</v>
+        <v>2265</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>6.9623271340009563E-2</v>
+        <v>8.3213773314203765E-2</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2479,27 +2479,27 @@
       </c>
       <c r="O18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>-0.39766081871345027</v>
+        <v>-0.39884393063583812</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2902</v>
+        <v>2872</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2812</v>
+        <v>2799</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>-3.1013094417642995E-2</v>
+        <v>-2.5417827298050089E-2</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2523,27 +2523,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11584685.638031436</v>
+        <v>13715739.655666236</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28439991.090680379</v>
+        <v>30857225.122215234</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>1.4549644227992307</v>
+        <v>1.2497674858874652</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1190</v>
+        <v>1218</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>4.8458149779735615E-2</v>
+        <v>6.5616797900262425E-2</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.3152889539129795E-4</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2603,27 +2603,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>57592953.799537219</v>
+        <v>62455214.851508647</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>48206739.535607196</v>
+        <v>53170556.161955953</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>-0.16297504546477082</v>
+        <v>-0.14866106395803103</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2229</v>
+        <v>2209</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2139</v>
+        <v>2092</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-4.037685060565277E-2</v>
+        <v>-5.2965142598460857E-2</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2639,27 +2639,27 @@
       </c>
       <c r="O20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>-0.7142857142857143</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2969</v>
+        <v>2972</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2775</v>
+        <v>2777</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-6.5341865948130629E-2</v>
+        <v>-6.5612382234185751E-2</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2683,27 +2683,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9055980.6224311255</v>
+        <v>9647857.3613462802</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7894030.6329214247</v>
+        <v>8653275.5065172911</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>-0.12830747303407652</v>
+        <v>-0.1030883664194433</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9940119760479056E-2</v>
+        <v>-8.5470085470085166E-3</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2731,15 +2731,15 @@
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-1.8382352941176516E-2</v>
+        <v>-2.5878003696857665E-2</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2763,27 +2763,27 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23687070.811500505</v>
+        <v>25727162.271941304</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21540252.204000156</v>
+        <v>23472141.842081539</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>-9.0632506846647698E-2</v>
+        <v>-8.7651347086932563E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1298</v>
+        <v>1348</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1446</v>
+        <v>1473</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>0.11402157164869031</v>
+        <v>9.2729970326409505E-2</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2799,27 +2799,27 @@
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>9.0909090909090828E-2</v>
+        <v>7.6923076923076872E-2</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1739</v>
+        <v>1749</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1728</v>
+        <v>1740</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>-6.3254744105808447E-3</v>
+        <v>-5.145797598627766E-3</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2843,27 +2843,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9478921.5549611673</v>
+        <v>10259830.90651048</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9013330.2175357286</v>
+        <v>9877911.5601799227</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>-4.9118598009892045E-2</v>
+        <v>-3.7224721324423227E-2</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>0.11351351351351346</v>
+        <v>7.4509803921568585E-2</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>-5.1252847380410027E-2</v>
+        <v>-5.0171037628278237E-2</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2923,27 +2923,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12129368.103966432</v>
+        <v>13074169.534061378</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11323368.874365836</v>
+        <v>12367446.731246172</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>-6.6450224174252281E-2</v>
+        <v>-5.4054890520887189E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>837</v>
+        <v>807</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>769</v>
+        <v>729</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>-8.1242532855436034E-2</v>
+        <v>-9.6654275092936781E-2</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2971,15 +2971,15 @@
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>-1.9144144144144115E-2</v>
+        <v>-1.7977528089887618E-2</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -3003,27 +3003,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2536402.8153050868</v>
+        <v>2752351.900354438</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2808535.7045010701</v>
+        <v>3125322.1816324871</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>0.10729087964809336</v>
+        <v>0.1355096640186233</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>0.33522727272727271</v>
+        <v>0.2807017543859649</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="P25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -3055,11 +3055,11 @@
       </c>
       <c r="S25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="4"/>
-        <v>-5.1948051948051965E-2</v>
+        <v>-5.6277056277056259E-2</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -3083,27 +3083,27 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22511788.425732885</v>
+        <v>24358751.544144496</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22367217.405995153</v>
+        <v>24602514.895429038</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>-6.422013969022311E-3</v>
+        <v>1.0007218590114331E-2</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1485</v>
+        <v>1545</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>0.14494988434849643</v>
+        <v>0.19489559164733183</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3135,11 +3135,11 @@
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1639</v>
+        <v>1646</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>-1.4431749849669218E-2</v>
+        <v>-1.0222489476849117E-2</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -3163,27 +3163,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18118545.915352695</v>
+        <v>19811258.757022385</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20204926.878771558</v>
+        <v>22132677.989444103</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>0.11515167790870984</v>
+        <v>0.1171767660446541</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>689</v>
+        <v>630</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>0.10416666666666674</v>
+        <v>1.5898251192367763E-3</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3211,15 +3211,15 @@
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>3.3333333333333437E-2</v>
+        <v>3.0998851894374235E-2</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -3243,31 +3243,31 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17752317.438190568</v>
+        <v>19404275.471009124</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19114856.538799368</v>
+        <v>21393659.220353145</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>7.6752745400866296E-2</v>
+        <v>0.10252295955683843</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>911</v>
+        <v>854</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>0.10157194679564685</v>
+        <v>3.6407766990291357E-2</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="N28" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3291,15 +3291,15 @@
       </c>
       <c r="R28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-5.070422535211272E-2</v>
+        <v>-4.1509433962264142E-2</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -3323,27 +3323,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24186906.744684663</v>
+        <v>26404188.141816933</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25226309.632355992</v>
+        <v>27596352.646259207</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>4.2973783239138141E-2</v>
+        <v>4.515058361344626E-2</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>812</v>
+        <v>838</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4038461538461564E-2</v>
+        <v>2.6960784313725394E-2</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3363,23 +3363,23 @@
       </c>
       <c r="P29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>2.5067144136078801E-2</v>
+        <v>3.0493273542600896E-2</v>
       </c>
       <c r="U29">
         <v>0</v>
@@ -3403,27 +3403,27 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34394456.147691317</v>
+        <v>37505222.301559903</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35006468.816651084</v>
+        <v>38482011.267993741</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>1.7793933601733869E-2</v>
+        <v>2.6044078837341278E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1169</v>
+        <v>1113</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>-1.3502109704641385E-2</v>
+        <v>-7.7879038939519418E-2</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3443,23 +3443,23 @@
       </c>
       <c r="P30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>-7.5394105551748192E-3</v>
+        <v>-5.4982817869415612E-3</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3483,27 +3483,27 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14133878.193473892</v>
+        <v>15398605.461348807</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13924727.038236933</v>
+        <v>15371358.076542115</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>-1.4797860316465128E-2</v>
+        <v>-1.7694709352145122E-3</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>520</v>
+        <v>581</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>612</v>
+        <v>794</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>0.17692307692307696</v>
+        <v>0.36660929432013778</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3531,15 +3531,15 @@
       </c>
       <c r="R31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>1.0309278350515427E-2</v>
+        <v>4.3988269794721369E-3</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3563,27 +3563,27 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>43001448.166093811</v>
+        <v>46536061.009953454</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26036926.729291752</v>
+        <v>29407824.984452795</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-0.39451046790973909</v>
+        <v>-0.36806372636130835</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1571</v>
+        <v>892</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1707</v>
+        <v>1680</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>8.6569064290261011E-2</v>
+        <v>0.88340807174887903</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3611,15 +3611,15 @@
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-4.52907874420998E-2</v>
+        <v>-4.3276661514683123E-2</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3643,27 +3643,27 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14132076.933236703</v>
+        <v>15552674.040534776</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14724372.928554051</v>
+        <v>16019371.822294367</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>4.1911461288775431E-2</v>
+        <v>3.0007558863719641E-2</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>887</v>
+        <v>774</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>-0.24464487034949267</v>
+        <v>-0.1472868217054264</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3691,15 +3691,15 @@
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>1.3095238095238049E-2</v>
+        <v>1.0663507109004655E-2</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3723,27 +3723,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13627139.337142861</v>
+        <v>14986852.341861239</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13006674.485248519</v>
+        <v>14185152.208508916</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>-4.553155556303512E-2</v>
+        <v>-5.3493563228952046E-2</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>746</v>
+        <v>538</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>-0.20375335120643434</v>
+        <v>0.11152416356877315</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3775,11 +3775,11 @@
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>-1.7449664429530221E-2</v>
+        <v>-2.6845637583892579E-2</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3803,27 +3803,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20545921.86789586</v>
+        <v>22114246.499472193</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22932126.399725944</v>
+        <v>25110758.092792481</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>0.11614005675543138</v>
+        <v>0.13550141052247944</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>465</v>
+        <v>822</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>0.95268817204301071</v>
+        <v>0.10827250608272498</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="O35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3847,19 +3847,19 @@
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="3"/>
-        <v>-0.2857142857142857</v>
+        <v>-0.58333333333333326</v>
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>2.3195876288659711E-2</v>
+        <v>2.7467811158798261E-2</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3883,27 +3883,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19120041.93568055</v>
+        <v>20741126.062683959</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21141554.628010023</v>
+        <v>22932356.491074044</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>0.10572741938170438</v>
+        <v>0.10564664723447192</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>858</v>
+        <v>837</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>5.7953144266337908E-2</v>
+        <v>5.1507537688442184E-2</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3923,23 +3923,23 @@
       </c>
       <c r="P36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="3"/>
-        <v>1.6416666666666666</v>
+        <v>1.65</v>
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1452</v>
+        <v>1433</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>8.764044943820215E-2</v>
+        <v>7.6634109691960939E-2</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3963,27 +3963,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34901512.498659305</v>
+        <v>38453663.605802923</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35002790.497653201</v>
+        <v>38312378.880640082</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>2.9018226358465959E-3</v>
+        <v>-3.6741551237141623E-3</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1575</v>
+        <v>1529</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1484</v>
+        <v>1557</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>-5.7777777777777817E-2</v>
+        <v>1.8312622629169439E-2</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4003,23 +4003,23 @@
       </c>
       <c r="P37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="3"/>
-        <v>2.4057971014492754</v>
+        <v>2.4347826086956523</v>
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2418</v>
+        <v>2397</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>-6.3275434243176165E-2</v>
+        <v>-5.4651647893199873E-2</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4043,27 +4043,27 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12522131.034147704</v>
+        <v>13607803.394892052</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12972219.559267271</v>
+        <v>14083966.5119655</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>3.5943444761293408E-2</v>
+        <v>3.4991916274465407E-2</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>447</v>
+        <v>570</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>3.3557046979865834E-2</v>
+        <v>-0.2192982456140351</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4091,15 +4091,15 @@
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>-4.0257648953301084E-2</v>
+        <v>-4.2071197411003292E-2</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4123,27 +4123,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>41927511.893101111</v>
+        <v>45449281.559613265</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>40159357.461528517</v>
+        <v>43927118.587503135</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>-4.2171699481731717E-2</v>
+        <v>-3.3491463888457584E-2</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1950</v>
+        <v>1914</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1850</v>
+        <v>1817</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1282051282051322E-2</v>
+        <v>-5.0679205851619669E-2</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4171,15 +4171,15 @@
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2064</v>
+        <v>2057</v>
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2040</v>
+        <v>2031</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>-1.1627906976744207E-2</v>
+        <v>-1.2639766650461848E-2</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4203,27 +4203,27 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27163671.010994777</v>
+        <v>29655636.505533084</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31332334.071481273</v>
+        <v>33967834.959300019</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>0.15346464249251079</v>
+        <v>0.14540906761392125</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>803</v>
+        <v>1422</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>1.9925280199252882E-2</v>
+        <v>-0.40506329113924056</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4255,11 +4255,11 @@
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>3.44444444444445E-2</v>
+        <v>3.3333333333333437E-2</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14178492.832121568</v>
+        <v>16068125.974080767</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22149087.91487515</v>
+        <v>24052081.674599729</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>0.5621609558313625</v>
+        <v>0.49688157246201281</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>919</v>
+        <v>908</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>944</v>
+        <v>970</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>2.7203482045701888E-2</v>
+        <v>6.8281938325991165E-2</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
@@ -4331,15 +4331,15 @@
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-2.7726432532347522E-2</v>
+        <v>-1.5726179463459777E-2</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4363,27 +4363,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21673565.670844473</v>
+        <v>23518097.944919869</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22463428.205046136</v>
+        <v>24303801.668385867</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>3.6443589679578947E-2</v>
+        <v>3.3408472288283697E-2</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>635</v>
+        <v>597</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>-2.457757296466978E-2</v>
+        <v>-4.7846889952153138E-2</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4411,15 +4411,15 @@
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>1.2121212121212199E-2</v>
+        <v>7.2202166064982976E-3</v>
       </c>
       <c r="U42">
         <v>1</v>
@@ -4443,27 +4443,27 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13895483.106158944</v>
+        <v>15130453.175075745</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13423472.227419101</v>
+        <v>14609642.865583366</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>-3.3968655507244039E-2</v>
+        <v>-3.4421329187304561E-2</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>5.3571428571428381E-3</v>
+        <v>5.6057866184448413E-2</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4491,15 +4491,15 @@
       </c>
       <c r="R43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>1.1315417256011262E-2</v>
+        <v>1.5580736543909346E-2</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4523,27 +4523,27 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12161003.483174358</v>
+        <v>13321177.692165183</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12527683.802709805</v>
+        <v>13640714.055751091</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>3.0152143286758859E-2</v>
+        <v>2.3987095658504876E-2</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>7.7138849929873743E-2</v>
+        <v>8.2058414464533991E-2</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4571,15 +4571,15 @@
       </c>
       <c r="R44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>2.1802325581395277E-2</v>
+        <v>2.6239067055393583E-2</v>
       </c>
       <c r="U44">
         <v>2</v>
@@ -4603,31 +4603,31 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37273755.084821194</v>
+        <v>40575137.286203943</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>41936647.835470937</v>
+        <v>45745588.58812362</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>0.1250985509787983</v>
+        <v>0.12742905256115278</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1078</v>
+        <v>2756</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1196</v>
+        <v>1136</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>0.10946196660482377</v>
+        <v>-0.58780841799709727</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="N45" s="12">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="O45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="P45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="3"/>
@@ -4651,15 +4651,15 @@
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>3.1400966183574797E-2</v>
+        <v>3.7096774193548399E-2</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4683,27 +4683,27 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17874087.659617409</v>
+        <v>19563741.756338328</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17870643.858846333</v>
+        <v>19453326.637208953</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>-1.926700168790596E-4</v>
+        <v>-5.6438650900512144E-3</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>881</v>
+        <v>1570</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>2.0431328036322416E-2</v>
+        <v>-0.42675159235668791</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4711,11 +4711,11 @@
       </c>
       <c r="M46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="2"/>
-        <v>-0.4285714285714286</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="O46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4731,15 +4731,15 @@
       </c>
       <c r="R46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>-3.8293216630196913E-2</v>
+        <v>-3.4140969162995582E-2</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4763,27 +4763,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32056870.004816383</v>
+        <v>34200115.304982483</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32663997.039998908</v>
+        <v>35513529.941505633</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>1.8939061583096217E-2</v>
+        <v>3.8403807262363365E-2</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1045</v>
+        <v>465</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1014</v>
+        <v>972</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>-2.966507177033495E-2</v>
+        <v>1.0903225806451613</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4811,15 +4811,15 @@
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1356</v>
+        <v>1345</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>4.4985250737463067E-2</v>
+        <v>5.0557620817843762E-2</v>
       </c>
       <c r="U47">
         <v>5</v>
@@ -4843,27 +4843,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16539048.45741608</v>
+        <v>17692903.869914349</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15061140.755258827</v>
+        <v>16698819.456651105</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>-8.9358689888508147E-2</v>
+        <v>-5.6185486598026579E-2</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>360</v>
+        <v>233</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>0.42777777777777781</v>
+        <v>1.1716738197424892</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4895,11 +4895,11 @@
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>1.6563146997929712E-2</v>
+        <v>1.8633540372670732E-2</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4923,27 +4923,27 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12081136.709517296</v>
+        <v>12885929.269668665</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13095908.736033432</v>
+        <v>14295788.226282325</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>8.3996402897809963E-2</v>
+        <v>0.10941073221100428</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>305</v>
+        <v>211</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>0.26229508196721318</v>
+        <v>0.97630331753554511</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="12">
         <f t="shared" si="3"/>
@@ -4971,15 +4971,15 @@
       </c>
       <c r="R49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>2.1929824561404132E-3</v>
+        <v>4.3763676148795838E-3</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -5003,27 +5003,27 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10520584.106780592</v>
+        <v>11147708.240657611</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5501887.3312636809</v>
+        <v>5589046.8414643016</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-0.4770359444474499</v>
+        <v>-0.49863714399340975</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>332</v>
+        <v>220</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-0.98493975903614461</v>
+        <v>-0.82727272727272727</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5051,15 +5051,15 @@
       </c>
       <c r="R50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="S50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="4"/>
-        <v>-6.9605568445475607E-2</v>
+        <v>-7.906976744186045E-2</v>
       </c>
       <c r="U50">
         <v>4</v>
@@ -5083,27 +5083,27 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24723580.217376906</v>
+        <v>26191668.071031023</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26527780.340592857</v>
+        <v>28462888.360719599</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>7.2974872868447838E-2</v>
+        <v>8.6715373894060255E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>925</v>
+        <v>661</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>962</v>
+        <v>889</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>4.0000000000000036E-2</v>
+        <v>0.34493192133131623</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="O51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5127,11 +5127,11 @@
       </c>
       <c r="Q51" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-4.5289855072463414E-3</v>
+        <v>-3.6264732547597323E-3</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5163,27 +5163,27 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23331162.81574592</v>
+        <v>25274443.649353232</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26543308.271027669</v>
+        <v>28675298.836824629</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>0.13767618359398326</v>
+        <v>0.13455707412014295</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>889</v>
+        <v>715</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>960</v>
+        <v>797</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>7.9865016872890937E-2</v>
+        <v>0.11468531468531462</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="O52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5207,19 +5207,19 @@
       </c>
       <c r="Q52" s="12">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>937</v>
+        <v>927</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>-5.8291457286432147E-2</v>
+        <v>-7.1142284569138292E-2</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5243,27 +5243,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46692177.299890816</v>
+        <v>49677371.10828805</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>48360579.666022353</v>
+        <v>52582289.558401659</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>3.5731946176248197E-2</v>
+        <v>5.8475687930051423E-2</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1445</v>
+        <v>1226</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1627</v>
+        <v>1642</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>0.12595155709342554</v>
+        <v>0.33931484502446985</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5283,23 +5283,23 @@
       </c>
       <c r="P53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q53" s="12">
         <f t="shared" si="3"/>
-        <v>0.83333333333333326</v>
+        <v>1</v>
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2076</v>
+        <v>2065</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>1.3005780346820872E-2</v>
+        <v>1.6949152542372836E-2</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5323,27 +5323,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11101958.599655284</v>
+        <v>11997117.736853795</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12869337.990031293</v>
+        <v>13982560.869168984</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>0.15919527842869874</v>
+        <v>0.16549334397345539</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>534</v>
+        <v>453</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>586</v>
+        <v>675</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>9.7378277153558068E-2</v>
+        <v>0.49006622516556297</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="O54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5367,19 +5367,19 @@
       </c>
       <c r="Q54" s="12">
         <f t="shared" si="3"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.5</v>
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>-4.1055718475073277E-2</v>
+        <v>-3.8067349926793503E-2</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5403,27 +5403,27 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19744310.44305547</v>
+        <v>21280371.70766744</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22427850.574070819</v>
+        <v>24407846.306572575</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>0.13591460379206155</v>
+        <v>0.1469652241919388</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>695</v>
+        <v>510</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>807</v>
+        <v>827</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>0.16115107913669058</v>
+        <v>0.6215686274509804</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="O55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5447,19 +5447,19 @@
       </c>
       <c r="Q55" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>4.2675893886966465E-2</v>
+        <v>4.9539170506912367E-2</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5483,27 +5483,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12108515.79752842</v>
+        <v>13008470.054326516</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12081050.832576821</v>
+        <v>12702688.915399697</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>-2.2682354642676872E-3</v>
+        <v>-2.350631070754694E-2</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>636</v>
+        <v>516</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>632</v>
+        <v>57</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>-6.2893081761006275E-3</v>
+        <v>-0.88953488372093026</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5531,15 +5531,15 @@
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-9.9999999999999978E-2</v>
+        <v>-0.10146862483311081</v>
       </c>
       <c r="U56">
         <v>2</v>
@@ -5563,27 +5563,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25953478.849800728</v>
+        <v>27692985.716273904</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28241591.85484669</v>
+        <v>30502819.256533097</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>8.816209257679275E-2</v>
+        <v>0.10146372691796768</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>986</v>
+        <v>807</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1112</v>
+        <v>1279</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>0.12778904665314395</v>
+        <v>0.58488228004956633</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5599,11 +5599,11 @@
       </c>
       <c r="O57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q57" s="12">
         <f t="shared" si="3"/>
@@ -5611,15 +5611,15 @@
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>4.5289855072463414E-3</v>
+        <v>-1.8066847335139746E-3</v>
       </c>
       <c r="U57">
         <v>2</v>
@@ -5643,27 +5643,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31393322.515753064</v>
+        <v>33951195.810102426</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38769776.034656703</v>
+        <v>41763405.554746158</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>0.23496887005834322</v>
+        <v>0.23010116604844755</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1510</v>
+        <v>1441</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1633</v>
+        <v>1494</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>8.1456953642384144E-2</v>
+        <v>3.6780013879250451E-2</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5679,27 +5679,27 @@
       </c>
       <c r="O58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q58" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1425</v>
+        <v>1436</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>0.12070175438596498</v>
+        <v>0.11281337047353768</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5723,27 +5723,27 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17452043.978152473</v>
+        <v>18629448.795252305</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15455780.272549629</v>
+        <v>16761125.185675364</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>-0.11438566783935955</v>
+        <v>-0.10028872191071381</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>685</v>
+        <v>648</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>812</v>
+        <v>790</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>0.18540145985401457</v>
+        <v>0.21913580246913589</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5771,15 +5771,15 @@
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>4.1504539559014342E-2</v>
+        <v>4.0051679586563305E-2</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5803,27 +5803,27 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19453163.939775139</v>
+        <v>20847380.402954869</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20408682.048246805</v>
+        <v>22020764.973671433</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>4.9118904843954647E-2</v>
+        <v>5.6284509038375452E-2</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>4.366812227074246E-2</v>
+        <v>3.1111111111111089E-2</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="O60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="Q60" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="R60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -5855,11 +5855,11 @@
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>-1.5360983102918557E-2</v>
+        <v>-1.228878648233489E-2</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5883,27 +5883,27 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>62712300.78279233</v>
+        <v>67327568.067904234</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>65608445.879055992</v>
+        <v>70670658.044179976</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>4.6181451806315055E-2</v>
+        <v>4.9654102653819532E-2</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1606</v>
+        <v>1641</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1794</v>
+        <v>1829</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>0.11706102117061024</v>
+        <v>0.11456429006703228</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5919,19 +5919,19 @@
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1970</v>
+        <v>1983</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>5.0761421319789335E-4</v>
+        <v>-6.0514372163388286E-3</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5963,27 +5963,27 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>45460845.578881703</v>
+        <v>49430448.945431069</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>46716196.328422241</v>
+        <v>50220349.921165459</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>2.761388912932361E-2</v>
+        <v>1.5980048585162665E-2</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1219</v>
+        <v>1265</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1265</v>
+        <v>1201</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>3.7735849056603765E-2</v>
+        <v>-5.0592885375494112E-2</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="O62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="P62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6007,19 +6007,19 @@
       </c>
       <c r="Q62" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>-7.6923076923076872E-2</v>
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>1.5812776723592714E-2</v>
+        <v>1.2634238787113006E-2</v>
       </c>
       <c r="U62">
         <v>9</v>
@@ -6043,27 +6043,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30167393.236838799</v>
+        <v>32493119.305810899</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31840007.43950006</v>
+        <v>34013930.676028676</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>5.5444439283496072E-2</v>
+        <v>4.6804105075433755E-2</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>-2.6027397260273921E-2</v>
+        <v>-4.7683923705722053E-2</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6087,19 +6087,19 @@
       </c>
       <c r="Q63" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.75</v>
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>1.2457531143827749E-2</v>
+        <v>9.0497737556560764E-3</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6123,27 +6123,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>45486578.400095366</v>
+        <v>49546807.447998308</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>41636311.204481982</v>
+        <v>45338783.339071438</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>-8.464622600862215E-2</v>
+        <v>-8.4930277563158629E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1437</v>
+        <v>1308</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1292</v>
+        <v>1302</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10090466249130137</v>
+        <v>-4.5871559633027248E-3</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="O64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6167,19 +6167,19 @@
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>1.6393442622950838E-2</v>
+        <v>8.1300813008129413E-3</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2335</v>
+        <v>2317</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2338</v>
+        <v>2329</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>1.2847965738758127E-3</v>
+        <v>5.1791109192922402E-3</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6203,27 +6203,27 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1088870.296364038</v>
+        <v>1348505.727031731</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3332193.916553128</v>
+        <v>3682667.934082624</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>2.0602303393526382</v>
+        <v>1.7309249491945011</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>415</v>
+        <v>250</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>-0.36144578313253017</v>
+        <v>0.12400000000000011</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6255,11 +6255,11 @@
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>-1.619433198380571E-2</v>
+        <v>-2.0242914979757054E-2</v>
       </c>
       <c r="U65">
         <v>2</v>
@@ -6283,27 +6283,27 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32343585.173141804</v>
+        <v>35127326.366053008</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31714020.902646456</v>
+        <v>34445460.314459853</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-1.9464888234410727E-2</v>
+        <v>-1.9411270999893371E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1542</v>
+        <v>1480</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1458</v>
+        <v>1576</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>-5.4474708171206254E-2</v>
+        <v>6.4864864864864868E-2</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="O66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6327,19 +6327,19 @@
       </c>
       <c r="Q66" s="12">
         <f t="shared" si="3"/>
-        <v>1.3333333333333335</v>
+        <v>1</v>
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1674</v>
+        <v>1669</v>
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1625</v>
+        <v>1608</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>-2.9271206690561491E-2</v>
+        <v>-3.6548831635709988E-2</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6363,27 +6363,27 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15328774.192921566</v>
+        <v>16812574.105930068</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14576827.875886289</v>
+        <v>15667692.503356764</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>-4.9054562848378724E-2</v>
+        <v>-6.8096746837207123E-2</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>-1.9543973941368087E-2</v>
+        <v>-6.2695924764890276E-2</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6411,15 +6411,15 @@
       </c>
       <c r="R67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>7.5136612021857951E-2</v>
+        <v>7.8804347826086918E-2</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6443,27 +6443,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21872709.188291144</v>
+        <v>23873577.731227577</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23086254.829625059</v>
+        <v>25445366.118607964</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>5.5482182425922177E-2</v>
+        <v>6.5837990647058531E-2</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>859</v>
+        <v>842</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>889</v>
+        <v>959</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>3.4924330616996402E-2</v>
+        <v>0.13895486935866974</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6491,15 +6491,15 @@
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1477</v>
+        <v>1464</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>7.8889700511322047E-2</v>
+        <v>7.0958302852962785E-2</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6523,27 +6523,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14513828.217951603</v>
+        <v>14656833.663769012</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18591108.258868024</v>
+        <v>20167933.173738983</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>0.28092381828478485</v>
+        <v>0.37600887315745024</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>597</v>
+        <v>982</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1361</v>
+        <v>1241</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>1.2797319932998326</v>
+        <v>0.26374745417515277</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6571,15 +6571,15 @@
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>2.0979020979021046E-2</v>
+        <v>2.8838659392049992E-2</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6603,27 +6603,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>39840425.618532181</v>
+        <v>43203204.558727421</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>41382219.443157539</v>
+        <v>45274446.644820362</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>3.8699230760932846E-2</v>
+        <v>4.7941862351378095E-2</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1229</v>
+        <v>1213</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>3.0105777054515892E-2</v>
+        <v>4.7815333882934796E-2</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6643,23 +6643,23 @@
       </c>
       <c r="P70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q70" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1737</v>
+        <v>1745</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>2.3028209556706924E-2</v>
+        <v>1.8911174785100293E-2</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6683,27 +6683,27 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8058967.8740208512</v>
+        <v>8716800.0374078844</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7736582.7318614321</v>
+        <v>8336159.5331871547</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-4.0003279228680189E-2</v>
+        <v>-4.3667458538365289E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>433</v>
+        <v>629</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>9.2378752886836057E-2</v>
+        <v>-0.33068362480127189</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6723,23 +6723,23 @@
       </c>
       <c r="P71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q71" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>-5.6092843326885911E-2</v>
+        <v>-5.0485436893203839E-2</v>
       </c>
       <c r="U71">
         <v>1</v>
@@ -6763,27 +6763,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12600460.760555159</v>
+        <v>13419610.797755742</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15138195.546056001</v>
+        <v>16320737.705918368</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>0.20140015779780351</v>
+        <v>0.21618562206348058</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>999</v>
+        <v>669</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>812</v>
+        <v>897</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>-0.18718718718718719</v>
+        <v>0.34080717488789247</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6811,15 +6811,15 @@
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>5.6179775280897903E-3</v>
+        <v>1.5873015873015817E-2</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6843,27 +6843,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12247960.588351307</v>
+        <v>13406864.351865375</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13531617.314519268</v>
+        <v>14939900.890034296</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>0.10480575250942681</v>
+        <v>0.11434713576076572</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>513</v>
+        <v>488</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>4.0567951318458473E-2</v>
+        <v>6.1855670103092564E-3</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6891,15 +6891,15 @@
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-3.9755351681957207E-2</v>
+        <v>-2.6073619631901801E-2</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6923,27 +6923,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10279087.37903594</v>
+        <v>11044050.643039128</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8513336.6178804133</v>
+        <v>9544700.5587438848</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>-0.17178088832640448</v>
+        <v>-0.13576088454830271</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>732</v>
+        <v>710</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1095</v>
+        <v>1030</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>0.49590163934426235</v>
+        <v>0.45070422535211274</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6963,23 +6963,23 @@
       </c>
       <c r="P74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q74" s="12">
         <f t="shared" si="8"/>
-        <v>-0.6</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>1.1686143572620988E-2</v>
+        <v>6.6555740432612254E-3</v>
       </c>
       <c r="U74">
         <v>1</v>
@@ -7003,27 +7003,27 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11214438.848868918</v>
+        <v>11871515.03801666</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9194851.3412616476</v>
+        <v>10204824.002210468</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>-0.18008814661385975</v>
+        <v>-0.14039413086441588</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>480</v>
+        <v>251</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>-3.5416666666666652E-2</v>
+        <v>0.84860557768924294</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7051,15 +7051,15 @@
       </c>
       <c r="R75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>-2.8953229398663738E-2</v>
+        <v>-1.5659955257270708E-2</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -7083,27 +7083,27 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29020876.322520785</v>
+        <v>31261131.096501935</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22449998.135948103</v>
+        <v>23598904.180730466</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>-0.22641901345596338</v>
+        <v>-0.24510395647932459</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>-0.28609271523178803</v>
+        <v>-0.27891156462585032</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7123,23 +7123,23 @@
       </c>
       <c r="P76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q76" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-0.11227701993704098</v>
+        <v>-9.9787685774946899E-2</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7163,27 +7163,27 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17509810.325102132</v>
+        <v>18891602.264381222</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17291531.897691596</v>
+        <v>19211296.435092594</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>-1.2466064643636421E-2</v>
+        <v>1.6922554595283579E-2</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>721</v>
+        <v>2118</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>-2.2191400832177521E-2</v>
+        <v>-0.67327667610953723</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7215,11 +7215,11 @@
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>2.5906735751295429E-3</v>
+        <v>5.1813471502590858E-3</v>
       </c>
       <c r="U77">
         <v>2</v>
@@ -7243,27 +7243,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14022555.382335631</v>
+        <v>15118369.682815623</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14540962.879546613</v>
+        <v>15852572.06871303</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>3.6969545355764799E-2</v>
+        <v>4.8563595235532775E-2</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>791</v>
+        <v>855</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>924</v>
+        <v>952</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>0.16814159292035402</v>
+        <v>0.1134502923976608</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7291,15 +7291,15 @@
       </c>
       <c r="R78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>-1.1410788381742698E-2</v>
+        <v>-8.3333333333333037E-3</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7323,27 +7323,27 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13097969.624595124</v>
+        <v>14524187.856017128</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17335025.564646862</v>
+        <v>18906157.439068951</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>0.3234895225360328</v>
+        <v>0.30170152207418921</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>891</v>
+        <v>842</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>905</v>
+        <v>849</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>1.5712682379348974E-2</v>
+        <v>8.3135391923989665E-3</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7371,15 +7371,15 @@
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-2.1021021021020991E-2</v>
+        <v>-2.8112449799196804E-2</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7403,27 +7403,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18310243.092242092</v>
+        <v>19671552.708550803</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20062269.907639056</v>
+        <v>22132214.210737165</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>9.5685611958875816E-2</v>
+        <v>0.12508730442598792</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>749</v>
+        <v>408</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>2.6702269692923997E-2</v>
+        <v>0.86029411764705888</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7451,15 +7451,15 @@
       </c>
       <c r="R80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>2.9490616621983934E-2</v>
+        <v>1.0568031704095038E-2</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7483,15 +7483,15 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8670745.7737258058</v>
+        <v>9375082.9609405603</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8159419.8209574521</v>
+        <v>8934225.0752158221</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>-5.8971392555157043E-2</v>
+        <v>-4.7024425016982341E-2</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
@@ -7499,11 +7499,11 @@
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>522</v>
+        <v>493</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>-3.3333333333333326E-2</v>
+        <v>-8.7037037037037024E-2</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7531,15 +7531,15 @@
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>-4.0492957746478875E-2</v>
+        <v>-4.0421792618629215E-2</v>
       </c>
       <c r="U81">
         <v>0</v>
@@ -7563,27 +7563,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35310344.073664188</v>
+        <v>38701029.284727588</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>42702965.826996572</v>
+        <v>46989513.872192614</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>0.20936136271880978</v>
+        <v>0.21416703226381295</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1290</v>
+        <v>1316</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1388</v>
+        <v>1372</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>7.5968992248061973E-2</v>
+        <v>4.2553191489361764E-2</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7611,15 +7611,15 @@
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1754</v>
+        <v>1762</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1778</v>
+        <v>1783</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>1.36830102622576E-2</v>
+        <v>1.191827468785478E-2</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7643,27 +7643,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7539509.8299834495</v>
+        <v>8622190.9655356202</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8983939.4270911943</v>
+        <v>9986112.4448090214</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>0.19158136665111503</v>
+        <v>0.15818734295322723</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>872</v>
+        <v>734</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>628</v>
+        <v>899</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>-0.27981651376146788</v>
+        <v>0.22479564032697552</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7691,15 +7691,15 @@
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>0.1212121212121211</v>
+        <v>0.11347517730496448</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7723,27 +7723,27 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16488973.74900602</v>
+        <v>17495104.84190416</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17466134.791588984</v>
+        <v>19009001.995999392</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>5.9261483307405216E-2</v>
+        <v>8.6532613995496277E-2</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>580</v>
+        <v>408</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>816</v>
+        <v>979</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>0.40689655172413786</v>
+        <v>1.3995098039215685</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7771,15 +7771,15 @@
       </c>
       <c r="R84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="S84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="T84" s="12">
         <f t="shared" si="9"/>
-        <v>5.5467511885895382E-2</v>
+        <v>3.2608695652173836E-2</v>
       </c>
       <c r="U84">
         <v>7</v>
@@ -7803,31 +7803,31 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4056251.955859642</v>
+        <v>4317447.3459969955</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4177272.1257785661</v>
+        <v>4177363.4227665081</v>
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>2.9835466641587427E-2</v>
+        <v>-3.2446006170838149E-2</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>309</v>
+        <v>380</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>-0.7799352750809061</v>
+        <v>-0.91315789473684206</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -7851,15 +7851,15 @@
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>3.8251366120218622E-2</v>
+        <v>3.8356164383561708E-2</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7898,43 +7898,43 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>84861</v>
+        <v>84798</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>963</v>
+        <v>1001</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>70217</v>
+        <v>71269</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>1652684078.2688403</v>
+        <v>1792079533.2534416</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84687</v>
+        <v>84642</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>71131</v>
+        <v>70910</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>1715218317.2305956</v>
+        <v>1868039006.9845848</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7994,7 +7994,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
@@ -8003,13 +8003,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F6" s="10">
-        <v>7384820.0516374568</v>
+        <v>8011855.9913176866</v>
       </c>
       <c r="G6" s="10">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="H6" s="10">
         <v>1</v>
@@ -8018,10 +8018,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K6" s="10">
-        <v>7794403.2465877896</v>
+        <v>8539462.2923211604</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -8029,22 +8029,22 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="C7" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="10">
         <v>2</v>
       </c>
       <c r="E7" s="10">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F7" s="10">
-        <v>8808432.9749075994</v>
+        <v>9589962.4832898322</v>
       </c>
       <c r="G7" s="10">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H7" s="10">
         <v>5</v>
@@ -8053,10 +8053,10 @@
         <v>3</v>
       </c>
       <c r="J7" s="10">
-        <v>515</v>
+        <v>634</v>
       </c>
       <c r="K7" s="10">
-        <v>8190359.7394492216</v>
+        <v>8996481.4656081535</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8064,22 +8064,22 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="C8" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" s="10">
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>690</v>
+        <v>724</v>
       </c>
       <c r="F8" s="10">
-        <v>10477595.383566588</v>
+        <v>11693170.217475448</v>
       </c>
       <c r="G8" s="10">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="H8" s="10">
         <v>4</v>
@@ -8088,10 +8088,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="K8" s="10">
-        <v>11063906.54678895</v>
+        <v>11439196.74842638</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8099,22 +8099,22 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1215</v>
+        <v>1208</v>
       </c>
       <c r="C9" s="10">
         <v>4</v>
       </c>
       <c r="D9" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="10">
-        <v>1021</v>
+        <v>2035</v>
       </c>
       <c r="F9" s="10">
-        <v>19011434.547334105</v>
+        <v>20529286.348929532</v>
       </c>
       <c r="G9" s="10">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="H9" s="10">
         <v>4</v>
@@ -8123,10 +8123,10 @@
         <v>2</v>
       </c>
       <c r="J9" s="10">
-        <v>968</v>
+        <v>1007</v>
       </c>
       <c r="K9" s="10">
-        <v>19871487.575189549</v>
+        <v>21858809.479129504</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8134,7 +8134,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -8143,10 +8143,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="F10" s="10">
-        <v>8381329.5959949316</v>
+        <v>9136539.7726296578</v>
       </c>
       <c r="G10" s="10">
         <v>392</v>
@@ -8158,10 +8158,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="K10" s="10">
-        <v>8985930.6731321104</v>
+        <v>9958782.7049773205</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8172,19 +8172,19 @@
         <v>383</v>
       </c>
       <c r="C11" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="10">
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="F11" s="10">
-        <v>7145519.7571021039</v>
+        <v>7743516.6435261397</v>
       </c>
       <c r="G11" s="10">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="H11" s="10">
         <v>1</v>
@@ -8193,10 +8193,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="K11" s="10">
-        <v>5498928.2696352452</v>
+        <v>6081677.9457779359</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8204,7 +8204,7 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C12" s="10">
         <v>1</v>
@@ -8213,25 +8213,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="10">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="F12" s="10">
-        <v>8340069.6906619277</v>
+        <v>9125846.8320685625</v>
       </c>
       <c r="G12" s="10">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="H12" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="10">
         <v>0</v>
       </c>
       <c r="J12" s="10">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="K12" s="10">
-        <v>8715775.2807155531</v>
+        <v>9528640.5381818991</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8239,7 +8239,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="10">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -8248,10 +8248,10 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F13" s="10">
-        <v>3747444.9194353758</v>
+        <v>4059495.7912112302</v>
       </c>
       <c r="G13" s="10">
         <v>178</v>
@@ -8263,10 +8263,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="K13" s="10">
-        <v>3950550.299179432</v>
+        <v>4278470.8679645592</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8274,22 +8274,22 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C14" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="10">
         <v>1</v>
       </c>
       <c r="E14" s="10">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="F14" s="10">
-        <v>586599.09295351198</v>
+        <v>832225.483727457</v>
       </c>
       <c r="G14" s="10">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H14" s="10">
         <v>0</v>
@@ -8298,10 +8298,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="K14" s="10">
-        <v>3899890.5906057432</v>
+        <v>4260676.8748711916</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8309,7 +8309,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C15" s="10">
         <v>1</v>
@@ -8318,10 +8318,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="10">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="F15" s="10">
-        <v>7940043.156108438</v>
+        <v>8440011.6415319797</v>
       </c>
       <c r="G15" s="10">
         <v>359</v>
@@ -8333,10 +8333,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K15" s="10">
-        <v>6730366.9863225957</v>
+        <v>7427057.5940592606</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8344,7 +8344,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -8353,13 +8353,13 @@
         <v>2</v>
       </c>
       <c r="E16" s="10">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="F16" s="10">
-        <v>3605945.15739296</v>
+        <v>3926643.4736452131</v>
       </c>
       <c r="G16" s="10">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
@@ -8368,10 +8368,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="K16" s="10">
-        <v>3309685.3118176642</v>
+        <v>3647125.4913574592</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8379,22 +8379,22 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
+        <v>244</v>
+      </c>
+      <c r="C17" s="10">
+        <v>1</v>
+      </c>
+      <c r="D17" s="10">
+        <v>2</v>
+      </c>
+      <c r="E17" s="10">
+        <v>232</v>
+      </c>
+      <c r="F17" s="10">
+        <v>4329889.7318454506</v>
+      </c>
+      <c r="G17" s="10">
         <v>242</v>
-      </c>
-      <c r="C17" s="10">
-        <v>1</v>
-      </c>
-      <c r="D17" s="10">
-        <v>2</v>
-      </c>
-      <c r="E17" s="10">
-        <v>1029</v>
-      </c>
-      <c r="F17" s="10">
-        <v>3977027.8671158012</v>
-      </c>
-      <c r="G17" s="10">
-        <v>246</v>
       </c>
       <c r="H17" s="10">
         <v>0</v>
@@ -8406,7 +8406,7 @@
         <v>220</v>
       </c>
       <c r="K17" s="10">
-        <v>4053726.7902464792</v>
+        <v>4468512.0865646908</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8414,22 +8414,22 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="C18" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="10">
         <v>3</v>
       </c>
       <c r="E18" s="10">
-        <v>1622</v>
+        <v>1327</v>
       </c>
       <c r="F18" s="10">
-        <v>13399000.366042772</v>
+        <v>15542536.569016691</v>
       </c>
       <c r="G18" s="10">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="H18" s="10">
         <v>4</v>
@@ -8438,10 +8438,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="10">
-        <v>1328</v>
+        <v>1269</v>
       </c>
       <c r="K18" s="10">
-        <v>22834765.983763617</v>
+        <v>24968411.489844091</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8458,10 +8458,10 @@
         <v>3</v>
       </c>
       <c r="E19" s="10">
-        <v>881</v>
+        <v>907</v>
       </c>
       <c r="F19" s="10">
-        <v>26643248.081871454</v>
+        <v>29238120.41858248</v>
       </c>
       <c r="G19" s="10">
         <v>1253</v>
@@ -8473,10 +8473,10 @@
         <v>2</v>
       </c>
       <c r="J19" s="10">
-        <v>944</v>
+        <v>889</v>
       </c>
       <c r="K19" s="10">
-        <v>33008994.284924474</v>
+        <v>35824755.92923595</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8484,7 +8484,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="C20" s="10">
         <v>2</v>
@@ -8493,13 +8493,13 @@
         <v>5</v>
       </c>
       <c r="E20" s="10">
-        <v>966</v>
+        <v>922</v>
       </c>
       <c r="F20" s="10">
-        <v>15828242.32627888</v>
+        <v>17096402.744824786</v>
       </c>
       <c r="G20" s="10">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="H20" s="10">
         <v>4</v>
@@ -8508,10 +8508,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>961</v>
+        <v>907</v>
       </c>
       <c r="K20" s="10">
-        <v>15843798.763286391</v>
+        <v>17290212.931036513</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8519,7 +8519,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="C21" s="10">
         <v>3</v>
@@ -8528,25 +8528,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>657</v>
+        <v>681</v>
       </c>
       <c r="F21" s="10">
-        <v>10913566.119168691</v>
+        <v>12161015.921806771</v>
       </c>
       <c r="G21" s="10">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H21" s="10">
         <v>0</v>
       </c>
       <c r="I21" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="10">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="K21" s="10">
-        <v>14999077.867172075</v>
+        <v>16203096.619572133</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8554,34 +8554,34 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2902</v>
+        <v>2872</v>
       </c>
       <c r="C22" s="10">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2097</v>
+        <v>2091</v>
       </c>
       <c r="F22" s="10">
-        <v>58775003.547264457</v>
+        <v>63455337.242055319</v>
       </c>
       <c r="G22" s="10">
-        <v>2812</v>
+        <v>2799</v>
       </c>
       <c r="H22" s="10">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I22" s="10">
         <v>12</v>
       </c>
       <c r="J22" s="10">
-        <v>2243</v>
+        <v>2265</v>
       </c>
       <c r="K22" s="10">
-        <v>53555984.147053935</v>
+        <v>58431495.578616232</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8589,7 +8589,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="C23" s="10">
         <v>3</v>
@@ -8598,10 +8598,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="10">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="F23" s="10">
-        <v>11584685.638031436</v>
+        <v>13715739.655666236</v>
       </c>
       <c r="G23" s="10">
         <v>1368</v>
@@ -8613,10 +8613,10 @@
         <v>2</v>
       </c>
       <c r="J23" s="10">
-        <v>1190</v>
+        <v>1218</v>
       </c>
       <c r="K23" s="10">
-        <v>28439991.090680379</v>
+        <v>30857225.122215234</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8624,34 +8624,34 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>2969</v>
+        <v>2972</v>
       </c>
       <c r="C24" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" s="10">
         <v>10</v>
       </c>
       <c r="E24" s="10">
-        <v>2229</v>
+        <v>2209</v>
       </c>
       <c r="F24" s="10">
-        <v>57592953.799537219</v>
+        <v>62455214.851508647</v>
       </c>
       <c r="G24" s="10">
-        <v>2775</v>
+        <v>2777</v>
       </c>
       <c r="H24" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2139</v>
+        <v>2092</v>
       </c>
       <c r="K24" s="10">
-        <v>48206739.535607196</v>
+        <v>53170556.161955953</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8659,7 +8659,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C25" s="10">
         <v>4</v>
@@ -8668,13 +8668,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="F25" s="10">
-        <v>9055980.6224311255</v>
+        <v>9647857.3613462802</v>
       </c>
       <c r="G25" s="10">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="H25" s="10">
         <v>2</v>
@@ -8683,10 +8683,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="K25" s="10">
-        <v>7894030.6329214247</v>
+        <v>8653275.5065172911</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8694,34 +8694,34 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1739</v>
+        <v>1749</v>
       </c>
       <c r="C26" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D26" s="10">
         <v>2</v>
       </c>
       <c r="E26" s="10">
-        <v>1298</v>
+        <v>1348</v>
       </c>
       <c r="F26" s="10">
-        <v>23687070.811500505</v>
+        <v>25727162.271941304</v>
       </c>
       <c r="G26" s="10">
-        <v>1728</v>
+        <v>1740</v>
       </c>
       <c r="H26" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I26" s="10">
         <v>1</v>
       </c>
       <c r="J26" s="10">
-        <v>1446</v>
+        <v>1473</v>
       </c>
       <c r="K26" s="10">
-        <v>21540252.204000156</v>
+        <v>23472141.842081539</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8729,7 +8729,7 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C27" s="10">
         <v>8</v>
@@ -8738,10 +8738,10 @@
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="F27" s="10">
-        <v>9478921.5549611673</v>
+        <v>10259830.90651048</v>
       </c>
       <c r="G27" s="10">
         <v>833</v>
@@ -8753,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="10">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="K27" s="10">
-        <v>9013330.2175357286</v>
+        <v>9877911.5601799227</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8764,7 +8764,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C28" s="10">
         <v>5</v>
@@ -8773,13 +8773,13 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>837</v>
+        <v>807</v>
       </c>
       <c r="F28" s="10">
-        <v>12129368.103966432</v>
+        <v>13074169.534061378</v>
       </c>
       <c r="G28" s="10">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="H28" s="10">
         <v>1</v>
@@ -8788,10 +8788,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="10">
-        <v>769</v>
+        <v>729</v>
       </c>
       <c r="K28" s="10">
-        <v>11323368.874365836</v>
+        <v>12367446.731246172</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8808,25 +8808,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="10">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F29" s="10">
-        <v>2536402.8153050868</v>
+        <v>2752351.900354438</v>
       </c>
       <c r="G29" s="10">
+        <v>218</v>
+      </c>
+      <c r="H29" s="10">
+        <v>1</v>
+      </c>
+      <c r="I29" s="10">
+        <v>0</v>
+      </c>
+      <c r="J29" s="10">
         <v>219</v>
       </c>
-      <c r="H29" s="10">
-        <v>0</v>
-      </c>
-      <c r="I29" s="10">
-        <v>0</v>
-      </c>
-      <c r="J29" s="10">
-        <v>235</v>
-      </c>
       <c r="K29" s="10">
-        <v>2808535.7045010701</v>
+        <v>3125322.1816324871</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8843,13 +8843,13 @@
         <v>6</v>
       </c>
       <c r="E30" s="10">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="F30" s="10">
-        <v>22511788.425732885</v>
+        <v>24358751.544144496</v>
       </c>
       <c r="G30" s="10">
-        <v>1639</v>
+        <v>1646</v>
       </c>
       <c r="H30" s="10">
         <v>2</v>
@@ -8858,10 +8858,10 @@
         <v>5</v>
       </c>
       <c r="J30" s="10">
-        <v>1485</v>
+        <v>1545</v>
       </c>
       <c r="K30" s="10">
-        <v>22367217.405995153</v>
+        <v>24602514.895429038</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8869,7 +8869,7 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
@@ -8878,13 +8878,13 @@
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="F31" s="10">
-        <v>18118545.915352695</v>
+        <v>19811258.757022385</v>
       </c>
       <c r="G31" s="10">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H31" s="10">
         <v>3</v>
@@ -8893,10 +8893,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>689</v>
+        <v>630</v>
       </c>
       <c r="K31" s="10">
-        <v>20204926.878771558</v>
+        <v>22132677.989444103</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8904,22 +8904,22 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
       </c>
       <c r="D32" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="10">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="F32" s="10">
-        <v>17752317.438190568</v>
+        <v>19404275.471009124</v>
       </c>
       <c r="G32" s="10">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="H32" s="10">
         <v>1</v>
@@ -8928,10 +8928,10 @@
         <v>2</v>
       </c>
       <c r="J32" s="10">
-        <v>911</v>
+        <v>854</v>
       </c>
       <c r="K32" s="10">
-        <v>19114856.538799368</v>
+        <v>21393659.220353145</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8939,7 +8939,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C33" s="10">
         <v>2</v>
@@ -8948,25 +8948,25 @@
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="F33" s="10">
-        <v>24186906.744684663</v>
+        <v>26404188.141816933</v>
       </c>
       <c r="G33" s="10">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="H33" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" s="10">
         <v>3</v>
       </c>
       <c r="J33" s="10">
-        <v>812</v>
+        <v>838</v>
       </c>
       <c r="K33" s="10">
-        <v>25226309.632355992</v>
+        <v>27596352.646259207</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8974,7 +8974,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="C34" s="10">
         <v>4</v>
@@ -8983,25 +8983,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="F34" s="10">
-        <v>34394456.147691317</v>
+        <v>37505222.301559903</v>
       </c>
       <c r="G34" s="10">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H34" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="10">
         <v>2</v>
       </c>
       <c r="J34" s="10">
-        <v>1169</v>
+        <v>1113</v>
       </c>
       <c r="K34" s="10">
-        <v>35006468.816651084</v>
+        <v>38482011.267993741</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -9009,7 +9009,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C35" s="10">
         <v>0</v>
@@ -9018,13 +9018,13 @@
         <v>5</v>
       </c>
       <c r="E35" s="10">
-        <v>520</v>
+        <v>581</v>
       </c>
       <c r="F35" s="10">
-        <v>14133878.193473892</v>
+        <v>15398605.461348807</v>
       </c>
       <c r="G35" s="10">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H35" s="10">
         <v>3</v>
@@ -9033,10 +9033,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>612</v>
+        <v>794</v>
       </c>
       <c r="K35" s="10">
-        <v>13924727.038236933</v>
+        <v>15371358.076542115</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9044,7 +9044,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="C36" s="10">
         <v>6</v>
@@ -9053,13 +9053,13 @@
         <v>11</v>
       </c>
       <c r="E36" s="10">
-        <v>1571</v>
+        <v>892</v>
       </c>
       <c r="F36" s="10">
-        <v>43001448.166093811</v>
+        <v>46536061.009953454</v>
       </c>
       <c r="G36" s="10">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="H36" s="10">
         <v>2</v>
@@ -9068,10 +9068,10 @@
         <v>6</v>
       </c>
       <c r="J36" s="10">
-        <v>1707</v>
+        <v>1680</v>
       </c>
       <c r="K36" s="10">
-        <v>26036926.729291752</v>
+        <v>29407824.984452795</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9079,7 +9079,7 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C37" s="10">
         <v>1</v>
@@ -9088,13 +9088,13 @@
         <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>887</v>
+        <v>774</v>
       </c>
       <c r="F37" s="10">
-        <v>14132076.933236703</v>
+        <v>15552674.040534776</v>
       </c>
       <c r="G37" s="10">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="H37" s="10">
         <v>2</v>
@@ -9103,10 +9103,10 @@
         <v>3</v>
       </c>
       <c r="J37" s="10">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="K37" s="10">
-        <v>14724372.928554051</v>
+        <v>16019371.822294367</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9123,13 +9123,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>746</v>
+        <v>538</v>
       </c>
       <c r="F38" s="10">
-        <v>13627139.337142861</v>
+        <v>14986852.341861239</v>
       </c>
       <c r="G38" s="10">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="H38" s="10">
         <v>1</v>
@@ -9138,10 +9138,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="K38" s="10">
-        <v>13006674.485248519</v>
+        <v>14185152.208508916</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9149,22 +9149,22 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="C39" s="10">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D39" s="10">
         <v>1</v>
       </c>
       <c r="E39" s="10">
-        <v>465</v>
+        <v>822</v>
       </c>
       <c r="F39" s="10">
-        <v>20545921.86789586</v>
+        <v>22114246.499472193</v>
       </c>
       <c r="G39" s="10">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="H39" s="10">
         <v>5</v>
@@ -9173,10 +9173,10 @@
         <v>2</v>
       </c>
       <c r="J39" s="10">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="K39" s="10">
-        <v>22932126.399725944</v>
+        <v>25110758.092792481</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9184,7 +9184,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="C40" s="10">
         <v>120</v>
@@ -9193,25 +9193,25 @@
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="F40" s="10">
-        <v>19120041.93568055</v>
+        <v>20741126.062683959</v>
       </c>
       <c r="G40" s="10">
-        <v>1452</v>
+        <v>1433</v>
       </c>
       <c r="H40" s="10">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I40" s="10">
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>858</v>
+        <v>837</v>
       </c>
       <c r="K40" s="10">
-        <v>21141554.628010023</v>
+        <v>22932356.491074044</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9219,7 +9219,7 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>2418</v>
+        <v>2397</v>
       </c>
       <c r="C41" s="10">
         <v>69</v>
@@ -9228,25 +9228,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="10">
-        <v>1575</v>
+        <v>1529</v>
       </c>
       <c r="F41" s="10">
-        <v>34901512.498659305</v>
+        <v>38453663.605802923</v>
       </c>
       <c r="G41" s="10">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="H41" s="10">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I41" s="10">
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1484</v>
+        <v>1557</v>
       </c>
       <c r="K41" s="10">
-        <v>35002790.497653201</v>
+        <v>38312378.880640082</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9254,7 +9254,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C42" s="10">
         <v>1</v>
@@ -9263,13 +9263,13 @@
         <v>6</v>
       </c>
       <c r="E42" s="10">
-        <v>447</v>
+        <v>570</v>
       </c>
       <c r="F42" s="10">
-        <v>12522131.034147704</v>
+        <v>13607803.394892052</v>
       </c>
       <c r="G42" s="10">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="H42" s="10">
         <v>4</v>
@@ -9278,10 +9278,10 @@
         <v>7</v>
       </c>
       <c r="J42" s="10">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="K42" s="10">
-        <v>12972219.559267271</v>
+        <v>14083966.5119655</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9289,7 +9289,7 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>2064</v>
+        <v>2057</v>
       </c>
       <c r="C43" s="10">
         <v>2</v>
@@ -9298,13 +9298,13 @@
         <v>6</v>
       </c>
       <c r="E43" s="10">
-        <v>1950</v>
+        <v>1914</v>
       </c>
       <c r="F43" s="10">
-        <v>41927511.893101111</v>
+        <v>45449281.559613265</v>
       </c>
       <c r="G43" s="10">
-        <v>2040</v>
+        <v>2031</v>
       </c>
       <c r="H43" s="10">
         <v>4</v>
@@ -9313,10 +9313,10 @@
         <v>5</v>
       </c>
       <c r="J43" s="10">
-        <v>1850</v>
+        <v>1817</v>
       </c>
       <c r="K43" s="10">
-        <v>40159357.461528517</v>
+        <v>43927118.587503135</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9333,13 +9333,13 @@
         <v>2</v>
       </c>
       <c r="E44" s="10">
-        <v>803</v>
+        <v>1422</v>
       </c>
       <c r="F44" s="10">
-        <v>27163671.010994777</v>
+        <v>29655636.505533084</v>
       </c>
       <c r="G44" s="10">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H44" s="10">
         <v>5</v>
@@ -9348,10 +9348,10 @@
         <v>4</v>
       </c>
       <c r="J44" s="10">
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="K44" s="10">
-        <v>31332334.071481273</v>
+        <v>33967834.959300019</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9359,7 +9359,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C45" s="10">
         <v>0</v>
@@ -9368,25 +9368,25 @@
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>919</v>
+        <v>908</v>
       </c>
       <c r="F45" s="10">
-        <v>14178492.832121568</v>
+        <v>16068125.974080767</v>
       </c>
       <c r="G45" s="10">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="H45" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="10">
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>944</v>
+        <v>970</v>
       </c>
       <c r="K45" s="10">
-        <v>22149087.91487515</v>
+        <v>24052081.674599729</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9394,7 +9394,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="C46" s="10">
         <v>3</v>
@@ -9403,13 +9403,13 @@
         <v>4</v>
       </c>
       <c r="E46" s="10">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="F46" s="10">
-        <v>21673565.670844473</v>
+        <v>23518097.944919869</v>
       </c>
       <c r="G46" s="10">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="H46" s="10">
         <v>2</v>
@@ -9418,10 +9418,10 @@
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>635</v>
+        <v>597</v>
       </c>
       <c r="K46" s="10">
-        <v>22463428.205046136</v>
+        <v>24303801.668385867</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9429,7 +9429,7 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C47" s="10">
         <v>2</v>
@@ -9438,13 +9438,13 @@
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="F47" s="10">
-        <v>13895483.106158944</v>
+        <v>15130453.175075745</v>
       </c>
       <c r="G47" s="10">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="H47" s="10">
         <v>0</v>
@@ -9453,10 +9453,10 @@
         <v>9</v>
       </c>
       <c r="J47" s="10">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="K47" s="10">
-        <v>13423472.227419101</v>
+        <v>14609642.865583366</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9464,7 +9464,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C48" s="10">
         <v>0</v>
@@ -9473,13 +9473,13 @@
         <v>2</v>
       </c>
       <c r="E48" s="10">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="F48" s="10">
-        <v>12161003.483174358</v>
+        <v>13321177.692165183</v>
       </c>
       <c r="G48" s="10">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
@@ -9488,10 +9488,10 @@
         <v>1</v>
       </c>
       <c r="J48" s="10">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="K48" s="10">
-        <v>12527683.802709805</v>
+        <v>13640714.055751091</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9499,34 +9499,34 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="C49" s="10">
         <v>0</v>
       </c>
       <c r="D49" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" s="10">
-        <v>1078</v>
+        <v>2756</v>
       </c>
       <c r="F49" s="10">
-        <v>37273755.084821194</v>
+        <v>40575137.286203943</v>
       </c>
       <c r="G49" s="10">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="H49" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" s="10">
         <v>6</v>
       </c>
       <c r="J49" s="10">
-        <v>1196</v>
+        <v>1136</v>
       </c>
       <c r="K49" s="10">
-        <v>41936647.835470937</v>
+        <v>45745588.58812362</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9534,7 +9534,7 @@
         <v>201</v>
       </c>
       <c r="B50" s="10">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C50" s="10">
         <v>0</v>
@@ -9543,13 +9543,13 @@
         <v>1</v>
       </c>
       <c r="E50" s="10">
-        <v>484</v>
+        <v>797</v>
       </c>
       <c r="F50" s="10">
-        <v>6162776.9085115492</v>
+        <v>6645353.4058702402</v>
       </c>
       <c r="G50" s="10">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H50" s="10">
         <v>1</v>
@@ -9558,10 +9558,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>482</v>
+        <v>448</v>
       </c>
       <c r="K50" s="10">
-        <v>6384247.944338074</v>
+        <v>6951924.3284576992</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9569,7 +9569,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="C51" s="10">
         <v>2</v>
@@ -9578,25 +9578,25 @@
         <v>7</v>
       </c>
       <c r="E51" s="10">
-        <v>881</v>
+        <v>1570</v>
       </c>
       <c r="F51" s="10">
-        <v>17874087.659617409</v>
+        <v>19563741.756338328</v>
       </c>
       <c r="G51" s="10">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="H51" s="10">
         <v>1</v>
       </c>
       <c r="I51" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51" s="10">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="K51" s="10">
-        <v>17870643.858846333</v>
+        <v>19453326.637208953</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9604,7 +9604,7 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1356</v>
+        <v>1345</v>
       </c>
       <c r="C52" s="10">
         <v>3</v>
@@ -9613,13 +9613,13 @@
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>1045</v>
+        <v>465</v>
       </c>
       <c r="F52" s="10">
-        <v>32056870.004816383</v>
+        <v>34200115.304982483</v>
       </c>
       <c r="G52" s="10">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="H52" s="10">
         <v>1</v>
@@ -9628,10 +9628,10 @@
         <v>11</v>
       </c>
       <c r="J52" s="10">
-        <v>1014</v>
+        <v>972</v>
       </c>
       <c r="K52" s="10">
-        <v>32663997.039998908</v>
+        <v>35513529.941505633</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9648,13 +9648,13 @@
         <v>6</v>
       </c>
       <c r="E53" s="10">
-        <v>360</v>
+        <v>233</v>
       </c>
       <c r="F53" s="10">
-        <v>16539048.45741608</v>
+        <v>17692903.869914349</v>
       </c>
       <c r="G53" s="10">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H53" s="10">
         <v>3</v>
@@ -9663,10 +9663,10 @@
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="K53" s="10">
-        <v>15061140.755258827</v>
+        <v>16698819.456651105</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9674,7 +9674,7 @@
         <v>81</v>
       </c>
       <c r="B54" s="10">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C54" s="10">
         <v>0</v>
@@ -9683,25 +9683,25 @@
         <v>4</v>
       </c>
       <c r="E54" s="10">
-        <v>305</v>
+        <v>211</v>
       </c>
       <c r="F54" s="10">
-        <v>12081136.709517296</v>
+        <v>12885929.269668665</v>
       </c>
       <c r="G54" s="10">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H54" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" s="10">
         <v>3</v>
       </c>
       <c r="J54" s="10">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="K54" s="10">
-        <v>13095908.736033432</v>
+        <v>14295788.226282325</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9709,7 +9709,7 @@
         <v>87</v>
       </c>
       <c r="B55" s="10">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C55" s="10">
         <v>1</v>
@@ -9718,13 +9718,13 @@
         <v>4</v>
       </c>
       <c r="E55" s="10">
-        <v>332</v>
+        <v>220</v>
       </c>
       <c r="F55" s="10">
-        <v>10520584.106780592</v>
+        <v>11147708.240657611</v>
       </c>
       <c r="G55" s="10">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H55" s="10">
         <v>0</v>
@@ -9733,10 +9733,10 @@
         <v>2</v>
       </c>
       <c r="J55" s="10">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="K55" s="10">
-        <v>5501887.3312636809</v>
+        <v>5589046.8414643016</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9744,19 +9744,19 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C56" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D56" s="10">
         <v>0</v>
       </c>
       <c r="E56" s="10">
-        <v>925</v>
+        <v>661</v>
       </c>
       <c r="F56" s="10">
-        <v>24723580.217376906</v>
+        <v>26191668.071031023</v>
       </c>
       <c r="G56" s="10">
         <v>1099</v>
@@ -9768,10 +9768,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>962</v>
+        <v>889</v>
       </c>
       <c r="K56" s="10">
-        <v>26527780.340592857</v>
+        <v>28462888.360719599</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9779,22 +9779,22 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="C57" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57" s="10">
         <v>1</v>
       </c>
       <c r="E57" s="10">
-        <v>889</v>
+        <v>715</v>
       </c>
       <c r="F57" s="10">
-        <v>23331162.81574592</v>
+        <v>25274443.649353232</v>
       </c>
       <c r="G57" s="10">
-        <v>937</v>
+        <v>927</v>
       </c>
       <c r="H57" s="10">
         <v>5</v>
@@ -9803,10 +9803,10 @@
         <v>2</v>
       </c>
       <c r="J57" s="10">
-        <v>960</v>
+        <v>797</v>
       </c>
       <c r="K57" s="10">
-        <v>26543308.271027669</v>
+        <v>28675298.836824629</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9814,7 +9814,7 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2076</v>
+        <v>2065</v>
       </c>
       <c r="C58" s="10">
         <v>6</v>
@@ -9823,25 +9823,25 @@
         <v>8</v>
       </c>
       <c r="E58" s="10">
-        <v>1445</v>
+        <v>1226</v>
       </c>
       <c r="F58" s="10">
-        <v>46692177.299890816</v>
+        <v>49677371.10828805</v>
       </c>
       <c r="G58" s="10">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="H58" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I58" s="10">
         <v>9</v>
       </c>
       <c r="J58" s="10">
-        <v>1627</v>
+        <v>1642</v>
       </c>
       <c r="K58" s="10">
-        <v>48360579.666022353</v>
+        <v>52582289.558401659</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9849,22 +9849,22 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C59" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" s="10">
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>534</v>
+        <v>453</v>
       </c>
       <c r="F59" s="10">
-        <v>11101958.599655284</v>
+        <v>11997117.736853795</v>
       </c>
       <c r="G59" s="10">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="H59" s="10">
         <v>2</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>586</v>
+        <v>675</v>
       </c>
       <c r="K59" s="10">
-        <v>12869337.990031293</v>
+        <v>13982560.869168984</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9884,22 +9884,22 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C60" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D60" s="10">
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>695</v>
+        <v>510</v>
       </c>
       <c r="F60" s="10">
-        <v>19744310.44305547</v>
+        <v>21280371.70766744</v>
       </c>
       <c r="G60" s="10">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="H60" s="10">
         <v>6</v>
@@ -9908,10 +9908,10 @@
         <v>6</v>
       </c>
       <c r="J60" s="10">
-        <v>807</v>
+        <v>827</v>
       </c>
       <c r="K60" s="10">
-        <v>22427850.574070819</v>
+        <v>24407846.306572575</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9919,7 +9919,7 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C61" s="10">
         <v>3</v>
@@ -9928,13 +9928,13 @@
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>636</v>
+        <v>516</v>
       </c>
       <c r="F61" s="10">
-        <v>12108515.79752842</v>
+        <v>13008470.054326516</v>
       </c>
       <c r="G61" s="10">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="H61" s="10">
         <v>0</v>
@@ -9943,10 +9943,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="10">
-        <v>632</v>
+        <v>57</v>
       </c>
       <c r="K61" s="10">
-        <v>12081050.832576821</v>
+        <v>12702688.915399697</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9954,34 +9954,34 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C62" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D62" s="10">
         <v>0</v>
       </c>
       <c r="E62" s="10">
-        <v>986</v>
+        <v>807</v>
       </c>
       <c r="F62" s="10">
-        <v>25953478.849800728</v>
+        <v>27692985.716273904</v>
       </c>
       <c r="G62" s="10">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="H62" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I62" s="10">
         <v>1</v>
       </c>
       <c r="J62" s="10">
-        <v>1112</v>
+        <v>1279</v>
       </c>
       <c r="K62" s="10">
-        <v>28241591.85484669</v>
+        <v>30502819.256533097</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9989,34 +9989,34 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1425</v>
+        <v>1436</v>
       </c>
       <c r="C63" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" s="10">
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1510</v>
+        <v>1441</v>
       </c>
       <c r="F63" s="10">
-        <v>31393322.515753064</v>
+        <v>33951195.810102426</v>
       </c>
       <c r="G63" s="10">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="H63" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63" s="10">
         <v>5</v>
       </c>
       <c r="J63" s="10">
-        <v>1633</v>
+        <v>1494</v>
       </c>
       <c r="K63" s="10">
-        <v>38769776.034656703</v>
+        <v>41763405.554746158</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -10024,7 +10024,7 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C64" s="10">
         <v>1</v>
@@ -10033,13 +10033,13 @@
         <v>4</v>
       </c>
       <c r="E64" s="10">
-        <v>685</v>
+        <v>648</v>
       </c>
       <c r="F64" s="10">
-        <v>17452043.978152473</v>
+        <v>18629448.795252305</v>
       </c>
       <c r="G64" s="10">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="H64" s="10">
         <v>4</v>
@@ -10048,10 +10048,10 @@
         <v>5</v>
       </c>
       <c r="J64" s="10">
-        <v>812</v>
+        <v>790</v>
       </c>
       <c r="K64" s="10">
-        <v>15455780.272549629</v>
+        <v>16761125.185675364</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10062,19 +10062,19 @@
         <v>651</v>
       </c>
       <c r="C65" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D65" s="10">
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="F65" s="10">
-        <v>19453163.939775139</v>
+        <v>20847380.402954869</v>
       </c>
       <c r="G65" s="10">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H65" s="10">
         <v>3</v>
@@ -10083,10 +10083,10 @@
         <v>7</v>
       </c>
       <c r="J65" s="10">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="K65" s="10">
-        <v>20408682.048246805</v>
+        <v>22020764.973671433</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10094,34 +10094,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>1970</v>
+        <v>1983</v>
       </c>
       <c r="C66" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D66" s="10">
         <v>10</v>
       </c>
       <c r="E66" s="10">
-        <v>1606</v>
+        <v>1641</v>
       </c>
       <c r="F66" s="10">
-        <v>62712300.78279233</v>
+        <v>67327568.067904234</v>
       </c>
       <c r="G66" s="10">
         <v>1971</v>
       </c>
       <c r="H66" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I66" s="10">
         <v>13</v>
       </c>
       <c r="J66" s="10">
-        <v>1794</v>
+        <v>1829</v>
       </c>
       <c r="K66" s="10">
-        <v>65608445.879055992</v>
+        <v>70670658.044179976</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10129,22 +10129,22 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="C67" s="10">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D67" s="10">
         <v>6</v>
       </c>
       <c r="E67" s="10">
-        <v>1219</v>
+        <v>1265</v>
       </c>
       <c r="F67" s="10">
-        <v>45460845.578881703</v>
+        <v>49430448.945431069</v>
       </c>
       <c r="G67" s="10">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="H67" s="10">
         <v>12</v>
@@ -10153,10 +10153,10 @@
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1265</v>
+        <v>1201</v>
       </c>
       <c r="K67" s="10">
-        <v>46716196.328422241</v>
+        <v>50220349.921165459</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10164,22 +10164,22 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C68" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68" s="10">
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="F68" s="10">
-        <v>30167393.236838799</v>
+        <v>32493119.305810899</v>
       </c>
       <c r="G68" s="10">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H68" s="10">
         <v>1</v>
@@ -10188,10 +10188,10 @@
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="K68" s="10">
-        <v>31840007.43950006</v>
+        <v>34013930.676028676</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10199,22 +10199,22 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>2335</v>
+        <v>2317</v>
       </c>
       <c r="C69" s="10">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D69" s="10">
         <v>12</v>
       </c>
       <c r="E69" s="10">
-        <v>1437</v>
+        <v>1308</v>
       </c>
       <c r="F69" s="10">
-        <v>45486578.400095366</v>
+        <v>49546807.447998308</v>
       </c>
       <c r="G69" s="10">
-        <v>2338</v>
+        <v>2329</v>
       </c>
       <c r="H69" s="10">
         <v>372</v>
@@ -10223,10 +10223,10 @@
         <v>13</v>
       </c>
       <c r="J69" s="10">
-        <v>1292</v>
+        <v>1302</v>
       </c>
       <c r="K69" s="10">
-        <v>41636311.204481982</v>
+        <v>45338783.339071438</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10243,13 +10243,13 @@
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>415</v>
+        <v>250</v>
       </c>
       <c r="F70" s="10">
-        <v>1088870.296364038</v>
+        <v>1348505.727031731</v>
       </c>
       <c r="G70" s="10">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H70" s="10">
         <v>2</v>
@@ -10258,10 +10258,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="10">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="K70" s="10">
-        <v>3332193.916553128</v>
+        <v>3682667.934082624</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10269,22 +10269,22 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1674</v>
+        <v>1669</v>
       </c>
       <c r="C71" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D71" s="10">
         <v>6</v>
       </c>
       <c r="E71" s="10">
-        <v>1542</v>
+        <v>1480</v>
       </c>
       <c r="F71" s="10">
-        <v>32343585.173141804</v>
+        <v>35127326.366053008</v>
       </c>
       <c r="G71" s="10">
-        <v>1625</v>
+        <v>1608</v>
       </c>
       <c r="H71" s="10">
         <v>14</v>
@@ -10293,10 +10293,10 @@
         <v>8</v>
       </c>
       <c r="J71" s="10">
-        <v>1458</v>
+        <v>1576</v>
       </c>
       <c r="K71" s="10">
-        <v>31714020.902646456</v>
+        <v>34445460.314459853</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10304,7 +10304,7 @@
         <v>12</v>
       </c>
       <c r="B72" s="10">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C72" s="10">
         <v>1</v>
@@ -10313,13 +10313,13 @@
         <v>3</v>
       </c>
       <c r="E72" s="10">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="F72" s="10">
-        <v>15328774.192921566</v>
+        <v>16812574.105930068</v>
       </c>
       <c r="G72" s="10">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H72" s="10">
         <v>2</v>
@@ -10328,10 +10328,10 @@
         <v>4</v>
       </c>
       <c r="J72" s="10">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="K72" s="10">
-        <v>14576827.875886289</v>
+        <v>15667692.503356764</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10339,7 +10339,7 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="C73" s="10">
         <v>19</v>
@@ -10348,13 +10348,13 @@
         <v>4</v>
       </c>
       <c r="E73" s="10">
-        <v>859</v>
+        <v>842</v>
       </c>
       <c r="F73" s="10">
-        <v>21872709.188291144</v>
+        <v>23873577.731227577</v>
       </c>
       <c r="G73" s="10">
-        <v>1477</v>
+        <v>1464</v>
       </c>
       <c r="H73" s="10">
         <v>1</v>
@@ -10363,10 +10363,10 @@
         <v>5</v>
       </c>
       <c r="J73" s="10">
-        <v>889</v>
+        <v>959</v>
       </c>
       <c r="K73" s="10">
-        <v>23086254.829625059</v>
+        <v>25445366.118607964</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10374,7 +10374,7 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="C74" s="10">
         <v>2</v>
@@ -10383,13 +10383,13 @@
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>597</v>
+        <v>982</v>
       </c>
       <c r="F74" s="10">
-        <v>14513828.217951603</v>
+        <v>14656833.663769012</v>
       </c>
       <c r="G74" s="10">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="H74" s="10">
         <v>2</v>
@@ -10398,10 +10398,10 @@
         <v>4</v>
       </c>
       <c r="J74" s="10">
-        <v>1361</v>
+        <v>1241</v>
       </c>
       <c r="K74" s="10">
-        <v>18591108.258868024</v>
+        <v>20167933.173738983</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10409,7 +10409,7 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1737</v>
+        <v>1745</v>
       </c>
       <c r="C75" s="10">
         <v>8</v>
@@ -10418,25 +10418,25 @@
         <v>4</v>
       </c>
       <c r="E75" s="10">
-        <v>1229</v>
+        <v>1213</v>
       </c>
       <c r="F75" s="10">
-        <v>39840425.618532181</v>
+        <v>43203204.558727421</v>
       </c>
       <c r="G75" s="10">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="H75" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I75" s="10">
         <v>7</v>
       </c>
       <c r="J75" s="10">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="K75" s="10">
-        <v>41382219.443157539</v>
+        <v>45274446.644820362</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10444,7 +10444,7 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C76" s="10">
         <v>2</v>
@@ -10453,25 +10453,25 @@
         <v>1</v>
       </c>
       <c r="E76" s="10">
-        <v>433</v>
+        <v>629</v>
       </c>
       <c r="F76" s="10">
-        <v>8058967.8740208512</v>
+        <v>8716800.0374078844</v>
       </c>
       <c r="G76" s="10">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H76" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I76" s="10">
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K76" s="10">
-        <v>7736582.7318614321</v>
+        <v>8336159.5331871547</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10479,7 +10479,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="C77" s="10">
         <v>3</v>
@@ -10488,13 +10488,13 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>999</v>
+        <v>669</v>
       </c>
       <c r="F77" s="10">
-        <v>12600460.760555159</v>
+        <v>13419610.797755742</v>
       </c>
       <c r="G77" s="10">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H77" s="10">
         <v>1</v>
@@ -10503,10 +10503,10 @@
         <v>0</v>
       </c>
       <c r="J77" s="10">
-        <v>812</v>
+        <v>897</v>
       </c>
       <c r="K77" s="10">
-        <v>15138195.546056001</v>
+        <v>16320737.705918368</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10514,7 +10514,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C78" s="10">
         <v>0</v>
@@ -10523,13 +10523,13 @@
         <v>3</v>
       </c>
       <c r="E78" s="10">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="F78" s="10">
-        <v>12247960.588351307</v>
+        <v>13406864.351865375</v>
       </c>
       <c r="G78" s="10">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="H78" s="10">
         <v>2</v>
@@ -10538,10 +10538,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>513</v>
+        <v>488</v>
       </c>
       <c r="K78" s="10">
-        <v>13531617.314519268</v>
+        <v>14939900.890034296</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10549,7 +10549,7 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C79" s="10">
         <v>5</v>
@@ -10558,25 +10558,25 @@
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>732</v>
+        <v>710</v>
       </c>
       <c r="F79" s="10">
-        <v>10279087.37903594</v>
+        <v>11044050.643039128</v>
       </c>
       <c r="G79" s="10">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H79" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I79" s="10">
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>1095</v>
+        <v>1030</v>
       </c>
       <c r="K79" s="10">
-        <v>8513336.6178804133</v>
+        <v>9544700.5587438848</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10584,7 +10584,7 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C80" s="10">
         <v>0</v>
@@ -10593,13 +10593,13 @@
         <v>7</v>
       </c>
       <c r="E80" s="10">
-        <v>480</v>
+        <v>251</v>
       </c>
       <c r="F80" s="10">
-        <v>11214438.848868918</v>
+        <v>11871515.03801666</v>
       </c>
       <c r="G80" s="10">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H80" s="10">
         <v>2</v>
@@ -10608,10 +10608,10 @@
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K80" s="10">
-        <v>9194851.3412616476</v>
+        <v>10204824.002210468</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10619,7 +10619,7 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="C81" s="10">
         <v>4</v>
@@ -10628,25 +10628,25 @@
         <v>3</v>
       </c>
       <c r="E81" s="10">
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="F81" s="10">
-        <v>29020876.322520785</v>
+        <v>31261131.096501935</v>
       </c>
       <c r="G81" s="10">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H81" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I81" s="10">
         <v>2</v>
       </c>
       <c r="J81" s="10">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="K81" s="10">
-        <v>22449998.135948103</v>
+        <v>23598904.180730466</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10663,13 +10663,13 @@
         <v>10</v>
       </c>
       <c r="E82" s="10">
-        <v>721</v>
+        <v>2118</v>
       </c>
       <c r="F82" s="10">
-        <v>17509810.325102132</v>
+        <v>18891602.264381222</v>
       </c>
       <c r="G82" s="10">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="H82" s="10">
         <v>3</v>
@@ -10678,10 +10678,10 @@
         <v>9</v>
       </c>
       <c r="J82" s="10">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="K82" s="10">
-        <v>17291531.897691596</v>
+        <v>19211296.435092594</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10689,7 +10689,7 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="C83" s="10">
         <v>1</v>
@@ -10698,13 +10698,13 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>791</v>
+        <v>855</v>
       </c>
       <c r="F83" s="10">
-        <v>14022555.382335631</v>
+        <v>15118369.682815623</v>
       </c>
       <c r="G83" s="10">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H83" s="10">
         <v>2</v>
@@ -10713,10 +10713,10 @@
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>924</v>
+        <v>952</v>
       </c>
       <c r="K83" s="10">
-        <v>14540962.879546613</v>
+        <v>15852572.06871303</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10724,7 +10724,7 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="C84" s="10">
         <v>2</v>
@@ -10733,13 +10733,13 @@
         <v>5</v>
       </c>
       <c r="E84" s="10">
-        <v>891</v>
+        <v>842</v>
       </c>
       <c r="F84" s="10">
-        <v>13097969.624595124</v>
+        <v>14524187.856017128</v>
       </c>
       <c r="G84" s="10">
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="H84" s="10">
         <v>1</v>
@@ -10748,10 +10748,10 @@
         <v>4</v>
       </c>
       <c r="J84" s="10">
-        <v>905</v>
+        <v>849</v>
       </c>
       <c r="K84" s="10">
-        <v>17335025.564646862</v>
+        <v>18906157.439068951</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10759,7 +10759,7 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="C85" s="10">
         <v>2</v>
@@ -10768,13 +10768,13 @@
         <v>6</v>
       </c>
       <c r="E85" s="10">
-        <v>749</v>
+        <v>408</v>
       </c>
       <c r="F85" s="10">
-        <v>18310243.092242092</v>
+        <v>19671552.708550803</v>
       </c>
       <c r="G85" s="10">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
@@ -10783,10 +10783,10 @@
         <v>7</v>
       </c>
       <c r="J85" s="10">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="K85" s="10">
-        <v>20062269.907639056</v>
+        <v>22132214.210737165</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10794,7 +10794,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C86" s="10">
         <v>1</v>
@@ -10806,10 +10806,10 @@
         <v>540</v>
       </c>
       <c r="F86" s="10">
-        <v>8670745.7737258058</v>
+        <v>9375082.9609405603</v>
       </c>
       <c r="G86" s="10">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H86" s="10">
         <v>4</v>
@@ -10818,10 +10818,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>522</v>
+        <v>493</v>
       </c>
       <c r="K86" s="10">
-        <v>8159419.8209574521</v>
+        <v>8934225.0752158221</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10829,7 +10829,7 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1754</v>
+        <v>1762</v>
       </c>
       <c r="C87" s="10">
         <v>0</v>
@@ -10838,13 +10838,13 @@
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1290</v>
+        <v>1316</v>
       </c>
       <c r="F87" s="10">
-        <v>35310344.073664188</v>
+        <v>38701029.284727588</v>
       </c>
       <c r="G87" s="10">
-        <v>1778</v>
+        <v>1783</v>
       </c>
       <c r="H87" s="10">
         <v>2</v>
@@ -10853,10 +10853,10 @@
         <v>9</v>
       </c>
       <c r="J87" s="10">
-        <v>1388</v>
+        <v>1372</v>
       </c>
       <c r="K87" s="10">
-        <v>42702965.826996572</v>
+        <v>46989513.872192614</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10864,7 +10864,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C88" s="10">
         <v>0</v>
@@ -10873,13 +10873,13 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>872</v>
+        <v>734</v>
       </c>
       <c r="F88" s="10">
-        <v>7539509.8299834495</v>
+        <v>8622190.9655356202</v>
       </c>
       <c r="G88" s="10">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H88" s="10">
         <v>2</v>
@@ -10888,10 +10888,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>628</v>
+        <v>899</v>
       </c>
       <c r="K88" s="10">
-        <v>8983939.4270911943</v>
+        <v>9986112.4448090214</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10899,7 +10899,7 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="C89" s="10">
         <v>4</v>
@@ -10908,13 +10908,13 @@
         <v>7</v>
       </c>
       <c r="E89" s="10">
-        <v>580</v>
+        <v>408</v>
       </c>
       <c r="F89" s="10">
-        <v>16488973.74900602</v>
+        <v>17495104.84190416</v>
       </c>
       <c r="G89" s="10">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H89" s="10">
         <v>5</v>
@@ -10923,10 +10923,10 @@
         <v>8</v>
       </c>
       <c r="J89" s="10">
-        <v>816</v>
+        <v>979</v>
       </c>
       <c r="K89" s="10">
-        <v>17466134.791588984</v>
+        <v>19009001.995999392</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10934,22 +10934,22 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C90" s="10">
         <v>2</v>
       </c>
       <c r="D90" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>309</v>
+        <v>380</v>
       </c>
       <c r="F90" s="10">
-        <v>4056251.955859642</v>
+        <v>4317447.3459969955</v>
       </c>
       <c r="G90" s="10">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -10958,10 +10958,10 @@
         <v>1</v>
       </c>
       <c r="J90" s="10">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="K90" s="10">
-        <v>4177272.1257785661</v>
+        <v>4177363.4227665081</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.35">
@@ -10969,34 +10969,34 @@
         <v>203</v>
       </c>
       <c r="B91" s="13">
-        <v>84861</v>
+        <v>84798</v>
       </c>
       <c r="C91" s="13">
-        <v>963</v>
+        <v>1001</v>
       </c>
       <c r="D91" s="13">
+        <v>319</v>
+      </c>
+      <c r="E91" s="13">
+        <v>71269</v>
+      </c>
+      <c r="F91" s="13">
+        <v>1792079533.2534416</v>
+      </c>
+      <c r="G91" s="13">
+        <v>84642</v>
+      </c>
+      <c r="H91" s="13">
+        <v>1296</v>
+      </c>
+      <c r="I91" s="13">
         <v>315</v>
       </c>
-      <c r="E91" s="13">
-        <v>70217</v>
-      </c>
-      <c r="F91" s="13">
-        <v>1652684078.2688403</v>
-      </c>
-      <c r="G91" s="13">
-        <v>84687</v>
-      </c>
-      <c r="H91" s="13">
-        <v>1272</v>
-      </c>
-      <c r="I91" s="13">
-        <v>313</v>
-      </c>
       <c r="J91" s="13">
-        <v>71131</v>
+        <v>70910</v>
       </c>
       <c r="K91" s="13">
-        <v>1715218317.2305956</v>
+        <v>1868039006.9845848</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -1163,27 +1163,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8011855.9913176866</v>
+        <v>8665292.4728072863</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8539462.2923211604</v>
+        <v>9238403.0792054478</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>6.585319326448591E-2</v>
+        <v>6.6138633888775278E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>1.9943019943019946E-2</v>
+        <v>-9.1397849462365621E-2</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1211,15 +1211,15 @@
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>2.857142857142847E-2</v>
+        <v>1.6627078384798155E-2</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1243,27 +1243,27 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9589962.4832898322</v>
+        <v>10292285.555236744</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8996481.4656081535</v>
+        <v>9762882.7996665835</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-6.1885645404327505E-2</v>
+        <v>-5.1436850710073645E-2</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>634</v>
+        <v>548</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>0.28600405679513186</v>
+        <v>0.11608961303462317</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1279,27 +1279,27 @@
       </c>
       <c r="O3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="12">
         <f t="shared" ref="Q3:Q66" si="3">IFERROR(P3/O3-1,0)</f>
-        <v>0.66666666666666674</v>
+        <v>0.5</v>
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-0.14525993883792054</v>
+        <v>-5.3680981595092048E-2</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1323,27 +1323,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11693170.217475448</v>
+        <v>12900162.010313369</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11439196.74842638</v>
+        <v>12259231.902439144</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>-2.1719812875853339E-2</v>
+        <v>-4.9683880509548417E-2</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>724</v>
+        <v>740</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>350</v>
+        <v>587</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>-0.51657458563535918</v>
+        <v>-0.20675675675675675</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1371,15 +1371,15 @@
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>767</v>
+        <v>584</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>3.5087719298245723E-2</v>
+        <v>-0.20544217687074828</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20529286.348929532</v>
+        <v>22209543.394173563</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21858809.479129504</v>
+        <v>23767288.77103918</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>6.4762267309369959E-2</v>
+        <v>7.0138559321947902E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2035</v>
+        <v>1021</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1007</v>
+        <v>973</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-0.50515970515970521</v>
+        <v>-4.7012732615083208E-2</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1439,11 +1439,11 @@
       </c>
       <c r="O5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="3"/>
@@ -1451,15 +1451,15 @@
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1228</v>
+        <v>1125</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>1.655629139072845E-2</v>
+        <v>-7.1015689512799351E-2</v>
       </c>
       <c r="U5">
         <v>1</v>
@@ -1483,27 +1483,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9136539.7726296578</v>
+        <v>9957490.6809830684</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9958782.7049773205</v>
+        <v>10891954.273123616</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>8.9995003886575997E-2</v>
+        <v>9.3845289147515665E-2</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>5.5696202531645644E-2</v>
+        <v>3.9164490861618884E-2</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1531,15 +1531,15 @@
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>392</v>
+        <v>472</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>-2.4875621890547261E-2</v>
+        <v>0.16256157635467972</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1563,27 +1563,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7743516.6435261397</v>
+        <v>8316802.9094818188</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6081677.9457779359</v>
+        <v>6679003.8727309201</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>-0.2146103345871363</v>
+        <v>-0.19692651786706128</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>1.4981273408239737E-2</v>
+        <v>3.66300366300365E-3</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1611,15 +1611,15 @@
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>379</v>
+        <v>312</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>-1.0443864229765065E-2</v>
+        <v>-0.1875</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -1643,27 +1643,27 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9125846.8320685625</v>
+        <v>9808730.1557455901</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9528640.5381818991</v>
+        <v>10260074.279205721</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>4.413767988061168E-2</v>
+        <v>4.6014531574787965E-2</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>496</v>
+        <v>455</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>505</v>
+        <v>461</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>1.8145161290322509E-2</v>
+        <v>1.318681318681314E-2</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1683,23 +1683,23 @@
       </c>
       <c r="P8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>632</v>
+        <v>608</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>6.2184873949579833E-2</v>
+        <v>1.6722408026755842E-2</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1723,27 +1723,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4059495.7912112302</v>
+        <v>4368337.5354776643</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4278470.8679645592</v>
+        <v>4562456.1766546061</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>5.394144692240066E-2</v>
+        <v>4.4437646953880749E-2</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>8.2089552238805874E-2</v>
+        <v>-8.0000000000000071E-3</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1775,11 +1775,11 @@
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>5.9523809523809534E-2</v>
+        <v>-0.13690476190476186</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1803,27 +1803,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>832225.483727457</v>
+        <v>1042028.0883094301</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4260676.8748711916</v>
+        <v>4635399.7879167013</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>4.1196183704781957</v>
+        <v>3.4484403442877447</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>242</v>
+        <v>192</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
+        <v>7.2625698324022325E-2</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1851,15 +1851,15 @@
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>0.11229946524064172</v>
+        <v>0.27368421052631575</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1883,27 +1883,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8440011.6415319797</v>
+        <v>8948611.6469514072</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7427057.5940592606</v>
+        <v>8006300.9612096557</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>-0.1200180865258681</v>
+        <v>-0.10530244499578612</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>360</v>
+        <v>279</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>8.3333333333333037E-3</v>
+        <v>0.23655913978494625</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1931,15 +1931,15 @@
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>359</v>
+        <v>438</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>-2.4456521739130488E-2</v>
+        <v>0.18699186991869921</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3926643.4736452131</v>
+        <v>4263391.5358173661</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3647125.4913574592</v>
+        <v>3915245.4085396952</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>-7.1184966031120123E-2</v>
+        <v>-8.1659431078014988E-2</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>-0.18250950570342206</v>
+        <v>-0.30769230769230771</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1991,11 +1991,11 @@
       </c>
       <c r="M12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2011,15 +2011,15 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>0.12918660287081329</v>
+        <v>6.6350710900473953E-2</v>
       </c>
       <c r="U12">
         <v>2</v>
@@ -2043,27 +2043,27 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4329889.7318454506</v>
+        <v>4667851.798819243</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4468512.0865646908</v>
+        <v>4870420.3489419278</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>3.2015215930258245E-2</v>
+        <v>4.3396525608187853E-2</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1724137931034475E-2</v>
+        <v>-7.999999999999996E-2</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>-8.1967213114754189E-3</v>
+        <v>6.9672131147541005E-2</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2123,27 +2123,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15542536.569016691</v>
+        <v>17549914.722498216</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24968411.489844091</v>
+        <v>26970696.540104352</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>0.60645666677197552</v>
+        <v>0.53679929313440544</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1327</v>
+        <v>1196</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.3707611152976611E-2</v>
+        <v>5.7692307692307709E-2</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2163,23 +2163,23 @@
       </c>
       <c r="P14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="3"/>
-        <v>0.33333333333333326</v>
+        <v>1</v>
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1404</v>
+        <v>1354</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>-2.023726448011165E-2</v>
+        <v>-4.9824561403508771E-2</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2203,27 +2203,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29238120.41858248</v>
+        <v>31902479.662608825</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35824755.92923595</v>
+        <v>38515117.497534238</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>0.22527561335534041</v>
+        <v>0.207276609995797</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9845644983461974E-2</v>
+        <v>-9.8684210526315264E-3</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2251,15 +2251,15 @@
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1253</v>
+        <v>1104</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>1.4574898785425061E-2</v>
+        <v>-0.1017087062652563</v>
       </c>
       <c r="U15">
         <v>3</v>
@@ -2283,27 +2283,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17096402.744824786</v>
+        <v>18358012.535915993</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17290212.931036513</v>
+        <v>18617387.113703057</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>1.1336313790946129E-2</v>
+        <v>1.4128685078497405E-2</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>907</v>
+        <v>939</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6268980477223471E-2</v>
+        <v>7.4370709382151068E-2</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2331,15 +2331,15 @@
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1018</v>
+        <v>1056</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>-5.859375E-3</v>
+        <v>2.7237354085603016E-2</v>
       </c>
       <c r="U16">
         <v>3</v>
@@ -2363,27 +2363,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12161015.921806771</v>
+        <v>13351489.596777396</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16203096.619572133</v>
+        <v>17444471.917847052</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>0.33238018301721173</v>
+        <v>0.30655623040425128</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>636</v>
+        <v>675</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>-6.607929515418498E-2</v>
+        <v>-1.171303074670571E-2</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2403,23 +2403,23 @@
       </c>
       <c r="P17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>906</v>
+        <v>761</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>3.3222591362125353E-3</v>
+        <v>-0.16004415011037532</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2443,27 +2443,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>63455337.242055319</v>
+        <v>68183269.217183471</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>58431495.578616232</v>
+        <v>63285344.748622917</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>-7.9171301923355197E-2</v>
+        <v>-7.1834696763501404E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2091</v>
+        <v>2034</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2265</v>
+        <v>2171</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>8.3213773314203765E-2</v>
+        <v>6.735496558505405E-2</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2483,23 +2483,23 @@
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>-0.39884393063583812</v>
+        <v>-0.39306358381502893</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2872</v>
+        <v>2849</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2799</v>
+        <v>2793</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>-2.5417827298050089E-2</v>
+        <v>-1.9656019656019708E-2</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2523,27 +2523,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13715739.655666236</v>
+        <v>15904666.583410226</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30857225.122215234</v>
+        <v>33239044.280500673</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>1.2497674858874652</v>
+        <v>1.0898925548789258</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1218</v>
+        <v>1163</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>6.5616797900262425E-2</v>
+        <v>2.1071115013169495E-2</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2571,15 +2571,15 @@
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1367</v>
+        <v>1374</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1368</v>
+        <v>1304</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>7.3152889539129795E-4</v>
+        <v>-5.0946142649199389E-2</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2603,27 +2603,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>62455214.851508647</v>
+        <v>67552670.420068413</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>53170556.161955953</v>
+        <v>58198730.291162997</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14866106395803103</v>
+        <v>-0.13846884321136421</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2209</v>
+        <v>2177</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2092</v>
+        <v>2146</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-5.2965142598460857E-2</v>
+        <v>-1.4239779513091411E-2</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2651,15 +2651,15 @@
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2972</v>
+        <v>2974</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2777</v>
+        <v>2498</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-6.5612382234185751E-2</v>
+        <v>-0.16005379959650301</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2683,27 +2683,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9647857.3613462802</v>
+        <v>10254185.087530892</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8653275.5065172911</v>
+        <v>9326802.7803758383</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>-0.1030883664194433</v>
+        <v>-9.0439396133267791E-2</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>-8.5470085470085166E-3</v>
+        <v>4.094827586206895E-2</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2731,15 +2731,15 @@
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-2.5878003696857665E-2</v>
+        <v>-7.0370370370370416E-2</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2763,31 +2763,31 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25727162.271941304</v>
+        <v>27775459.775627609</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23472141.842081539</v>
+        <v>25275052.162944004</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>-8.7651347086932563E-2</v>
+        <v>-9.0022186234975043E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1348</v>
+        <v>1306</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1473</v>
+        <v>1492</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>9.2729970326409505E-2</v>
+        <v>0.14241960183767222</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -2795,11 +2795,11 @@
       </c>
       <c r="N22" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2807,19 +2807,19 @@
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>7.6923076923076872E-2</v>
+        <v>-6.6666666666666652E-2</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1749</v>
+        <v>1728</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1740</v>
+        <v>1859</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>-5.145797598627766E-3</v>
+        <v>7.5810185185185119E-2</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2843,27 +2843,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10259830.90651048</v>
+        <v>11036402.959192213</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9877911.5601799227</v>
+        <v>10793154.824868249</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>-3.7224721324423227E-2</v>
+        <v>-2.2040526720833675E-2</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>7.4509803921568585E-2</v>
+        <v>6.4643799472295482E-2</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2883,23 +2883,23 @@
       </c>
       <c r="P23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.375</v>
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>833</v>
+        <v>885</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>-5.0171037628278237E-2</v>
+        <v>1.1428571428571344E-2</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2923,27 +2923,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13074169.534061378</v>
+        <v>14021428.057064189</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12367446.731246172</v>
+        <v>13439375.56318808</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>-5.4054890520887189E-2</v>
+        <v>-4.1511641432476099E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>807</v>
+        <v>872</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>729</v>
+        <v>763</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>-9.6654275092936781E-2</v>
+        <v>-0.125</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2971,15 +2971,15 @@
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>874</v>
+        <v>888</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>-1.7977528089887618E-2</v>
+        <v>1.1273957158963732E-3</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -3003,27 +3003,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2752351.900354438</v>
+        <v>2987521.6738292631</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3125322.1816324871</v>
+        <v>3444507.7473005932</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>0.1355096640186233</v>
+        <v>0.15296493996161953</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>0.2807017543859649</v>
+        <v>0.24444444444444446</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3051,15 +3051,15 @@
       </c>
       <c r="R25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="S25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="4"/>
-        <v>-5.6277056277056259E-2</v>
+        <v>1.304347826086949E-2</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -3083,31 +3083,31 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24358751.544144496</v>
+        <v>26097918.150558844</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24602514.895429038</v>
+        <v>26699945.286994319</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>1.0007218590114331E-2</v>
+        <v>2.3068013814833144E-2</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1293</v>
+        <v>1500</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1545</v>
+        <v>1624</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>0.19489559164733183</v>
+        <v>8.2666666666666666E-2</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="N26" s="12">
         <f t="shared" si="2"/>
-        <v>-0.16666666666666663</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3123,23 +3123,23 @@
       </c>
       <c r="P26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="3"/>
-        <v>-0.77777777777777779</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1646</v>
+        <v>1827</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>-1.0222489476849117E-2</v>
+        <v>0.10060240963855427</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -3163,27 +3163,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19811258.757022385</v>
+        <v>21408157.92547648</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22132677.989444103</v>
+        <v>23972515.811498009</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>0.1171767660446541</v>
+        <v>0.11978414466804033</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>629</v>
+        <v>558</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>630</v>
+        <v>669</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>1.5898251192367763E-3</v>
+        <v>0.19892473118279574</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3211,15 +3211,15 @@
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>898</v>
+        <v>795</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>3.0998851894374235E-2</v>
+        <v>-9.1428571428571415E-2</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -3243,27 +3243,27 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19404275.471009124</v>
+        <v>20992871.884413186</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21393659.220353145</v>
+        <v>23572892.259057939</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>0.10252295955683843</v>
+        <v>0.1228998294683239</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>824</v>
+        <v>608</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>3.6407766990291357E-2</v>
+        <v>0.44901315789473695</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3291,15 +3291,15 @@
       </c>
       <c r="R28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1016</v>
+        <v>1052</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-4.1509433962264142E-2</v>
+        <v>-8.4825636192271681E-3</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -3323,27 +3323,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26404188.141816933</v>
+        <v>28355830.721760739</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27596352.646259207</v>
+        <v>29858563.383784257</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>4.515058361344626E-2</v>
+        <v>5.2995543553950419E-2</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>816</v>
+        <v>851</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>838</v>
+        <v>854</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>2.6960784313725394E-2</v>
+        <v>3.5252643948295859E-3</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3371,15 +3371,15 @@
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1149</v>
+        <v>1010</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>3.0493273542600896E-2</v>
+        <v>-9.4982078853046548E-2</v>
       </c>
       <c r="U29">
         <v>0</v>
@@ -3403,31 +3403,31 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37505222.301559903</v>
+        <v>40601238.013903379</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38482011.267993741</v>
+        <v>41739242.360557027</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>2.6044078837341278E-2</v>
+        <v>2.8028809029516655E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1207</v>
+        <v>1178</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1113</v>
+        <v>1201</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>-7.7879038939519418E-2</v>
+        <v>1.9524617996604432E-2</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="N30" s="12">
         <f t="shared" si="2"/>
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="O30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3451,15 +3451,15 @@
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1455</v>
+        <v>1448</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1447</v>
+        <v>1321</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>-5.4982817869415612E-3</v>
+        <v>-8.7707182320441945E-2</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3483,27 +3483,27 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15398605.461348807</v>
+        <v>16636175.449088316</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15371358.076542115</v>
+        <v>16939342.25355164</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>-1.7694709352145122E-3</v>
+        <v>1.8223347390817324E-2</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>581</v>
+        <v>493</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>794</v>
+        <v>762</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>0.36660929432013778</v>
+        <v>0.54563894523326573</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3531,15 +3531,15 @@
       </c>
       <c r="R31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>685</v>
+        <v>807</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>4.3988269794721369E-3</v>
+        <v>0.17982456140350878</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3563,31 +3563,31 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46536061.009953454</v>
+        <v>46539327.260969058</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29407824.984452795</v>
+        <v>32734730.545260098</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-0.36806372636130835</v>
+        <v>-0.29662218016817798</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>892</v>
+        <v>70</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1680</v>
+        <v>1613</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>0.88340807174887903</v>
+        <v>22.042857142857144</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N32" s="12">
         <f t="shared" si="2"/>
-        <v>-0.45454545454545459</v>
+        <v>-0.4</v>
       </c>
       <c r="O32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3603,23 +3603,23 @@
       </c>
       <c r="P32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.5</v>
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1941</v>
+        <v>1925</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1857</v>
+        <v>1785</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-4.3276661514683123E-2</v>
+        <v>-7.2727272727272751E-2</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3643,27 +3643,27 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15552674.040534776</v>
+        <v>16874087.423591021</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16019371.822294367</v>
+        <v>17298861.003520712</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>3.0007558863719641E-2</v>
+        <v>2.5173129027163288E-2</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>-0.1472868217054264</v>
+        <v>-0.1315453384418902</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="O33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -3695,11 +3695,11 @@
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>853</v>
+        <v>799</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>1.0663507109004655E-2</v>
+        <v>-5.331753554502372E-2</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3723,27 +3723,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14986852.341861239</v>
+        <v>16191205.913323352</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14185152.208508916</v>
+        <v>15397482.675662059</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>-5.3493563228952046E-2</v>
+        <v>-4.9021872855570137E-2</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>598</v>
+        <v>633</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>0.11152416356877315</v>
+        <v>0.12633451957295372</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3775,11 +3775,11 @@
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>725</v>
+        <v>801</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>-2.6845637583892579E-2</v>
+        <v>7.5167785234899309E-2</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3803,27 +3803,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22114246.499472193</v>
+        <v>23979908.496460751</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25110758.092792481</v>
+        <v>27238703.996070687</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>0.13550141052247944</v>
+        <v>0.13589691137023774</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>822</v>
+        <v>868</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>0.10827250608272498</v>
+        <v>4.8387096774193505E-2</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3851,15 +3851,15 @@
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1197</v>
+        <v>1428</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>2.7467811158798261E-2</v>
+        <v>0.2310344827586206</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3883,27 +3883,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20741126.062683959</v>
+        <v>22374902.800021451</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22932356.491074044</v>
+        <v>24757046.481234096</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>0.10564664723447192</v>
+        <v>0.10646498456343512</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>837</v>
+        <v>905</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>5.1507537688442184E-2</v>
+        <v>9.5641646489104115E-2</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3931,15 +3931,15 @@
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1331</v>
+        <v>1319</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1433</v>
+        <v>1395</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>7.6634109691960939E-2</v>
+        <v>5.7619408642911374E-2</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3963,27 +3963,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38453663.605802923</v>
+        <v>41518349.605261825</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38312378.880640082</v>
+        <v>41478113.936420672</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>-3.6741551237141623E-3</v>
+        <v>-9.6910568998276325E-4</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1529</v>
+        <v>1405</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>1.8312622629169439E-2</v>
+        <v>4.1992882562277511E-2</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4003,23 +4003,23 @@
       </c>
       <c r="P37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="3"/>
-        <v>2.4347826086956523</v>
+        <v>2.4492753623188408</v>
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2397</v>
+        <v>2372</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2266</v>
+        <v>2354</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>-5.4651647893199873E-2</v>
+        <v>-7.5885328836424737E-3</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4043,27 +4043,27 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13607803.394892052</v>
+        <v>14781644.391173327</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14083966.5119655</v>
+        <v>15234974.245374314</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>3.4991916274465407E-2</v>
+        <v>3.0668431887840963E-2</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>570</v>
+        <v>668</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>-0.2192982456140351</v>
+        <v>-0.33832335329341312</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4091,15 +4091,15 @@
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>592</v>
+        <v>538</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>-4.2071197411003292E-2</v>
+        <v>-0.13085621970920835</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4123,27 +4123,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>45449281.559613265</v>
+        <v>48800547.351421833</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43927118.587503135</v>
+        <v>47432872.324979059</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>-3.3491463888457584E-2</v>
+        <v>-2.8025813247418929E-2</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1817</v>
+        <v>1857</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>-5.0679205851619669E-2</v>
+        <v>-3.0793319415448828E-2</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4171,15 +4171,15 @@
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>-1.2639766650461848E-2</v>
+        <v>-1.6019417475728104E-2</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4203,31 +4203,31 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29655636.505533084</v>
+        <v>32614535.508652512</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33967834.959300019</v>
+        <v>36694418.119907491</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>0.14540906761392125</v>
+        <v>0.12509399712813951</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1422</v>
+        <v>2049</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>846</v>
+        <v>875</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>-0.40506329113924056</v>
+        <v>-0.57296242069302106</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="N40" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="O40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4251,15 +4251,15 @@
       </c>
       <c r="R40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>930</v>
+        <v>989</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>3.3333333333333437E-2</v>
+        <v>9.1611479028697484E-2</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16068125.974080767</v>
+        <v>17773873.790777944</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24052081.674599729</v>
+        <v>26012267.611628871</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>0.49688157246201281</v>
+        <v>0.46351143919596494</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>908</v>
+        <v>969</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>970</v>
+        <v>934</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>6.8281938325991165E-2</v>
+        <v>-3.6119711042311708E-2</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4327,19 +4327,19 @@
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-1.5726179463459777E-2</v>
+        <v>-2.4816176470588203E-2</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4363,27 +4363,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23518097.944919869</v>
+        <v>25294917.477437437</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24303801.668385867</v>
+        <v>26258702.513062768</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>3.3408472288283697E-2</v>
+        <v>3.8101924486806826E-2</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>627</v>
+        <v>590</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>597</v>
+        <v>636</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>-4.7846889952153138E-2</v>
+        <v>7.7966101694915357E-2</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4411,15 +4411,15 @@
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>837</v>
+        <v>725</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>7.2202166064982976E-3</v>
+        <v>-0.13173652694610782</v>
       </c>
       <c r="U42">
         <v>1</v>
@@ -4443,27 +4443,27 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15130453.175075745</v>
+        <v>16227351.047975589</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14609642.865583366</v>
+        <v>15777654.210746672</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>-3.4421329187304561E-2</v>
+        <v>-2.7712276384445289E-2</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>553</v>
+        <v>587</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>5.6057866184448413E-2</v>
+        <v>-4.4293015332197649E-2</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4491,15 +4491,15 @@
       </c>
       <c r="R43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>717</v>
+        <v>700</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>1.5580736543909346E-2</v>
+        <v>-1.4265335235378318E-3</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4523,27 +4523,27 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13321177.692165183</v>
+        <v>14358233.121239796</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13640714.055751091</v>
+        <v>14765811.497357111</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>2.3987095658504876E-2</v>
+        <v>2.8386387982125338E-2</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>719</v>
+        <v>676</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>778</v>
+        <v>803</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>8.2058414464533991E-2</v>
+        <v>0.18786982248520712</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4571,15 +4571,15 @@
       </c>
       <c r="R44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>704</v>
+        <v>789</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>2.6239067055393583E-2</v>
+        <v>0.15350877192982448</v>
       </c>
       <c r="U44">
         <v>2</v>
@@ -4603,27 +4603,27 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>40575137.286203943</v>
+        <v>43788229.833009563</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>45745588.58812362</v>
+        <v>49134791.486482561</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>0.12742905256115278</v>
+        <v>0.12210042913044439</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2756</v>
+        <v>1098</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1136</v>
+        <v>1123</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>-0.58780841799709727</v>
+        <v>2.2768670309653904E-2</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4651,15 +4651,15 @@
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1286</v>
+        <v>1159</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>3.7096774193548399E-2</v>
+        <v>-6.2297734627831725E-2</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4683,27 +4683,27 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19563741.756338328</v>
+        <v>21077266.831570905</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19453326.637208953</v>
+        <v>20804392.415884595</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>-5.6438650900512144E-3</v>
+        <v>-1.2946385215258593E-2</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1570</v>
+        <v>910</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>900</v>
+        <v>886</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>-0.42675159235668791</v>
+        <v>-2.6373626373626391E-2</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4731,15 +4731,15 @@
       </c>
       <c r="R46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>877</v>
+        <v>908</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>-3.4140969162995582E-2</v>
+        <v>-2.19780219780219E-3</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4763,27 +4763,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34200115.304982483</v>
+        <v>36799819.563541561</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35513529.941505633</v>
+        <v>38255043.889359169</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>3.8403807262363365E-2</v>
+        <v>3.9544333180897784E-2</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>465</v>
+        <v>1025</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>972</v>
+        <v>1044</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>1.0903225806451613</v>
+        <v>1.8536585365853675E-2</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4799,27 +4799,27 @@
       </c>
       <c r="O47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q47" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.25</v>
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1413</v>
+        <v>1443</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>5.0557620817843762E-2</v>
+        <v>7.1269487750556859E-2</v>
       </c>
       <c r="U47">
         <v>5</v>
@@ -4843,27 +4843,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17692903.869914349</v>
+        <v>18998431.435199615</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16698819.456651105</v>
+        <v>18181613.774843927</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>-5.6185486598026579E-2</v>
+        <v>-4.2993952587176087E-2</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>233</v>
+        <v>365</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>506</v>
+        <v>400</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>1.1716738197424892</v>
+        <v>9.5890410958904049E-2</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4891,15 +4891,15 @@
       </c>
       <c r="R48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>1.8633540372670732E-2</v>
+        <v>1.8595041322314154E-2</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4923,27 +4923,27 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12885929.269668665</v>
+        <v>13867349.453376597</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14295788.226282325</v>
+        <v>15464289.961397316</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>0.10941073221100428</v>
+        <v>0.11515830861476384</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>211</v>
+        <v>315</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>417</v>
+        <v>373</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>0.97630331753554511</v>
+        <v>0.18412698412698414</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4971,15 +4971,15 @@
       </c>
       <c r="R49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>459</v>
+        <v>506</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>4.3763676148795838E-3</v>
+        <v>0.10239651416121998</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -5003,27 +5003,27 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11147708.240657611</v>
+        <v>11991960.514846284</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5589046.8414643016</v>
+        <v>5719922.5869477298</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-0.49863714399340975</v>
+        <v>-0.52302022843834806</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>220</v>
+        <v>327</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>38</v>
+        <v>278</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-0.82727272727272727</v>
+        <v>-0.14984709480122327</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5043,23 +5043,23 @@
       </c>
       <c r="P50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="S50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>396</v>
+        <v>116</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="4"/>
-        <v>-7.906976744186045E-2</v>
+        <v>-0.72705882352941176</v>
       </c>
       <c r="U50">
         <v>4</v>
@@ -5083,27 +5083,27 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26191668.071031023</v>
+        <v>28403417.987599976</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28462888.360719599</v>
+        <v>30195865.25279944</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>8.6715373894060255E-2</v>
+        <v>6.3106745321354962E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>661</v>
+        <v>974</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>0.34493192133131623</v>
+        <v>-7.0841889117043144E-2</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5119,27 +5119,27 @@
       </c>
       <c r="O51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q51" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="R51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1099</v>
+        <v>941</v>
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-3.6264732547597323E-3</v>
+        <v>-0.14918625678119346</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5163,27 +5163,27 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25274443.649353232</v>
+        <v>27544676.485392641</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28675298.836824629</v>
+        <v>30524186.608173389</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>0.13455707412014295</v>
+        <v>0.10817008957650409</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>715</v>
+        <v>917</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>0.11468531468531462</v>
+        <v>-0.1275899672846238</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5215,11 +5215,11 @@
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>927</v>
+        <v>947</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>-7.1142284569138292E-2</v>
+        <v>-5.1102204408817631E-2</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5243,27 +5243,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>49677371.10828805</v>
+        <v>53312926.280314647</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>52582289.558401659</v>
+        <v>56661351.157900929</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>5.8475687930051423E-2</v>
+        <v>6.280699843750015E-2</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1226</v>
+        <v>1517</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1642</v>
+        <v>1850</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>0.33931484502446985</v>
+        <v>0.21951219512195119</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5279,11 +5279,11 @@
       </c>
       <c r="O53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q53" s="12">
         <f t="shared" si="3"/>
@@ -5291,15 +5291,15 @@
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2065</v>
+        <v>2057</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2100</v>
+        <v>2123</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>1.6949152542372836E-2</v>
+        <v>3.2085561497326109E-2</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5323,27 +5323,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11997117.736853795</v>
+        <v>13156051.392773269</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13982560.869168984</v>
+        <v>14826348.495922143</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>0.16549334397345539</v>
+        <v>0.12696036624380946</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>453</v>
+        <v>567</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>675</v>
+        <v>507</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>0.49006622516556297</v>
+        <v>-0.10582010582010581</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5371,15 +5371,15 @@
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>657</v>
+        <v>560</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>-3.8067349926793503E-2</v>
+        <v>-0.17525773195876293</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5403,27 +5403,27 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21280371.70766744</v>
+        <v>22949848.91231928</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24407846.306572575</v>
+        <v>26561103.572443023</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>0.1469652241919388</v>
+        <v>0.15735418014822988</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>510</v>
+        <v>738</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>827</v>
+        <v>865</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>0.6215686274509804</v>
+        <v>0.17208672086720878</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="O55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5447,19 +5447,19 @@
       </c>
       <c r="Q55" s="12">
         <f t="shared" si="3"/>
-        <v>0.19999999999999996</v>
+        <v>0</v>
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>911</v>
+        <v>1050</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>4.9539170506912367E-2</v>
+        <v>0.20551090700344421</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5483,27 +5483,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13008470.054326516</v>
+        <v>14245013.316192299</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12702688.915399697</v>
+        <v>13109236.528265854</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>-2.350631070754694E-2</v>
+        <v>-7.9731535711195733E-2</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>516</v>
+        <v>625</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>57</v>
+        <v>526</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>-0.88953488372093026</v>
+        <v>-0.15839999999999999</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5531,15 +5531,15 @@
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>673</v>
+        <v>411</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-0.10146862483311081</v>
+        <v>-0.44832214765100675</v>
       </c>
       <c r="U56">
         <v>2</v>
@@ -5563,27 +5563,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27692985.716273904</v>
+        <v>29939617.972537749</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30502819.256533097</v>
+        <v>32682821.514900204</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>0.10146372691796768</v>
+        <v>9.1624533916186524E-2</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>807</v>
+        <v>963</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1279</v>
+        <v>1190</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>0.58488228004956633</v>
+        <v>0.2357217030114227</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5603,23 +5603,23 @@
       </c>
       <c r="P57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q57" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1105</v>
+        <v>1292</v>
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>-1.8066847335139746E-3</v>
+        <v>0.16291629162916288</v>
       </c>
       <c r="U57">
         <v>2</v>
@@ -5643,27 +5643,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33951195.810102426</v>
+        <v>37000002.653800093</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>41763405.554746158</v>
+        <v>44797837.205057278</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>0.23010116604844755</v>
+        <v>0.21075227005304842</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1441</v>
+        <v>1471</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1494</v>
+        <v>1513</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>3.6780013879250451E-2</v>
+        <v>2.8552005438477135E-2</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5691,15 +5691,15 @@
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>0.11281337047353768</v>
+        <v>0.11103400416377518</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5723,27 +5723,27 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18629448.795252305</v>
+        <v>19983891.374101069</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16761125.185675364</v>
+        <v>18318451.973164391</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>-0.10028872191071381</v>
+        <v>-8.3339093961202759E-2</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>648</v>
+        <v>705</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>790</v>
+        <v>763</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>0.21913580246913589</v>
+        <v>8.2269503546099187E-2</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5771,15 +5771,15 @@
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>805</v>
+        <v>873</v>
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>4.0051679586563305E-2</v>
+        <v>0.13082901554404147</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5803,27 +5803,27 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20847380.402954869</v>
+        <v>22367781.080104113</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22020764.973671433</v>
+        <v>23871295.559602365</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>5.6284509038375452E-2</v>
+        <v>6.7217864575561892E-2</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>3.1111111111111089E-2</v>
+        <v>2.1008403361344463E-2</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5851,15 +5851,15 @@
       </c>
       <c r="R60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>643</v>
+        <v>585</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>-1.228878648233489E-2</v>
+        <v>-9.4427244582043324E-2</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5883,27 +5883,27 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>67327568.067904234</v>
+        <v>72623824.220833898</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>70670658.044179976</v>
+        <v>76429257.720611393</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>4.9654102653819532E-2</v>
+        <v>5.239924419576103E-2</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1641</v>
+        <v>1619</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1829</v>
+        <v>1674</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>0.11456429006703228</v>
+        <v>3.3971587399629355E-2</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5911,15 +5911,15 @@
       </c>
       <c r="M61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N61" s="12">
         <f t="shared" si="2"/>
-        <v>0.30000000000000004</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5927,19 +5927,19 @@
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
-        <v>0.44444444444444442</v>
+        <v>0.18181818181818188</v>
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1983</v>
+        <v>1996</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1971</v>
+        <v>2063</v>
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>-6.0514372163388286E-3</v>
+        <v>3.356713426853708E-2</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5963,27 +5963,27 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>49430448.945431069</v>
+        <v>53751877.713151284</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>50220349.921165459</v>
+        <v>54327698.607676938</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>1.5980048585162665E-2</v>
+        <v>1.0712572639760554E-2</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1265</v>
+        <v>1229</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1201</v>
+        <v>1243</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>-5.0592885375494112E-2</v>
+        <v>1.1391375101708734E-2</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="O62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6007,19 +6007,19 @@
       </c>
       <c r="Q62" s="12">
         <f t="shared" si="3"/>
-        <v>-7.6923076923076872E-2</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1603</v>
+        <v>1594</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>1.2634238787113006E-2</v>
+        <v>7.5853350189634128E-3</v>
       </c>
       <c r="U62">
         <v>9</v>
@@ -6043,27 +6043,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32493119.305810899</v>
+        <v>35023411.856107965</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34013930.676028676</v>
+        <v>36681052.563683063</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>4.6804105075433755E-2</v>
+        <v>4.7329503886869517E-2</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>734</v>
+        <v>764</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>699</v>
+        <v>734</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>-4.7683923705722053E-2</v>
+        <v>-3.9267015706806241E-2</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6079,27 +6079,27 @@
       </c>
       <c r="O63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="12">
         <f t="shared" si="3"/>
-        <v>-0.75</v>
+        <v>-0.6</v>
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>9.0497737556560764E-3</v>
+        <v>3.1638418079096065E-2</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6123,27 +6123,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>49546807.447998308</v>
+        <v>52986952.666871026</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>45338783.339071438</v>
+        <v>49029776.551765636</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>-8.4930277563158629E-2</v>
+        <v>-7.4682085229248019E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1308</v>
+        <v>1327</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1302</v>
+        <v>1272</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>-4.5871559633027248E-3</v>
+        <v>-4.1446872645064081E-2</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="O64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6167,19 +6167,19 @@
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>8.1300813008129413E-3</v>
+        <v>2.6954177897573484E-3</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2317</v>
+        <v>2297</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2329</v>
+        <v>2015</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>5.1791109192922402E-3</v>
+        <v>-0.12276882890727037</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6203,27 +6203,27 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1348505.727031731</v>
+        <v>1604743.4340360931</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3682667.934082624</v>
+        <v>4030673.95379342</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>1.7309249491945011</v>
+        <v>1.5117248454202206</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>250</v>
+        <v>286</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>0.12400000000000011</v>
+        <v>-3.8461538461538436E-2</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6251,15 +6251,15 @@
       </c>
       <c r="R65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>-2.0242914979757054E-2</v>
+        <v>0.16393442622950816</v>
       </c>
       <c r="U65">
         <v>2</v>
@@ -6283,27 +6283,27 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35127326.366053008</v>
+        <v>37741415.05560144</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34445460.314459853</v>
+        <v>37080322.484695628</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-1.9411270999893371E-2</v>
+        <v>-1.7516369482487026E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1480</v>
+        <v>1518</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1576</v>
+        <v>1479</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>6.4864864864864868E-2</v>
+        <v>-2.5691699604743046E-2</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6323,23 +6323,23 @@
       </c>
       <c r="P66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q66" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1608</v>
+        <v>1690</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>-3.6548831635709988E-2</v>
+        <v>1.3797240551889578E-2</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6363,19 +6363,19 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16812574.105930068</v>
+        <v>18215056.68860703</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15667692.503356764</v>
+        <v>16713241.139799256</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>-6.8096746837207123E-2</v>
+        <v>-8.2449128459046395E-2</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>-6.2695924764890276E-2</v>
+        <v>-2.1276595744680882E-2</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6415,11 +6415,11 @@
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>794</v>
+        <v>652</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>7.8804347826086918E-2</v>
+        <v>-0.11413043478260865</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6443,27 +6443,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23873577.731227577</v>
+        <v>25802788.754436146</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25445366.118607964</v>
+        <v>27816969.776097447</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>6.5837990647058531E-2</v>
+        <v>7.8060594179573339E-2</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>959</v>
+        <v>924</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>0.13895486935866974</v>
+        <v>6.3291139240506222E-2</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="O68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6487,19 +6487,19 @@
       </c>
       <c r="Q68" s="12">
         <f t="shared" si="8"/>
-        <v>-0.94736842105263164</v>
+        <v>-0.95</v>
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1464</v>
+        <v>1399</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>7.0958302852962785E-2</v>
+        <v>1.8936635105608168E-2</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6523,27 +6523,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14656833.663769012</v>
+        <v>15960149.230632352</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20167933.173738983</v>
+        <v>21612087.804990321</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>0.37600887315745024</v>
+        <v>0.35412817842017352</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>982</v>
+        <v>1214</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1241</v>
+        <v>1312</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>0.26374745417515277</v>
+        <v>8.0724876441515603E-2</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6563,23 +6563,23 @@
       </c>
       <c r="P69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q69" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1320</v>
+        <v>1396</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>2.8838659392049992E-2</v>
+        <v>9.2331768388106417E-2</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6603,27 +6603,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>43203204.558727421</v>
+        <v>46580676.905710757</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>45274446.644820362</v>
+        <v>49256726.466358557</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>4.7941862351378095E-2</v>
+        <v>5.7449778286062569E-2</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1213</v>
+        <v>1228</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1271</v>
+        <v>1317</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>4.7815333882934796E-2</v>
+        <v>7.2475570032573211E-2</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="O70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6647,19 +6647,19 @@
       </c>
       <c r="Q70" s="12">
         <f t="shared" si="8"/>
-        <v>0.125</v>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1778</v>
+        <v>1605</v>
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>1.8911174785100293E-2</v>
+        <v>-8.2857142857142851E-2</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6683,27 +6683,27 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8716800.0374078844</v>
+        <v>9383646.5454543922</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8336159.5331871547</v>
+        <v>8960062.0347378012</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-4.3667458538365289E-2</v>
+        <v>-4.514071461075897E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>629</v>
+        <v>440</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>-0.33068362480127189</v>
+        <v>-1.5909090909090873E-2</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6711,11 +6711,11 @@
       </c>
       <c r="M71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N71" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6731,15 +6731,15 @@
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>-5.0485436893203839E-2</v>
+        <v>-0.11025145067698261</v>
       </c>
       <c r="U71">
         <v>1</v>
@@ -6763,27 +6763,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13419610.797755742</v>
+        <v>14552442.544222549</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16320737.705918368</v>
+        <v>17409108.331550773</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>0.21618562206348058</v>
+        <v>0.19630146476423271</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>669</v>
+        <v>774</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>897</v>
+        <v>747</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>0.34080717488789247</v>
+        <v>-3.4883720930232509E-2</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6811,15 +6811,15 @@
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>896</v>
+        <v>782</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>1.5873015873015817E-2</v>
+        <v>-0.11738148984198649</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6843,27 +6843,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13406864.351865375</v>
+        <v>14615906.519403487</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14939900.890034296</v>
+        <v>16261279.578989357</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>0.11434713576076572</v>
+        <v>0.1125741367736266</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>6.1855670103092564E-3</v>
+        <v>-8.2987551867219622E-3</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6891,15 +6891,15 @@
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>635</v>
+        <v>589</v>
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-2.6073619631901801E-2</v>
+        <v>-9.5238095238095233E-2</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6923,27 +6923,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11044050.643039128</v>
+        <v>11825950.763445076</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9544700.5587438848</v>
+        <v>10410105.269862575</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>-0.13576088454830271</v>
+        <v>-0.1197236080128955</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1030</v>
+        <v>790</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>0.45070422535211274</v>
+        <v>8.9655172413793061E-2</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6963,23 +6963,23 @@
       </c>
       <c r="P74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q74" s="12">
         <f t="shared" si="8"/>
-        <v>-0.19999999999999996</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>605</v>
+        <v>800</v>
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>6.6555740432612254E-3</v>
+        <v>0.30718954248366015</v>
       </c>
       <c r="U74">
         <v>1</v>
@@ -7003,27 +7003,27 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11871515.03801666</v>
+        <v>12707889.856647348</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10204824.002210468</v>
+        <v>11224853.807416515</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>-0.14039413086441588</v>
+        <v>-0.11670199112208024</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>251</v>
+        <v>459</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>0.84860557768924294</v>
+        <v>1.5250544662309462E-2</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="P75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q75" s="12">
         <f t="shared" si="8"/>
@@ -7051,15 +7051,15 @@
       </c>
       <c r="R75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>-1.5659955257270708E-2</v>
+        <v>0.12162162162162171</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -7083,27 +7083,27 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31261131.096501935</v>
+        <v>33856213.568945937</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23598904.180730466</v>
+        <v>25767122.084004831</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>-0.24510395647932459</v>
+        <v>-0.23892487175118404</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>530</v>
+        <v>749</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>-0.27891156462585032</v>
+        <v>-9.2592592592593004E-3</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7111,15 +7111,15 @@
       </c>
       <c r="M76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N76" s="12">
         <f t="shared" si="7"/>
-        <v>-0.33333333333333337</v>
+        <v>0</v>
       </c>
       <c r="O76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7127,19 +7127,19 @@
       </c>
       <c r="Q76" s="12">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-9.9787685774946899E-2</v>
+        <v>-0.2021276595744681</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7163,27 +7163,27 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18891602.264381222</v>
+        <v>20147404.699376933</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19211296.435092594</v>
+        <v>20795729.777784407</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>1.6922554595283579E-2</v>
+        <v>3.2179086491845865E-2</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2118</v>
+        <v>709</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>692</v>
+        <v>741</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>-0.67327667610953723</v>
+        <v>4.5133991537376517E-2</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7211,15 +7211,15 @@
       </c>
       <c r="R77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>776</v>
+        <v>789</v>
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>5.1813471502590858E-3</v>
+        <v>2.3346303501945442E-2</v>
       </c>
       <c r="U77">
         <v>2</v>
@@ -7243,27 +7243,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15118369.682815623</v>
+        <v>16295988.162141008</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15852572.06871303</v>
+        <v>17212098.434398443</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>4.8563595235532775E-2</v>
+        <v>5.621692057838823E-2</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>952</v>
+        <v>974</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>0.1134502923976608</v>
+        <v>0.11569301260022913</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="O78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7287,19 +7287,19 @@
       </c>
       <c r="Q78" s="12">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>952</v>
+        <v>1100</v>
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>-8.3333333333333037E-3</v>
+        <v>0.14702815432742433</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7323,27 +7323,27 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14524187.856017128</v>
+        <v>16008993.220043994</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18906157.439068951</v>
+        <v>20575678.3225642</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>0.30170152207418921</v>
+        <v>0.28525748245070814</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>849</v>
+        <v>860</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>8.3135391923989665E-3</v>
+        <v>2.5029797377830842E-2</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7363,23 +7363,23 @@
       </c>
       <c r="P79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="12">
         <f t="shared" si="8"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>968</v>
+        <v>941</v>
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-2.8112449799196804E-2</v>
+        <v>-5.1411290322580627E-2</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7403,27 +7403,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19671552.708550803</v>
+        <v>21222145.549389083</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22132214.210737165</v>
+        <v>24021340.943134073</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>0.12508730442598792</v>
+        <v>0.13189973592587911</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>408</v>
+        <v>733</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>759</v>
+        <v>784</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>0.86029411764705888</v>
+        <v>6.9577080491132426E-2</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7455,11 +7455,11 @@
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>765</v>
+        <v>844</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>1.0568031704095038E-2</v>
+        <v>0.11492734478203426</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7483,27 +7483,27 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9375082.9609405603</v>
+        <v>10050763.988478778</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8934225.0752158221</v>
+        <v>9531836.5712453369</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>-4.7024425016982341E-2</v>
+        <v>-5.1630643981720126E-2</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>540</v>
+        <v>493</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>-8.7037037037037024E-2</v>
+        <v>1.8255578093306246E-2</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7531,15 +7531,15 @@
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>546</v>
+        <v>593</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>-4.0421792618629215E-2</v>
+        <v>5.7040998217468886E-2</v>
       </c>
       <c r="U81">
         <v>0</v>
@@ -7563,27 +7563,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38701029.284727588</v>
+        <v>42084775.50188525</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>46989513.872192614</v>
+        <v>51153393.19780989</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>0.21416703226381295</v>
+        <v>0.21548452113088734</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1316</v>
+        <v>1348</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1372</v>
+        <v>1448</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>4.2553191489361764E-2</v>
+        <v>7.4183976261127604E-2</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7611,15 +7611,15 @@
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1762</v>
+        <v>1767</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1783</v>
+        <v>1661</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>1.191827468785478E-2</v>
+        <v>-5.9988681380871545E-2</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7643,27 +7643,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8622190.9655356202</v>
+        <v>9931053.6177717447</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9986112.4448090214</v>
+        <v>11320774.287268532</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>0.15818734295322723</v>
+        <v>0.13993688111902491</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>734</v>
+        <v>900</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>899</v>
+        <v>763</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>0.22479564032697552</v>
+        <v>-0.15222222222222226</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7691,15 +7691,15 @@
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>628</v>
+        <v>925</v>
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>0.11347517730496448</v>
+        <v>0.64590747330960863</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7723,27 +7723,27 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17495104.84190416</v>
+        <v>18693370.236158248</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19009001.995999392</v>
+        <v>20146519.231406134</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>8.6532613995496277E-2</v>
+        <v>7.7736062405541206E-2</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>408</v>
+        <v>543</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>979</v>
+        <v>522</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>1.3995098039215685</v>
+        <v>-3.8674033149171283E-2</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7771,15 +7771,15 @@
       </c>
       <c r="R84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="S84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>665</v>
+        <v>766</v>
       </c>
       <c r="T84" s="12">
         <f t="shared" si="9"/>
-        <v>3.2608695652173836E-2</v>
+        <v>0.18392581143740339</v>
       </c>
       <c r="U84">
         <v>7</v>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4317447.3459969955</v>
+        <v>4601412.716901565</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
@@ -7811,19 +7811,19 @@
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>-3.2446006170838149E-2</v>
+        <v>-9.2156326811866029E-2</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>-0.91315789473684206</v>
+        <v>-0.96132596685082872</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7851,15 +7851,15 @@
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>379</v>
+        <v>100</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>3.8356164383561708E-2</v>
+        <v>-0.72375690607734811</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7898,31 +7898,31 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>84798</v>
+        <v>84698</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>1001</v>
+        <v>1022</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>71269</v>
+        <v>69168</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>1792079533.2534416</v>
+        <v>1934635103.3523769</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84642</v>
+        <v>83602</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>1296</v>
+        <v>1321</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
@@ -7930,11 +7930,11 @@
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>70910</v>
+        <v>71073</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>1868039006.9845848</v>
+        <v>2019834901.3869331</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7994,7 +7994,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
@@ -8003,13 +8003,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="F6" s="10">
-        <v>8011855.9913176866</v>
+        <v>8665292.4728072863</v>
       </c>
       <c r="G6" s="10">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="H6" s="10">
         <v>1</v>
@@ -8018,10 +8018,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="K6" s="10">
-        <v>8539462.2923211604</v>
+        <v>9238403.0792054478</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -8029,34 +8029,34 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C7" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="10">
         <v>2</v>
       </c>
       <c r="E7" s="10">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F7" s="10">
-        <v>9589962.4832898322</v>
+        <v>10292285.555236744</v>
       </c>
       <c r="G7" s="10">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="H7" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="10">
         <v>3</v>
       </c>
       <c r="J7" s="10">
-        <v>634</v>
+        <v>548</v>
       </c>
       <c r="K7" s="10">
-        <v>8996481.4656081535</v>
+        <v>9762882.7996665835</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8064,7 +8064,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="C8" s="10">
         <v>6</v>
@@ -8073,13 +8073,13 @@
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>724</v>
+        <v>740</v>
       </c>
       <c r="F8" s="10">
-        <v>11693170.217475448</v>
+        <v>12900162.010313369</v>
       </c>
       <c r="G8" s="10">
-        <v>767</v>
+        <v>584</v>
       </c>
       <c r="H8" s="10">
         <v>4</v>
@@ -8088,10 +8088,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>350</v>
+        <v>587</v>
       </c>
       <c r="K8" s="10">
-        <v>11439196.74842638</v>
+        <v>12259231.902439144</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8099,34 +8099,34 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="C9" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="10">
         <v>4</v>
       </c>
       <c r="E9" s="10">
-        <v>2035</v>
+        <v>1021</v>
       </c>
       <c r="F9" s="10">
-        <v>20529286.348929532</v>
+        <v>22209543.394173563</v>
       </c>
       <c r="G9" s="10">
-        <v>1228</v>
+        <v>1125</v>
       </c>
       <c r="H9" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="10">
         <v>2</v>
       </c>
       <c r="J9" s="10">
-        <v>1007</v>
+        <v>973</v>
       </c>
       <c r="K9" s="10">
-        <v>21858809.479129504</v>
+        <v>23767288.77103918</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8134,7 +8134,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -8143,13 +8143,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="F10" s="10">
-        <v>9136539.7726296578</v>
+        <v>9957490.6809830684</v>
       </c>
       <c r="G10" s="10">
-        <v>392</v>
+        <v>472</v>
       </c>
       <c r="H10" s="10">
         <v>3</v>
@@ -8158,10 +8158,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="K10" s="10">
-        <v>9958782.7049773205</v>
+        <v>10891954.273123616</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8169,7 +8169,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -8178,13 +8178,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F11" s="10">
-        <v>7743516.6435261397</v>
+        <v>8316802.9094818188</v>
       </c>
       <c r="G11" s="10">
-        <v>379</v>
+        <v>312</v>
       </c>
       <c r="H11" s="10">
         <v>1</v>
@@ -8193,10 +8193,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K11" s="10">
-        <v>6081677.9457779359</v>
+        <v>6679003.8727309201</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8204,7 +8204,7 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C12" s="10">
         <v>1</v>
@@ -8213,25 +8213,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="10">
-        <v>496</v>
+        <v>455</v>
       </c>
       <c r="F12" s="10">
-        <v>9125846.8320685625</v>
+        <v>9808730.1557455901</v>
       </c>
       <c r="G12" s="10">
-        <v>632</v>
+        <v>608</v>
       </c>
       <c r="H12" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="10">
         <v>0</v>
       </c>
       <c r="J12" s="10">
-        <v>505</v>
+        <v>461</v>
       </c>
       <c r="K12" s="10">
-        <v>9528640.5381818991</v>
+        <v>10260074.279205721</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8248,13 +8248,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="F13" s="10">
-        <v>4059495.7912112302</v>
+        <v>4368337.5354776643</v>
       </c>
       <c r="G13" s="10">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
@@ -8263,10 +8263,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="K13" s="10">
-        <v>4278470.8679645592</v>
+        <v>4562456.1766546061</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8274,7 +8274,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -8283,13 +8283,13 @@
         <v>1</v>
       </c>
       <c r="E14" s="10">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="F14" s="10">
-        <v>832225.483727457</v>
+        <v>1042028.0883094301</v>
       </c>
       <c r="G14" s="10">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="H14" s="10">
         <v>0</v>
@@ -8298,10 +8298,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>242</v>
+        <v>192</v>
       </c>
       <c r="K14" s="10">
-        <v>4260676.8748711916</v>
+        <v>4635399.7879167013</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8309,7 +8309,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C15" s="10">
         <v>1</v>
@@ -8318,13 +8318,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="10">
-        <v>360</v>
+        <v>279</v>
       </c>
       <c r="F15" s="10">
-        <v>8440011.6415319797</v>
+        <v>8948611.6469514072</v>
       </c>
       <c r="G15" s="10">
-        <v>359</v>
+        <v>438</v>
       </c>
       <c r="H15" s="10">
         <v>4</v>
@@ -8333,10 +8333,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="K15" s="10">
-        <v>7427057.5940592606</v>
+        <v>8006300.9612096557</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8344,7 +8344,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -8353,25 +8353,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="10">
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="F16" s="10">
-        <v>3926643.4736452131</v>
+        <v>4263391.5358173661</v>
       </c>
       <c r="G16" s="10">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
       </c>
       <c r="I16" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="10">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K16" s="10">
-        <v>3647125.4913574592</v>
+        <v>3915245.4085396952</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8388,13 +8388,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="10">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F17" s="10">
-        <v>4329889.7318454506</v>
+        <v>4667851.798819243</v>
       </c>
       <c r="G17" s="10">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="H17" s="10">
         <v>0</v>
@@ -8403,10 +8403,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="10">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="K17" s="10">
-        <v>4468512.0865646908</v>
+        <v>4870420.3489419278</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8414,7 +8414,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="C18" s="10">
         <v>3</v>
@@ -8423,25 +8423,25 @@
         <v>3</v>
       </c>
       <c r="E18" s="10">
-        <v>1327</v>
+        <v>1196</v>
       </c>
       <c r="F18" s="10">
-        <v>15542536.569016691</v>
+        <v>17549914.722498216</v>
       </c>
       <c r="G18" s="10">
-        <v>1404</v>
+        <v>1354</v>
       </c>
       <c r="H18" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I18" s="10">
         <v>5</v>
       </c>
       <c r="J18" s="10">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="K18" s="10">
-        <v>24968411.489844091</v>
+        <v>26970696.540104352</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8449,7 +8449,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
@@ -8458,13 +8458,13 @@
         <v>3</v>
       </c>
       <c r="E19" s="10">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="F19" s="10">
-        <v>29238120.41858248</v>
+        <v>31902479.662608825</v>
       </c>
       <c r="G19" s="10">
-        <v>1253</v>
+        <v>1104</v>
       </c>
       <c r="H19" s="10">
         <v>0</v>
@@ -8473,10 +8473,10 @@
         <v>2</v>
       </c>
       <c r="J19" s="10">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="K19" s="10">
-        <v>35824755.92923595</v>
+        <v>38515117.497534238</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8484,7 +8484,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C20" s="10">
         <v>2</v>
@@ -8493,13 +8493,13 @@
         <v>5</v>
       </c>
       <c r="E20" s="10">
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="F20" s="10">
-        <v>17096402.744824786</v>
+        <v>18358012.535915993</v>
       </c>
       <c r="G20" s="10">
-        <v>1018</v>
+        <v>1056</v>
       </c>
       <c r="H20" s="10">
         <v>4</v>
@@ -8508,10 +8508,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>907</v>
+        <v>939</v>
       </c>
       <c r="K20" s="10">
-        <v>17290212.931036513</v>
+        <v>18617387.113703057</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8519,7 +8519,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C21" s="10">
         <v>3</v>
@@ -8528,25 +8528,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="F21" s="10">
-        <v>12161015.921806771</v>
+        <v>13351489.596777396</v>
       </c>
       <c r="G21" s="10">
-        <v>906</v>
+        <v>761</v>
       </c>
       <c r="H21" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="10">
         <v>4</v>
       </c>
       <c r="J21" s="10">
-        <v>636</v>
+        <v>675</v>
       </c>
       <c r="K21" s="10">
-        <v>16203096.619572133</v>
+        <v>17444471.917847052</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8554,7 +8554,7 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2872</v>
+        <v>2849</v>
       </c>
       <c r="C22" s="10">
         <v>173</v>
@@ -8563,25 +8563,25 @@
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2091</v>
+        <v>2034</v>
       </c>
       <c r="F22" s="10">
-        <v>63455337.242055319</v>
+        <v>68183269.217183471</v>
       </c>
       <c r="G22" s="10">
-        <v>2799</v>
+        <v>2793</v>
       </c>
       <c r="H22" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I22" s="10">
         <v>12</v>
       </c>
       <c r="J22" s="10">
-        <v>2265</v>
+        <v>2171</v>
       </c>
       <c r="K22" s="10">
-        <v>58431495.578616232</v>
+        <v>63285344.748622917</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8589,7 +8589,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1367</v>
+        <v>1374</v>
       </c>
       <c r="C23" s="10">
         <v>3</v>
@@ -8598,13 +8598,13 @@
         <v>1</v>
       </c>
       <c r="E23" s="10">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="F23" s="10">
-        <v>13715739.655666236</v>
+        <v>15904666.583410226</v>
       </c>
       <c r="G23" s="10">
-        <v>1368</v>
+        <v>1304</v>
       </c>
       <c r="H23" s="10">
         <v>5</v>
@@ -8613,10 +8613,10 @@
         <v>2</v>
       </c>
       <c r="J23" s="10">
-        <v>1218</v>
+        <v>1163</v>
       </c>
       <c r="K23" s="10">
-        <v>30857225.122215234</v>
+        <v>33239044.280500673</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8624,7 +8624,7 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>2972</v>
+        <v>2974</v>
       </c>
       <c r="C24" s="10">
         <v>15</v>
@@ -8633,13 +8633,13 @@
         <v>10</v>
       </c>
       <c r="E24" s="10">
-        <v>2209</v>
+        <v>2177</v>
       </c>
       <c r="F24" s="10">
-        <v>62455214.851508647</v>
+        <v>67552670.420068413</v>
       </c>
       <c r="G24" s="10">
-        <v>2777</v>
+        <v>2498</v>
       </c>
       <c r="H24" s="10">
         <v>5</v>
@@ -8648,10 +8648,10 @@
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2092</v>
+        <v>2146</v>
       </c>
       <c r="K24" s="10">
-        <v>53170556.161955953</v>
+        <v>58198730.291162997</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8659,7 +8659,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C25" s="10">
         <v>4</v>
@@ -8668,13 +8668,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F25" s="10">
-        <v>9647857.3613462802</v>
+        <v>10254185.087530892</v>
       </c>
       <c r="G25" s="10">
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="H25" s="10">
         <v>2</v>
@@ -8683,10 +8683,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="K25" s="10">
-        <v>8653275.5065172911</v>
+        <v>9326802.7803758383</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8694,22 +8694,22 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1749</v>
+        <v>1728</v>
       </c>
       <c r="C26" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>1348</v>
+        <v>1306</v>
       </c>
       <c r="F26" s="10">
-        <v>25727162.271941304</v>
+        <v>27775459.775627609</v>
       </c>
       <c r="G26" s="10">
-        <v>1740</v>
+        <v>1859</v>
       </c>
       <c r="H26" s="10">
         <v>14</v>
@@ -8718,10 +8718,10 @@
         <v>1</v>
       </c>
       <c r="J26" s="10">
-        <v>1473</v>
+        <v>1492</v>
       </c>
       <c r="K26" s="10">
-        <v>23472141.842081539</v>
+        <v>25275052.162944004</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8729,7 +8729,7 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C27" s="10">
         <v>8</v>
@@ -8738,25 +8738,25 @@
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F27" s="10">
-        <v>10259830.90651048</v>
+        <v>11036402.959192213</v>
       </c>
       <c r="G27" s="10">
-        <v>833</v>
+        <v>885</v>
       </c>
       <c r="H27" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" s="10">
         <v>0</v>
       </c>
       <c r="J27" s="10">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="K27" s="10">
-        <v>9877911.5601799227</v>
+        <v>10793154.824868249</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8764,7 +8764,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C28" s="10">
         <v>5</v>
@@ -8773,13 +8773,13 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>807</v>
+        <v>872</v>
       </c>
       <c r="F28" s="10">
-        <v>13074169.534061378</v>
+        <v>14021428.057064189</v>
       </c>
       <c r="G28" s="10">
-        <v>874</v>
+        <v>888</v>
       </c>
       <c r="H28" s="10">
         <v>1</v>
@@ -8788,10 +8788,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="10">
-        <v>729</v>
+        <v>763</v>
       </c>
       <c r="K28" s="10">
-        <v>12367446.731246172</v>
+        <v>13439375.56318808</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8799,7 +8799,7 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -8808,13 +8808,13 @@
         <v>2</v>
       </c>
       <c r="E29" s="10">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="F29" s="10">
-        <v>2752351.900354438</v>
+        <v>2987521.6738292631</v>
       </c>
       <c r="G29" s="10">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="H29" s="10">
         <v>1</v>
@@ -8823,10 +8823,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="10">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K29" s="10">
-        <v>3125322.1816324871</v>
+        <v>3444507.7473005932</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8834,34 +8834,34 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="C30" s="10">
         <v>9</v>
       </c>
       <c r="D30" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1293</v>
+        <v>1500</v>
       </c>
       <c r="F30" s="10">
-        <v>24358751.544144496</v>
+        <v>26097918.150558844</v>
       </c>
       <c r="G30" s="10">
-        <v>1646</v>
+        <v>1827</v>
       </c>
       <c r="H30" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="10">
         <v>5</v>
       </c>
       <c r="J30" s="10">
-        <v>1545</v>
+        <v>1624</v>
       </c>
       <c r="K30" s="10">
-        <v>24602514.895429038</v>
+        <v>26699945.286994319</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8869,7 +8869,7 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
@@ -8878,13 +8878,13 @@
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>629</v>
+        <v>558</v>
       </c>
       <c r="F31" s="10">
-        <v>19811258.757022385</v>
+        <v>21408157.92547648</v>
       </c>
       <c r="G31" s="10">
-        <v>898</v>
+        <v>795</v>
       </c>
       <c r="H31" s="10">
         <v>3</v>
@@ -8893,10 +8893,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>630</v>
+        <v>669</v>
       </c>
       <c r="K31" s="10">
-        <v>22132677.989444103</v>
+        <v>23972515.811498009</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8904,7 +8904,7 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
@@ -8913,13 +8913,13 @@
         <v>2</v>
       </c>
       <c r="E32" s="10">
-        <v>824</v>
+        <v>608</v>
       </c>
       <c r="F32" s="10">
-        <v>19404275.471009124</v>
+        <v>20992871.884413186</v>
       </c>
       <c r="G32" s="10">
-        <v>1016</v>
+        <v>1052</v>
       </c>
       <c r="H32" s="10">
         <v>1</v>
@@ -8928,10 +8928,10 @@
         <v>2</v>
       </c>
       <c r="J32" s="10">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="K32" s="10">
-        <v>21393659.220353145</v>
+        <v>23572892.259057939</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8939,7 +8939,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C33" s="10">
         <v>2</v>
@@ -8948,13 +8948,13 @@
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>816</v>
+        <v>851</v>
       </c>
       <c r="F33" s="10">
-        <v>26404188.141816933</v>
+        <v>28355830.721760739</v>
       </c>
       <c r="G33" s="10">
-        <v>1149</v>
+        <v>1010</v>
       </c>
       <c r="H33" s="10">
         <v>2</v>
@@ -8963,10 +8963,10 @@
         <v>3</v>
       </c>
       <c r="J33" s="10">
-        <v>838</v>
+        <v>854</v>
       </c>
       <c r="K33" s="10">
-        <v>27596352.646259207</v>
+        <v>29858563.383784257</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8974,22 +8974,22 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1455</v>
+        <v>1448</v>
       </c>
       <c r="C34" s="10">
         <v>4</v>
       </c>
       <c r="D34" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="10">
-        <v>1207</v>
+        <v>1178</v>
       </c>
       <c r="F34" s="10">
-        <v>37505222.301559903</v>
+        <v>40601238.013903379</v>
       </c>
       <c r="G34" s="10">
-        <v>1447</v>
+        <v>1321</v>
       </c>
       <c r="H34" s="10">
         <v>3</v>
@@ -8998,10 +8998,10 @@
         <v>2</v>
       </c>
       <c r="J34" s="10">
-        <v>1113</v>
+        <v>1201</v>
       </c>
       <c r="K34" s="10">
-        <v>38482011.267993741</v>
+        <v>41739242.360557027</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -9009,7 +9009,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C35" s="10">
         <v>0</v>
@@ -9018,13 +9018,13 @@
         <v>5</v>
       </c>
       <c r="E35" s="10">
-        <v>581</v>
+        <v>493</v>
       </c>
       <c r="F35" s="10">
-        <v>15398605.461348807</v>
+        <v>16636175.449088316</v>
       </c>
       <c r="G35" s="10">
-        <v>685</v>
+        <v>807</v>
       </c>
       <c r="H35" s="10">
         <v>3</v>
@@ -9033,10 +9033,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>794</v>
+        <v>762</v>
       </c>
       <c r="K35" s="10">
-        <v>15371358.076542115</v>
+        <v>16939342.25355164</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9044,34 +9044,34 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1941</v>
+        <v>1925</v>
       </c>
       <c r="C36" s="10">
         <v>6</v>
       </c>
       <c r="D36" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E36" s="10">
-        <v>892</v>
+        <v>70</v>
       </c>
       <c r="F36" s="10">
-        <v>46536061.009953454</v>
+        <v>46539327.260969058</v>
       </c>
       <c r="G36" s="10">
-        <v>1857</v>
+        <v>1785</v>
       </c>
       <c r="H36" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="10">
         <v>6</v>
       </c>
       <c r="J36" s="10">
-        <v>1680</v>
+        <v>1613</v>
       </c>
       <c r="K36" s="10">
-        <v>29407824.984452795</v>
+        <v>32734730.545260098</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9082,19 +9082,19 @@
         <v>844</v>
       </c>
       <c r="C37" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="10">
         <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="F37" s="10">
-        <v>15552674.040534776</v>
+        <v>16874087.423591021</v>
       </c>
       <c r="G37" s="10">
-        <v>853</v>
+        <v>799</v>
       </c>
       <c r="H37" s="10">
         <v>2</v>
@@ -9103,10 +9103,10 @@
         <v>3</v>
       </c>
       <c r="J37" s="10">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="K37" s="10">
-        <v>16019371.822294367</v>
+        <v>17298861.003520712</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9123,13 +9123,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="F38" s="10">
-        <v>14986852.341861239</v>
+        <v>16191205.913323352</v>
       </c>
       <c r="G38" s="10">
-        <v>725</v>
+        <v>801</v>
       </c>
       <c r="H38" s="10">
         <v>1</v>
@@ -9138,10 +9138,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>598</v>
+        <v>633</v>
       </c>
       <c r="K38" s="10">
-        <v>14185152.208508916</v>
+        <v>15397482.675662059</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9149,7 +9149,7 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="C39" s="10">
         <v>12</v>
@@ -9158,13 +9158,13 @@
         <v>1</v>
       </c>
       <c r="E39" s="10">
-        <v>822</v>
+        <v>868</v>
       </c>
       <c r="F39" s="10">
-        <v>22114246.499472193</v>
+        <v>23979908.496460751</v>
       </c>
       <c r="G39" s="10">
-        <v>1197</v>
+        <v>1428</v>
       </c>
       <c r="H39" s="10">
         <v>5</v>
@@ -9173,10 +9173,10 @@
         <v>2</v>
       </c>
       <c r="J39" s="10">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="K39" s="10">
-        <v>25110758.092792481</v>
+        <v>27238703.996070687</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9184,7 +9184,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1331</v>
+        <v>1319</v>
       </c>
       <c r="C40" s="10">
         <v>120</v>
@@ -9193,13 +9193,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="F40" s="10">
-        <v>20741126.062683959</v>
+        <v>22374902.800021451</v>
       </c>
       <c r="G40" s="10">
-        <v>1433</v>
+        <v>1395</v>
       </c>
       <c r="H40" s="10">
         <v>318</v>
@@ -9208,10 +9208,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>837</v>
+        <v>905</v>
       </c>
       <c r="K40" s="10">
-        <v>22932356.491074044</v>
+        <v>24757046.481234096</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9219,7 +9219,7 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>2397</v>
+        <v>2372</v>
       </c>
       <c r="C41" s="10">
         <v>69</v>
@@ -9228,25 +9228,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="10">
-        <v>1529</v>
+        <v>1405</v>
       </c>
       <c r="F41" s="10">
-        <v>38453663.605802923</v>
+        <v>41518349.605261825</v>
       </c>
       <c r="G41" s="10">
-        <v>2266</v>
+        <v>2354</v>
       </c>
       <c r="H41" s="10">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I41" s="10">
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="K41" s="10">
-        <v>38312378.880640082</v>
+        <v>41478113.936420672</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9254,7 +9254,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C42" s="10">
         <v>1</v>
@@ -9263,13 +9263,13 @@
         <v>6</v>
       </c>
       <c r="E42" s="10">
-        <v>570</v>
+        <v>668</v>
       </c>
       <c r="F42" s="10">
-        <v>13607803.394892052</v>
+        <v>14781644.391173327</v>
       </c>
       <c r="G42" s="10">
-        <v>592</v>
+        <v>538</v>
       </c>
       <c r="H42" s="10">
         <v>4</v>
@@ -9278,10 +9278,10 @@
         <v>7</v>
       </c>
       <c r="J42" s="10">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="K42" s="10">
-        <v>14083966.5119655</v>
+        <v>15234974.245374314</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9289,7 +9289,7 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="C43" s="10">
         <v>2</v>
@@ -9298,13 +9298,13 @@
         <v>6</v>
       </c>
       <c r="E43" s="10">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="F43" s="10">
-        <v>45449281.559613265</v>
+        <v>48800547.351421833</v>
       </c>
       <c r="G43" s="10">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="H43" s="10">
         <v>4</v>
@@ -9313,10 +9313,10 @@
         <v>5</v>
       </c>
       <c r="J43" s="10">
-        <v>1817</v>
+        <v>1857</v>
       </c>
       <c r="K43" s="10">
-        <v>43927118.587503135</v>
+        <v>47432872.324979059</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9324,22 +9324,22 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="C44" s="10">
         <v>3</v>
       </c>
       <c r="D44" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" s="10">
-        <v>1422</v>
+        <v>2049</v>
       </c>
       <c r="F44" s="10">
-        <v>29655636.505533084</v>
+        <v>32614535.508652512</v>
       </c>
       <c r="G44" s="10">
-        <v>930</v>
+        <v>989</v>
       </c>
       <c r="H44" s="10">
         <v>5</v>
@@ -9348,10 +9348,10 @@
         <v>4</v>
       </c>
       <c r="J44" s="10">
-        <v>846</v>
+        <v>875</v>
       </c>
       <c r="K44" s="10">
-        <v>33967834.959300019</v>
+        <v>36694418.119907491</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9359,22 +9359,22 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="C45" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" s="10">
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>908</v>
+        <v>969</v>
       </c>
       <c r="F45" s="10">
-        <v>16068125.974080767</v>
+        <v>17773873.790777944</v>
       </c>
       <c r="G45" s="10">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="H45" s="10">
         <v>6</v>
@@ -9383,10 +9383,10 @@
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>970</v>
+        <v>934</v>
       </c>
       <c r="K45" s="10">
-        <v>24052081.674599729</v>
+        <v>26012267.611628871</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9394,7 +9394,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C46" s="10">
         <v>3</v>
@@ -9403,13 +9403,13 @@
         <v>4</v>
       </c>
       <c r="E46" s="10">
-        <v>627</v>
+        <v>590</v>
       </c>
       <c r="F46" s="10">
-        <v>23518097.944919869</v>
+        <v>25294917.477437437</v>
       </c>
       <c r="G46" s="10">
-        <v>837</v>
+        <v>725</v>
       </c>
       <c r="H46" s="10">
         <v>2</v>
@@ -9418,10 +9418,10 @@
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>597</v>
+        <v>636</v>
       </c>
       <c r="K46" s="10">
-        <v>24303801.668385867</v>
+        <v>26258702.513062768</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9429,7 +9429,7 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="C47" s="10">
         <v>2</v>
@@ -9438,13 +9438,13 @@
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>553</v>
+        <v>587</v>
       </c>
       <c r="F47" s="10">
-        <v>15130453.175075745</v>
+        <v>16227351.047975589</v>
       </c>
       <c r="G47" s="10">
-        <v>717</v>
+        <v>700</v>
       </c>
       <c r="H47" s="10">
         <v>0</v>
@@ -9453,10 +9453,10 @@
         <v>9</v>
       </c>
       <c r="J47" s="10">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="K47" s="10">
-        <v>14609642.865583366</v>
+        <v>15777654.210746672</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9464,7 +9464,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C48" s="10">
         <v>0</v>
@@ -9473,13 +9473,13 @@
         <v>2</v>
       </c>
       <c r="E48" s="10">
-        <v>719</v>
+        <v>676</v>
       </c>
       <c r="F48" s="10">
-        <v>13321177.692165183</v>
+        <v>14358233.121239796</v>
       </c>
       <c r="G48" s="10">
-        <v>704</v>
+        <v>789</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
@@ -9488,10 +9488,10 @@
         <v>1</v>
       </c>
       <c r="J48" s="10">
-        <v>778</v>
+        <v>803</v>
       </c>
       <c r="K48" s="10">
-        <v>13640714.055751091</v>
+        <v>14765811.497357111</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9499,7 +9499,7 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="C49" s="10">
         <v>0</v>
@@ -9508,13 +9508,13 @@
         <v>5</v>
       </c>
       <c r="E49" s="10">
-        <v>2756</v>
+        <v>1098</v>
       </c>
       <c r="F49" s="10">
-        <v>40575137.286203943</v>
+        <v>43788229.833009563</v>
       </c>
       <c r="G49" s="10">
-        <v>1286</v>
+        <v>1159</v>
       </c>
       <c r="H49" s="10">
         <v>3</v>
@@ -9523,10 +9523,10 @@
         <v>6</v>
       </c>
       <c r="J49" s="10">
-        <v>1136</v>
+        <v>1123</v>
       </c>
       <c r="K49" s="10">
-        <v>45745588.58812362</v>
+        <v>49134791.486482561</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9534,7 +9534,7 @@
         <v>201</v>
       </c>
       <c r="B50" s="10">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C50" s="10">
         <v>0</v>
@@ -9543,13 +9543,13 @@
         <v>1</v>
       </c>
       <c r="E50" s="10">
-        <v>797</v>
+        <v>467</v>
       </c>
       <c r="F50" s="10">
-        <v>6645353.4058702402</v>
+        <v>7200859.8401143793</v>
       </c>
       <c r="G50" s="10">
-        <v>449</v>
+        <v>488</v>
       </c>
       <c r="H50" s="10">
         <v>1</v>
@@ -9558,10 +9558,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="K50" s="10">
-        <v>6951924.3284576992</v>
+        <v>7518789.3938841689</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9569,7 +9569,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C51" s="10">
         <v>2</v>
@@ -9578,13 +9578,13 @@
         <v>7</v>
       </c>
       <c r="E51" s="10">
-        <v>1570</v>
+        <v>910</v>
       </c>
       <c r="F51" s="10">
-        <v>19563741.756338328</v>
+        <v>21077266.831570905</v>
       </c>
       <c r="G51" s="10">
-        <v>877</v>
+        <v>908</v>
       </c>
       <c r="H51" s="10">
         <v>1</v>
@@ -9593,10 +9593,10 @@
         <v>5</v>
       </c>
       <c r="J51" s="10">
-        <v>900</v>
+        <v>886</v>
       </c>
       <c r="K51" s="10">
-        <v>19453326.637208953</v>
+        <v>20804392.415884595</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9604,34 +9604,34 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="C52" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" s="10">
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>465</v>
+        <v>1025</v>
       </c>
       <c r="F52" s="10">
-        <v>34200115.304982483</v>
+        <v>36799819.563541561</v>
       </c>
       <c r="G52" s="10">
-        <v>1413</v>
+        <v>1443</v>
       </c>
       <c r="H52" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" s="10">
         <v>11</v>
       </c>
       <c r="J52" s="10">
-        <v>972</v>
+        <v>1044</v>
       </c>
       <c r="K52" s="10">
-        <v>35513529.941505633</v>
+        <v>38255043.889359169</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9639,7 +9639,7 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C53" s="10">
         <v>1</v>
@@ -9648,13 +9648,13 @@
         <v>6</v>
       </c>
       <c r="E53" s="10">
-        <v>233</v>
+        <v>365</v>
       </c>
       <c r="F53" s="10">
-        <v>17692903.869914349</v>
+        <v>18998431.435199615</v>
       </c>
       <c r="G53" s="10">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H53" s="10">
         <v>3</v>
@@ -9663,10 +9663,10 @@
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>506</v>
+        <v>400</v>
       </c>
       <c r="K53" s="10">
-        <v>16698819.456651105</v>
+        <v>18181613.774843927</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9674,7 +9674,7 @@
         <v>81</v>
       </c>
       <c r="B54" s="10">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C54" s="10">
         <v>0</v>
@@ -9683,13 +9683,13 @@
         <v>4</v>
       </c>
       <c r="E54" s="10">
-        <v>211</v>
+        <v>315</v>
       </c>
       <c r="F54" s="10">
-        <v>12885929.269668665</v>
+        <v>13867349.453376597</v>
       </c>
       <c r="G54" s="10">
-        <v>459</v>
+        <v>506</v>
       </c>
       <c r="H54" s="10">
         <v>2</v>
@@ -9698,10 +9698,10 @@
         <v>3</v>
       </c>
       <c r="J54" s="10">
-        <v>417</v>
+        <v>373</v>
       </c>
       <c r="K54" s="10">
-        <v>14295788.226282325</v>
+        <v>15464289.961397316</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9709,7 +9709,7 @@
         <v>87</v>
       </c>
       <c r="B55" s="10">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C55" s="10">
         <v>1</v>
@@ -9718,25 +9718,25 @@
         <v>4</v>
       </c>
       <c r="E55" s="10">
-        <v>220</v>
+        <v>327</v>
       </c>
       <c r="F55" s="10">
-        <v>11147708.240657611</v>
+        <v>11991960.514846284</v>
       </c>
       <c r="G55" s="10">
-        <v>396</v>
+        <v>116</v>
       </c>
       <c r="H55" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="10">
         <v>2</v>
       </c>
       <c r="J55" s="10">
-        <v>38</v>
+        <v>278</v>
       </c>
       <c r="K55" s="10">
-        <v>5589046.8414643016</v>
+        <v>5719922.5869477298</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9744,34 +9744,34 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="C56" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56" s="10">
         <v>0</v>
       </c>
       <c r="E56" s="10">
-        <v>661</v>
+        <v>974</v>
       </c>
       <c r="F56" s="10">
-        <v>26191668.071031023</v>
+        <v>28403417.987599976</v>
       </c>
       <c r="G56" s="10">
-        <v>1099</v>
+        <v>941</v>
       </c>
       <c r="H56" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56" s="10">
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="K56" s="10">
-        <v>28462888.360719599</v>
+        <v>30195865.25279944</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9788,13 +9788,13 @@
         <v>1</v>
       </c>
       <c r="E57" s="10">
-        <v>715</v>
+        <v>917</v>
       </c>
       <c r="F57" s="10">
-        <v>25274443.649353232</v>
+        <v>27544676.485392641</v>
       </c>
       <c r="G57" s="10">
-        <v>927</v>
+        <v>947</v>
       </c>
       <c r="H57" s="10">
         <v>5</v>
@@ -9803,10 +9803,10 @@
         <v>2</v>
       </c>
       <c r="J57" s="10">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="K57" s="10">
-        <v>28675298.836824629</v>
+        <v>30524186.608173389</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9814,34 +9814,34 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2065</v>
+        <v>2057</v>
       </c>
       <c r="C58" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D58" s="10">
         <v>8</v>
       </c>
       <c r="E58" s="10">
-        <v>1226</v>
+        <v>1517</v>
       </c>
       <c r="F58" s="10">
-        <v>49677371.10828805</v>
+        <v>53312926.280314647</v>
       </c>
       <c r="G58" s="10">
-        <v>2100</v>
+        <v>2123</v>
       </c>
       <c r="H58" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I58" s="10">
         <v>9</v>
       </c>
       <c r="J58" s="10">
-        <v>1642</v>
+        <v>1850</v>
       </c>
       <c r="K58" s="10">
-        <v>52582289.558401659</v>
+        <v>56661351.157900929</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9849,7 +9849,7 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C59" s="10">
         <v>4</v>
@@ -9858,13 +9858,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>453</v>
+        <v>567</v>
       </c>
       <c r="F59" s="10">
-        <v>11997117.736853795</v>
+        <v>13156051.392773269</v>
       </c>
       <c r="G59" s="10">
-        <v>657</v>
+        <v>560</v>
       </c>
       <c r="H59" s="10">
         <v>2</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>675</v>
+        <v>507</v>
       </c>
       <c r="K59" s="10">
-        <v>13982560.869168984</v>
+        <v>14826348.495922143</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9884,22 +9884,22 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C60" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D60" s="10">
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>510</v>
+        <v>738</v>
       </c>
       <c r="F60" s="10">
-        <v>21280371.70766744</v>
+        <v>22949848.91231928</v>
       </c>
       <c r="G60" s="10">
-        <v>911</v>
+        <v>1050</v>
       </c>
       <c r="H60" s="10">
         <v>6</v>
@@ -9908,10 +9908,10 @@
         <v>6</v>
       </c>
       <c r="J60" s="10">
-        <v>827</v>
+        <v>865</v>
       </c>
       <c r="K60" s="10">
-        <v>24407846.306572575</v>
+        <v>26561103.572443023</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9919,7 +9919,7 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C61" s="10">
         <v>3</v>
@@ -9928,13 +9928,13 @@
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>516</v>
+        <v>625</v>
       </c>
       <c r="F61" s="10">
-        <v>13008470.054326516</v>
+        <v>14245013.316192299</v>
       </c>
       <c r="G61" s="10">
-        <v>673</v>
+        <v>411</v>
       </c>
       <c r="H61" s="10">
         <v>0</v>
@@ -9943,10 +9943,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="10">
-        <v>57</v>
+        <v>526</v>
       </c>
       <c r="K61" s="10">
-        <v>12702688.915399697</v>
+        <v>13109236.528265854</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9954,7 +9954,7 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="C62" s="10">
         <v>5</v>
@@ -9963,25 +9963,25 @@
         <v>0</v>
       </c>
       <c r="E62" s="10">
-        <v>807</v>
+        <v>963</v>
       </c>
       <c r="F62" s="10">
-        <v>27692985.716273904</v>
+        <v>29939617.972537749</v>
       </c>
       <c r="G62" s="10">
-        <v>1105</v>
+        <v>1292</v>
       </c>
       <c r="H62" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I62" s="10">
         <v>1</v>
       </c>
       <c r="J62" s="10">
-        <v>1279</v>
+        <v>1190</v>
       </c>
       <c r="K62" s="10">
-        <v>30502819.256533097</v>
+        <v>32682821.514900204</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9989,7 +9989,7 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="C63" s="10">
         <v>4</v>
@@ -9998,13 +9998,13 @@
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1441</v>
+        <v>1471</v>
       </c>
       <c r="F63" s="10">
-        <v>33951195.810102426</v>
+        <v>37000002.653800093</v>
       </c>
       <c r="G63" s="10">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="H63" s="10">
         <v>7</v>
@@ -10013,10 +10013,10 @@
         <v>5</v>
       </c>
       <c r="J63" s="10">
-        <v>1494</v>
+        <v>1513</v>
       </c>
       <c r="K63" s="10">
-        <v>41763405.554746158</v>
+        <v>44797837.205057278</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -10024,7 +10024,7 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C64" s="10">
         <v>1</v>
@@ -10033,13 +10033,13 @@
         <v>4</v>
       </c>
       <c r="E64" s="10">
-        <v>648</v>
+        <v>705</v>
       </c>
       <c r="F64" s="10">
-        <v>18629448.795252305</v>
+        <v>19983891.374101069</v>
       </c>
       <c r="G64" s="10">
-        <v>805</v>
+        <v>873</v>
       </c>
       <c r="H64" s="10">
         <v>4</v>
@@ -10048,10 +10048,10 @@
         <v>5</v>
       </c>
       <c r="J64" s="10">
-        <v>790</v>
+        <v>763</v>
       </c>
       <c r="K64" s="10">
-        <v>16761125.185675364</v>
+        <v>18318451.973164391</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10059,7 +10059,7 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C65" s="10">
         <v>7</v>
@@ -10068,13 +10068,13 @@
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="F65" s="10">
-        <v>20847380.402954869</v>
+        <v>22367781.080104113</v>
       </c>
       <c r="G65" s="10">
-        <v>643</v>
+        <v>585</v>
       </c>
       <c r="H65" s="10">
         <v>3</v>
@@ -10083,10 +10083,10 @@
         <v>7</v>
       </c>
       <c r="J65" s="10">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="K65" s="10">
-        <v>22020764.973671433</v>
+        <v>23871295.559602365</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10094,34 +10094,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>1983</v>
+        <v>1996</v>
       </c>
       <c r="C66" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D66" s="10">
         <v>10</v>
       </c>
       <c r="E66" s="10">
-        <v>1641</v>
+        <v>1619</v>
       </c>
       <c r="F66" s="10">
-        <v>67327568.067904234</v>
+        <v>72623824.220833898</v>
       </c>
       <c r="G66" s="10">
-        <v>1971</v>
+        <v>2063</v>
       </c>
       <c r="H66" s="10">
         <v>13</v>
       </c>
       <c r="I66" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J66" s="10">
-        <v>1829</v>
+        <v>1674</v>
       </c>
       <c r="K66" s="10">
-        <v>70670658.044179976</v>
+        <v>76429257.720611393</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10129,22 +10129,22 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="C67" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D67" s="10">
         <v>6</v>
       </c>
       <c r="E67" s="10">
-        <v>1265</v>
+        <v>1229</v>
       </c>
       <c r="F67" s="10">
-        <v>49430448.945431069</v>
+        <v>53751877.713151284</v>
       </c>
       <c r="G67" s="10">
-        <v>1603</v>
+        <v>1594</v>
       </c>
       <c r="H67" s="10">
         <v>12</v>
@@ -10153,10 +10153,10 @@
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1201</v>
+        <v>1243</v>
       </c>
       <c r="K67" s="10">
-        <v>50220349.921165459</v>
+        <v>54327698.607676938</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10164,34 +10164,34 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C68" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D68" s="10">
         <v>1</v>
       </c>
       <c r="E68" s="10">
+        <v>764</v>
+      </c>
+      <c r="F68" s="10">
+        <v>35023411.856107965</v>
+      </c>
+      <c r="G68" s="10">
+        <v>913</v>
+      </c>
+      <c r="H68" s="10">
+        <v>2</v>
+      </c>
+      <c r="I68" s="10">
+        <v>1</v>
+      </c>
+      <c r="J68" s="10">
         <v>734</v>
       </c>
-      <c r="F68" s="10">
-        <v>32493119.305810899</v>
-      </c>
-      <c r="G68" s="10">
-        <v>892</v>
-      </c>
-      <c r="H68" s="10">
-        <v>1</v>
-      </c>
-      <c r="I68" s="10">
-        <v>1</v>
-      </c>
-      <c r="J68" s="10">
-        <v>699</v>
-      </c>
       <c r="K68" s="10">
-        <v>34013930.676028676</v>
+        <v>36681052.563683063</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10199,22 +10199,22 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>2317</v>
+        <v>2297</v>
       </c>
       <c r="C69" s="10">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D69" s="10">
         <v>12</v>
       </c>
       <c r="E69" s="10">
-        <v>1308</v>
+        <v>1327</v>
       </c>
       <c r="F69" s="10">
-        <v>49546807.447998308</v>
+        <v>52986952.666871026</v>
       </c>
       <c r="G69" s="10">
-        <v>2329</v>
+        <v>2015</v>
       </c>
       <c r="H69" s="10">
         <v>372</v>
@@ -10223,10 +10223,10 @@
         <v>13</v>
       </c>
       <c r="J69" s="10">
-        <v>1302</v>
+        <v>1272</v>
       </c>
       <c r="K69" s="10">
-        <v>45338783.339071438</v>
+        <v>49029776.551765636</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10234,7 +10234,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C70" s="10">
         <v>0</v>
@@ -10243,13 +10243,13 @@
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>250</v>
+        <v>286</v>
       </c>
       <c r="F70" s="10">
-        <v>1348505.727031731</v>
+        <v>1604743.4340360931</v>
       </c>
       <c r="G70" s="10">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="H70" s="10">
         <v>2</v>
@@ -10258,10 +10258,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="10">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="K70" s="10">
-        <v>3682667.934082624</v>
+        <v>4030673.95379342</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10269,7 +10269,7 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="C71" s="10">
         <v>7</v>
@@ -10278,25 +10278,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="10">
-        <v>1480</v>
+        <v>1518</v>
       </c>
       <c r="F71" s="10">
-        <v>35127326.366053008</v>
+        <v>37741415.05560144</v>
       </c>
       <c r="G71" s="10">
-        <v>1608</v>
+        <v>1690</v>
       </c>
       <c r="H71" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I71" s="10">
         <v>8</v>
       </c>
       <c r="J71" s="10">
-        <v>1576</v>
+        <v>1479</v>
       </c>
       <c r="K71" s="10">
-        <v>34445460.314459853</v>
+        <v>37080322.484695628</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10313,13 +10313,13 @@
         <v>3</v>
       </c>
       <c r="E72" s="10">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="F72" s="10">
-        <v>16812574.105930068</v>
+        <v>18215056.68860703</v>
       </c>
       <c r="G72" s="10">
-        <v>794</v>
+        <v>652</v>
       </c>
       <c r="H72" s="10">
         <v>2</v>
@@ -10331,7 +10331,7 @@
         <v>598</v>
       </c>
       <c r="K72" s="10">
-        <v>15667692.503356764</v>
+        <v>16713241.139799256</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10339,22 +10339,22 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="C73" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D73" s="10">
         <v>4</v>
       </c>
       <c r="E73" s="10">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="F73" s="10">
-        <v>23873577.731227577</v>
+        <v>25802788.754436146</v>
       </c>
       <c r="G73" s="10">
-        <v>1464</v>
+        <v>1399</v>
       </c>
       <c r="H73" s="10">
         <v>1</v>
@@ -10363,10 +10363,10 @@
         <v>5</v>
       </c>
       <c r="J73" s="10">
-        <v>959</v>
+        <v>924</v>
       </c>
       <c r="K73" s="10">
-        <v>25445366.118607964</v>
+        <v>27816969.776097447</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10374,7 +10374,7 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C74" s="10">
         <v>2</v>
@@ -10383,25 +10383,25 @@
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>982</v>
+        <v>1214</v>
       </c>
       <c r="F74" s="10">
-        <v>14656833.663769012</v>
+        <v>15960149.230632352</v>
       </c>
       <c r="G74" s="10">
-        <v>1320</v>
+        <v>1396</v>
       </c>
       <c r="H74" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I74" s="10">
         <v>4</v>
       </c>
       <c r="J74" s="10">
-        <v>1241</v>
+        <v>1312</v>
       </c>
       <c r="K74" s="10">
-        <v>20167933.173738983</v>
+        <v>21612087.804990321</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10409,22 +10409,22 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="C75" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D75" s="10">
         <v>4</v>
       </c>
       <c r="E75" s="10">
-        <v>1213</v>
+        <v>1228</v>
       </c>
       <c r="F75" s="10">
-        <v>43203204.558727421</v>
+        <v>46580676.905710757</v>
       </c>
       <c r="G75" s="10">
-        <v>1778</v>
+        <v>1605</v>
       </c>
       <c r="H75" s="10">
         <v>9</v>
@@ -10433,10 +10433,10 @@
         <v>7</v>
       </c>
       <c r="J75" s="10">
-        <v>1271</v>
+        <v>1317</v>
       </c>
       <c r="K75" s="10">
-        <v>45274446.644820362</v>
+        <v>49256726.466358557</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10444,7 +10444,7 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C76" s="10">
         <v>2</v>
@@ -10453,25 +10453,25 @@
         <v>1</v>
       </c>
       <c r="E76" s="10">
-        <v>629</v>
+        <v>440</v>
       </c>
       <c r="F76" s="10">
-        <v>8716800.0374078844</v>
+        <v>9383646.5454543922</v>
       </c>
       <c r="G76" s="10">
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="H76" s="10">
         <v>4</v>
       </c>
       <c r="I76" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" s="10">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="K76" s="10">
-        <v>8336159.5331871547</v>
+        <v>8960062.0347378012</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10479,7 +10479,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C77" s="10">
         <v>3</v>
@@ -10488,13 +10488,13 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>669</v>
+        <v>774</v>
       </c>
       <c r="F77" s="10">
-        <v>13419610.797755742</v>
+        <v>14552442.544222549</v>
       </c>
       <c r="G77" s="10">
-        <v>896</v>
+        <v>782</v>
       </c>
       <c r="H77" s="10">
         <v>1</v>
@@ -10503,10 +10503,10 @@
         <v>0</v>
       </c>
       <c r="J77" s="10">
-        <v>897</v>
+        <v>747</v>
       </c>
       <c r="K77" s="10">
-        <v>16320737.705918368</v>
+        <v>17409108.331550773</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10514,7 +10514,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C78" s="10">
         <v>0</v>
@@ -10523,13 +10523,13 @@
         <v>3</v>
       </c>
       <c r="E78" s="10">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F78" s="10">
-        <v>13406864.351865375</v>
+        <v>14615906.519403487</v>
       </c>
       <c r="G78" s="10">
-        <v>635</v>
+        <v>589</v>
       </c>
       <c r="H78" s="10">
         <v>2</v>
@@ -10538,10 +10538,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="K78" s="10">
-        <v>14939900.890034296</v>
+        <v>16261279.578989357</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10549,7 +10549,7 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="C79" s="10">
         <v>5</v>
@@ -10558,25 +10558,25 @@
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="F79" s="10">
-        <v>11044050.643039128</v>
+        <v>11825950.763445076</v>
       </c>
       <c r="G79" s="10">
-        <v>605</v>
+        <v>800</v>
       </c>
       <c r="H79" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I79" s="10">
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>1030</v>
+        <v>790</v>
       </c>
       <c r="K79" s="10">
-        <v>9544700.5587438848</v>
+        <v>10410105.269862575</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10584,7 +10584,7 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C80" s="10">
         <v>0</v>
@@ -10593,25 +10593,25 @@
         <v>7</v>
       </c>
       <c r="E80" s="10">
-        <v>251</v>
+        <v>459</v>
       </c>
       <c r="F80" s="10">
-        <v>11871515.03801666</v>
+        <v>12707889.856647348</v>
       </c>
       <c r="G80" s="10">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="H80" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I80" s="10">
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K80" s="10">
-        <v>10204824.002210468</v>
+        <v>11224853.807416515</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10619,34 +10619,34 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C81" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D81" s="10">
         <v>3</v>
       </c>
       <c r="E81" s="10">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="F81" s="10">
-        <v>31261131.096501935</v>
+        <v>33856213.568945937</v>
       </c>
       <c r="G81" s="10">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="H81" s="10">
         <v>5</v>
       </c>
       <c r="I81" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>530</v>
+        <v>749</v>
       </c>
       <c r="K81" s="10">
-        <v>23598904.180730466</v>
+        <v>25767122.084004831</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10654,7 +10654,7 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C82" s="10">
         <v>2</v>
@@ -10663,13 +10663,13 @@
         <v>10</v>
       </c>
       <c r="E82" s="10">
-        <v>2118</v>
+        <v>709</v>
       </c>
       <c r="F82" s="10">
-        <v>18891602.264381222</v>
+        <v>20147404.699376933</v>
       </c>
       <c r="G82" s="10">
-        <v>776</v>
+        <v>789</v>
       </c>
       <c r="H82" s="10">
         <v>3</v>
@@ -10678,10 +10678,10 @@
         <v>9</v>
       </c>
       <c r="J82" s="10">
-        <v>692</v>
+        <v>741</v>
       </c>
       <c r="K82" s="10">
-        <v>19211296.435092594</v>
+        <v>20795729.777784407</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10689,22 +10689,22 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C83" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" s="10">
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="F83" s="10">
-        <v>15118369.682815623</v>
+        <v>16295988.162141008</v>
       </c>
       <c r="G83" s="10">
-        <v>952</v>
+        <v>1100</v>
       </c>
       <c r="H83" s="10">
         <v>2</v>
@@ -10713,10 +10713,10 @@
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>952</v>
+        <v>974</v>
       </c>
       <c r="K83" s="10">
-        <v>15852572.06871303</v>
+        <v>17212098.434398443</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10724,7 +10724,7 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C84" s="10">
         <v>2</v>
@@ -10733,25 +10733,25 @@
         <v>5</v>
       </c>
       <c r="E84" s="10">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="F84" s="10">
-        <v>14524187.856017128</v>
+        <v>16008993.220043994</v>
       </c>
       <c r="G84" s="10">
-        <v>968</v>
+        <v>941</v>
       </c>
       <c r="H84" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" s="10">
         <v>4</v>
       </c>
       <c r="J84" s="10">
-        <v>849</v>
+        <v>860</v>
       </c>
       <c r="K84" s="10">
-        <v>18906157.439068951</v>
+        <v>20575678.3225642</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10768,13 +10768,13 @@
         <v>6</v>
       </c>
       <c r="E85" s="10">
-        <v>408</v>
+        <v>733</v>
       </c>
       <c r="F85" s="10">
-        <v>19671552.708550803</v>
+        <v>21222145.549389083</v>
       </c>
       <c r="G85" s="10">
-        <v>765</v>
+        <v>844</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
@@ -10783,10 +10783,10 @@
         <v>7</v>
       </c>
       <c r="J85" s="10">
-        <v>759</v>
+        <v>784</v>
       </c>
       <c r="K85" s="10">
-        <v>22132214.210737165</v>
+        <v>24021340.943134073</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10794,7 +10794,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C86" s="10">
         <v>1</v>
@@ -10803,13 +10803,13 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>540</v>
+        <v>493</v>
       </c>
       <c r="F86" s="10">
-        <v>9375082.9609405603</v>
+        <v>10050763.988478778</v>
       </c>
       <c r="G86" s="10">
-        <v>546</v>
+        <v>593</v>
       </c>
       <c r="H86" s="10">
         <v>4</v>
@@ -10818,10 +10818,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="K86" s="10">
-        <v>8934225.0752158221</v>
+        <v>9531836.5712453369</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10829,7 +10829,7 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1762</v>
+        <v>1767</v>
       </c>
       <c r="C87" s="10">
         <v>0</v>
@@ -10838,13 +10838,13 @@
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1316</v>
+        <v>1348</v>
       </c>
       <c r="F87" s="10">
-        <v>38701029.284727588</v>
+        <v>42084775.50188525</v>
       </c>
       <c r="G87" s="10">
-        <v>1783</v>
+        <v>1661</v>
       </c>
       <c r="H87" s="10">
         <v>2</v>
@@ -10853,10 +10853,10 @@
         <v>9</v>
       </c>
       <c r="J87" s="10">
-        <v>1372</v>
+        <v>1448</v>
       </c>
       <c r="K87" s="10">
-        <v>46989513.872192614</v>
+        <v>51153393.19780989</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10864,7 +10864,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C88" s="10">
         <v>0</v>
@@ -10873,13 +10873,13 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>734</v>
+        <v>900</v>
       </c>
       <c r="F88" s="10">
-        <v>8622190.9655356202</v>
+        <v>9931053.6177717447</v>
       </c>
       <c r="G88" s="10">
-        <v>628</v>
+        <v>925</v>
       </c>
       <c r="H88" s="10">
         <v>2</v>
@@ -10888,10 +10888,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>899</v>
+        <v>763</v>
       </c>
       <c r="K88" s="10">
-        <v>9986112.4448090214</v>
+        <v>11320774.287268532</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10899,7 +10899,7 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C89" s="10">
         <v>4</v>
@@ -10908,13 +10908,13 @@
         <v>7</v>
       </c>
       <c r="E89" s="10">
-        <v>408</v>
+        <v>543</v>
       </c>
       <c r="F89" s="10">
-        <v>17495104.84190416</v>
+        <v>18693370.236158248</v>
       </c>
       <c r="G89" s="10">
-        <v>665</v>
+        <v>766</v>
       </c>
       <c r="H89" s="10">
         <v>5</v>
@@ -10923,10 +10923,10 @@
         <v>8</v>
       </c>
       <c r="J89" s="10">
-        <v>979</v>
+        <v>522</v>
       </c>
       <c r="K89" s="10">
-        <v>19009001.995999392</v>
+        <v>20146519.231406134</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10934,7 +10934,7 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C90" s="10">
         <v>2</v>
@@ -10943,13 +10943,13 @@
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="F90" s="10">
-        <v>4317447.3459969955</v>
+        <v>4601412.716901565</v>
       </c>
       <c r="G90" s="10">
-        <v>379</v>
+        <v>100</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -10958,7 +10958,7 @@
         <v>1</v>
       </c>
       <c r="J90" s="10">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K90" s="10">
         <v>4177363.4227665081</v>
@@ -10969,34 +10969,34 @@
         <v>203</v>
       </c>
       <c r="B91" s="13">
-        <v>84798</v>
+        <v>84698</v>
       </c>
       <c r="C91" s="13">
-        <v>1001</v>
+        <v>1022</v>
       </c>
       <c r="D91" s="13">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E91" s="13">
-        <v>71269</v>
+        <v>69168</v>
       </c>
       <c r="F91" s="13">
-        <v>1792079533.2534416</v>
+        <v>1934635103.3523769</v>
       </c>
       <c r="G91" s="13">
-        <v>84642</v>
+        <v>83602</v>
       </c>
       <c r="H91" s="13">
-        <v>1296</v>
+        <v>1321</v>
       </c>
       <c r="I91" s="13">
         <v>315</v>
       </c>
       <c r="J91" s="13">
-        <v>70910</v>
+        <v>71073</v>
       </c>
       <c r="K91" s="13">
-        <v>1868039006.9845848</v>
+        <v>2019834901.3869331</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1163,27 +1163,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8665292.4728072863</v>
+        <v>10031059.186713256</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9238403.0792054478</v>
+        <v>10451748.424652403</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>6.6138633888775278E-2</v>
+        <v>4.1938665709038592E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>372</v>
+        <v>430</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>-9.1397849462365621E-2</v>
+        <v>-0.22790697674418603</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1211,15 +1211,15 @@
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>1.6627078384798155E-2</v>
+        <v>4.3478260869565188E-2</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1243,31 +1243,31 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10292285.555236744</v>
+        <v>11847668.973308677</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9762882.7996665835</v>
+        <v>11365040.339451777</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-5.1436850710073645E-2</v>
+        <v>-4.0736168012813545E-2</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>491</v>
+        <v>544</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>548</v>
+        <v>592</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>0.11608961303462317</v>
+        <v>8.8235294117646967E-2</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="N3" s="12">
         <f t="shared" ref="N3:N66" si="2">IFERROR(M3/L3-1,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1291,15 +1291,15 @@
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>617</v>
+        <v>555</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-5.3680981595092048E-2</v>
+        <v>-0.13145539906103287</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1323,27 +1323,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12900162.010313369</v>
+        <v>15693282.493840273</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12259231.902439144</v>
+        <v>13027212.983451417</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>-4.9683880509548417E-2</v>
+        <v>-0.16988603317599793</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>740</v>
+        <v>803</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>587</v>
+        <v>307</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>-0.20675675675675675</v>
+        <v>-0.61768368617683689</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1371,15 +1371,15 @@
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>584</v>
+        <v>767</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>-0.20544217687074828</v>
+        <v>1.4550264550264647E-2</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22209543.394173563</v>
+        <v>25636221.356210988</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23767288.77103918</v>
+        <v>27343918.425037589</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>7.0138559321947902E-2</v>
+        <v>6.6612666706939327E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1021</v>
+        <v>1123</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>973</v>
+        <v>955</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-4.7012732615083208E-2</v>
+        <v>-0.1495992876224399</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1443,23 +1443,23 @@
       </c>
       <c r="P5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1125</v>
+        <v>1222</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>-7.1015689512799351E-2</v>
+        <v>1.3266998341625147E-2</v>
       </c>
       <c r="U5">
         <v>1</v>
@@ -1483,27 +1483,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9957490.6809830684</v>
+        <v>11567766.085140552</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10891954.273123616</v>
+        <v>12437976.728047604</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>9.3845289147515665E-2</v>
+        <v>7.5227199141317813E-2</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>3.9164490861618884E-2</v>
+        <v>-2.1220159151193685E-2</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1523,23 +1523,23 @@
       </c>
       <c r="P6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>472</v>
+        <v>392</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>0.16256157635467972</v>
+        <v>-4.6228710462287159E-2</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1563,27 +1563,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8316802.9094818188</v>
+        <v>9574246.6887910403</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6679003.8727309201</v>
+        <v>7884637.3578127623</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>-0.19692651786706128</v>
+        <v>-0.17647438862802356</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>3.66300366300365E-3</v>
+        <v>-1.4285714285714235E-2</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1603,23 +1603,23 @@
       </c>
       <c r="P7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>-0.1875</v>
+        <v>-1.8372703412073532E-2</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -1643,19 +1643,19 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9808730.1557455901</v>
+        <v>11358396.529773155</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10260074.279205721</v>
+        <v>11563533.990490887</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>4.6014531574787965E-2</v>
+        <v>1.8060424301970412E-2</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>455</v>
+        <v>516</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>1.318681318681314E-2</v>
+        <v>-0.10658914728682167</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="O8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1687,19 +1687,19 @@
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>608</v>
+        <v>635</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>1.6722408026755842E-2</v>
+        <v>6.7226890756302504E-2</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1723,27 +1723,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4368337.5354776643</v>
+        <v>5043289.1807349501</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4562456.1766546061</v>
+        <v>5164313.8401981639</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>4.4437646953880749E-2</v>
+        <v>2.3997168341153285E-2</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>-8.0000000000000071E-3</v>
+        <v>-3.1746031746031744E-2</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1775,11 +1775,11 @@
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>-0.13690476190476186</v>
+        <v>4.7619047619047672E-2</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1803,27 +1803,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1042028.0883094301</v>
+        <v>1745372.714907849</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4635399.7879167013</v>
+        <v>5210121.033227575</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>3.4484403442877447</v>
+        <v>1.9851051232359018</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>7.2625698324022325E-2</v>
+        <v>-0.32203389830508478</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1851,15 +1851,15 @@
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>0.27368421052631575</v>
+        <v>0.12365591397849451</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1883,27 +1883,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8948611.6469514072</v>
+        <v>10047490.355405016</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8006300.9612096557</v>
+        <v>9232093.1963549405</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>-0.10530244499578612</v>
+        <v>-8.1154311196868667E-2</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>279</v>
+        <v>375</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>0.23655913978494625</v>
+        <v>2.666666666666595E-3</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1923,23 +1923,23 @@
       </c>
       <c r="P11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>0.18699186991869921</v>
+        <v>-5.0531914893616969E-2</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4263391.5358173661</v>
+        <v>4958031.3880373193</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3915245.4085396952</v>
+        <v>4506119.9493312472</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>-8.1659431078014988E-2</v>
+        <v>-9.1147353321812119E-2</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>-0.30769230769230771</v>
+        <v>-0.24913494809688586</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1991,11 +1991,11 @@
       </c>
       <c r="M12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="P12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="12">
         <f t="shared" si="3"/>
@@ -2011,15 +2011,15 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>6.6350710900473953E-2</v>
+        <v>8.7155963302752326E-2</v>
       </c>
       <c r="U12">
         <v>2</v>
@@ -2043,27 +2043,27 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4667851.798819243</v>
+        <v>5380823.6863983767</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4870420.3489419278</v>
+        <v>5726064.83562293</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>4.3396525608187853E-2</v>
+        <v>6.4161394118386061E-2</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>-7.999999999999996E-2</v>
+        <v>-7.5999999999999956E-2</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2091,15 +2091,15 @@
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>6.9672131147541005E-2</v>
+        <v>-5.600000000000005E-2</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2123,27 +2123,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17549914.722498216</v>
+        <v>21396343.684887961</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26970696.540104352</v>
+        <v>30850756.8154644</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>0.53679929313440544</v>
+        <v>0.44187050226034663</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1196</v>
+        <v>1023</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1265</v>
+        <v>1239</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>5.7692307692307709E-2</v>
+        <v>0.21114369501466279</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2163,23 +2163,23 @@
       </c>
       <c r="P14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>1.6666666666666665</v>
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1425</v>
+        <v>1435</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1354</v>
+        <v>1397</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>-4.9824561403508771E-2</v>
+        <v>-2.6480836236933758E-2</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2203,27 +2203,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31902479.662608825</v>
+        <v>37588029.534986168</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38515117.497534238</v>
+        <v>43478586.493676245</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>0.207276609995797</v>
+        <v>0.15671364079373373</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>912</v>
+        <v>888</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>903</v>
+        <v>934</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>-9.8684210526315264E-3</v>
+        <v>5.1801801801801828E-2</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2251,15 +2251,15 @@
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1229</v>
+        <v>1241</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1104</v>
+        <v>1252</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>-0.1017087062652563</v>
+        <v>8.8638195004029363E-3</v>
       </c>
       <c r="U15">
         <v>3</v>
@@ -2283,27 +2283,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18358012.535915993</v>
+        <v>21212507.702614099</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18617387.113703057</v>
+        <v>21010450.610085927</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>1.4128685078497405E-2</v>
+        <v>-9.5253750928878667E-3</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>874</v>
+        <v>1135</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>939</v>
+        <v>964</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>7.4370709382151068E-2</v>
+        <v>-0.15066079295154189</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2319,15 +2319,15 @@
       </c>
       <c r="O16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -2335,11 +2335,11 @@
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1056</v>
+        <v>1015</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>2.7237354085603016E-2</v>
+        <v>-1.2645914396887115E-2</v>
       </c>
       <c r="U16">
         <v>3</v>
@@ -2363,27 +2363,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13351489.596777396</v>
+        <v>16152779.022945462</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17444471.917847052</v>
+        <v>20384337.964686051</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>0.30655623040425128</v>
+        <v>0.26197095470256504</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>675</v>
+        <v>767</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>-1.171303074670571E-2</v>
+        <v>0.16388467374810323</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="O17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2407,19 +2407,19 @@
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.75</v>
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>761</v>
+        <v>915</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>-0.16004415011037532</v>
+        <v>1.094091903719896E-3</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2443,27 +2443,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>68183269.217183471</v>
+        <v>77653874.701062784</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>63285344.748622917</v>
+        <v>73261977.766638085</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>-7.1834696763501404E-2</v>
+        <v>-5.6557344386636177E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2171</v>
+        <v>2196</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>6.735496558505405E-2</v>
+        <v>8.1773399014778425E-2</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2479,27 +2479,27 @@
       </c>
       <c r="O18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>-0.39306358381502893</v>
+        <v>-0.33522727272727271</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2849</v>
+        <v>2824</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2793</v>
+        <v>2756</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>-1.9656019656019708E-2</v>
+        <v>-2.4079320113314484E-2</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2523,27 +2523,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15904666.583410226</v>
+        <v>20823267.672696736</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33239044.280500673</v>
+        <v>38461930.24138011</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>1.0898925548789258</v>
+        <v>0.84706506423153827</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>2.1071115013169495E-2</v>
+        <v>6.1900610287707103E-2</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="O19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2567,19 +2567,19 @@
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <v>0</v>
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1304</v>
+        <v>1363</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>-5.0946142649199389E-2</v>
+        <v>-1.0167029774872938E-2</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2603,27 +2603,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>67552670.420068413</v>
+        <v>78189279.719223753</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>58198730.291162997</v>
+        <v>68713287.365769863</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>-0.13846884321136421</v>
+        <v>-0.12119298690922853</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2177</v>
+        <v>2154</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2146</v>
+        <v>2185</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4239779513091411E-2</v>
+        <v>1.4391829155060432E-2</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="O20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2647,19 +2647,19 @@
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.6875</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2974</v>
+        <v>2957</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2498</v>
+        <v>2776</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-0.16005379959650301</v>
+        <v>-6.1210686506594558E-2</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2683,27 +2683,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10254185.087530892</v>
+        <v>11618026.828046735</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9326802.7803758383</v>
+        <v>10481400.58186681</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>-9.0439396133267791E-2</v>
+        <v>-9.783298515338501E-2</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>483</v>
+        <v>398</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>4.094827586206895E-2</v>
+        <v>-0.12141280353200878</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2731,15 +2731,15 @@
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-7.0370370370370416E-2</v>
+        <v>-3.1894934333958735E-2</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2763,27 +2763,27 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27775459.775627609</v>
+        <v>31902604.980764087</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25275052.162944004</v>
+        <v>29385357.135773905</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>-9.0022186234975043E-2</v>
+        <v>-7.890414737316831E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1306</v>
+        <v>1279</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1492</v>
+        <v>1573</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>0.14241960183767222</v>
+        <v>0.22986708365910857</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2799,27 +2799,27 @@
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>-6.6666666666666652E-2</v>
+        <v>-5.8823529411764719E-2</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1728</v>
+        <v>1714</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1859</v>
+        <v>1744</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>7.5810185185185119E-2</v>
+        <v>1.7502917152858899E-2</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2843,27 +2843,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11036402.959192213</v>
+        <v>12991656.7694692</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10793154.824868249</v>
+        <v>12337413.658601355</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>-2.2040526720833675E-2</v>
+        <v>-5.0358712709016151E-2</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>758</v>
+        <v>894</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>807</v>
+        <v>843</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>6.4643799472295482E-2</v>
+        <v>-5.7046979865771785E-2</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2879,27 +2879,27 @@
       </c>
       <c r="O23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="3"/>
-        <v>-0.375</v>
+        <v>-0.4</v>
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>885</v>
+        <v>839</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>1.1428571428571344E-2</v>
+        <v>-4.6590909090909127E-2</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2923,27 +2923,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14021428.057064189</v>
+        <v>16148057.481919851</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13439375.56318808</v>
+        <v>15970386.192980677</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>-4.1511641432476099E-2</v>
+        <v>-1.1002641595628693E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>-0.125</v>
+        <v>-0.10103329506314584</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2963,23 +2963,23 @@
       </c>
       <c r="P24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="3"/>
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>1.1273957158963732E-3</v>
+        <v>-7.9185520361990669E-3</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -3003,27 +3003,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2987521.6738292631</v>
+        <v>3545079.2402608488</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3444507.7473005932</v>
+        <v>4033521.2907017982</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>0.15296493996161953</v>
+        <v>0.13778029131021885</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>224</v>
+        <v>166</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>0.24444444444444446</v>
+        <v>-6.7415730337078705E-2</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3051,15 +3051,15 @@
       </c>
       <c r="R25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="S25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="4"/>
-        <v>1.304347826086949E-2</v>
+        <v>-2.2321428571428603E-2</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -3083,27 +3083,27 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26097918.150558844</v>
+        <v>30369760.083999842</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26699945.286994319</v>
+        <v>30813505.786671042</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>2.3068013814833144E-2</v>
+        <v>1.4611432604137775E-2</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1500</v>
+        <v>1456</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1624</v>
+        <v>1431</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>8.2666666666666666E-2</v>
+        <v>-1.717032967032972E-2</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3111,15 +3111,15 @@
       </c>
       <c r="M26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="O26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3127,19 +3127,19 @@
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.7</v>
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1660</v>
+        <v>1647</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1827</v>
+        <v>1651</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>0.10060240963855427</v>
+        <v>2.4286581663630624E-3</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -3163,27 +3163,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21408157.92547648</v>
+        <v>25130828.725072499</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23972515.811498009</v>
+        <v>27992379.158031393</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>0.11978414466804033</v>
+        <v>0.1138661388473825</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>558</v>
+        <v>683</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>0.19892473118279574</v>
+        <v>-4.3923865300146137E-3</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="O27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -3215,11 +3215,11 @@
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>795</v>
+        <v>895</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>-9.1428571428571415E-2</v>
+        <v>2.2857142857142909E-2</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -3243,27 +3243,27 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20992871.884413186</v>
+        <v>24348017.987532649</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23572892.259057939</v>
+        <v>27339018.879904401</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>0.1228998294683239</v>
+        <v>0.12284371129934635</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>608</v>
+        <v>813</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>881</v>
+        <v>915</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>0.44901315789473695</v>
+        <v>0.1254612546125462</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3271,11 +3271,11 @@
       </c>
       <c r="M28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3291,15 +3291,15 @@
       </c>
       <c r="R28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1061</v>
+        <v>1052</v>
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1052</v>
+        <v>1013</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-8.4825636192271681E-3</v>
+        <v>-3.7072243346007561E-2</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -3323,27 +3323,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28355830.721760739</v>
+        <v>33287094.194697849</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29858563.383784257</v>
+        <v>33866219.070671238</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>5.2995543553950419E-2</v>
+        <v>1.7397880168994684E-2</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>851</v>
+        <v>865</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>854</v>
+        <v>804</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>3.5252643948295859E-3</v>
+        <v>-7.0520231213872853E-2</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="O29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3367,19 +3367,19 @@
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1010</v>
+        <v>1140</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>-9.4982078853046548E-2</v>
+        <v>1.4234875444839812E-2</v>
       </c>
       <c r="U29">
         <v>0</v>
@@ -3403,27 +3403,27 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>40601238.013903379</v>
+        <v>46940123.260832466</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>41739242.360557027</v>
+        <v>48286581.885638237</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>2.8028809029516655E-2</v>
+        <v>2.8684599256885157E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1178</v>
+        <v>1108</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>1.9524617996604432E-2</v>
+        <v>9.566787003610111E-2</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3443,23 +3443,23 @@
       </c>
       <c r="P30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="3"/>
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1448</v>
+        <v>1453</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1321</v>
+        <v>1453</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>-8.7707182320441945E-2</v>
+        <v>0</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3483,27 +3483,27 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16636175.449088316</v>
+        <v>19339477.823665723</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16939342.25355164</v>
+        <v>19612777.992599472</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>1.8223347390817324E-2</v>
+        <v>1.4131724311569061E-2</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>493</v>
+        <v>566</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>762</v>
+        <v>577</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>0.54563894523326573</v>
+        <v>1.9434628975264934E-2</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3519,27 +3519,27 @@
       </c>
       <c r="O31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>807</v>
+        <v>679</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>0.17982456140350878</v>
+        <v>-8.7591240875912746E-3</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3563,39 +3563,39 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46539327.260969058</v>
+        <v>46678468.479174599</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32734730.545260098</v>
+        <v>39716345.829926766</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-0.29662218016817798</v>
+        <v>-0.14915062289059366</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>70</v>
+        <v>985</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1613</v>
+        <v>1632</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>22.042857142857144</v>
+        <v>0.65685279187817258</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="2"/>
-        <v>-0.4</v>
+        <v>-0.22222222222222221</v>
       </c>
       <c r="O32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3611,15 +3611,15 @@
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1925</v>
+        <v>1906</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1785</v>
+        <v>1856</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-7.2727272727272751E-2</v>
+        <v>-2.6232948583420734E-2</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3643,27 +3643,27 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16874087.423591021</v>
+        <v>19600077.597591951</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17298861.003520712</v>
+        <v>19603837.280351806</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>2.5173129027163288E-2</v>
+        <v>1.9181978954607715E-4</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>783</v>
+        <v>673</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>-0.1315453384418902</v>
+        <v>3.7147102526003062E-2</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3671,11 +3671,11 @@
       </c>
       <c r="M33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3691,15 +3691,15 @@
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>799</v>
+        <v>847</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>-5.331753554502372E-2</v>
+        <v>-9.3567251461987855E-3</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3723,27 +3723,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16191205.913323352</v>
+        <v>18503531.759908363</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15397482.675662059</v>
+        <v>17848929.749518771</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>-4.9021872855570137E-2</v>
+        <v>-3.5377138747529235E-2</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>562</v>
+        <v>458</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>0.12633451957295372</v>
+        <v>0.27074235807860259</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3767,19 +3767,19 @@
       </c>
       <c r="Q34" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>801</v>
+        <v>731</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>7.5167785234899309E-2</v>
+        <v>-2.0107238605898137E-2</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3803,27 +3803,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23979908.496460751</v>
+        <v>27886563.921537865</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27238703.996070687</v>
+        <v>31244315.963416766</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>0.13589691137023774</v>
+        <v>0.12040752139009792</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>868</v>
+        <v>837</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>910</v>
+        <v>896</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>4.8387096774193505E-2</v>
+        <v>7.0489844683393033E-2</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3839,27 +3839,27 @@
       </c>
       <c r="O35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="3"/>
-        <v>-0.58333333333333326</v>
+        <v>-0.6</v>
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1428</v>
+        <v>1195</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>0.2310344827586206</v>
+        <v>3.1951640759930955E-2</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3883,27 +3883,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22374902.800021451</v>
+        <v>25980146.357264768</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24757046.481234096</v>
+        <v>28569315.557240028</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>0.10646498456343512</v>
+        <v>9.9659530949919306E-2</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>826</v>
+        <v>806</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>9.5641646489104115E-2</v>
+        <v>0.14888337468982638</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3931,15 +3931,15 @@
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1395</v>
+        <v>1368</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>5.7619408642911374E-2</v>
+        <v>4.0304182509505626E-2</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3963,27 +3963,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>41518349.605261825</v>
+        <v>47828167.354593977</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>41478113.936420672</v>
+        <v>47327626.983007781</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>-9.6910568998276325E-4</v>
+        <v>-1.0465388896781946E-2</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1405</v>
+        <v>1627</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1464</v>
+        <v>1348</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>4.1992882562277511E-2</v>
+        <v>-0.17148125384142598</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="O37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4007,19 +4007,19 @@
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="3"/>
-        <v>2.4492753623188408</v>
+        <v>2.4</v>
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2372</v>
+        <v>2319</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2354</v>
+        <v>2231</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>-7.5885328836424737E-3</v>
+        <v>-3.794739111686074E-2</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4043,27 +4043,27 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14781644.391173327</v>
+        <v>17239734.609239098</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15234974.245374314</v>
+        <v>17601943.18951926</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>3.0668431887840963E-2</v>
+        <v>2.1010101865840181E-2</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>668</v>
+        <v>485</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>-0.33832335329341312</v>
+        <v>-5.97938144329897E-2</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4091,15 +4091,15 @@
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>538</v>
+        <v>586</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>-0.13085621970920835</v>
+        <v>-6.0897435897435903E-2</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4123,27 +4123,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>48800547.351421833</v>
+        <v>55863457.338151634</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>47432872.324979059</v>
+        <v>53820568.949218951</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>-2.8025813247418929E-2</v>
+        <v>-3.6569315367767308E-2</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1916</v>
+        <v>1813</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1857</v>
+        <v>1899</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0793319415448828E-2</v>
+        <v>4.7435190292333118E-2</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="O39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -4175,11 +4175,11 @@
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2027</v>
+        <v>2037</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>-1.6019417475728104E-2</v>
+        <v>-1.1165048543689271E-2</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4203,31 +4203,31 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32614535.508652512</v>
+        <v>38794693.14317365</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>36694418.119907491</v>
+        <v>42105567.733273089</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>0.12509399712813951</v>
+        <v>8.5343492159623446E-2</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2049</v>
+        <v>1214</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>-0.57296242069302106</v>
+        <v>-0.27594728171334426</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="N40" s="12">
         <f t="shared" si="2"/>
-        <v>0.33333333333333326</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4243,23 +4243,23 @@
       </c>
       <c r="P40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <v>1</v>
       </c>
       <c r="R40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>989</v>
+        <v>934</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>9.1611479028697484E-2</v>
+        <v>3.4330011074197087E-2</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17773873.790777944</v>
+        <v>21326951.017018501</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26012267.611628871</v>
+        <v>29772505.600011189</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>0.46351143919596494</v>
+        <v>0.39600384397438226</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>969</v>
+        <v>936</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>934</v>
+        <v>981</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>-3.6119711042311708E-2</v>
+        <v>4.8076923076923128E-2</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -4335,11 +4335,11 @@
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-2.4816176470588203E-2</v>
+        <v>-2.0220588235294157E-2</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4363,27 +4363,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25294917.477437437</v>
+        <v>28987672.484540347</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26258702.513062768</v>
+        <v>30625362.113111999</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>3.8101924486806826E-2</v>
+        <v>5.6496071888664456E-2</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>590</v>
+        <v>564</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>7.7966101694915357E-2</v>
+        <v>0.15780141843971629</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4391,15 +4391,15 @@
       </c>
       <c r="M42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4407,19 +4407,19 @@
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="3"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.6</v>
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>725</v>
+        <v>832</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>-0.13173652694610782</v>
+        <v>-1.2004801920768582E-3</v>
       </c>
       <c r="U42">
         <v>1</v>
@@ -4443,27 +4443,27 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16227351.047975589</v>
+        <v>18797706.720624097</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15777654.210746672</v>
+        <v>18111709.274998784</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>-2.7712276384445289E-2</v>
+        <v>-3.6493677437400618E-2</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>587</v>
+        <v>1046</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>-4.4293015332197649E-2</v>
+        <v>-0.44837476099426388</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4491,15 +4491,15 @@
       </c>
       <c r="R43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>-1.4265335235378318E-3</v>
+        <v>3.463203463203457E-2</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4523,27 +4523,27 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14358233.121239796</v>
+        <v>16326037.684438676</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14765811.497357111</v>
+        <v>16974532.487811487</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>2.8386387982125338E-2</v>
+        <v>3.9721505971466176E-2</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>676</v>
+        <v>475</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>0.18786982248520712</v>
+        <v>0.68421052631578938</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4551,11 +4551,11 @@
       </c>
       <c r="M44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4571,15 +4571,15 @@
       </c>
       <c r="R44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>789</v>
+        <v>705</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>0.15350877192982448</v>
+        <v>2.7696793002915499E-2</v>
       </c>
       <c r="U44">
         <v>2</v>
@@ -4603,27 +4603,27 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>43788229.833009563</v>
+        <v>50350879.089841045</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>49134791.486482561</v>
+        <v>55925546.402918451</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>0.12210042913044439</v>
+        <v>0.11071638497374647</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1098</v>
+        <v>1074</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1123</v>
+        <v>1140</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>2.2768670309653904E-2</v>
+        <v>6.1452513966480549E-2</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4639,27 +4639,27 @@
       </c>
       <c r="O45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1159</v>
+        <v>1287</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>-6.2297734627831725E-2</v>
+        <v>4.0420371867421201E-2</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4683,27 +4683,27 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21077266.831570905</v>
+        <v>24329645.084981102</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20804392.415884595</v>
+        <v>24008510.265390374</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>-1.2946385215258593E-2</v>
+        <v>-1.3199321998698998E-2</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>886</v>
+        <v>916</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>-2.6373626373626391E-2</v>
+        <v>-5.4288816503800241E-3</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4723,23 +4723,23 @@
       </c>
       <c r="P46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>-2.19780219780219E-3</v>
+        <v>-3.066812705366917E-2</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4763,27 +4763,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36799819.563541561</v>
+        <v>42604532.316107005</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38255043.889359169</v>
+        <v>43979107.294347867</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>3.9544333180897784E-2</v>
+        <v>3.2263585668353745E-2</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1025</v>
+        <v>956</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1044</v>
+        <v>1138</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>1.8536585365853675E-2</v>
+        <v>0.19037656903765687</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4811,15 +4811,15 @@
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1443</v>
+        <v>1419</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>7.1269487750556859E-2</v>
+        <v>5.2670623145400608E-2</v>
       </c>
       <c r="U47">
         <v>5</v>
@@ -4843,27 +4843,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18998431.435199615</v>
+        <v>22005709.005341128</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18181613.774843927</v>
+        <v>21167858.625659622</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>-4.2993952587176087E-2</v>
+        <v>-3.807422789595849E-2</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>9.5890410958904049E-2</v>
+        <v>6.8965517241379226E-2</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4883,23 +4883,23 @@
       </c>
       <c r="P48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>1.8595041322314154E-2</v>
+        <v>2.2587268993839782E-2</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4923,27 +4923,27 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13867349.453376597</v>
+        <v>16006981.240799496</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15464289.961397316</v>
+        <v>17965408.831571799</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>0.11515830861476384</v>
+        <v>0.12234834047162813</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>373</v>
+        <v>460</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>0.18412698412698414</v>
+        <v>0.52317880794701987</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4971,15 +4971,15 @@
       </c>
       <c r="R49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>506</v>
+        <v>461</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>0.10239651416121998</v>
+        <v>6.5502183406114245E-3</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -5003,27 +5003,27 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11991960.514846284</v>
+        <v>13856935.277226221</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5719922.5869477298</v>
+        <v>5873087.196715177</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-0.52302022843834806</v>
+        <v>-0.57616261610404162</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>278</v>
+        <v>10</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-0.14984709480122327</v>
+        <v>-0.9668874172185431</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5031,11 +5031,11 @@
       </c>
       <c r="M50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N50" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>-0.75</v>
       </c>
       <c r="O50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5051,15 +5051,15 @@
       </c>
       <c r="R50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="S50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>116</v>
+        <v>385</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="4"/>
-        <v>-0.72705882352941176</v>
+        <v>-8.7677725118483374E-2</v>
       </c>
       <c r="U50">
         <v>4</v>
@@ -5083,27 +5083,27 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28403417.987599976</v>
+        <v>32922233.232268192</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30195865.25279944</v>
+        <v>34613136.454139821</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>6.3106745321354962E-2</v>
+        <v>5.1360526181265298E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>974</v>
+        <v>872</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>905</v>
+        <v>940</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>-7.0841889117043144E-2</v>
+        <v>7.7981651376146877E-2</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5131,15 +5131,15 @@
       </c>
       <c r="R51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>941</v>
+        <v>1103</v>
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-0.14918625678119346</v>
+        <v>-9.0579710144922387E-4</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5163,27 +5163,27 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27544676.485392641</v>
+        <v>32767497.85062144</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30524186.608173389</v>
+        <v>35690534.982378751</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>0.10817008957650409</v>
+        <v>8.9205381048094834E-2</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>917</v>
+        <v>1002</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>800</v>
+        <v>963</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>-0.1275899672846238</v>
+        <v>-3.8922155688622784E-2</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="O52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5207,19 +5207,19 @@
       </c>
       <c r="Q52" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="R52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>-5.1102204408817631E-2</v>
+        <v>-6.0878243512974106E-2</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5243,27 +5243,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>53312926.280314647</v>
+        <v>61113798.319160461</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>56661351.157900929</v>
+        <v>64882425.838394135</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>6.280699843750015E-2</v>
+        <v>6.1665738718323704E-2</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1517</v>
+        <v>1601</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1850</v>
+        <v>1658</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>0.21951219512195119</v>
+        <v>3.5602748282323571E-2</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5279,27 +5279,27 @@
       </c>
       <c r="O53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q53" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2057</v>
+        <v>2048</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2123</v>
+        <v>2073</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>3.2085561497326109E-2</v>
+        <v>1.220703125E-2</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5323,27 +5323,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13156051.392773269</v>
+        <v>15237386.793200787</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14826348.495922143</v>
+        <v>16923572.104882669</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>0.12696036624380946</v>
+        <v>0.1106610558993153</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>567</v>
+        <v>447</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10582010582010581</v>
+        <v>0.14093959731543615</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5371,15 +5371,15 @@
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>560</v>
+        <v>662</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>-0.17525773195876293</v>
+        <v>-2.0710059171597628E-2</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5403,27 +5403,27 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22949848.91231928</v>
+        <v>26569100.705542248</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26561103.572443023</v>
+        <v>30353544.458011288</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>0.15735418014822988</v>
+        <v>0.14243778118088946</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>738</v>
+        <v>715</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>865</v>
+        <v>738</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>0.17208672086720878</v>
+        <v>3.2167832167832255E-2</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5443,23 +5443,23 @@
       </c>
       <c r="P55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q55" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1050</v>
+        <v>922</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>0.20551090700344421</v>
+        <v>6.2211981566820285E-2</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5483,27 +5483,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14245013.316192299</v>
+        <v>16880304.095586132</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13109236.528265854</v>
+        <v>15435179.114867197</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>-7.9731535711195733E-2</v>
+        <v>-8.5610127195327457E-2</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>625</v>
+        <v>740</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>526</v>
+        <v>613</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>-0.15839999999999999</v>
+        <v>-0.17162162162162165</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="O56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5531,15 +5531,15 @@
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>411</v>
+        <v>678</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-0.44832214765100675</v>
+        <v>-9.9601593625498031E-2</v>
       </c>
       <c r="U56">
         <v>2</v>
@@ -5563,27 +5563,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29939617.972537749</v>
+        <v>34340368.090365291</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32682821.514900204</v>
+        <v>37729757.422791846</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>9.1624533916186524E-2</v>
+        <v>9.8699854454312064E-2</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>963</v>
+        <v>869</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1190</v>
+        <v>1163</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>0.2357217030114227</v>
+        <v>0.33831990794016109</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5611,15 +5611,15 @@
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1292</v>
+        <v>1099</v>
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>0.16291629162916288</v>
+        <v>-1.1690647482014427E-2</v>
       </c>
       <c r="U57">
         <v>2</v>
@@ -5643,27 +5643,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37000002.653800093</v>
+        <v>43422115.586745128</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>44797837.205057278</v>
+        <v>51933160.195166431</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>0.21075227005304842</v>
+        <v>0.19600713814642767</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1471</v>
+        <v>1339</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1513</v>
+        <v>1618</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>2.8552005438477135E-2</v>
+        <v>0.20836445108289769</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5679,27 +5679,27 @@
       </c>
       <c r="O58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q58" s="12">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1441</v>
+        <v>1478</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1601</v>
+        <v>1621</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>0.11103400416377518</v>
+        <v>9.6752368064952687E-2</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5723,27 +5723,27 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19983891.374101069</v>
+        <v>23207604.557711422</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18318451.973164391</v>
+        <v>21502821.729210172</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>-8.3339093961202759E-2</v>
+        <v>-7.3457940230836294E-2</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>8.2269503546099187E-2</v>
+        <v>9.6681096681096701E-2</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="O59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5767,19 +5767,19 @@
       </c>
       <c r="Q59" s="12">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>873</v>
+        <v>798</v>
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>0.13082901554404147</v>
+        <v>3.771131339401812E-2</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5803,27 +5803,27 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22367781.080104113</v>
+        <v>25855386.35664548</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23871295.559602365</v>
+        <v>27515605.348086242</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>6.7217864575561892E-2</v>
+        <v>6.421172627397409E-2</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>2.1008403361344463E-2</v>
+        <v>-2.1367521367521292E-3</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5843,23 +5843,23 @@
       </c>
       <c r="P60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q60" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="R60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>585</v>
+        <v>644</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>-9.4427244582043324E-2</v>
+        <v>9.4043887147334804E-3</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5883,31 +5883,31 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>72623824.220833898</v>
+        <v>83988262.907164082</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>76429257.720611393</v>
+        <v>87322079.567863107</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>5.239924419576103E-2</v>
+        <v>3.9693839892653182E-2</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1619</v>
+        <v>1969</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1674</v>
+        <v>1637</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>3.3971587399629355E-2</v>
+        <v>-0.16861350939563235</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="N61" s="12">
         <f t="shared" si="2"/>
-        <v>0.19999999999999996</v>
+        <v>9.0909090909090828E-2</v>
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5923,23 +5923,23 @@
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
-        <v>0.18181818181818188</v>
+        <v>0.63636363636363646</v>
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1996</v>
+        <v>1983</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2063</v>
+        <v>1957</v>
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>3.356713426853708E-2</v>
+        <v>-1.3111447302067591E-2</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5963,27 +5963,27 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>53751877.713151284</v>
+        <v>62144411.904331289</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>54327698.607676938</v>
+        <v>63302163.709051661</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>1.0712572639760554E-2</v>
+        <v>1.8630022704256621E-2</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1229</v>
+        <v>1096</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1243</v>
+        <v>1318</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>1.1391375101708734E-2</v>
+        <v>0.20255474452554734</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5991,35 +5991,35 @@
       </c>
       <c r="M62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N62" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="O62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q62" s="12">
         <f t="shared" si="3"/>
-        <v>-0.1428571428571429</v>
+        <v>-0.1875</v>
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>7.5853350189634128E-3</v>
+        <v>8.8439671509792372E-3</v>
       </c>
       <c r="U62">
         <v>9</v>
@@ -6043,27 +6043,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35023411.856107965</v>
+        <v>40291786.850265786</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>36681052.563683063</v>
+        <v>42230040.117961869</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>4.7329503886869517E-2</v>
+        <v>4.8105418478934903E-2</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>764</v>
+        <v>720</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>-3.9267015706806241E-2</v>
+        <v>3.1944444444444553E-2</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6087,19 +6087,19 @@
       </c>
       <c r="Q63" s="12">
         <f t="shared" si="3"/>
-        <v>-0.6</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>913</v>
+        <v>896</v>
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>3.1638418079096065E-2</v>
+        <v>3.3594624860022737E-3</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6123,27 +6123,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>52986952.666871026</v>
+        <v>60482844.879700385</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>49029776.551765636</v>
+        <v>56679542.814377584</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>-7.4682085229248019E-2</v>
+        <v>-6.2882327590369158E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1327</v>
+        <v>1405</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1272</v>
+        <v>1337</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>-4.1446872645064081E-2</v>
+        <v>-4.8398576512455493E-2</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6159,27 +6159,27 @@
       </c>
       <c r="O64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>372</v>
+        <v>462</v>
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>2.6954177897573484E-3</v>
+        <v>0.23860589812332433</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2297</v>
+        <v>2275</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2015</v>
+        <v>2369</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>-0.12276882890727037</v>
+        <v>4.1318681318681216E-2</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6203,27 +6203,27 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1604743.4340360931</v>
+        <v>2049584.514477622</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4030673.95379342</v>
+        <v>4609199.2052098904</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>1.5117248454202206</v>
+        <v>1.2488456429349233</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>286</v>
+        <v>246</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>-3.8461538461538436E-2</v>
+        <v>-2.4390243902439046E-2</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6251,15 +6251,15 @@
       </c>
       <c r="R65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>0.16393442622950816</v>
+        <v>0</v>
       </c>
       <c r="U65">
         <v>2</v>
@@ -6283,27 +6283,27 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37741415.05560144</v>
+        <v>43221691.643919691</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>37080322.484695628</v>
+        <v>42527106.473903023</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-1.7516369482487026E-2</v>
+        <v>-1.6070291180155127E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1518</v>
+        <v>1620</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1479</v>
+        <v>1580</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5691699604743046E-2</v>
+        <v>-2.4691358024691357E-2</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6319,27 +6319,27 @@
       </c>
       <c r="O66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q66" s="12">
         <f t="shared" si="3"/>
-        <v>1.1428571428571428</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1667</v>
+        <v>1659</v>
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1690</v>
+        <v>1592</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>1.3797240551889578E-2</v>
+        <v>-4.0385774562989751E-2</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6363,27 +6363,27 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18215056.68860703</v>
+        <v>20584123.922306944</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16713241.139799256</v>
+        <v>19382725.801420636</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>-8.2449128459046395E-2</v>
+        <v>-5.8365278280527511E-2</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>598</v>
+        <v>647</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>-2.1276595744680882E-2</v>
+        <v>9.4754653130287636E-2</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6399,27 +6399,27 @@
       </c>
       <c r="O67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q67" s="12">
         <f t="shared" ref="Q67:Q85" si="8">IFERROR(P67/O67-1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>652</v>
+        <v>791</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>-0.11413043478260865</v>
+        <v>6.8918918918918992E-2</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6443,27 +6443,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25802788.754436146</v>
+        <v>30147825.724716209</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27816969.776097447</v>
+        <v>32338446.233785421</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>7.8060594179573339E-2</v>
+        <v>7.26626367377885E-2</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>869</v>
+        <v>1057</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>924</v>
+        <v>952</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>6.3291139240506222E-2</v>
+        <v>-9.9337748344370813E-2</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6479,27 +6479,27 @@
       </c>
       <c r="O68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="Q68" s="12">
         <f t="shared" si="8"/>
-        <v>-0.95</v>
+        <v>2</v>
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1373</v>
+        <v>1362</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1399</v>
+        <v>1484</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>1.8936635105608168E-2</v>
+        <v>8.9574155653450838E-2</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6523,27 +6523,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15960149.230632352</v>
+        <v>18961499.08903724</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21612087.804990321</v>
+        <v>24722694.050578289</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>0.35412817842017352</v>
+        <v>0.30383647065499875</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1214</v>
+        <v>1206</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1312</v>
+        <v>1420</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>8.0724876441515603E-2</v>
+        <v>0.17744610281923712</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6559,27 +6559,27 @@
       </c>
       <c r="O69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q69" s="12">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1278</v>
+        <v>1262</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1396</v>
+        <v>1340</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>9.2331768388106417E-2</v>
+        <v>6.1806656101426327E-2</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6603,27 +6603,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46580676.905710757</v>
+        <v>53783637.746164359</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>49256726.466358557</v>
+        <v>56895215.540526107</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>5.7449778286062569E-2</v>
+        <v>5.7853613566398288E-2</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1228</v>
+        <v>1165</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1317</v>
+        <v>1308</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>7.2475570032573211E-2</v>
+        <v>0.12274678111587978</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6643,23 +6643,23 @@
       </c>
       <c r="P70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q70" s="12">
         <f t="shared" si="8"/>
-        <v>-9.9999999999999978E-2</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1605</v>
+        <v>1798</v>
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>-8.2857142857142851E-2</v>
+        <v>2.6255707762557146E-2</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6683,27 +6683,27 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9383646.5454543922</v>
+        <v>10904494.48472932</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8960062.0347378012</v>
+        <v>10133380.339113291</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-4.514071461075897E-2</v>
+        <v>-7.0715258437325845E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>-1.5909090909090873E-2</v>
+        <v>-7.407407407407407E-2</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6711,11 +6711,11 @@
       </c>
       <c r="M71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N71" s="12">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6731,15 +6731,15 @@
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>-0.11025145067698261</v>
+        <v>-4.125736738703345E-2</v>
       </c>
       <c r="U71">
         <v>1</v>
@@ -6763,27 +6763,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14552442.544222549</v>
+        <v>17298035.563470758</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17409108.331550773</v>
+        <v>20101925.882868141</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>0.19630146476423271</v>
+        <v>0.16209299079708894</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>774</v>
+        <v>1324</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>747</v>
+        <v>771</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>-3.4883720930232509E-2</v>
+        <v>-0.41767371601208458</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6803,23 +6803,23 @@
       </c>
       <c r="P72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="12">
         <f t="shared" si="8"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>782</v>
+        <v>888</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>-0.11738148984198649</v>
+        <v>7.9455164585697791E-3</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6843,27 +6843,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14615906.519403487</v>
+        <v>17062080.811463322</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16261279.578989357</v>
+        <v>19008135.274495997</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>0.1125741367736266</v>
+        <v>0.11405727616324501</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>-8.2987551867219622E-3</v>
+        <v>-4.7619047619047672E-2</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6891,15 +6891,15 @@
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>589</v>
+        <v>636</v>
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-9.5238095238095233E-2</v>
+        <v>-1.3953488372092981E-2</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6923,27 +6923,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11825950.763445076</v>
+        <v>13406292.038853647</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10410105.269862575</v>
+        <v>12587822.709509639</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>-0.1197236080128955</v>
+        <v>-6.1051133823726067E-2</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>725</v>
+        <v>700</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>790</v>
+        <v>1099</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>8.9655172413793061E-2</v>
+        <v>0.57000000000000006</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6959,27 +6959,27 @@
       </c>
       <c r="O74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q74" s="12">
         <f t="shared" si="8"/>
-        <v>0.19999999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>800</v>
+        <v>629</v>
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>0.30718954248366015</v>
+        <v>3.1147540983606614E-2</v>
       </c>
       <c r="U74">
         <v>1</v>
@@ -7003,27 +7003,27 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12707889.856647348</v>
+        <v>14534308.575940792</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11224853.807416515</v>
+        <v>13056774.364971524</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>-0.11670199112208024</v>
+        <v>-0.10165837633412345</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>1.5250544662309462E-2</v>
+        <v>0.13827160493827151</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7047,19 +7047,19 @@
       </c>
       <c r="Q75" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>498</v>
+        <v>445</v>
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>0.12162162162162171</v>
+        <v>-2.2421524663677195E-3</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -7083,27 +7083,27 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33856213.568945937</v>
+        <v>38552320.650037184</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25767122.084004831</v>
+        <v>31224051.282621074</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>-0.23892487175118404</v>
+        <v>-0.19008633576015455</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>756</v>
+        <v>502</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>749</v>
+        <v>777</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>-9.2592592592593004E-3</v>
+        <v>0.547808764940239</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7131,15 +7131,15 @@
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>940</v>
+        <v>930</v>
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>750</v>
+        <v>873</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-0.2021276595744681</v>
+        <v>-6.1290322580645151E-2</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7163,27 +7163,27 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20147404.699376933</v>
+        <v>22945629.138666265</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20795729.777784407</v>
+        <v>23789675.00632247</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>3.2179086491845865E-2</v>
+        <v>3.6784603401171623E-2</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>709</v>
+        <v>681</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>741</v>
+        <v>719</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>4.5133991537376517E-2</v>
+        <v>5.580029368575623E-2</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7211,15 +7211,15 @@
       </c>
       <c r="R77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>2.3346303501945442E-2</v>
+        <v>7.7419354838710319E-3</v>
       </c>
       <c r="U77">
         <v>2</v>
@@ -7243,27 +7243,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16295988.162141008</v>
+        <v>18897104.306166232</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17212098.434398443</v>
+        <v>19078223.4680488</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>5.621692057838823E-2</v>
+        <v>9.5844928909805116E-3</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>873</v>
+        <v>919</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>974</v>
+        <v>771</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>0.11569301260022913</v>
+        <v>-0.1610446137105549</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="O78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7287,19 +7287,19 @@
       </c>
       <c r="Q78" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1100</v>
+        <v>949</v>
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>0.14702815432742433</v>
+        <v>-1.2486992715920908E-2</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7323,27 +7323,27 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16008993.220043994</v>
+        <v>18943363.690892089</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20575678.3225642</v>
+        <v>23083990.683582705</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>0.28525748245070814</v>
+        <v>0.21857929036549173</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>860</v>
+        <v>693</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>2.5029797377830842E-2</v>
+        <v>-0.19324796274738065</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7371,15 +7371,15 @@
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>941</v>
+        <v>969</v>
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-5.1411290322580627E-2</v>
+        <v>-2.4169184290030232E-2</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7403,27 +7403,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21222145.549389083</v>
+        <v>24876612.513585679</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24021340.943134073</v>
+        <v>27850529.967314817</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>0.13189973592587911</v>
+        <v>0.11954672092532759</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>733</v>
+        <v>791</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>784</v>
+        <v>724</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>6.9577080491132426E-2</v>
+        <v>-8.4702907711757258E-2</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7455,11 +7455,11 @@
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>844</v>
+        <v>762</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>0.11492734478203426</v>
+        <v>6.6050198150593431E-3</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7483,27 +7483,27 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10050763.988478778</v>
+        <v>11491400.052304247</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9531836.5712453369</v>
+        <v>10714929.701390397</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>-5.1630643981720126E-2</v>
+        <v>-6.7569691019342182E-2</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>493</v>
+        <v>587</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>1.8255578093306246E-2</v>
+        <v>-7.4957410562180526E-2</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7531,15 +7531,15 @@
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>593</v>
+        <v>540</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>5.7040998217468886E-2</v>
+        <v>-4.5936395759717308E-2</v>
       </c>
       <c r="U81">
         <v>0</v>
@@ -7563,27 +7563,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42084775.50188525</v>
+        <v>48346216.085946538</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>51153393.19780989</v>
+        <v>58448649.984140679</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>0.21548452113088734</v>
+        <v>0.20896017757076879</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1348</v>
+        <v>1068</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1448</v>
+        <v>1408</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>7.4183976261127604E-2</v>
+        <v>0.31835205992509352</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="O82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7611,15 +7611,15 @@
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1767</v>
+        <v>1770</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1661</v>
+        <v>1798</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>-5.9988681380871545E-2</v>
+        <v>1.5819209039547921E-2</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7643,27 +7643,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9931053.6177717447</v>
+        <v>11404405.748291109</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11320774.287268532</v>
+        <v>12978754.33964923</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>0.13993688111902491</v>
+        <v>0.13804740256580494</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>900</v>
+        <v>606</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>763</v>
+        <v>739</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>-0.15222222222222226</v>
+        <v>0.21947194719471952</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7691,15 +7691,15 @@
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>925</v>
+        <v>630</v>
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>0.64590747330960863</v>
+        <v>0.11111111111111116</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7723,27 +7723,27 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18693370.236158248</v>
+        <v>21469701.985500403</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20146519.231406134</v>
+        <v>23423151.156611502</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>7.7736062405541206E-2</v>
+        <v>9.0986319811535488E-2</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>522</v>
+        <v>741</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>-3.8674033149171283E-2</v>
+        <v>0.30228471001757473</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7771,15 +7771,15 @@
       </c>
       <c r="R84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="S84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>766</v>
+        <v>680</v>
       </c>
       <c r="T84" s="12">
         <f t="shared" si="9"/>
-        <v>0.18392581143740339</v>
+        <v>5.2631578947368363E-2</v>
       </c>
       <c r="U84">
         <v>7</v>
@@ -7803,27 +7803,27 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4601412.716901565</v>
+        <v>5260642.5641915696</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4177363.4227665081</v>
+        <v>4319308.1950398814</v>
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>-9.2156326811866029E-2</v>
+        <v>-0.17893904740063782</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>362</v>
+        <v>296</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>-0.96132596685082872</v>
+        <v>-0.3817567567567568</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7851,15 +7851,15 @@
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>100</v>
+        <v>374</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>-0.72375690607734811</v>
+        <v>5.9490084985835745E-2</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7898,43 +7898,43 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>84698</v>
+        <v>84549</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>1022</v>
+        <v>1079</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>69168</v>
+        <v>69895</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>1934635103.3523769</v>
+        <v>2236113285.2862201</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>83602</v>
+        <v>84637</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>1321</v>
+        <v>1539</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>71073</v>
+        <v>71296</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>2019834901.3869331</v>
+        <v>2327481078.9661198</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7994,7 +7994,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
@@ -8003,13 +8003,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>372</v>
+        <v>430</v>
       </c>
       <c r="F6" s="10">
-        <v>8665292.4728072863</v>
+        <v>10031059.186713256</v>
       </c>
       <c r="G6" s="10">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H6" s="10">
         <v>1</v>
@@ -8018,10 +8018,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="K6" s="10">
-        <v>9238403.0792054478</v>
+        <v>10451748.424652403</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -8029,22 +8029,22 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="C7" s="10">
         <v>4</v>
       </c>
       <c r="D7" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="10">
-        <v>491</v>
+        <v>544</v>
       </c>
       <c r="F7" s="10">
-        <v>10292285.555236744</v>
+        <v>11847668.973308677</v>
       </c>
       <c r="G7" s="10">
-        <v>617</v>
+        <v>555</v>
       </c>
       <c r="H7" s="10">
         <v>6</v>
@@ -8053,10 +8053,10 @@
         <v>3</v>
       </c>
       <c r="J7" s="10">
-        <v>548</v>
+        <v>592</v>
       </c>
       <c r="K7" s="10">
-        <v>9762882.7996665835</v>
+        <v>11365040.339451777</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8064,7 +8064,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="C8" s="10">
         <v>6</v>
@@ -8073,13 +8073,13 @@
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>740</v>
+        <v>803</v>
       </c>
       <c r="F8" s="10">
-        <v>12900162.010313369</v>
+        <v>15693282.493840273</v>
       </c>
       <c r="G8" s="10">
-        <v>584</v>
+        <v>767</v>
       </c>
       <c r="H8" s="10">
         <v>4</v>
@@ -8088,10 +8088,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>587</v>
+        <v>307</v>
       </c>
       <c r="K8" s="10">
-        <v>12259231.902439144</v>
+        <v>13027212.983451417</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8099,7 +8099,7 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="C9" s="10">
         <v>5</v>
@@ -8108,25 +8108,25 @@
         <v>4</v>
       </c>
       <c r="E9" s="10">
-        <v>1021</v>
+        <v>1123</v>
       </c>
       <c r="F9" s="10">
-        <v>22209543.394173563</v>
+        <v>25636221.356210988</v>
       </c>
       <c r="G9" s="10">
-        <v>1125</v>
+        <v>1222</v>
       </c>
       <c r="H9" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I9" s="10">
         <v>2</v>
       </c>
       <c r="J9" s="10">
-        <v>973</v>
+        <v>955</v>
       </c>
       <c r="K9" s="10">
-        <v>23767288.77103918</v>
+        <v>27343918.425037589</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8134,7 +8134,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -8143,25 +8143,25 @@
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="F10" s="10">
-        <v>9957490.6809830684</v>
+        <v>11567766.085140552</v>
       </c>
       <c r="G10" s="10">
-        <v>472</v>
+        <v>392</v>
       </c>
       <c r="H10" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="10">
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="K10" s="10">
-        <v>10891954.273123616</v>
+        <v>12437976.728047604</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8169,7 +8169,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -8178,25 +8178,25 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="F11" s="10">
-        <v>8316802.9094818188</v>
+        <v>9574246.6887910403</v>
       </c>
       <c r="G11" s="10">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="H11" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="10">
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K11" s="10">
-        <v>6679003.8727309201</v>
+        <v>7884637.3578127623</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8204,22 +8204,22 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C12" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="10">
         <v>3</v>
       </c>
       <c r="E12" s="10">
-        <v>455</v>
+        <v>516</v>
       </c>
       <c r="F12" s="10">
-        <v>9808730.1557455901</v>
+        <v>11358396.529773155</v>
       </c>
       <c r="G12" s="10">
-        <v>608</v>
+        <v>635</v>
       </c>
       <c r="H12" s="10">
         <v>5</v>
@@ -8231,7 +8231,7 @@
         <v>461</v>
       </c>
       <c r="K12" s="10">
-        <v>10260074.279205721</v>
+        <v>11563533.990490887</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8248,13 +8248,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F13" s="10">
-        <v>4368337.5354776643</v>
+        <v>5043289.1807349501</v>
       </c>
       <c r="G13" s="10">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
@@ -8263,10 +8263,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K13" s="10">
-        <v>4562456.1766546061</v>
+        <v>5164313.8401981639</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8274,7 +8274,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -8283,13 +8283,13 @@
         <v>1</v>
       </c>
       <c r="E14" s="10">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="F14" s="10">
-        <v>1042028.0883094301</v>
+        <v>1745372.714907849</v>
       </c>
       <c r="G14" s="10">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="H14" s="10">
         <v>0</v>
@@ -8298,10 +8298,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="K14" s="10">
-        <v>4635399.7879167013</v>
+        <v>5210121.033227575</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8309,7 +8309,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C15" s="10">
         <v>1</v>
@@ -8318,25 +8318,25 @@
         <v>1</v>
       </c>
       <c r="E15" s="10">
-        <v>279</v>
+        <v>375</v>
       </c>
       <c r="F15" s="10">
-        <v>8948611.6469514072</v>
+        <v>10047490.355405016</v>
       </c>
       <c r="G15" s="10">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H15" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" s="10">
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="K15" s="10">
-        <v>8006300.9612096557</v>
+        <v>9232093.1963549405</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8344,7 +8344,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -8353,25 +8353,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="10">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="F16" s="10">
-        <v>4263391.5358173661</v>
+        <v>4958031.3880373193</v>
       </c>
       <c r="G16" s="10">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="H16" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K16" s="10">
-        <v>3915245.4085396952</v>
+        <v>4506119.9493312472</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8379,7 +8379,7 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C17" s="10">
         <v>1</v>
@@ -8388,13 +8388,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="10">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="F17" s="10">
-        <v>4667851.798819243</v>
+        <v>5380823.6863983767</v>
       </c>
       <c r="G17" s="10">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="H17" s="10">
         <v>0</v>
@@ -8403,10 +8403,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="10">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="K17" s="10">
-        <v>4870420.3489419278</v>
+        <v>5726064.83562293</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8414,7 +8414,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1425</v>
+        <v>1435</v>
       </c>
       <c r="C18" s="10">
         <v>3</v>
@@ -8423,25 +8423,25 @@
         <v>3</v>
       </c>
       <c r="E18" s="10">
-        <v>1196</v>
+        <v>1023</v>
       </c>
       <c r="F18" s="10">
-        <v>17549914.722498216</v>
+        <v>21396343.684887961</v>
       </c>
       <c r="G18" s="10">
-        <v>1354</v>
+        <v>1397</v>
       </c>
       <c r="H18" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I18" s="10">
         <v>5</v>
       </c>
       <c r="J18" s="10">
-        <v>1265</v>
+        <v>1239</v>
       </c>
       <c r="K18" s="10">
-        <v>26970696.540104352</v>
+        <v>30850756.8154644</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8449,7 +8449,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1229</v>
+        <v>1241</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
@@ -8458,13 +8458,13 @@
         <v>3</v>
       </c>
       <c r="E19" s="10">
-        <v>912</v>
+        <v>888</v>
       </c>
       <c r="F19" s="10">
-        <v>31902479.662608825</v>
+        <v>37588029.534986168</v>
       </c>
       <c r="G19" s="10">
-        <v>1104</v>
+        <v>1252</v>
       </c>
       <c r="H19" s="10">
         <v>0</v>
@@ -8473,10 +8473,10 @@
         <v>2</v>
       </c>
       <c r="J19" s="10">
-        <v>903</v>
+        <v>934</v>
       </c>
       <c r="K19" s="10">
-        <v>38515117.497534238</v>
+        <v>43478586.493676245</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8487,31 +8487,31 @@
         <v>1028</v>
       </c>
       <c r="C20" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="10">
         <v>5</v>
       </c>
       <c r="E20" s="10">
-        <v>874</v>
+        <v>1135</v>
       </c>
       <c r="F20" s="10">
-        <v>18358012.535915993</v>
+        <v>21212507.702614099</v>
       </c>
       <c r="G20" s="10">
-        <v>1056</v>
+        <v>1015</v>
       </c>
       <c r="H20" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="10">
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>939</v>
+        <v>964</v>
       </c>
       <c r="K20" s="10">
-        <v>18617387.113703057</v>
+        <v>21010450.610085927</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8519,22 +8519,22 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="C21" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="10">
         <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="F21" s="10">
-        <v>13351489.596777396</v>
+        <v>16152779.022945462</v>
       </c>
       <c r="G21" s="10">
-        <v>761</v>
+        <v>915</v>
       </c>
       <c r="H21" s="10">
         <v>1</v>
@@ -8543,10 +8543,10 @@
         <v>4</v>
       </c>
       <c r="J21" s="10">
-        <v>675</v>
+        <v>767</v>
       </c>
       <c r="K21" s="10">
-        <v>17444471.917847052</v>
+        <v>20384337.964686051</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8554,34 +8554,34 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2849</v>
+        <v>2824</v>
       </c>
       <c r="C22" s="10">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="F22" s="10">
-        <v>68183269.217183471</v>
+        <v>77653874.701062784</v>
       </c>
       <c r="G22" s="10">
-        <v>2793</v>
+        <v>2756</v>
       </c>
       <c r="H22" s="10">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I22" s="10">
         <v>12</v>
       </c>
       <c r="J22" s="10">
-        <v>2171</v>
+        <v>2196</v>
       </c>
       <c r="K22" s="10">
-        <v>63285344.748622917</v>
+        <v>73261977.766638085</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8589,22 +8589,22 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="C23" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" s="10">
         <v>1</v>
       </c>
       <c r="E23" s="10">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="F23" s="10">
-        <v>15904666.583410226</v>
+        <v>20823267.672696736</v>
       </c>
       <c r="G23" s="10">
-        <v>1304</v>
+        <v>1363</v>
       </c>
       <c r="H23" s="10">
         <v>5</v>
@@ -8613,10 +8613,10 @@
         <v>2</v>
       </c>
       <c r="J23" s="10">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="K23" s="10">
-        <v>33239044.280500673</v>
+        <v>38461930.24138011</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8624,22 +8624,22 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>2974</v>
+        <v>2957</v>
       </c>
       <c r="C24" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="10">
         <v>10</v>
       </c>
       <c r="E24" s="10">
-        <v>2177</v>
+        <v>2154</v>
       </c>
       <c r="F24" s="10">
-        <v>67552670.420068413</v>
+        <v>78189279.719223753</v>
       </c>
       <c r="G24" s="10">
-        <v>2498</v>
+        <v>2776</v>
       </c>
       <c r="H24" s="10">
         <v>5</v>
@@ -8648,10 +8648,10 @@
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2146</v>
+        <v>2185</v>
       </c>
       <c r="K24" s="10">
-        <v>58198730.291162997</v>
+        <v>68713287.365769863</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8659,7 +8659,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="C25" s="10">
         <v>4</v>
@@ -8668,13 +8668,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="F25" s="10">
-        <v>10254185.087530892</v>
+        <v>11618026.828046735</v>
       </c>
       <c r="G25" s="10">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="H25" s="10">
         <v>2</v>
@@ -8683,10 +8683,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>483</v>
+        <v>398</v>
       </c>
       <c r="K25" s="10">
-        <v>9326802.7803758383</v>
+        <v>10481400.58186681</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8694,34 +8694,34 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1728</v>
+        <v>1714</v>
       </c>
       <c r="C26" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D26" s="10">
         <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>1306</v>
+        <v>1279</v>
       </c>
       <c r="F26" s="10">
-        <v>27775459.775627609</v>
+        <v>31902604.980764087</v>
       </c>
       <c r="G26" s="10">
-        <v>1859</v>
+        <v>1744</v>
       </c>
       <c r="H26" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I26" s="10">
         <v>1</v>
       </c>
       <c r="J26" s="10">
-        <v>1492</v>
+        <v>1573</v>
       </c>
       <c r="K26" s="10">
-        <v>25275052.162944004</v>
+        <v>29385357.135773905</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8729,34 +8729,34 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="C27" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" s="10">
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>758</v>
+        <v>894</v>
       </c>
       <c r="F27" s="10">
-        <v>11036402.959192213</v>
+        <v>12991656.7694692</v>
       </c>
       <c r="G27" s="10">
-        <v>885</v>
+        <v>839</v>
       </c>
       <c r="H27" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="10">
         <v>0</v>
       </c>
       <c r="J27" s="10">
-        <v>807</v>
+        <v>843</v>
       </c>
       <c r="K27" s="10">
-        <v>10793154.824868249</v>
+        <v>12337413.658601355</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8764,7 +8764,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="C28" s="10">
         <v>5</v>
@@ -8773,25 +8773,25 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F28" s="10">
-        <v>14021428.057064189</v>
+        <v>16148057.481919851</v>
       </c>
       <c r="G28" s="10">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="H28" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28" s="10">
         <v>0</v>
       </c>
       <c r="J28" s="10">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="K28" s="10">
-        <v>13439375.56318808</v>
+        <v>15970386.192980677</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8799,7 +8799,7 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -8808,13 +8808,13 @@
         <v>2</v>
       </c>
       <c r="E29" s="10">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F29" s="10">
-        <v>2987521.6738292631</v>
+        <v>3545079.2402608488</v>
       </c>
       <c r="G29" s="10">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="H29" s="10">
         <v>1</v>
@@ -8823,10 +8823,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="10">
-        <v>224</v>
+        <v>166</v>
       </c>
       <c r="K29" s="10">
-        <v>3444507.7473005932</v>
+        <v>4033521.2907017982</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8834,34 +8834,34 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1660</v>
+        <v>1647</v>
       </c>
       <c r="C30" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="10">
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1500</v>
+        <v>1456</v>
       </c>
       <c r="F30" s="10">
-        <v>26097918.150558844</v>
+        <v>30369760.083999842</v>
       </c>
       <c r="G30" s="10">
-        <v>1827</v>
+        <v>1651</v>
       </c>
       <c r="H30" s="10">
         <v>3</v>
       </c>
       <c r="I30" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="10">
-        <v>1624</v>
+        <v>1431</v>
       </c>
       <c r="K30" s="10">
-        <v>26699945.286994319</v>
+        <v>30813505.786671042</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8872,19 +8872,19 @@
         <v>875</v>
       </c>
       <c r="C31" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="10">
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>558</v>
+        <v>683</v>
       </c>
       <c r="F31" s="10">
-        <v>21408157.92547648</v>
+        <v>25130828.725072499</v>
       </c>
       <c r="G31" s="10">
-        <v>795</v>
+        <v>895</v>
       </c>
       <c r="H31" s="10">
         <v>3</v>
@@ -8893,10 +8893,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="K31" s="10">
-        <v>23972515.811498009</v>
+        <v>27992379.158031393</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8904,7 +8904,7 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1061</v>
+        <v>1052</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
@@ -8913,25 +8913,25 @@
         <v>2</v>
       </c>
       <c r="E32" s="10">
-        <v>608</v>
+        <v>813</v>
       </c>
       <c r="F32" s="10">
-        <v>20992871.884413186</v>
+        <v>24348017.987532649</v>
       </c>
       <c r="G32" s="10">
-        <v>1052</v>
+        <v>1013</v>
       </c>
       <c r="H32" s="10">
         <v>1</v>
       </c>
       <c r="I32" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="10">
-        <v>881</v>
+        <v>915</v>
       </c>
       <c r="K32" s="10">
-        <v>23572892.259057939</v>
+        <v>27339018.879904401</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8939,22 +8939,22 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="C33" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" s="10">
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>851</v>
+        <v>865</v>
       </c>
       <c r="F33" s="10">
-        <v>28355830.721760739</v>
+        <v>33287094.194697849</v>
       </c>
       <c r="G33" s="10">
-        <v>1010</v>
+        <v>1140</v>
       </c>
       <c r="H33" s="10">
         <v>2</v>
@@ -8963,10 +8963,10 @@
         <v>3</v>
       </c>
       <c r="J33" s="10">
-        <v>854</v>
+        <v>804</v>
       </c>
       <c r="K33" s="10">
-        <v>29858563.383784257</v>
+        <v>33866219.070671238</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8974,7 +8974,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1448</v>
+        <v>1453</v>
       </c>
       <c r="C34" s="10">
         <v>4</v>
@@ -8983,25 +8983,25 @@
         <v>4</v>
       </c>
       <c r="E34" s="10">
-        <v>1178</v>
+        <v>1108</v>
       </c>
       <c r="F34" s="10">
-        <v>40601238.013903379</v>
+        <v>46940123.260832466</v>
       </c>
       <c r="G34" s="10">
-        <v>1321</v>
+        <v>1453</v>
       </c>
       <c r="H34" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="10">
         <v>2</v>
       </c>
       <c r="J34" s="10">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="K34" s="10">
-        <v>41739242.360557027</v>
+        <v>48286581.885638237</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -9009,34 +9009,34 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C35" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="10">
         <v>5</v>
       </c>
       <c r="E35" s="10">
-        <v>493</v>
+        <v>566</v>
       </c>
       <c r="F35" s="10">
-        <v>16636175.449088316</v>
+        <v>19339477.823665723</v>
       </c>
       <c r="G35" s="10">
-        <v>807</v>
+        <v>679</v>
       </c>
       <c r="H35" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="10">
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>762</v>
+        <v>577</v>
       </c>
       <c r="K35" s="10">
-        <v>16939342.25355164</v>
+        <v>19612777.992599472</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9044,34 +9044,34 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1925</v>
+        <v>1906</v>
       </c>
       <c r="C36" s="10">
         <v>6</v>
       </c>
       <c r="D36" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="10">
-        <v>70</v>
+        <v>985</v>
       </c>
       <c r="F36" s="10">
-        <v>46539327.260969058</v>
+        <v>46678468.479174599</v>
       </c>
       <c r="G36" s="10">
-        <v>1785</v>
+        <v>1856</v>
       </c>
       <c r="H36" s="10">
         <v>3</v>
       </c>
       <c r="I36" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J36" s="10">
-        <v>1613</v>
+        <v>1632</v>
       </c>
       <c r="K36" s="10">
-        <v>32734730.545260098</v>
+        <v>39716345.829926766</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9079,7 +9079,7 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="C37" s="10">
         <v>2</v>
@@ -9088,25 +9088,25 @@
         <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>783</v>
+        <v>673</v>
       </c>
       <c r="F37" s="10">
-        <v>16874087.423591021</v>
+        <v>19600077.597591951</v>
       </c>
       <c r="G37" s="10">
-        <v>799</v>
+        <v>847</v>
       </c>
       <c r="H37" s="10">
         <v>2</v>
       </c>
       <c r="I37" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37" s="10">
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="K37" s="10">
-        <v>17298861.003520712</v>
+        <v>19603837.280351806</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9114,22 +9114,22 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C38" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="10">
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>562</v>
+        <v>458</v>
       </c>
       <c r="F38" s="10">
-        <v>16191205.913323352</v>
+        <v>18503531.759908363</v>
       </c>
       <c r="G38" s="10">
-        <v>801</v>
+        <v>731</v>
       </c>
       <c r="H38" s="10">
         <v>1</v>
@@ -9138,10 +9138,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="K38" s="10">
-        <v>15397482.675662059</v>
+        <v>17848929.749518771</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9149,34 +9149,34 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C39" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D39" s="10">
         <v>1</v>
       </c>
       <c r="E39" s="10">
-        <v>868</v>
+        <v>837</v>
       </c>
       <c r="F39" s="10">
-        <v>23979908.496460751</v>
+        <v>27886563.921537865</v>
       </c>
       <c r="G39" s="10">
-        <v>1428</v>
+        <v>1195</v>
       </c>
       <c r="H39" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" s="10">
         <v>2</v>
       </c>
       <c r="J39" s="10">
-        <v>910</v>
+        <v>896</v>
       </c>
       <c r="K39" s="10">
-        <v>27238703.996070687</v>
+        <v>31244315.963416766</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9184,7 +9184,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="C40" s="10">
         <v>120</v>
@@ -9193,13 +9193,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>826</v>
+        <v>806</v>
       </c>
       <c r="F40" s="10">
-        <v>22374902.800021451</v>
+        <v>25980146.357264768</v>
       </c>
       <c r="G40" s="10">
-        <v>1395</v>
+        <v>1368</v>
       </c>
       <c r="H40" s="10">
         <v>318</v>
@@ -9208,10 +9208,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="K40" s="10">
-        <v>24757046.481234096</v>
+        <v>28569315.557240028</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9219,22 +9219,22 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>2372</v>
+        <v>2319</v>
       </c>
       <c r="C41" s="10">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D41" s="10">
         <v>5</v>
       </c>
       <c r="E41" s="10">
-        <v>1405</v>
+        <v>1627</v>
       </c>
       <c r="F41" s="10">
-        <v>41518349.605261825</v>
+        <v>47828167.354593977</v>
       </c>
       <c r="G41" s="10">
-        <v>2354</v>
+        <v>2231</v>
       </c>
       <c r="H41" s="10">
         <v>238</v>
@@ -9243,10 +9243,10 @@
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1464</v>
+        <v>1348</v>
       </c>
       <c r="K41" s="10">
-        <v>41478113.936420672</v>
+        <v>47327626.983007781</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9254,7 +9254,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="C42" s="10">
         <v>1</v>
@@ -9263,13 +9263,13 @@
         <v>6</v>
       </c>
       <c r="E42" s="10">
-        <v>668</v>
+        <v>485</v>
       </c>
       <c r="F42" s="10">
-        <v>14781644.391173327</v>
+        <v>17239734.609239098</v>
       </c>
       <c r="G42" s="10">
-        <v>538</v>
+        <v>586</v>
       </c>
       <c r="H42" s="10">
         <v>4</v>
@@ -9278,10 +9278,10 @@
         <v>7</v>
       </c>
       <c r="J42" s="10">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="K42" s="10">
-        <v>15234974.245374314</v>
+        <v>17601943.18951926</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9292,19 +9292,19 @@
         <v>2060</v>
       </c>
       <c r="C43" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" s="10">
         <v>6</v>
       </c>
       <c r="E43" s="10">
-        <v>1916</v>
+        <v>1813</v>
       </c>
       <c r="F43" s="10">
-        <v>48800547.351421833</v>
+        <v>55863457.338151634</v>
       </c>
       <c r="G43" s="10">
-        <v>2027</v>
+        <v>2037</v>
       </c>
       <c r="H43" s="10">
         <v>4</v>
@@ -9313,10 +9313,10 @@
         <v>5</v>
       </c>
       <c r="J43" s="10">
-        <v>1857</v>
+        <v>1899</v>
       </c>
       <c r="K43" s="10">
-        <v>47432872.324979059</v>
+        <v>53820568.949218951</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9324,34 +9324,34 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="C44" s="10">
         <v>3</v>
       </c>
       <c r="D44" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>2049</v>
+        <v>1214</v>
       </c>
       <c r="F44" s="10">
-        <v>32614535.508652512</v>
+        <v>38794693.14317365</v>
       </c>
       <c r="G44" s="10">
-        <v>989</v>
+        <v>934</v>
       </c>
       <c r="H44" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44" s="10">
         <v>4</v>
       </c>
       <c r="J44" s="10">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="K44" s="10">
-        <v>36694418.119907491</v>
+        <v>42105567.733273089</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9362,19 +9362,19 @@
         <v>1088</v>
       </c>
       <c r="C45" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45" s="10">
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>969</v>
+        <v>936</v>
       </c>
       <c r="F45" s="10">
-        <v>17773873.790777944</v>
+        <v>21326951.017018501</v>
       </c>
       <c r="G45" s="10">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="H45" s="10">
         <v>6</v>
@@ -9383,10 +9383,10 @@
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>934</v>
+        <v>981</v>
       </c>
       <c r="K45" s="10">
-        <v>26012267.611628871</v>
+        <v>29772505.600011189</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9394,34 +9394,34 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C46" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" s="10">
         <v>4</v>
       </c>
       <c r="E46" s="10">
-        <v>590</v>
+        <v>564</v>
       </c>
       <c r="F46" s="10">
-        <v>25294917.477437437</v>
+        <v>28987672.484540347</v>
       </c>
       <c r="G46" s="10">
-        <v>725</v>
+        <v>832</v>
       </c>
       <c r="H46" s="10">
         <v>2</v>
       </c>
       <c r="I46" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J46" s="10">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="K46" s="10">
-        <v>26258702.513062768</v>
+        <v>30625362.113111999</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9429,7 +9429,7 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="C47" s="10">
         <v>2</v>
@@ -9438,13 +9438,13 @@
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>587</v>
+        <v>1046</v>
       </c>
       <c r="F47" s="10">
-        <v>16227351.047975589</v>
+        <v>18797706.720624097</v>
       </c>
       <c r="G47" s="10">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="H47" s="10">
         <v>0</v>
@@ -9453,10 +9453,10 @@
         <v>9</v>
       </c>
       <c r="J47" s="10">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="K47" s="10">
-        <v>15777654.210746672</v>
+        <v>18111709.274998784</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9464,7 +9464,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C48" s="10">
         <v>0</v>
@@ -9473,25 +9473,25 @@
         <v>2</v>
       </c>
       <c r="E48" s="10">
-        <v>676</v>
+        <v>475</v>
       </c>
       <c r="F48" s="10">
-        <v>14358233.121239796</v>
+        <v>16326037.684438676</v>
       </c>
       <c r="G48" s="10">
-        <v>789</v>
+        <v>705</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
       </c>
       <c r="I48" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48" s="10">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="K48" s="10">
-        <v>14765811.497357111</v>
+        <v>16974532.487811487</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9499,34 +9499,34 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C49" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49" s="10">
         <v>5</v>
       </c>
       <c r="E49" s="10">
-        <v>1098</v>
+        <v>1074</v>
       </c>
       <c r="F49" s="10">
-        <v>43788229.833009563</v>
+        <v>50350879.089841045</v>
       </c>
       <c r="G49" s="10">
-        <v>1159</v>
+        <v>1287</v>
       </c>
       <c r="H49" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I49" s="10">
         <v>6</v>
       </c>
       <c r="J49" s="10">
-        <v>1123</v>
+        <v>1140</v>
       </c>
       <c r="K49" s="10">
-        <v>49134791.486482561</v>
+        <v>55925546.402918451</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9534,22 +9534,22 @@
         <v>201</v>
       </c>
       <c r="B50" s="10">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C50" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="10">
         <v>1</v>
       </c>
       <c r="E50" s="10">
-        <v>467</v>
+        <v>429</v>
       </c>
       <c r="F50" s="10">
-        <v>7200859.8401143793</v>
+        <v>8260863.7707575997</v>
       </c>
       <c r="G50" s="10">
-        <v>488</v>
+        <v>453</v>
       </c>
       <c r="H50" s="10">
         <v>1</v>
@@ -9558,10 +9558,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>467</v>
+        <v>496</v>
       </c>
       <c r="K50" s="10">
-        <v>7518789.3938841689</v>
+        <v>8658076.1250030715</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9569,7 +9569,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C51" s="10">
         <v>2</v>
@@ -9578,25 +9578,25 @@
         <v>7</v>
       </c>
       <c r="E51" s="10">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="F51" s="10">
-        <v>21077266.831570905</v>
+        <v>24329645.084981102</v>
       </c>
       <c r="G51" s="10">
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="H51" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="10">
         <v>5</v>
       </c>
       <c r="J51" s="10">
-        <v>886</v>
+        <v>916</v>
       </c>
       <c r="K51" s="10">
-        <v>20804392.415884595</v>
+        <v>24008510.265390374</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9604,7 +9604,7 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C52" s="10">
         <v>4</v>
@@ -9613,13 +9613,13 @@
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>1025</v>
+        <v>956</v>
       </c>
       <c r="F52" s="10">
-        <v>36799819.563541561</v>
+        <v>42604532.316107005</v>
       </c>
       <c r="G52" s="10">
-        <v>1443</v>
+        <v>1419</v>
       </c>
       <c r="H52" s="10">
         <v>3</v>
@@ -9628,10 +9628,10 @@
         <v>11</v>
       </c>
       <c r="J52" s="10">
-        <v>1044</v>
+        <v>1138</v>
       </c>
       <c r="K52" s="10">
-        <v>38255043.889359169</v>
+        <v>43979107.294347867</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9639,7 +9639,7 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C53" s="10">
         <v>1</v>
@@ -9648,25 +9648,25 @@
         <v>6</v>
       </c>
       <c r="E53" s="10">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="F53" s="10">
-        <v>18998431.435199615</v>
+        <v>22005709.005341128</v>
       </c>
       <c r="G53" s="10">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="H53" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" s="10">
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K53" s="10">
-        <v>18181613.774843927</v>
+        <v>21167858.625659622</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9674,7 +9674,7 @@
         <v>81</v>
       </c>
       <c r="B54" s="10">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C54" s="10">
         <v>0</v>
@@ -9683,13 +9683,13 @@
         <v>4</v>
       </c>
       <c r="E54" s="10">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="F54" s="10">
-        <v>13867349.453376597</v>
+        <v>16006981.240799496</v>
       </c>
       <c r="G54" s="10">
-        <v>506</v>
+        <v>461</v>
       </c>
       <c r="H54" s="10">
         <v>2</v>
@@ -9698,10 +9698,10 @@
         <v>3</v>
       </c>
       <c r="J54" s="10">
-        <v>373</v>
+        <v>460</v>
       </c>
       <c r="K54" s="10">
-        <v>15464289.961397316</v>
+        <v>17965408.831571799</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9709,7 +9709,7 @@
         <v>87</v>
       </c>
       <c r="B55" s="10">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C55" s="10">
         <v>1</v>
@@ -9718,25 +9718,25 @@
         <v>4</v>
       </c>
       <c r="E55" s="10">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="F55" s="10">
-        <v>11991960.514846284</v>
+        <v>13856935.277226221</v>
       </c>
       <c r="G55" s="10">
-        <v>116</v>
+        <v>385</v>
       </c>
       <c r="H55" s="10">
         <v>1</v>
       </c>
       <c r="I55" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" s="10">
-        <v>278</v>
+        <v>10</v>
       </c>
       <c r="K55" s="10">
-        <v>5719922.5869477298</v>
+        <v>5873087.196715177</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9744,7 +9744,7 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="C56" s="10">
         <v>5</v>
@@ -9753,13 +9753,13 @@
         <v>0</v>
       </c>
       <c r="E56" s="10">
-        <v>974</v>
+        <v>872</v>
       </c>
       <c r="F56" s="10">
-        <v>28403417.987599976</v>
+        <v>32922233.232268192</v>
       </c>
       <c r="G56" s="10">
-        <v>941</v>
+        <v>1103</v>
       </c>
       <c r="H56" s="10">
         <v>3</v>
@@ -9768,10 +9768,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>905</v>
+        <v>940</v>
       </c>
       <c r="K56" s="10">
-        <v>30195865.25279944</v>
+        <v>34613136.454139821</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9779,22 +9779,22 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="C57" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D57" s="10">
         <v>1</v>
       </c>
       <c r="E57" s="10">
-        <v>917</v>
+        <v>1002</v>
       </c>
       <c r="F57" s="10">
-        <v>27544676.485392641</v>
+        <v>32767497.85062144</v>
       </c>
       <c r="G57" s="10">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="H57" s="10">
         <v>5</v>
@@ -9803,10 +9803,10 @@
         <v>2</v>
       </c>
       <c r="J57" s="10">
-        <v>800</v>
+        <v>963</v>
       </c>
       <c r="K57" s="10">
-        <v>30524186.608173389</v>
+        <v>35690534.982378751</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9814,34 +9814,34 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2057</v>
+        <v>2048</v>
       </c>
       <c r="C58" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D58" s="10">
         <v>8</v>
       </c>
       <c r="E58" s="10">
-        <v>1517</v>
+        <v>1601</v>
       </c>
       <c r="F58" s="10">
-        <v>53312926.280314647</v>
+        <v>61113798.319160461</v>
       </c>
       <c r="G58" s="10">
-        <v>2123</v>
+        <v>2073</v>
       </c>
       <c r="H58" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I58" s="10">
         <v>9</v>
       </c>
       <c r="J58" s="10">
-        <v>1850</v>
+        <v>1658</v>
       </c>
       <c r="K58" s="10">
-        <v>56661351.157900929</v>
+        <v>64882425.838394135</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9849,7 +9849,7 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C59" s="10">
         <v>4</v>
@@ -9858,13 +9858,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>567</v>
+        <v>447</v>
       </c>
       <c r="F59" s="10">
-        <v>13156051.392773269</v>
+        <v>15237386.793200787</v>
       </c>
       <c r="G59" s="10">
-        <v>560</v>
+        <v>662</v>
       </c>
       <c r="H59" s="10">
         <v>2</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K59" s="10">
-        <v>14826348.495922143</v>
+        <v>16923572.104882669</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9884,7 +9884,7 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="C60" s="10">
         <v>6</v>
@@ -9893,25 +9893,25 @@
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>738</v>
+        <v>715</v>
       </c>
       <c r="F60" s="10">
-        <v>22949848.91231928</v>
+        <v>26569100.705542248</v>
       </c>
       <c r="G60" s="10">
-        <v>1050</v>
+        <v>922</v>
       </c>
       <c r="H60" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I60" s="10">
         <v>6</v>
       </c>
       <c r="J60" s="10">
-        <v>865</v>
+        <v>738</v>
       </c>
       <c r="K60" s="10">
-        <v>26561103.572443023</v>
+        <v>30353544.458011288</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9919,22 +9919,22 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="C61" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" s="10">
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>625</v>
+        <v>740</v>
       </c>
       <c r="F61" s="10">
-        <v>14245013.316192299</v>
+        <v>16880304.095586132</v>
       </c>
       <c r="G61" s="10">
-        <v>411</v>
+        <v>678</v>
       </c>
       <c r="H61" s="10">
         <v>0</v>
@@ -9943,10 +9943,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="10">
-        <v>526</v>
+        <v>613</v>
       </c>
       <c r="K61" s="10">
-        <v>13109236.528265854</v>
+        <v>15435179.114867197</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9954,7 +9954,7 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C62" s="10">
         <v>5</v>
@@ -9963,13 +9963,13 @@
         <v>0</v>
       </c>
       <c r="E62" s="10">
-        <v>963</v>
+        <v>869</v>
       </c>
       <c r="F62" s="10">
-        <v>29939617.972537749</v>
+        <v>34340368.090365291</v>
       </c>
       <c r="G62" s="10">
-        <v>1292</v>
+        <v>1099</v>
       </c>
       <c r="H62" s="10">
         <v>6</v>
@@ -9978,10 +9978,10 @@
         <v>1</v>
       </c>
       <c r="J62" s="10">
-        <v>1190</v>
+        <v>1163</v>
       </c>
       <c r="K62" s="10">
-        <v>32682821.514900204</v>
+        <v>37729757.422791846</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9989,34 +9989,34 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1441</v>
+        <v>1478</v>
       </c>
       <c r="C63" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63" s="10">
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1471</v>
+        <v>1339</v>
       </c>
       <c r="F63" s="10">
-        <v>37000002.653800093</v>
+        <v>43422115.586745128</v>
       </c>
       <c r="G63" s="10">
-        <v>1601</v>
+        <v>1621</v>
       </c>
       <c r="H63" s="10">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I63" s="10">
         <v>5</v>
       </c>
       <c r="J63" s="10">
-        <v>1513</v>
+        <v>1618</v>
       </c>
       <c r="K63" s="10">
-        <v>44797837.205057278</v>
+        <v>51933160.195166431</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -10024,22 +10024,22 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C64" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" s="10">
         <v>4</v>
       </c>
       <c r="E64" s="10">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="F64" s="10">
-        <v>19983891.374101069</v>
+        <v>23207604.557711422</v>
       </c>
       <c r="G64" s="10">
-        <v>873</v>
+        <v>798</v>
       </c>
       <c r="H64" s="10">
         <v>4</v>
@@ -10048,10 +10048,10 @@
         <v>5</v>
       </c>
       <c r="J64" s="10">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="K64" s="10">
-        <v>18318451.973164391</v>
+        <v>21502821.729210172</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10059,7 +10059,7 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C65" s="10">
         <v>7</v>
@@ -10068,25 +10068,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F65" s="10">
-        <v>22367781.080104113</v>
+        <v>25855386.35664548</v>
       </c>
       <c r="G65" s="10">
-        <v>585</v>
+        <v>644</v>
       </c>
       <c r="H65" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I65" s="10">
         <v>7</v>
       </c>
       <c r="J65" s="10">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="K65" s="10">
-        <v>23871295.559602365</v>
+        <v>27515605.348086242</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10094,34 +10094,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>1996</v>
+        <v>1983</v>
       </c>
       <c r="C66" s="10">
         <v>11</v>
       </c>
       <c r="D66" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E66" s="10">
-        <v>1619</v>
+        <v>1969</v>
       </c>
       <c r="F66" s="10">
-        <v>72623824.220833898</v>
+        <v>83988262.907164082</v>
       </c>
       <c r="G66" s="10">
-        <v>2063</v>
+        <v>1957</v>
       </c>
       <c r="H66" s="10">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I66" s="10">
         <v>12</v>
       </c>
       <c r="J66" s="10">
-        <v>1674</v>
+        <v>1637</v>
       </c>
       <c r="K66" s="10">
-        <v>76429257.720611393</v>
+        <v>87322079.567863107</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10129,34 +10129,34 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="C67" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D67" s="10">
         <v>6</v>
       </c>
       <c r="E67" s="10">
-        <v>1229</v>
+        <v>1096</v>
       </c>
       <c r="F67" s="10">
-        <v>53751877.713151284</v>
+        <v>62144411.904331289</v>
       </c>
       <c r="G67" s="10">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="H67" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I67" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J67" s="10">
-        <v>1243</v>
+        <v>1318</v>
       </c>
       <c r="K67" s="10">
-        <v>54327698.607676938</v>
+        <v>63302163.709051661</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10164,22 +10164,22 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C68" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D68" s="10">
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>764</v>
+        <v>720</v>
       </c>
       <c r="F68" s="10">
-        <v>35023411.856107965</v>
+        <v>40291786.850265786</v>
       </c>
       <c r="G68" s="10">
-        <v>913</v>
+        <v>896</v>
       </c>
       <c r="H68" s="10">
         <v>2</v>
@@ -10188,10 +10188,10 @@
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="K68" s="10">
-        <v>36681052.563683063</v>
+        <v>42230040.117961869</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10199,34 +10199,34 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>2297</v>
+        <v>2275</v>
       </c>
       <c r="C69" s="10">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D69" s="10">
         <v>12</v>
       </c>
       <c r="E69" s="10">
-        <v>1327</v>
+        <v>1405</v>
       </c>
       <c r="F69" s="10">
-        <v>52986952.666871026</v>
+        <v>60482844.879700385</v>
       </c>
       <c r="G69" s="10">
-        <v>2015</v>
+        <v>2369</v>
       </c>
       <c r="H69" s="10">
-        <v>372</v>
+        <v>462</v>
       </c>
       <c r="I69" s="10">
         <v>13</v>
       </c>
       <c r="J69" s="10">
-        <v>1272</v>
+        <v>1337</v>
       </c>
       <c r="K69" s="10">
-        <v>49029776.551765636</v>
+        <v>56679542.814377584</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10234,7 +10234,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C70" s="10">
         <v>0</v>
@@ -10243,13 +10243,13 @@
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>286</v>
+        <v>246</v>
       </c>
       <c r="F70" s="10">
-        <v>1604743.4340360931</v>
+        <v>2049584.514477622</v>
       </c>
       <c r="G70" s="10">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="H70" s="10">
         <v>2</v>
@@ -10258,10 +10258,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="10">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="K70" s="10">
-        <v>4030673.95379342</v>
+        <v>4609199.2052098904</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10269,34 +10269,34 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1667</v>
+        <v>1659</v>
       </c>
       <c r="C71" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D71" s="10">
         <v>6</v>
       </c>
       <c r="E71" s="10">
-        <v>1518</v>
+        <v>1620</v>
       </c>
       <c r="F71" s="10">
-        <v>37741415.05560144</v>
+        <v>43221691.643919691</v>
       </c>
       <c r="G71" s="10">
-        <v>1690</v>
+        <v>1592</v>
       </c>
       <c r="H71" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I71" s="10">
         <v>8</v>
       </c>
       <c r="J71" s="10">
-        <v>1479</v>
+        <v>1580</v>
       </c>
       <c r="K71" s="10">
-        <v>37080322.484695628</v>
+        <v>42527106.473903023</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10304,34 +10304,34 @@
         <v>12</v>
       </c>
       <c r="B72" s="10">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C72" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72" s="10">
         <v>3</v>
       </c>
       <c r="E72" s="10">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="F72" s="10">
-        <v>18215056.68860703</v>
+        <v>20584123.922306944</v>
       </c>
       <c r="G72" s="10">
-        <v>652</v>
+        <v>791</v>
       </c>
       <c r="H72" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I72" s="10">
         <v>4</v>
       </c>
       <c r="J72" s="10">
-        <v>598</v>
+        <v>647</v>
       </c>
       <c r="K72" s="10">
-        <v>16713241.139799256</v>
+        <v>19382725.801420636</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10339,34 +10339,34 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1373</v>
+        <v>1362</v>
       </c>
       <c r="C73" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D73" s="10">
         <v>4</v>
       </c>
       <c r="E73" s="10">
-        <v>869</v>
+        <v>1057</v>
       </c>
       <c r="F73" s="10">
-        <v>25802788.754436146</v>
+        <v>30147825.724716209</v>
       </c>
       <c r="G73" s="10">
-        <v>1399</v>
+        <v>1484</v>
       </c>
       <c r="H73" s="10">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="I73" s="10">
         <v>5</v>
       </c>
       <c r="J73" s="10">
-        <v>924</v>
+        <v>952</v>
       </c>
       <c r="K73" s="10">
-        <v>27816969.776097447</v>
+        <v>32338446.233785421</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10374,34 +10374,34 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1278</v>
+        <v>1262</v>
       </c>
       <c r="C74" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D74" s="10">
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>1214</v>
+        <v>1206</v>
       </c>
       <c r="F74" s="10">
-        <v>15960149.230632352</v>
+        <v>18961499.08903724</v>
       </c>
       <c r="G74" s="10">
-        <v>1396</v>
+        <v>1340</v>
       </c>
       <c r="H74" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I74" s="10">
         <v>4</v>
       </c>
       <c r="J74" s="10">
-        <v>1312</v>
+        <v>1420</v>
       </c>
       <c r="K74" s="10">
-        <v>21612087.804990321</v>
+        <v>24722694.050578289</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10409,7 +10409,7 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="C75" s="10">
         <v>10</v>
@@ -10418,25 +10418,25 @@
         <v>4</v>
       </c>
       <c r="E75" s="10">
-        <v>1228</v>
+        <v>1165</v>
       </c>
       <c r="F75" s="10">
-        <v>46580676.905710757</v>
+        <v>53783637.746164359</v>
       </c>
       <c r="G75" s="10">
-        <v>1605</v>
+        <v>1798</v>
       </c>
       <c r="H75" s="10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I75" s="10">
         <v>7</v>
       </c>
       <c r="J75" s="10">
-        <v>1317</v>
+        <v>1308</v>
       </c>
       <c r="K75" s="10">
-        <v>49256726.466358557</v>
+        <v>56895215.540526107</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10444,7 +10444,7 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C76" s="10">
         <v>2</v>
@@ -10453,25 +10453,25 @@
         <v>1</v>
       </c>
       <c r="E76" s="10">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="F76" s="10">
-        <v>9383646.5454543922</v>
+        <v>10904494.48472932</v>
       </c>
       <c r="G76" s="10">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="H76" s="10">
         <v>4</v>
       </c>
       <c r="I76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="K76" s="10">
-        <v>8960062.0347378012</v>
+        <v>10133380.339113291</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10479,7 +10479,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C77" s="10">
         <v>3</v>
@@ -10488,25 +10488,25 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>774</v>
+        <v>1324</v>
       </c>
       <c r="F77" s="10">
-        <v>14552442.544222549</v>
+        <v>17298035.563470758</v>
       </c>
       <c r="G77" s="10">
-        <v>782</v>
+        <v>888</v>
       </c>
       <c r="H77" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" s="10">
         <v>0</v>
       </c>
       <c r="J77" s="10">
-        <v>747</v>
+        <v>771</v>
       </c>
       <c r="K77" s="10">
-        <v>17409108.331550773</v>
+        <v>20101925.882868141</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10514,7 +10514,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C78" s="10">
         <v>0</v>
@@ -10523,13 +10523,13 @@
         <v>3</v>
       </c>
       <c r="E78" s="10">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="F78" s="10">
-        <v>14615906.519403487</v>
+        <v>17062080.811463322</v>
       </c>
       <c r="G78" s="10">
-        <v>589</v>
+        <v>636</v>
       </c>
       <c r="H78" s="10">
         <v>2</v>
@@ -10538,10 +10538,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K78" s="10">
-        <v>16261279.578989357</v>
+        <v>19008135.274495997</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10549,34 +10549,34 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C79" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D79" s="10">
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>725</v>
+        <v>700</v>
       </c>
       <c r="F79" s="10">
-        <v>11825950.763445076</v>
+        <v>13406292.038853647</v>
       </c>
       <c r="G79" s="10">
-        <v>800</v>
+        <v>629</v>
       </c>
       <c r="H79" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I79" s="10">
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>790</v>
+        <v>1099</v>
       </c>
       <c r="K79" s="10">
-        <v>10410105.269862575</v>
+        <v>12587822.709509639</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10584,22 +10584,22 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C80" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80" s="10">
         <v>7</v>
       </c>
       <c r="E80" s="10">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="F80" s="10">
-        <v>12707889.856647348</v>
+        <v>14534308.575940792</v>
       </c>
       <c r="G80" s="10">
-        <v>498</v>
+        <v>445</v>
       </c>
       <c r="H80" s="10">
         <v>3</v>
@@ -10608,10 +10608,10 @@
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="K80" s="10">
-        <v>11224853.807416515</v>
+        <v>13056774.364971524</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10619,7 +10619,7 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>940</v>
+        <v>930</v>
       </c>
       <c r="C81" s="10">
         <v>5</v>
@@ -10628,13 +10628,13 @@
         <v>3</v>
       </c>
       <c r="E81" s="10">
-        <v>756</v>
+        <v>502</v>
       </c>
       <c r="F81" s="10">
-        <v>33856213.568945937</v>
+        <v>38552320.650037184</v>
       </c>
       <c r="G81" s="10">
-        <v>750</v>
+        <v>873</v>
       </c>
       <c r="H81" s="10">
         <v>5</v>
@@ -10643,10 +10643,10 @@
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>749</v>
+        <v>777</v>
       </c>
       <c r="K81" s="10">
-        <v>25767122.084004831</v>
+        <v>31224051.282621074</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10654,7 +10654,7 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C82" s="10">
         <v>2</v>
@@ -10663,13 +10663,13 @@
         <v>10</v>
       </c>
       <c r="E82" s="10">
-        <v>709</v>
+        <v>681</v>
       </c>
       <c r="F82" s="10">
-        <v>20147404.699376933</v>
+        <v>22945629.138666265</v>
       </c>
       <c r="G82" s="10">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="H82" s="10">
         <v>3</v>
@@ -10678,10 +10678,10 @@
         <v>9</v>
       </c>
       <c r="J82" s="10">
-        <v>741</v>
+        <v>719</v>
       </c>
       <c r="K82" s="10">
-        <v>20795729.777784407</v>
+        <v>23789675.00632247</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10689,22 +10689,22 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C83" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" s="10">
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>873</v>
+        <v>919</v>
       </c>
       <c r="F83" s="10">
-        <v>16295988.162141008</v>
+        <v>18897104.306166232</v>
       </c>
       <c r="G83" s="10">
-        <v>1100</v>
+        <v>949</v>
       </c>
       <c r="H83" s="10">
         <v>2</v>
@@ -10713,10 +10713,10 @@
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>974</v>
+        <v>771</v>
       </c>
       <c r="K83" s="10">
-        <v>17212098.434398443</v>
+        <v>19078223.4680488</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10724,7 +10724,7 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C84" s="10">
         <v>2</v>
@@ -10733,13 +10733,13 @@
         <v>5</v>
       </c>
       <c r="E84" s="10">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="F84" s="10">
-        <v>16008993.220043994</v>
+        <v>18943363.690892089</v>
       </c>
       <c r="G84" s="10">
-        <v>941</v>
+        <v>969</v>
       </c>
       <c r="H84" s="10">
         <v>2</v>
@@ -10748,10 +10748,10 @@
         <v>4</v>
       </c>
       <c r="J84" s="10">
-        <v>860</v>
+        <v>693</v>
       </c>
       <c r="K84" s="10">
-        <v>20575678.3225642</v>
+        <v>23083990.683582705</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10768,13 +10768,13 @@
         <v>6</v>
       </c>
       <c r="E85" s="10">
-        <v>733</v>
+        <v>791</v>
       </c>
       <c r="F85" s="10">
-        <v>21222145.549389083</v>
+        <v>24876612.513585679</v>
       </c>
       <c r="G85" s="10">
-        <v>844</v>
+        <v>762</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
@@ -10783,10 +10783,10 @@
         <v>7</v>
       </c>
       <c r="J85" s="10">
-        <v>784</v>
+        <v>724</v>
       </c>
       <c r="K85" s="10">
-        <v>24021340.943134073</v>
+        <v>27850529.967314817</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10794,7 +10794,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C86" s="10">
         <v>1</v>
@@ -10803,13 +10803,13 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>493</v>
+        <v>587</v>
       </c>
       <c r="F86" s="10">
-        <v>10050763.988478778</v>
+        <v>11491400.052304247</v>
       </c>
       <c r="G86" s="10">
-        <v>593</v>
+        <v>540</v>
       </c>
       <c r="H86" s="10">
         <v>4</v>
@@ -10818,10 +10818,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="K86" s="10">
-        <v>9531836.5712453369</v>
+        <v>10714929.701390397</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10829,22 +10829,22 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1767</v>
+        <v>1770</v>
       </c>
       <c r="C87" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D87" s="10">
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1348</v>
+        <v>1068</v>
       </c>
       <c r="F87" s="10">
-        <v>42084775.50188525</v>
+        <v>48346216.085946538</v>
       </c>
       <c r="G87" s="10">
-        <v>1661</v>
+        <v>1798</v>
       </c>
       <c r="H87" s="10">
         <v>2</v>
@@ -10853,10 +10853,10 @@
         <v>9</v>
       </c>
       <c r="J87" s="10">
-        <v>1448</v>
+        <v>1408</v>
       </c>
       <c r="K87" s="10">
-        <v>51153393.19780989</v>
+        <v>58448649.984140679</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10864,7 +10864,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C88" s="10">
         <v>0</v>
@@ -10873,13 +10873,13 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>900</v>
+        <v>606</v>
       </c>
       <c r="F88" s="10">
-        <v>9931053.6177717447</v>
+        <v>11404405.748291109</v>
       </c>
       <c r="G88" s="10">
-        <v>925</v>
+        <v>630</v>
       </c>
       <c r="H88" s="10">
         <v>2</v>
@@ -10888,10 +10888,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>763</v>
+        <v>739</v>
       </c>
       <c r="K88" s="10">
-        <v>11320774.287268532</v>
+        <v>12978754.33964923</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10899,7 +10899,7 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C89" s="10">
         <v>4</v>
@@ -10908,13 +10908,13 @@
         <v>7</v>
       </c>
       <c r="E89" s="10">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="F89" s="10">
-        <v>18693370.236158248</v>
+        <v>21469701.985500403</v>
       </c>
       <c r="G89" s="10">
-        <v>766</v>
+        <v>680</v>
       </c>
       <c r="H89" s="10">
         <v>5</v>
@@ -10923,10 +10923,10 @@
         <v>8</v>
       </c>
       <c r="J89" s="10">
-        <v>522</v>
+        <v>741</v>
       </c>
       <c r="K89" s="10">
-        <v>20146519.231406134</v>
+        <v>23423151.156611502</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10934,7 +10934,7 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C90" s="10">
         <v>2</v>
@@ -10943,13 +10943,13 @@
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>362</v>
+        <v>296</v>
       </c>
       <c r="F90" s="10">
-        <v>4601412.716901565</v>
+        <v>5260642.5641915696</v>
       </c>
       <c r="G90" s="10">
-        <v>100</v>
+        <v>374</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -10958,10 +10958,10 @@
         <v>1</v>
       </c>
       <c r="J90" s="10">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="K90" s="10">
-        <v>4177363.4227665081</v>
+        <v>4319308.1950398814</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.35">
@@ -10969,34 +10969,34 @@
         <v>203</v>
       </c>
       <c r="B91" s="13">
-        <v>84698</v>
+        <v>84549</v>
       </c>
       <c r="C91" s="13">
-        <v>1022</v>
+        <v>1079</v>
       </c>
       <c r="D91" s="13">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E91" s="13">
-        <v>69168</v>
+        <v>69895</v>
       </c>
       <c r="F91" s="13">
-        <v>1934635103.3523769</v>
+        <v>2236113285.2862201</v>
       </c>
       <c r="G91" s="13">
-        <v>83602</v>
+        <v>84637</v>
       </c>
       <c r="H91" s="13">
-        <v>1321</v>
+        <v>1539</v>
       </c>
       <c r="I91" s="13">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="J91" s="13">
-        <v>71073</v>
+        <v>71296</v>
       </c>
       <c r="K91" s="13">
-        <v>2019834901.3869331</v>
+        <v>2327481078.9661198</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1163,27 +1163,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10031059.186713256</v>
+        <v>11605840.967956211</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10451748.424652403</v>
+        <v>11745234.344032858</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>4.1938665709038592E-2</v>
+        <v>1.2010622621963618E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>-0.22790697674418603</v>
+        <v>-0.19859813084112155</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1211,15 +1211,15 @@
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>4.3478260869565188E-2</v>
+        <v>-3.1325301204819245E-2</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1243,27 +1243,27 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11847668.973308677</v>
+        <v>13599176.772227382</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11365040.339451777</v>
+        <v>12757065.964702409</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-4.0736168012813545E-2</v>
+        <v>-6.1923660647220657E-2</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>544</v>
+        <v>519</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>592</v>
+        <v>522</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>8.8235294117646967E-2</v>
+        <v>5.7803468208093012E-3</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="O3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Q3" s="12">
         <f t="shared" ref="Q3:Q66" si="3">IFERROR(P3/O3-1,0)</f>
-        <v>0.5</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -1295,11 +1295,11 @@
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>555</v>
+        <v>523</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-0.13145539906103287</v>
+        <v>-0.18153364632237867</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1323,27 +1323,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15693282.493840273</v>
+        <v>18579857.885549702</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13027212.983451417</v>
+        <v>14199336.303547801</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>-0.16988603317599793</v>
+        <v>-0.23576722755284407</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>307</v>
+        <v>534</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>-0.61768368617683689</v>
+        <v>-0.32405063291139236</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1359,27 +1359,27 @@
       </c>
       <c r="O4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="3"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>767</v>
+        <v>680</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>1.4550264550264647E-2</v>
+        <v>-0.10994764397905754</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25636221.356210988</v>
+        <v>29318297.392397735</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27343918.425037589</v>
+        <v>30652409.729366504</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>6.6612666706939327E-2</v>
+        <v>4.5504427460876462E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1123</v>
+        <v>1107</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>955</v>
+        <v>988</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-0.1495992876224399</v>
+        <v>-0.1074977416440831</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1439,27 +1439,27 @@
       </c>
       <c r="O5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0.125</v>
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1222</v>
+        <v>1013</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>1.3266998341625147E-2</v>
+        <v>-0.15863787375415284</v>
       </c>
       <c r="U5">
         <v>1</v>
@@ -1483,27 +1483,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11567766.085140552</v>
+        <v>13283507.106397798</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12437976.728047604</v>
+        <v>14049843.096260291</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>7.5227199141317813E-2</v>
+        <v>5.7690787811104371E-2</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1220159151193685E-2</v>
+        <v>5.2054794520547842E-2</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1531,15 +1531,15 @@
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>392</v>
+        <v>446</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>-4.6228710462287159E-2</v>
+        <v>9.3137254901960675E-2</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1563,27 +1563,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9574246.6887910403</v>
+        <v>10853864.931478668</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7884637.3578127623</v>
+        <v>8990943.7944361828</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>-0.17647438862802356</v>
+        <v>-0.17163666111594877</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4285714285714235E-2</v>
+        <v>-0.10069444444444442</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1611,15 +1611,15 @@
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>374</v>
+        <v>288</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>-1.8372703412073532E-2</v>
+        <v>-0.25388601036269431</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -1643,31 +1643,31 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11358396.529773155</v>
+        <v>13059467.406061232</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11563533.990490887</v>
+        <v>12805254.646765212</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>1.8060424301970412E-2</v>
+        <v>-1.9465783051614616E-2</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10658914728682167</v>
+        <v>-0.16000000000000003</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="P8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -1695,11 +1695,11 @@
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>635</v>
+        <v>549</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>6.7226890756302504E-2</v>
+        <v>-7.7310924369747847E-2</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1723,27 +1723,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5043289.1807349501</v>
+        <v>5741955.8301954772</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5164313.8401981639</v>
+        <v>5817133.5092633413</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>2.3997168341153285E-2</v>
+        <v>1.3092695466677684E-2</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>-3.1746031746031744E-2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1771,15 +1771,15 @@
       </c>
       <c r="R9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>4.7619047619047672E-2</v>
+        <v>-4.705882352941182E-2</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1803,27 +1803,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1745372.714907849</v>
+        <v>2514733.047916695</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5210121.033227575</v>
+        <v>5792518.2435795534</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>1.9851051232359018</v>
+        <v>1.3034326639077283</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>-0.32203389830508478</v>
+        <v>-6.3953488372093026E-2</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1843,11 +1843,11 @@
       </c>
       <c r="P10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -1855,11 +1855,11 @@
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>0.12365591397849451</v>
+        <v>6.4516129032258007E-2</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1883,27 +1883,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10047490.355405016</v>
+        <v>11277110.458755046</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9232093.1963549405</v>
+        <v>10388805.87979324</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>-8.1154311196868667E-2</v>
+        <v>-7.8770584203346705E-2</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>2.666666666666595E-3</v>
+        <v>-8.3333333333333037E-3</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1919,27 +1919,27 @@
       </c>
       <c r="O11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>357</v>
+        <v>441</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>-5.0531914893616969E-2</v>
+        <v>0.15748031496062986</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4958031.3880373193</v>
+        <v>5807814.7055882718</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4506119.9493312472</v>
+        <v>5110223.9326150976</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>-9.1147353321812119E-2</v>
+        <v>-0.12011243614606937</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>-0.24913494809688586</v>
+        <v>-8.98876404494382E-2</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2011,15 +2011,15 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>8.7155963302752326E-2</v>
+        <v>4.5454545454545414E-2</v>
       </c>
       <c r="U12">
         <v>2</v>
@@ -2043,19 +2043,19 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5380823.6863983767</v>
+        <v>6163624.0632635523</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5726064.83562293</v>
+        <v>6597285.5653288113</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>6.4161394118386061E-2</v>
+        <v>7.0358201216386584E-2</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>-7.5999999999999956E-2</v>
+        <v>8.733624454148492E-3</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2083,23 +2083,23 @@
       </c>
       <c r="P13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>-5.600000000000005E-2</v>
+        <v>0.18672199170124482</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2123,27 +2123,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21396343.684887961</v>
+        <v>25128238.575954139</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30850756.8154644</v>
+        <v>35041852.324905545</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>0.44187050226034663</v>
+        <v>0.3945208383383465</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1023</v>
+        <v>1101</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1239</v>
+        <v>1270</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>0.21114369501466279</v>
+        <v>0.15349682107175289</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2151,15 +2151,15 @@
       </c>
       <c r="M14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="2"/>
-        <v>0.66666666666666674</v>
+        <v>1</v>
       </c>
       <c r="O14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2167,19 +2167,19 @@
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="3"/>
-        <v>1.6666666666666665</v>
+        <v>1</v>
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1435</v>
+        <v>1428</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1397</v>
+        <v>1411</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>-2.6480836236933758E-2</v>
+        <v>-1.1904761904761862E-2</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2203,27 +2203,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37588029.534986168</v>
+        <v>43125207.394685581</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43478586.493676245</v>
+        <v>48844413.069735177</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>0.15671364079373373</v>
+        <v>0.13261862424699644</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>934</v>
+        <v>908</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>5.1801801801801828E-2</v>
+        <v>1.4525139664804509E-2</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="O15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2251,15 +2251,15 @@
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1252</v>
+        <v>1151</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>8.8638195004029363E-3</v>
+        <v>-6.8016194331983804E-2</v>
       </c>
       <c r="U15">
         <v>3</v>
@@ -2283,27 +2283,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21212507.702614099</v>
+        <v>23325512.922970474</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21010450.610085927</v>
+        <v>23662126.798789363</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>-9.5253750928878667E-3</v>
+        <v>1.4431145712872961E-2</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1135</v>
+        <v>894</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>964</v>
+        <v>903</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>-0.15066079295154189</v>
+        <v>1.0067114093959662E-2</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2323,11 +2323,11 @@
       </c>
       <c r="P16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <v>1</v>
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -2335,11 +2335,11 @@
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1015</v>
+        <v>1074</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>-1.2645914396887115E-2</v>
+        <v>4.474708171206232E-2</v>
       </c>
       <c r="U16">
         <v>3</v>
@@ -2363,27 +2363,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16152779.022945462</v>
+        <v>18890377.12714364</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20384337.964686051</v>
+        <v>22825110.871727254</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>0.26197095470256504</v>
+        <v>0.20829302232033164</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>767</v>
+        <v>667</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>0.16388467374810323</v>
+        <v>-4.166666666666663E-2</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2411,15 +2411,15 @@
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>915</v>
+        <v>785</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>1.094091903719896E-3</v>
+        <v>-0.14301310043668125</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2443,27 +2443,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>77653874.701062784</v>
+        <v>86538124.393357381</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>73261977.766638085</v>
+        <v>82403650.006621614</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>-5.6557344386636177E-2</v>
+        <v>-4.777633460071995E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2030</v>
+        <v>2092</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2196</v>
+        <v>2200</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>8.1773399014778425E-2</v>
+        <v>5.1625239005736123E-2</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2479,27 +2479,27 @@
       </c>
       <c r="O18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>-0.33522727272727271</v>
+        <v>-0.34806629834254144</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2824</v>
+        <v>2813</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2756</v>
+        <v>2724</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>-2.4079320113314484E-2</v>
+        <v>-3.1638819765375081E-2</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2523,27 +2523,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20823267.672696736</v>
+        <v>26002211.72344863</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38461930.24138011</v>
+        <v>43335722.521319821</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>0.84706506423153827</v>
+        <v>0.66661678561135407</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1147</v>
+        <v>1167</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1218</v>
+        <v>1190</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>6.1900610287707103E-2</v>
+        <v>1.9708654670094194E-2</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="O19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2567,19 +2567,19 @@
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.16666666666666663</v>
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1363</v>
+        <v>1267</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>-1.0167029774872938E-2</v>
+        <v>-8.2548877624909478E-2</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2603,27 +2603,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>78189279.719223753</v>
+        <v>87558270.252023414</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>68713287.365769863</v>
+        <v>78374783.039749846</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>-0.12119298690922853</v>
+        <v>-0.10488429232144802</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2154</v>
+        <v>2002</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2185</v>
+        <v>2147</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>1.4391829155060432E-2</v>
+        <v>7.2427572427572473E-2</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2639,27 +2639,27 @@
       </c>
       <c r="O20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>-0.6875</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2957</v>
+        <v>2936</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2776</v>
+        <v>2548</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-6.1210686506594558E-2</v>
+        <v>-0.13215258855585832</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2683,27 +2683,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11618026.828046735</v>
+        <v>13183778.010977268</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10481400.58186681</v>
+        <v>11826239.269592175</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>-9.783298515338501E-2</v>
+        <v>-0.10297038832531613</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>453</v>
+        <v>482</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>398</v>
+        <v>476</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12141280353200878</v>
+        <v>-1.2448132780082943E-2</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="O21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -2735,11 +2735,11 @@
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-3.1894934333958735E-2</v>
+        <v>-9.3808630393996228E-2</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2763,27 +2763,27 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31902604.980764087</v>
+        <v>36192562.219717629</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29385357.135773905</v>
+        <v>32935272.975362118</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>-7.890414737316831E-2</v>
+        <v>-8.9998857350335526E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1279</v>
+        <v>1381</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1573</v>
+        <v>1449</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>0.22986708365910857</v>
+        <v>4.9239681390296886E-2</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2807,19 +2807,19 @@
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>-5.8823529411764719E-2</v>
+        <v>-0.11111111111111116</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1714</v>
+        <v>1698</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1744</v>
+        <v>1876</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>1.7502917152858899E-2</v>
+        <v>0.10482921083627805</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2843,27 +2843,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12991656.7694692</v>
+        <v>15022021.249958932</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12337413.658601355</v>
+        <v>13972572.86172664</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>-5.0358712709016151E-2</v>
+        <v>-6.986066460498197E-2</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>894</v>
+        <v>867</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>843</v>
+        <v>780</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>-5.7046979865771785E-2</v>
+        <v>-0.10034602076124566</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2891,15 +2891,15 @@
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>839</v>
+        <v>904</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>-4.6590909090909127E-2</v>
+        <v>3.1963470319634757E-2</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2923,27 +2923,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16148057.481919851</v>
+        <v>18344574.830965456</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15970386.192980677</v>
+        <v>18270548.609162889</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>-1.1002641595628693E-2</v>
+        <v>-4.0353195691191779E-3</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>871</v>
+        <v>759</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>783</v>
+        <v>760</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10103329506314584</v>
+        <v>1.3175230566535578E-3</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2963,23 +2963,23 @@
       </c>
       <c r="P24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="3"/>
-        <v>-0.4</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>-7.9185520361990669E-3</v>
+        <v>2.4000000000000021E-2</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -3003,27 +3003,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3545079.2402608488</v>
+        <v>4146758.08022347</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4033521.2907017982</v>
+        <v>4544499.9292088114</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>0.13778029131021885</v>
+        <v>9.5916337845275645E-2</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>-6.7415730337078705E-2</v>
+        <v>-0.203125</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3051,15 +3051,15 @@
       </c>
       <c r="R25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="S25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="4"/>
-        <v>-2.2321428571428603E-2</v>
+        <v>-0.19298245614035092</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -3083,19 +3083,19 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30369760.083999842</v>
+        <v>34683862.559180304</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30813505.786671042</v>
+        <v>34833450.097463757</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>1.4611432604137775E-2</v>
+        <v>4.3128857989278568E-3</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1456</v>
+        <v>1384</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>-1.717032967032972E-2</v>
+        <v>3.3959537572254339E-2</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3131,15 +3131,15 @@
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1647</v>
+        <v>1653</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1651</v>
+        <v>1686</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>2.4286581663630624E-3</v>
+        <v>1.9963702359346636E-2</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -3163,27 +3163,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25130828.725072499</v>
+        <v>28942176.601938333</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27992379.158031393</v>
+        <v>31477197.298174005</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>0.1138661388473825</v>
+        <v>8.7589151676515486E-2</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>-4.3923865300146137E-3</v>
+        <v>2.8776978417266452E-3</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="O27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3207,19 +3207,19 @@
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>895</v>
+        <v>839</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>2.2857142857142909E-2</v>
+        <v>-4.2237442922374413E-2</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -3243,31 +3243,31 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24348017.987532649</v>
+        <v>27322835.150993686</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27339018.879904401</v>
+        <v>31575073.436375592</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>0.12284371129934635</v>
+        <v>0.15562946750887452</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>813</v>
+        <v>623</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>915</v>
+        <v>868</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>0.1254612546125462</v>
+        <v>0.39325842696629221</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="N28" s="12">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="O28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3291,15 +3291,15 @@
       </c>
       <c r="R28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-3.7072243346007561E-2</v>
+        <v>-3.5440613026819889E-2</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -3323,27 +3323,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33287094.194697849</v>
+        <v>38750202.555159338</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33866219.070671238</v>
+        <v>38158631.406307779</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>1.7397880168994684E-2</v>
+        <v>-1.5266272428111294E-2</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>865</v>
+        <v>1017</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>-7.0520231213872853E-2</v>
+        <v>-0.19469026548672563</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3371,15 +3371,15 @@
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1140</v>
+        <v>993</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>1.4234875444839812E-2</v>
+        <v>-0.11339285714285718</v>
       </c>
       <c r="U29">
         <v>0</v>
@@ -3403,27 +3403,27 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46940123.260832466</v>
+        <v>49704479.1329192</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>48286581.885638237</v>
+        <v>51670729.287840143</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>2.8684599256885157E-2</v>
+        <v>3.9558812187988401E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1108</v>
+        <v>1153</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1214</v>
+        <v>261</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>9.566787003610111E-2</v>
+        <v>-0.77363399826539458</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3443,23 +3443,23 @@
       </c>
       <c r="P30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1453</v>
+        <v>598</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-0.586159169550173</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3483,27 +3483,27 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19339477.823665723</v>
+        <v>22482772.205797095</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19612777.992599472</v>
+        <v>22045431.28545827</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>1.4131724311569061E-2</v>
+        <v>-1.9452268445172338E-2</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>566</v>
+        <v>657</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>577</v>
+        <v>487</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>1.9434628975264934E-2</v>
+        <v>-0.25875190258751901</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3531,15 +3531,15 @@
       </c>
       <c r="R31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>-8.7591240875912746E-3</v>
+        <v>-4.1547277936962779E-2</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3563,27 +3563,27 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46678468.479174599</v>
+        <v>54659271.855845027</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>39716345.829926766</v>
+        <v>46584687.457568675</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14915062289059366</v>
+        <v>-0.14772579516923967</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>985</v>
+        <v>1597</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1632</v>
+        <v>1612</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>0.65685279187817258</v>
+        <v>9.3926111458986217E-3</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="O32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3607,19 +3607,19 @@
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1906</v>
+        <v>1923</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1856</v>
+        <v>1778</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-2.6232948583420734E-2</v>
+        <v>-7.5403016120644817E-2</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3643,27 +3643,27 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19600077.597591951</v>
+        <v>22656058.277334604</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19603837.280351806</v>
+        <v>22394741.412024934</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>1.9181978954607715E-4</v>
+        <v>-1.1534083383387794E-2</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>673</v>
+        <v>699</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>698</v>
+        <v>1430</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>3.7147102526003062E-2</v>
+        <v>1.0457796852646637</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3671,15 +3671,15 @@
       </c>
       <c r="M33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3687,19 +3687,19 @@
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>847</v>
+        <v>1266</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>-9.3567251461987855E-3</v>
+        <v>0.47724620770128356</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3723,27 +3723,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18503531.759908363</v>
+        <v>20514275.541951414</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17848929.749518771</v>
+        <v>20280297.833904956</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>-3.5377138747529235E-2</v>
+        <v>-1.1405604237301858E-2</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>458</v>
+        <v>560</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>0.27074235807860259</v>
+        <v>4.2857142857142927E-2</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3759,27 +3759,27 @@
       </c>
       <c r="O34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>731</v>
+        <v>764</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>-2.0107238605898137E-2</v>
+        <v>2.1390374331550888E-2</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3803,27 +3803,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27886563.921537865</v>
+        <v>31706807.770847913</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31244315.963416766</v>
+        <v>35210619.986819968</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>0.12040752139009792</v>
+        <v>0.11050662183638527</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>896</v>
+        <v>951</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>7.0489844683393033E-2</v>
+        <v>0.12014134275618371</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="O35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3847,19 +3847,19 @@
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="3"/>
-        <v>-0.6</v>
+        <v>-0.64705882352941169</v>
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1195</v>
+        <v>1383</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>3.1951640759930955E-2</v>
+        <v>0.19018932874354566</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3883,27 +3883,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25980146.357264768</v>
+        <v>30008831.32454332</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28569315.557240028</v>
+        <v>32153124.55919506</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>9.9659530949919306E-2</v>
+        <v>7.1455406292279866E-2</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>806</v>
+        <v>880</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>926</v>
+        <v>870</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>0.14888337468982638</v>
+        <v>-1.1363636363636354E-2</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3919,27 +3919,27 @@
       </c>
       <c r="O36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>318</v>
+        <v>391</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="3"/>
-        <v>1.65</v>
+        <v>2.2314049586776861</v>
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1315</v>
+        <v>1271</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1368</v>
+        <v>1309</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>4.0304182509505626E-2</v>
+        <v>2.9897718332021928E-2</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3963,27 +3963,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>47828167.354593977</v>
+        <v>54089568.346732005</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>47327626.983007781</v>
+        <v>53090474.700370014</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>-1.0465388896781946E-2</v>
+        <v>-1.8471096680925059E-2</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1627</v>
+        <v>1420</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1348</v>
+        <v>1436</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>-0.17148125384142598</v>
+        <v>1.1267605633802802E-2</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4003,23 +4003,23 @@
       </c>
       <c r="P37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="3"/>
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2319</v>
+        <v>2274</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2231</v>
+        <v>2316</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>-3.794739111686074E-2</v>
+        <v>1.846965699208436E-2</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4043,27 +4043,27 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17239734.609239098</v>
+        <v>19559864.968351118</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17601943.18951926</v>
+        <v>20014278.607087888</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>2.1010101865840181E-2</v>
+        <v>2.3231941502256603E-2</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>-5.97938144329897E-2</v>
+        <v>-4.3749999999999956E-2</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4091,15 +4091,15 @@
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>586</v>
+        <v>516</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>-6.0897435897435903E-2</v>
+        <v>-0.16908212560386471</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4123,27 +4123,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>55863457.338151634</v>
+        <v>62806648.991798967</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>53820568.949218951</v>
+        <v>61438729.827034511</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>-3.6569315367767308E-2</v>
+        <v>-2.1779846349437859E-2</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1813</v>
+        <v>1899</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1899</v>
+        <v>2156</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>4.7435190292333118E-2</v>
+        <v>0.1353343865192207</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4159,27 +4159,27 @@
       </c>
       <c r="O39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="3"/>
-        <v>0.33333333333333326</v>
+        <v>0.25</v>
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2060</v>
+        <v>2052</v>
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2037</v>
+        <v>2293</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>-1.1165048543689271E-2</v>
+        <v>0.11744639376218324</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4203,27 +4203,27 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38794693.14317365</v>
+        <v>43715380.459994063</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>42105567.733273089</v>
+        <v>47264068.682267107</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>8.5343492159623446E-2</v>
+        <v>8.1177109404791947E-2</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1214</v>
+        <v>849</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>879</v>
+        <v>830</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>-0.27594728171334426</v>
+        <v>-2.2379269729093099E-2</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4251,15 +4251,15 @@
       </c>
       <c r="R40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>934</v>
+        <v>1015</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>3.4330011074197087E-2</v>
+        <v>0.13028953229398654</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21326951.017018501</v>
+        <v>25162534.388928577</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29772505.600011189</v>
+        <v>33425173.710316837</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>0.39600384397438226</v>
+        <v>0.32837071153785646</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>936</v>
+        <v>1095</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>981</v>
+        <v>941</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>4.8076923076923128E-2</v>
+        <v>-0.14063926940639271</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4319,27 +4319,27 @@
       </c>
       <c r="O41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1066</v>
+        <v>1121</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-2.0220588235294157E-2</v>
+        <v>2.1877848678213407E-2</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4363,27 +4363,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28987672.484540347</v>
+        <v>32737539.875770304</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30625362.113111999</v>
+        <v>34760498.561225682</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>5.6496071888664456E-2</v>
+        <v>6.1793240821757855E-2</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>0.15780141843971629</v>
+        <v>0.17801047120418856</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4403,23 +4403,23 @@
       </c>
       <c r="P42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="3"/>
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>832</v>
+        <v>728</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>-1.2004801920768582E-3</v>
+        <v>-0.12289156626506026</v>
       </c>
       <c r="U42">
         <v>1</v>
@@ -4443,43 +4443,43 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18797706.720624097</v>
+        <v>21253968.086201899</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18111709.274998784</v>
+        <v>20575729.222999271</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>-3.6493677437400618E-2</v>
+        <v>-3.1911164091892097E-2</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1046</v>
+        <v>671</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>577</v>
+        <v>558</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>-0.44837476099426388</v>
+        <v>-0.16840536512667659</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="2"/>
-        <v>-9.9999999999999978E-2</v>
+        <v>-0.27272727272727271</v>
       </c>
       <c r="O43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4491,15 +4491,15 @@
       </c>
       <c r="R43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>3.463203463203457E-2</v>
+        <v>1.1412268188302432E-2</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4523,31 +4523,31 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16326037.684438676</v>
+        <v>18181143.725431334</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16974532.487811487</v>
+        <v>19303865.027933616</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>3.9721505971466176E-2</v>
+        <v>6.175196233292235E-2</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>475</v>
+        <v>732</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>800</v>
+        <v>744</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>0.68421052631578938</v>
+        <v>1.6393442622950838E-2</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="N44" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4571,15 +4571,15 @@
       </c>
       <c r="R44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>705</v>
+        <v>795</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>2.7696793002915499E-2</v>
+        <v>0.15217391304347827</v>
       </c>
       <c r="U44">
         <v>2</v>
@@ -4603,27 +4603,27 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>50350879.089841045</v>
+        <v>58056100.845717795</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>55925546.402918451</v>
+        <v>62385273.714933924</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>0.11071638497374647</v>
+        <v>7.4568784436984004E-2</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1074</v>
+        <v>1454</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1140</v>
+        <v>1094</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>6.1452513966480549E-2</v>
+        <v>-0.24759284731774411</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4651,15 +4651,15 @@
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1287</v>
+        <v>1195</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>4.0420371867421201E-2</v>
+        <v>-3.4733441033925727E-2</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4683,27 +4683,27 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24329645.084981102</v>
+        <v>27501290.30900624</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24008510.265390374</v>
+        <v>27142791.840424143</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>-1.3199321998698998E-2</v>
+        <v>-1.3035696309299905E-2</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>-5.4288816503800241E-3</v>
+        <v>-1.2779552715655007E-2</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4727,19 +4727,19 @@
       </c>
       <c r="Q46" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>885</v>
+        <v>938</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>-3.066812705366917E-2</v>
+        <v>3.076923076923066E-2</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4763,27 +4763,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42604532.316107005</v>
+        <v>48007052.156097807</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43979107.294347867</v>
+        <v>49754972.721462965</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>3.2263585668353745E-2</v>
+        <v>3.6409662473790183E-2</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1138</v>
+        <v>1097</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>0.19037656903765687</v>
+        <v>0.15352260778128279</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="O47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4807,19 +4807,19 @@
       </c>
       <c r="Q47" s="12">
         <f t="shared" si="3"/>
-        <v>-0.25</v>
+        <v>-0.4</v>
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1419</v>
+        <v>1495</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>5.2670623145400608E-2</v>
+        <v>0.11152416356877315</v>
       </c>
       <c r="U47">
         <v>5</v>
@@ -4843,27 +4843,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22005709.005341128</v>
+        <v>24801070.576041028</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21167858.625659622</v>
+        <v>24039362.163346086</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>-3.807422789595849E-2</v>
+        <v>-3.0712723080220106E-2</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>6.8965517241379226E-2</v>
+        <v>6.2162162162162193E-2</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4891,15 +4891,15 @@
       </c>
       <c r="R48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>2.2587268993839782E-2</v>
+        <v>6.1855670103092564E-3</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4923,27 +4923,27 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16006981.240799496</v>
+        <v>18011128.017276742</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17965408.831571799</v>
+        <v>20227997.511374339</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>0.12234834047162813</v>
+        <v>0.12308332337492245</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>460</v>
+        <v>359</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>0.52317880794701987</v>
+        <v>0.1433121019108281</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4971,15 +4971,15 @@
       </c>
       <c r="R49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>6.5502183406114245E-3</v>
+        <v>-2.6315789473684181E-2</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -5003,27 +5003,27 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13856935.277226221</v>
+        <v>15806729.969322076</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5873087.196715177</v>
+        <v>6362445.1973371059</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-0.57616261610404162</v>
+        <v>-0.59748504531389934</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>10</v>
+        <v>315</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-0.9668874172185431</v>
+        <v>-5.9701492537313383E-2</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="O50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="Q50" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -5055,11 +5055,11 @@
       </c>
       <c r="S50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>385</v>
+        <v>221</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="4"/>
-        <v>-8.7677725118483374E-2</v>
+        <v>-0.476303317535545</v>
       </c>
       <c r="U50">
         <v>4</v>
@@ -5083,31 +5083,31 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32922233.232268192</v>
+        <v>37145639.08092615</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34613136.454139821</v>
+        <v>39087199.660863936</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>5.1360526181265298E-2</v>
+        <v>5.2268869993268074E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>872</v>
+        <v>921</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>7.7981651376146877E-2</v>
+        <v>8.6862106406080386E-3</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="N51" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5135,11 +5135,11 @@
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1103</v>
+        <v>972</v>
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-9.0579710144922387E-4</v>
+        <v>-0.11956521739130432</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5163,27 +5163,27 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32767497.85062144</v>
+        <v>38646435.694154151</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35690534.982378751</v>
+        <v>40674626.262159429</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>8.9205381048094834E-2</v>
+        <v>5.2480663004895733E-2</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1002</v>
+        <v>926</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>963</v>
+        <v>883</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>-3.8922155688622784E-2</v>
+        <v>-4.643628509719222E-2</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5211,15 +5211,15 @@
       </c>
       <c r="R52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>941</v>
+        <v>1110</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>-6.0878243512974106E-2</v>
+        <v>0.10009910802775024</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5243,27 +5243,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>61113798.319160461</v>
+        <v>69493810.821061969</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>64882425.838394135</v>
+        <v>72374424.098745659</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>6.1665738718323704E-2</v>
+        <v>4.1451364425832304E-2</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1601</v>
+        <v>1773</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1658</v>
+        <v>1501</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>3.5602748282323571E-2</v>
+        <v>-0.15341229554427527</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5279,27 +5279,27 @@
       </c>
       <c r="O53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q53" s="12">
         <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2048</v>
+        <v>2036</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2073</v>
+        <v>1846</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>1.220703125E-2</v>
+        <v>-9.3320235756385039E-2</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5323,27 +5323,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15237386.793200787</v>
+        <v>17384753.173172586</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16923572.104882669</v>
+        <v>18923708.401292492</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>0.1106610558993153</v>
+        <v>8.8523271673178305E-2</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>447</v>
+        <v>498</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>0.14093959731543615</v>
+        <v>9.4377510040160706E-2</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5371,15 +5371,15 @@
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>662</v>
+        <v>562</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>-2.0710059171597628E-2</v>
+        <v>-0.18786127167630062</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5403,27 +5403,27 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26569100.705542248</v>
+        <v>30326520.036693711</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30353544.458011288</v>
+        <v>34240647.79706008</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>0.14243778118088946</v>
+        <v>0.12906616900423962</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>715</v>
+        <v>790</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>738</v>
+        <v>775</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>3.2167832167832255E-2</v>
+        <v>-1.8987341772151889E-2</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5451,15 +5451,15 @@
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>922</v>
+        <v>903</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>6.2211981566820285E-2</v>
+        <v>4.7563805104408274E-2</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5483,27 +5483,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16880304.095586132</v>
+        <v>19194844.171725195</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15435179.114867197</v>
+        <v>17557864.945764679</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>-8.5610127195327457E-2</v>
+        <v>-8.5282235756404479E-2</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>740</v>
+        <v>658</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>613</v>
+        <v>574</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>-0.17162162162162165</v>
+        <v>-0.12765957446808507</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5531,15 +5531,15 @@
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-9.9601593625498031E-2</v>
+        <v>-0.11126005361930291</v>
       </c>
       <c r="U56">
         <v>2</v>
@@ -5563,27 +5563,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34340368.090365291</v>
+        <v>38667760.821667828</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>37729757.422791846</v>
+        <v>42707054.597119845</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>9.8699854454312064E-2</v>
+        <v>0.10446153823286708</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>869</v>
+        <v>938</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1163</v>
+        <v>1062</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>0.33831990794016109</v>
+        <v>0.13219616204690832</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5607,19 +5607,19 @@
       </c>
       <c r="Q57" s="12">
         <f t="shared" si="3"/>
-        <v>0.19999999999999996</v>
+        <v>0</v>
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1099</v>
+        <v>1156</v>
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>-1.1690647482014427E-2</v>
+        <v>4.1441441441441462E-2</v>
       </c>
       <c r="U57">
         <v>2</v>
@@ -5643,27 +5643,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>43422115.586745128</v>
+        <v>47149145.488019548</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>51933160.195166431</v>
+        <v>59553692.350798987</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>0.19600713814642767</v>
+        <v>0.26309165806475532</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1339</v>
+        <v>1041</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1618</v>
+        <v>1603</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>0.20836445108289769</v>
+        <v>0.53986551392891458</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5679,27 +5679,27 @@
       </c>
       <c r="O58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q58" s="12">
         <f t="shared" si="3"/>
-        <v>1.6</v>
+        <v>1.125</v>
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1478</v>
+        <v>1497</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1621</v>
+        <v>1748</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>9.6752368064952687E-2</v>
+        <v>0.16766867067468261</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5723,27 +5723,27 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23207604.557711422</v>
+        <v>26294359.603784792</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21502821.729210172</v>
+        <v>24696556.024657793</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>-7.3457940230836294E-2</v>
+        <v>-6.0766019907060653E-2</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>693</v>
+        <v>754</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>760</v>
+        <v>809</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>9.6681096681096701E-2</v>
+        <v>7.2944297082228049E-2</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5771,15 +5771,15 @@
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>798</v>
+        <v>875</v>
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>3.771131339401812E-2</v>
+        <v>0.14528795811518314</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5803,27 +5803,27 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25855386.35664548</v>
+        <v>29381517.297919996</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27515605.348086242</v>
+        <v>30966755.450658873</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>6.421172627397409E-2</v>
+        <v>5.3953583699065888E-2</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1367521367521292E-3</v>
+        <v>2.1276595744681437E-3</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="O60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5847,19 +5847,19 @@
       </c>
       <c r="Q60" s="12">
         <f t="shared" si="3"/>
-        <v>-0.2857142857142857</v>
+        <v>-0.5</v>
       </c>
       <c r="R60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>644</v>
+        <v>567</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>9.4043887147334804E-3</v>
+        <v>-0.10849056603773588</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5883,27 +5883,27 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>83988262.907164082</v>
+        <v>94637122.61423178</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>87322079.567863107</v>
+        <v>98297860.045866206</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>3.9693839892653182E-2</v>
+        <v>3.8681833624175654E-2</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1969</v>
+        <v>1567</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1637</v>
+        <v>1667</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>-0.16861350939563235</v>
+        <v>6.3816209317166583E-2</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5919,27 +5919,27 @@
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
-        <v>0.63636363636363646</v>
+        <v>0.35714285714285721</v>
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1983</v>
+        <v>1990</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1957</v>
+        <v>1973</v>
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>-1.3111447302067591E-2</v>
+        <v>-8.5427135678391997E-3</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5963,27 +5963,27 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>62144411.904331289</v>
+        <v>70773748.576810673</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>63302163.709051661</v>
+        <v>71935440.42983456</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>1.8630022704256621E-2</v>
+        <v>1.6414163109689017E-2</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1096</v>
+        <v>1356</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1318</v>
+        <v>1328</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>0.20255474452554734</v>
+        <v>-2.0648967551622377E-2</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6003,23 +6003,23 @@
       </c>
       <c r="P62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q62" s="12">
         <f t="shared" si="3"/>
-        <v>-0.1875</v>
+        <v>-0.125</v>
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1597</v>
+        <v>1671</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>8.8439671509792372E-3</v>
+        <v>4.5028142589118136E-2</v>
       </c>
       <c r="U62">
         <v>9</v>
@@ -6043,27 +6043,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>40291786.850265786</v>
+        <v>45665609.810448475</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>42230040.117961869</v>
+        <v>47462901.347901933</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>4.8105418478934903E-2</v>
+        <v>3.9357659843233472E-2</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>720</v>
+        <v>654</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>3.1944444444444553E-2</v>
+        <v>0.11926605504587151</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6087,19 +6087,19 @@
       </c>
       <c r="Q63" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>896</v>
+        <v>937</v>
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>3.3594624860022737E-3</v>
+        <v>4.8098434004474333E-2</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6123,27 +6123,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>60482844.879700385</v>
+        <v>67656800.451480851</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>56679542.814377584</v>
+        <v>64152120.69018504</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>-6.2882327590369158E-2</v>
+        <v>-5.180084984670752E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1405</v>
+        <v>1245</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1337</v>
+        <v>1327</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>-4.8398576512455493E-2</v>
+        <v>6.5863453815261153E-2</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6159,27 +6159,27 @@
       </c>
       <c r="O64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>462</v>
+        <v>513</v>
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>0.23860589812332433</v>
+        <v>0.36074270557029187</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2275</v>
+        <v>2204</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2369</v>
+        <v>2091</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>4.1318681318681216E-2</v>
+        <v>-5.1270417422867531E-2</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6203,15 +6203,15 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2049584.514477622</v>
+        <v>2633379.3830935382</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4609199.2052098904</v>
+        <v>5153593.4177207183</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>1.2488456429349233</v>
+        <v>0.95702656852526191</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
@@ -6219,11 +6219,11 @@
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4390243902439046E-2</v>
+        <v>7.3170731707317138E-2</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6251,15 +6251,15 @@
       </c>
       <c r="R65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.1587301587301626E-2</v>
       </c>
       <c r="U65">
         <v>2</v>
@@ -6283,27 +6283,27 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>43221691.643919691</v>
+        <v>48997107.208894491</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>42527106.473903023</v>
+        <v>47950631.785390586</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-1.6070291180155127E-2</v>
+        <v>-2.1357902192926548E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1620</v>
+        <v>1571</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1580</v>
+        <v>1523</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4691358024691357E-2</v>
+        <v>-3.0553787396562671E-2</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6323,23 +6323,23 @@
       </c>
       <c r="P66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q66" s="12">
         <f t="shared" si="3"/>
-        <v>0.88888888888888884</v>
+        <v>1</v>
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1592</v>
+        <v>1715</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>-4.0385774562989751E-2</v>
+        <v>3.1268791340950175E-2</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6363,27 +6363,27 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20584123.922306944</v>
+        <v>23101263.016764838</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19382725.801420636</v>
+        <v>22046341.14536155</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>-5.8365278280527511E-2</v>
+        <v>-4.566511669243889E-2</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>647</v>
+        <v>612</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>9.4754653130287636E-2</v>
+        <v>-3.2573289902280145E-3</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6403,23 +6403,23 @@
       </c>
       <c r="P67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q67" s="12">
         <f t="shared" ref="Q67:Q85" si="8">IFERROR(P67/O67-1,0)</f>
-        <v>0</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>791</v>
+        <v>877</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>6.8918918918918992E-2</v>
+        <v>0.18673883626522336</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6443,27 +6443,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30147825.724716209</v>
+        <v>34973917.453895658</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32338446.233785421</v>
+        <v>36678397.562773459</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>7.26626367377885E-2</v>
+        <v>4.8735750323787075E-2</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1057</v>
+        <v>982</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>952</v>
+        <v>1117</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>-9.9337748344370813E-2</v>
+        <v>0.13747454175152751</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="O68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6487,19 +6487,19 @@
       </c>
       <c r="Q68" s="12">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>1.8695652173913042</v>
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1362</v>
+        <v>1391</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1484</v>
+        <v>1378</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>8.9574155653450838E-2</v>
+        <v>-9.3457943925233655E-3</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6523,27 +6523,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18961499.08903724</v>
+        <v>22203502.898916803</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24722694.050578289</v>
+        <v>27770658.560409263</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>0.30383647065499875</v>
+        <v>0.25073321479216015</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1420</v>
+        <v>1377</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>0.17744610281923712</v>
+        <v>0.13990066225165565</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6559,27 +6559,27 @@
       </c>
       <c r="O69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q69" s="12">
         <f t="shared" si="8"/>
-        <v>-0.19999999999999996</v>
+        <v>0</v>
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1262</v>
+        <v>1253</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1340</v>
+        <v>1561</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>6.1806656101426327E-2</v>
+        <v>0.24581005586592175</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6603,31 +6603,31 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>53783637.746164359</v>
+        <v>61243048.896313921</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>56895215.540526107</v>
+        <v>63578906.020253301</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>5.7853613566398288E-2</v>
+        <v>3.8140771337071167E-2</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1165</v>
+        <v>1241</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1308</v>
+        <v>1292</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>0.12274678111587978</v>
+        <v>4.1095890410958846E-2</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -6635,31 +6635,31 @@
       </c>
       <c r="N70" s="12">
         <f t="shared" si="7"/>
-        <v>0.75</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="O70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q70" s="12">
         <f t="shared" si="8"/>
-        <v>0.19999999999999996</v>
+        <v>7.6923076923076872E-2</v>
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1752</v>
+        <v>1758</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1798</v>
+        <v>1564</v>
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>2.6255707762557146E-2</v>
+        <v>-0.11035267349260525</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6683,27 +6683,27 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10904494.48472932</v>
+        <v>12389661.65920596</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10133380.339113291</v>
+        <v>11379397.772014776</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-7.0715258437325845E-2</v>
+        <v>-8.1540877788258359E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>-7.407407407407407E-2</v>
+        <v>-4.7727272727272729E-2</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6731,15 +6731,15 @@
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>-4.125736738703345E-2</v>
+        <v>-6.903353057199213E-2</v>
       </c>
       <c r="U71">
         <v>1</v>
@@ -6763,27 +6763,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17298035.563470758</v>
+        <v>19944616.410577688</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20101925.882868141</v>
+        <v>22860464.684708528</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>0.16209299079708894</v>
+        <v>0.14619726015810519</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1324</v>
+        <v>791</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>771</v>
+        <v>835</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>-0.41767371601208458</v>
+        <v>5.5625790139064435E-2</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6811,15 +6811,15 @@
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>888</v>
+        <v>831</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>7.9455164585697791E-3</v>
+        <v>-5.4607508532423243E-2</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6843,27 +6843,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17062080.811463322</v>
+        <v>19632821.125206627</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19008135.274495997</v>
+        <v>21790440.960611559</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>0.11405727616324501</v>
+        <v>0.10989861424626124</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>-4.7619047619047672E-2</v>
+        <v>-4.1067761806981018E-3</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="O73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="Q73" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -6895,11 +6895,11 @@
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>636</v>
+        <v>596</v>
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-1.3953488372092981E-2</v>
+        <v>-7.5968992248061973E-2</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6923,27 +6923,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13406292.038853647</v>
+        <v>14969353.601374509</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12587822.709509639</v>
+        <v>14624074.907011259</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>-6.1051133823726067E-2</v>
+        <v>-2.306570501023808E-2</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>700</v>
+        <v>596</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1099</v>
+        <v>897</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>0.57000000000000006</v>
+        <v>0.50503355704697994</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6963,23 +6963,23 @@
       </c>
       <c r="P74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q74" s="12">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>629</v>
+        <v>934</v>
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>3.1147540983606614E-2</v>
+        <v>0.51623376623376616</v>
       </c>
       <c r="U74">
         <v>1</v>
@@ -7003,27 +7003,27 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14534308.575940792</v>
+        <v>16533756.493633192</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13056774.364971524</v>
+        <v>14984463.80901321</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>-0.10165837633412345</v>
+        <v>-9.3704820511695708E-2</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>0.13827160493827151</v>
+        <v>-4.2462845010615702E-2</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7031,11 +7031,11 @@
       </c>
       <c r="M75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N75" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.14285714285714279</v>
       </c>
       <c r="O75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7051,15 +7051,15 @@
       </c>
       <c r="R75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>-2.2421524663677195E-3</v>
+        <v>2.9411764705882248E-2</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -7083,27 +7083,27 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38552320.650037184</v>
+        <v>43975831.586132079</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31224051.282621074</v>
+        <v>36846421.380385205</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>-0.19008633576015455</v>
+        <v>-0.16212110035447647</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>502</v>
+        <v>911</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>777</v>
+        <v>716</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>0.547808764940239</v>
+        <v>-0.21405049396267839</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7119,27 +7119,27 @@
       </c>
       <c r="O76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q76" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>873</v>
+        <v>821</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-6.1290322580645151E-2</v>
+        <v>-0.10663764961915123</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7163,27 +7163,27 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22945629.138666265</v>
+        <v>25803193.875584789</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23789675.00632247</v>
+        <v>26570428.250516757</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>3.6784603401171623E-2</v>
+        <v>2.9734085579922409E-2</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>5.580029368575623E-2</v>
+        <v>5.0432276657060626E-2</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7211,15 +7211,15 @@
       </c>
       <c r="R77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>7.7419354838710319E-3</v>
+        <v>2.9792746113989743E-2</v>
       </c>
       <c r="U77">
         <v>2</v>
@@ -7243,27 +7243,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18897104.306166232</v>
+        <v>21430456.487673119</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19078223.4680488</v>
+        <v>21496542.429334331</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>9.5844928909805116E-3</v>
+        <v>3.0837393360811927E-3</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>919</v>
+        <v>969</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>771</v>
+        <v>912</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>-0.1610446137105549</v>
+        <v>-5.8823529411764719E-2</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7283,11 +7283,11 @@
       </c>
       <c r="P78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q78" s="12">
         <f t="shared" si="8"/>
-        <v>-0.33333333333333337</v>
+        <v>0</v>
       </c>
       <c r="R78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -7295,11 +7295,11 @@
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>949</v>
+        <v>1014</v>
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>-1.2486992715920908E-2</v>
+        <v>5.5150884495317465E-2</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7323,27 +7323,27 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18943363.690892089</v>
+        <v>22212680.787092481</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23083990.683582705</v>
+        <v>25862734.284609228</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>0.21857929036549173</v>
+        <v>0.16432296184788964</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>693</v>
+        <v>829</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>-0.19324796274738065</v>
+        <v>-4.2725173210161671E-2</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7371,15 +7371,15 @@
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>969</v>
+        <v>887</v>
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-2.4169184290030232E-2</v>
+        <v>-0.10943775100401609</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7403,27 +7403,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24876612.513585679</v>
+        <v>28452287.495797113</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27850529.967314817</v>
+        <v>31363755.234437577</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>0.11954672092532759</v>
+        <v>0.10232807253443288</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>791</v>
+        <v>743</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>-8.4702907711757258E-2</v>
+        <v>-2.2880215343203281E-2</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7443,23 +7443,23 @@
       </c>
       <c r="P80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q80" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>762</v>
+        <v>778</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>6.6050198150593431E-3</v>
+        <v>2.5032938076416267E-2</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7483,27 +7483,27 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11491400.052304247</v>
+        <v>13050905.489939887</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10714929.701390397</v>
+        <v>11988485.977876555</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>-6.7569691019342182E-2</v>
+        <v>-8.1405808423199666E-2</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>587</v>
+        <v>522</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>-7.4957410562180526E-2</v>
+        <v>5.1724137931034475E-2</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="O81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7527,19 +7527,19 @@
       </c>
       <c r="Q81" s="12">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>540</v>
+        <v>611</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>-4.5936395759717308E-2</v>
+        <v>8.1415929203539905E-2</v>
       </c>
       <c r="U81">
         <v>0</v>
@@ -7563,27 +7563,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>48346216.085946538</v>
+        <v>54521234.381260686</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>58448649.984140679</v>
+        <v>66487916.797526561</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>0.20896017757076879</v>
+        <v>0.21948663767559351</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1068</v>
+        <v>1312</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1408</v>
+        <v>1380</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>0.31835205992509352</v>
+        <v>5.1829268292682862E-2</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="O82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7607,19 +7607,19 @@
       </c>
       <c r="Q82" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1770</v>
+        <v>1764</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1798</v>
+        <v>1639</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>1.5819209039547921E-2</v>
+        <v>-7.0861678004535134E-2</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7643,27 +7643,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11404405.748291109</v>
+        <v>12629426.927350204</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12978754.33964923</v>
+        <v>14912277.198876899</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>0.13804740256580494</v>
+        <v>0.1807564416547649</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>606</v>
+        <v>671</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>739</v>
+        <v>928</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>0.21947194719471952</v>
+        <v>0.38301043219076014</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7691,15 +7691,15 @@
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>630</v>
+        <v>858</v>
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>0.11111111111111116</v>
+        <v>0.48442906574394473</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7723,27 +7723,27 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21469701.985500403</v>
+        <v>24516929.914394263</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23423151.156611502</v>
+        <v>26691110.077262778</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>9.0986319811535488E-2</v>
+        <v>8.8680767553690254E-2</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>569</v>
+        <v>641</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>741</v>
+        <v>581</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>0.30228471001757473</v>
+        <v>-9.3603744149766022E-2</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7771,15 +7771,15 @@
       </c>
       <c r="R84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="S84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>680</v>
+        <v>806</v>
       </c>
       <c r="T84" s="12">
         <f t="shared" si="9"/>
-        <v>5.2631578947368363E-2</v>
+        <v>0.27733755942947691</v>
       </c>
       <c r="U84">
         <v>7</v>
@@ -7803,27 +7803,27 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5260642.5641915696</v>
+        <v>5910987.391414376</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4319308.1950398814</v>
+        <v>4445161.1584503073</v>
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>-0.17893904740063782</v>
+        <v>-0.24798331241463312</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>296</v>
+        <v>380</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>-0.3817567567567568</v>
+        <v>-0.40789473684210531</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7851,15 +7851,15 @@
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>374</v>
+        <v>192</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>5.9490084985835745E-2</v>
+        <v>-0.46368715083798884</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7898,11 +7898,11 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>84549</v>
+        <v>84407</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>1079</v>
+        <v>1140</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
@@ -7910,31 +7910,31 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>69895</v>
+        <v>70297</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>2236113285.2862201</v>
+        <v>2541296940.4072208</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84637</v>
+        <v>83705</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>1539</v>
+        <v>1727</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>71296</v>
+        <v>71011</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>2327481078.9661198</v>
+        <v>2629013067.6293702</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7994,7 +7994,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
@@ -8003,13 +8003,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F6" s="10">
-        <v>10031059.186713256</v>
+        <v>11605840.967956211</v>
       </c>
       <c r="G6" s="10">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="H6" s="10">
         <v>1</v>
@@ -8018,10 +8018,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="K6" s="10">
-        <v>10451748.424652403</v>
+        <v>11745234.344032858</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -8032,19 +8032,19 @@
         <v>639</v>
       </c>
       <c r="C7" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="10">
         <v>3</v>
       </c>
       <c r="E7" s="10">
-        <v>544</v>
+        <v>519</v>
       </c>
       <c r="F7" s="10">
-        <v>11847668.973308677</v>
+        <v>13599176.772227382</v>
       </c>
       <c r="G7" s="10">
-        <v>555</v>
+        <v>523</v>
       </c>
       <c r="H7" s="10">
         <v>6</v>
@@ -8053,10 +8053,10 @@
         <v>3</v>
       </c>
       <c r="J7" s="10">
-        <v>592</v>
+        <v>522</v>
       </c>
       <c r="K7" s="10">
-        <v>11365040.339451777</v>
+        <v>12757065.964702409</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8064,34 +8064,34 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="C8" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="10">
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="F8" s="10">
-        <v>15693282.493840273</v>
+        <v>18579857.885549702</v>
       </c>
       <c r="G8" s="10">
-        <v>767</v>
+        <v>680</v>
       </c>
       <c r="H8" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>307</v>
+        <v>534</v>
       </c>
       <c r="K8" s="10">
-        <v>13027212.983451417</v>
+        <v>14199336.303547801</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8099,34 +8099,34 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C9" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9" s="10">
         <v>4</v>
       </c>
       <c r="E9" s="10">
-        <v>1123</v>
+        <v>1107</v>
       </c>
       <c r="F9" s="10">
-        <v>25636221.356210988</v>
+        <v>29318297.392397735</v>
       </c>
       <c r="G9" s="10">
-        <v>1222</v>
+        <v>1013</v>
       </c>
       <c r="H9" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="10">
         <v>2</v>
       </c>
       <c r="J9" s="10">
-        <v>955</v>
+        <v>988</v>
       </c>
       <c r="K9" s="10">
-        <v>27343918.425037589</v>
+        <v>30652409.729366504</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8134,7 +8134,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -8143,13 +8143,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="F10" s="10">
-        <v>11567766.085140552</v>
+        <v>13283507.106397798</v>
       </c>
       <c r="G10" s="10">
-        <v>392</v>
+        <v>446</v>
       </c>
       <c r="H10" s="10">
         <v>4</v>
@@ -8158,10 +8158,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="K10" s="10">
-        <v>12437976.728047604</v>
+        <v>14049843.096260291</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8169,7 +8169,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -8178,13 +8178,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F11" s="10">
-        <v>9574246.6887910403</v>
+        <v>10853864.931478668</v>
       </c>
       <c r="G11" s="10">
-        <v>374</v>
+        <v>288</v>
       </c>
       <c r="H11" s="10">
         <v>2</v>
@@ -8193,10 +8193,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="K11" s="10">
-        <v>7884637.3578127623</v>
+        <v>8990943.7944361828</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8210,28 +8210,28 @@
         <v>2</v>
       </c>
       <c r="D12" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="10">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="F12" s="10">
-        <v>11358396.529773155</v>
+        <v>13059467.406061232</v>
       </c>
       <c r="G12" s="10">
-        <v>635</v>
+        <v>549</v>
       </c>
       <c r="H12" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="10">
         <v>0</v>
       </c>
       <c r="J12" s="10">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="K12" s="10">
-        <v>11563533.990490887</v>
+        <v>12805254.646765212</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8239,7 +8239,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="10">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -8248,13 +8248,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F13" s="10">
-        <v>5043289.1807349501</v>
+        <v>5741955.8301954772</v>
       </c>
       <c r="G13" s="10">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
@@ -8263,10 +8263,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="K13" s="10">
-        <v>5164313.8401981639</v>
+        <v>5817133.5092633413</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8283,25 +8283,25 @@
         <v>1</v>
       </c>
       <c r="E14" s="10">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="F14" s="10">
-        <v>1745372.714907849</v>
+        <v>2514733.047916695</v>
       </c>
       <c r="G14" s="10">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="H14" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="10">
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K14" s="10">
-        <v>5210121.033227575</v>
+        <v>5792518.2435795534</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8309,34 +8309,34 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C15" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
       </c>
       <c r="E15" s="10">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="F15" s="10">
-        <v>10047490.355405016</v>
+        <v>11277110.458755046</v>
       </c>
       <c r="G15" s="10">
+        <v>441</v>
+      </c>
+      <c r="H15" s="10">
+        <v>6</v>
+      </c>
+      <c r="I15" s="10">
+        <v>1</v>
+      </c>
+      <c r="J15" s="10">
         <v>357</v>
       </c>
-      <c r="H15" s="10">
-        <v>5</v>
-      </c>
-      <c r="I15" s="10">
-        <v>1</v>
-      </c>
-      <c r="J15" s="10">
-        <v>376</v>
-      </c>
       <c r="K15" s="10">
-        <v>9232093.1963549405</v>
+        <v>10388805.87979324</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8344,7 +8344,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -8353,13 +8353,13 @@
         <v>2</v>
       </c>
       <c r="E16" s="10">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="F16" s="10">
-        <v>4958031.3880373193</v>
+        <v>5807814.7055882718</v>
       </c>
       <c r="G16" s="10">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="H16" s="10">
         <v>1</v>
@@ -8368,10 +8368,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="K16" s="10">
-        <v>4506119.9493312472</v>
+        <v>5110223.9326150976</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8379,7 +8379,7 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C17" s="10">
         <v>1</v>
@@ -8388,16 +8388,16 @@
         <v>2</v>
       </c>
       <c r="E17" s="10">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="F17" s="10">
-        <v>5380823.6863983767</v>
+        <v>6163624.0632635523</v>
       </c>
       <c r="G17" s="10">
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="H17" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="10">
         <v>0</v>
@@ -8406,7 +8406,7 @@
         <v>231</v>
       </c>
       <c r="K17" s="10">
-        <v>5726064.83562293</v>
+        <v>6597285.5653288113</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8414,34 +8414,34 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1435</v>
+        <v>1428</v>
       </c>
       <c r="C18" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="10">
         <v>3</v>
       </c>
       <c r="E18" s="10">
-        <v>1023</v>
+        <v>1101</v>
       </c>
       <c r="F18" s="10">
-        <v>21396343.684887961</v>
+        <v>25128238.575954139</v>
       </c>
       <c r="G18" s="10">
-        <v>1397</v>
+        <v>1411</v>
       </c>
       <c r="H18" s="10">
         <v>8</v>
       </c>
       <c r="I18" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="10">
-        <v>1239</v>
+        <v>1270</v>
       </c>
       <c r="K18" s="10">
-        <v>30850756.8154644</v>
+        <v>35041852.324905545</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8449,22 +8449,22 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="C19" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="10">
         <v>3</v>
       </c>
       <c r="E19" s="10">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="F19" s="10">
-        <v>37588029.534986168</v>
+        <v>43125207.394685581</v>
       </c>
       <c r="G19" s="10">
-        <v>1252</v>
+        <v>1151</v>
       </c>
       <c r="H19" s="10">
         <v>0</v>
@@ -8473,10 +8473,10 @@
         <v>2</v>
       </c>
       <c r="J19" s="10">
-        <v>934</v>
+        <v>908</v>
       </c>
       <c r="K19" s="10">
-        <v>43478586.493676245</v>
+        <v>48844413.069735177</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8493,25 +8493,25 @@
         <v>5</v>
       </c>
       <c r="E20" s="10">
-        <v>1135</v>
+        <v>894</v>
       </c>
       <c r="F20" s="10">
-        <v>21212507.702614099</v>
+        <v>23325512.922970474</v>
       </c>
       <c r="G20" s="10">
-        <v>1015</v>
+        <v>1074</v>
       </c>
       <c r="H20" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="10">
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>964</v>
+        <v>903</v>
       </c>
       <c r="K20" s="10">
-        <v>21010450.610085927</v>
+        <v>23662126.798789363</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8519,7 +8519,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C21" s="10">
         <v>4</v>
@@ -8528,13 +8528,13 @@
         <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="F21" s="10">
-        <v>16152779.022945462</v>
+        <v>18890377.12714364</v>
       </c>
       <c r="G21" s="10">
-        <v>915</v>
+        <v>785</v>
       </c>
       <c r="H21" s="10">
         <v>1</v>
@@ -8543,10 +8543,10 @@
         <v>4</v>
       </c>
       <c r="J21" s="10">
-        <v>767</v>
+        <v>667</v>
       </c>
       <c r="K21" s="10">
-        <v>20384337.964686051</v>
+        <v>22825110.871727254</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8554,34 +8554,34 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2824</v>
+        <v>2813</v>
       </c>
       <c r="C22" s="10">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2030</v>
+        <v>2092</v>
       </c>
       <c r="F22" s="10">
-        <v>77653874.701062784</v>
+        <v>86538124.393357381</v>
       </c>
       <c r="G22" s="10">
-        <v>2756</v>
+        <v>2724</v>
       </c>
       <c r="H22" s="10">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I22" s="10">
         <v>12</v>
       </c>
       <c r="J22" s="10">
-        <v>2196</v>
+        <v>2200</v>
       </c>
       <c r="K22" s="10">
-        <v>73261977.766638085</v>
+        <v>82403650.006621614</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8589,22 +8589,22 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="C23" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="10">
         <v>1</v>
       </c>
       <c r="E23" s="10">
-        <v>1147</v>
+        <v>1167</v>
       </c>
       <c r="F23" s="10">
-        <v>20823267.672696736</v>
+        <v>26002211.72344863</v>
       </c>
       <c r="G23" s="10">
-        <v>1363</v>
+        <v>1267</v>
       </c>
       <c r="H23" s="10">
         <v>5</v>
@@ -8613,10 +8613,10 @@
         <v>2</v>
       </c>
       <c r="J23" s="10">
-        <v>1218</v>
+        <v>1190</v>
       </c>
       <c r="K23" s="10">
-        <v>38461930.24138011</v>
+        <v>43335722.521319821</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8624,34 +8624,34 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>2957</v>
+        <v>2936</v>
       </c>
       <c r="C24" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D24" s="10">
         <v>10</v>
       </c>
       <c r="E24" s="10">
-        <v>2154</v>
+        <v>2002</v>
       </c>
       <c r="F24" s="10">
-        <v>78189279.719223753</v>
+        <v>87558270.252023414</v>
       </c>
       <c r="G24" s="10">
-        <v>2776</v>
+        <v>2548</v>
       </c>
       <c r="H24" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2185</v>
+        <v>2147</v>
       </c>
       <c r="K24" s="10">
-        <v>68713287.365769863</v>
+        <v>78374783.039749846</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8662,19 +8662,19 @@
         <v>533</v>
       </c>
       <c r="C25" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="10">
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>453</v>
+        <v>482</v>
       </c>
       <c r="F25" s="10">
-        <v>11618026.828046735</v>
+        <v>13183778.010977268</v>
       </c>
       <c r="G25" s="10">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="H25" s="10">
         <v>2</v>
@@ -8683,10 +8683,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>398</v>
+        <v>476</v>
       </c>
       <c r="K25" s="10">
-        <v>10481400.58186681</v>
+        <v>11826239.269592175</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8694,22 +8694,22 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1714</v>
+        <v>1698</v>
       </c>
       <c r="C26" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D26" s="10">
         <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>1279</v>
+        <v>1381</v>
       </c>
       <c r="F26" s="10">
-        <v>31902604.980764087</v>
+        <v>36192562.219717629</v>
       </c>
       <c r="G26" s="10">
-        <v>1744</v>
+        <v>1876</v>
       </c>
       <c r="H26" s="10">
         <v>16</v>
@@ -8718,10 +8718,10 @@
         <v>1</v>
       </c>
       <c r="J26" s="10">
-        <v>1573</v>
+        <v>1449</v>
       </c>
       <c r="K26" s="10">
-        <v>29385357.135773905</v>
+        <v>32935272.975362118</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8729,7 +8729,7 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C27" s="10">
         <v>10</v>
@@ -8738,13 +8738,13 @@
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>894</v>
+        <v>867</v>
       </c>
       <c r="F27" s="10">
-        <v>12991656.7694692</v>
+        <v>15022021.249958932</v>
       </c>
       <c r="G27" s="10">
-        <v>839</v>
+        <v>904</v>
       </c>
       <c r="H27" s="10">
         <v>6</v>
@@ -8753,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="10">
-        <v>843</v>
+        <v>780</v>
       </c>
       <c r="K27" s="10">
-        <v>12337413.658601355</v>
+        <v>13972572.86172664</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8764,7 +8764,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="C28" s="10">
         <v>5</v>
@@ -8773,25 +8773,25 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>871</v>
+        <v>759</v>
       </c>
       <c r="F28" s="10">
-        <v>16148057.481919851</v>
+        <v>18344574.830965456</v>
       </c>
       <c r="G28" s="10">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="H28" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="10">
         <v>0</v>
       </c>
       <c r="J28" s="10">
-        <v>783</v>
+        <v>760</v>
       </c>
       <c r="K28" s="10">
-        <v>15970386.192980677</v>
+        <v>18270548.609162889</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8799,7 +8799,7 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -8808,13 +8808,13 @@
         <v>2</v>
       </c>
       <c r="E29" s="10">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F29" s="10">
-        <v>3545079.2402608488</v>
+        <v>4146758.08022347</v>
       </c>
       <c r="G29" s="10">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="H29" s="10">
         <v>1</v>
@@ -8823,10 +8823,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="10">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K29" s="10">
-        <v>4033521.2907017982</v>
+        <v>4544499.9292088114</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8834,7 +8834,7 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1647</v>
+        <v>1653</v>
       </c>
       <c r="C30" s="10">
         <v>10</v>
@@ -8843,13 +8843,13 @@
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1456</v>
+        <v>1384</v>
       </c>
       <c r="F30" s="10">
-        <v>30369760.083999842</v>
+        <v>34683862.559180304</v>
       </c>
       <c r="G30" s="10">
-        <v>1651</v>
+        <v>1686</v>
       </c>
       <c r="H30" s="10">
         <v>3</v>
@@ -8861,7 +8861,7 @@
         <v>1431</v>
       </c>
       <c r="K30" s="10">
-        <v>30813505.786671042</v>
+        <v>34833450.097463757</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8869,22 +8869,22 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C31" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="10">
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="F31" s="10">
-        <v>25130828.725072499</v>
+        <v>28942176.601938333</v>
       </c>
       <c r="G31" s="10">
-        <v>895</v>
+        <v>839</v>
       </c>
       <c r="H31" s="10">
         <v>3</v>
@@ -8893,10 +8893,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="K31" s="10">
-        <v>27992379.158031393</v>
+        <v>31477197.298174005</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8904,22 +8904,22 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
       </c>
       <c r="D32" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>813</v>
+        <v>623</v>
       </c>
       <c r="F32" s="10">
-        <v>24348017.987532649</v>
+        <v>27322835.150993686</v>
       </c>
       <c r="G32" s="10">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="H32" s="10">
         <v>1</v>
@@ -8928,10 +8928,10 @@
         <v>3</v>
       </c>
       <c r="J32" s="10">
-        <v>915</v>
+        <v>868</v>
       </c>
       <c r="K32" s="10">
-        <v>27339018.879904401</v>
+        <v>31575073.436375592</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8939,7 +8939,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="C33" s="10">
         <v>3</v>
@@ -8948,13 +8948,13 @@
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>865</v>
+        <v>1017</v>
       </c>
       <c r="F33" s="10">
-        <v>33287094.194697849</v>
+        <v>38750202.555159338</v>
       </c>
       <c r="G33" s="10">
-        <v>1140</v>
+        <v>993</v>
       </c>
       <c r="H33" s="10">
         <v>2</v>
@@ -8963,10 +8963,10 @@
         <v>3</v>
       </c>
       <c r="J33" s="10">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="K33" s="10">
-        <v>33866219.070671238</v>
+        <v>38158631.406307779</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8974,7 +8974,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="C34" s="10">
         <v>4</v>
@@ -8983,25 +8983,25 @@
         <v>4</v>
       </c>
       <c r="E34" s="10">
-        <v>1108</v>
+        <v>1153</v>
       </c>
       <c r="F34" s="10">
-        <v>46940123.260832466</v>
+        <v>49704479.1329192</v>
       </c>
       <c r="G34" s="10">
-        <v>1453</v>
+        <v>598</v>
       </c>
       <c r="H34" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" s="10">
         <v>2</v>
       </c>
       <c r="J34" s="10">
-        <v>1214</v>
+        <v>261</v>
       </c>
       <c r="K34" s="10">
-        <v>48286581.885638237</v>
+        <v>51670729.287840143</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -9009,7 +9009,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="C35" s="10">
         <v>1</v>
@@ -9018,13 +9018,13 @@
         <v>5</v>
       </c>
       <c r="E35" s="10">
-        <v>566</v>
+        <v>657</v>
       </c>
       <c r="F35" s="10">
-        <v>19339477.823665723</v>
+        <v>22482772.205797095</v>
       </c>
       <c r="G35" s="10">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="H35" s="10">
         <v>4</v>
@@ -9033,10 +9033,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>577</v>
+        <v>487</v>
       </c>
       <c r="K35" s="10">
-        <v>19612777.992599472</v>
+        <v>22045431.28545827</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9044,22 +9044,22 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1906</v>
+        <v>1923</v>
       </c>
       <c r="C36" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D36" s="10">
         <v>9</v>
       </c>
       <c r="E36" s="10">
-        <v>985</v>
+        <v>1597</v>
       </c>
       <c r="F36" s="10">
-        <v>46678468.479174599</v>
+        <v>54659271.855845027</v>
       </c>
       <c r="G36" s="10">
-        <v>1856</v>
+        <v>1778</v>
       </c>
       <c r="H36" s="10">
         <v>3</v>
@@ -9068,10 +9068,10 @@
         <v>7</v>
       </c>
       <c r="J36" s="10">
-        <v>1632</v>
+        <v>1612</v>
       </c>
       <c r="K36" s="10">
-        <v>39716345.829926766</v>
+        <v>46584687.457568675</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9079,34 +9079,34 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C37" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" s="10">
         <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>673</v>
+        <v>699</v>
       </c>
       <c r="F37" s="10">
-        <v>19600077.597591951</v>
+        <v>22656058.277334604</v>
       </c>
       <c r="G37" s="10">
-        <v>847</v>
+        <v>1266</v>
       </c>
       <c r="H37" s="10">
         <v>2</v>
       </c>
       <c r="I37" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J37" s="10">
-        <v>698</v>
+        <v>1430</v>
       </c>
       <c r="K37" s="10">
-        <v>19603837.280351806</v>
+        <v>22394741.412024934</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9114,34 +9114,34 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C38" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" s="10">
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>458</v>
+        <v>560</v>
       </c>
       <c r="F38" s="10">
-        <v>18503531.759908363</v>
+        <v>20514275.541951414</v>
       </c>
       <c r="G38" s="10">
-        <v>731</v>
+        <v>764</v>
       </c>
       <c r="H38" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="10">
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K38" s="10">
-        <v>17848929.749518771</v>
+        <v>20280297.833904956</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9149,22 +9149,22 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="C39" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D39" s="10">
         <v>1</v>
       </c>
       <c r="E39" s="10">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="F39" s="10">
-        <v>27886563.921537865</v>
+        <v>31706807.770847913</v>
       </c>
       <c r="G39" s="10">
-        <v>1195</v>
+        <v>1383</v>
       </c>
       <c r="H39" s="10">
         <v>6</v>
@@ -9173,10 +9173,10 @@
         <v>2</v>
       </c>
       <c r="J39" s="10">
-        <v>896</v>
+        <v>951</v>
       </c>
       <c r="K39" s="10">
-        <v>31244315.963416766</v>
+        <v>35210619.986819968</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9184,34 +9184,34 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1315</v>
+        <v>1271</v>
       </c>
       <c r="C40" s="10">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D40" s="10">
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>806</v>
+        <v>880</v>
       </c>
       <c r="F40" s="10">
-        <v>25980146.357264768</v>
+        <v>30008831.32454332</v>
       </c>
       <c r="G40" s="10">
-        <v>1368</v>
+        <v>1309</v>
       </c>
       <c r="H40" s="10">
-        <v>318</v>
+        <v>391</v>
       </c>
       <c r="I40" s="10">
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>926</v>
+        <v>870</v>
       </c>
       <c r="K40" s="10">
-        <v>28569315.557240028</v>
+        <v>32153124.55919506</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9219,7 +9219,7 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>2319</v>
+        <v>2274</v>
       </c>
       <c r="C41" s="10">
         <v>70</v>
@@ -9228,25 +9228,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="10">
-        <v>1627</v>
+        <v>1420</v>
       </c>
       <c r="F41" s="10">
-        <v>47828167.354593977</v>
+        <v>54089568.346732005</v>
       </c>
       <c r="G41" s="10">
-        <v>2231</v>
+        <v>2316</v>
       </c>
       <c r="H41" s="10">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="I41" s="10">
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1348</v>
+        <v>1436</v>
       </c>
       <c r="K41" s="10">
-        <v>47327626.983007781</v>
+        <v>53090474.700370014</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9254,7 +9254,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C42" s="10">
         <v>1</v>
@@ -9263,13 +9263,13 @@
         <v>6</v>
       </c>
       <c r="E42" s="10">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F42" s="10">
-        <v>17239734.609239098</v>
+        <v>19559864.968351118</v>
       </c>
       <c r="G42" s="10">
-        <v>586</v>
+        <v>516</v>
       </c>
       <c r="H42" s="10">
         <v>4</v>
@@ -9278,10 +9278,10 @@
         <v>7</v>
       </c>
       <c r="J42" s="10">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K42" s="10">
-        <v>17601943.18951926</v>
+        <v>20014278.607087888</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9289,34 +9289,34 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>2060</v>
+        <v>2052</v>
       </c>
       <c r="C43" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" s="10">
         <v>6</v>
       </c>
       <c r="E43" s="10">
-        <v>1813</v>
+        <v>1899</v>
       </c>
       <c r="F43" s="10">
-        <v>55863457.338151634</v>
+        <v>62806648.991798967</v>
       </c>
       <c r="G43" s="10">
-        <v>2037</v>
+        <v>2293</v>
       </c>
       <c r="H43" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43" s="10">
         <v>5</v>
       </c>
       <c r="J43" s="10">
-        <v>1899</v>
+        <v>2156</v>
       </c>
       <c r="K43" s="10">
-        <v>53820568.949218951</v>
+        <v>61438729.827034511</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9324,7 +9324,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="C44" s="10">
         <v>3</v>
@@ -9333,13 +9333,13 @@
         <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>1214</v>
+        <v>849</v>
       </c>
       <c r="F44" s="10">
-        <v>38794693.14317365</v>
+        <v>43715380.459994063</v>
       </c>
       <c r="G44" s="10">
-        <v>934</v>
+        <v>1015</v>
       </c>
       <c r="H44" s="10">
         <v>6</v>
@@ -9348,10 +9348,10 @@
         <v>4</v>
       </c>
       <c r="J44" s="10">
-        <v>879</v>
+        <v>830</v>
       </c>
       <c r="K44" s="10">
-        <v>42105567.733273089</v>
+        <v>47264068.682267107</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9359,34 +9359,34 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="C45" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" s="10">
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>936</v>
+        <v>1095</v>
       </c>
       <c r="F45" s="10">
-        <v>21326951.017018501</v>
+        <v>25162534.388928577</v>
       </c>
       <c r="G45" s="10">
-        <v>1066</v>
+        <v>1121</v>
       </c>
       <c r="H45" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I45" s="10">
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>981</v>
+        <v>941</v>
       </c>
       <c r="K45" s="10">
-        <v>29772505.600011189</v>
+        <v>33425173.710316837</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9394,7 +9394,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C46" s="10">
         <v>5</v>
@@ -9403,25 +9403,25 @@
         <v>4</v>
       </c>
       <c r="E46" s="10">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="F46" s="10">
-        <v>28987672.484540347</v>
+        <v>32737539.875770304</v>
       </c>
       <c r="G46" s="10">
-        <v>832</v>
+        <v>728</v>
       </c>
       <c r="H46" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" s="10">
         <v>5</v>
       </c>
       <c r="J46" s="10">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="K46" s="10">
-        <v>30625362.113111999</v>
+        <v>34760498.561225682</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9429,34 +9429,34 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="C47" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E47" s="10">
-        <v>1046</v>
+        <v>671</v>
       </c>
       <c r="F47" s="10">
-        <v>18797706.720624097</v>
+        <v>21253968.086201899</v>
       </c>
       <c r="G47" s="10">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="H47" s="10">
         <v>0</v>
       </c>
       <c r="I47" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J47" s="10">
-        <v>577</v>
+        <v>558</v>
       </c>
       <c r="K47" s="10">
-        <v>18111709.274998784</v>
+        <v>20575729.222999271</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9464,22 +9464,22 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C48" s="10">
         <v>0</v>
       </c>
       <c r="D48" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>475</v>
+        <v>732</v>
       </c>
       <c r="F48" s="10">
-        <v>16326037.684438676</v>
+        <v>18181143.725431334</v>
       </c>
       <c r="G48" s="10">
-        <v>705</v>
+        <v>795</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
@@ -9488,10 +9488,10 @@
         <v>2</v>
       </c>
       <c r="J48" s="10">
-        <v>800</v>
+        <v>744</v>
       </c>
       <c r="K48" s="10">
-        <v>16974532.487811487</v>
+        <v>19303865.027933616</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9499,7 +9499,7 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C49" s="10">
         <v>2</v>
@@ -9508,13 +9508,13 @@
         <v>5</v>
       </c>
       <c r="E49" s="10">
-        <v>1074</v>
+        <v>1454</v>
       </c>
       <c r="F49" s="10">
-        <v>50350879.089841045</v>
+        <v>58056100.845717795</v>
       </c>
       <c r="G49" s="10">
-        <v>1287</v>
+        <v>1195</v>
       </c>
       <c r="H49" s="10">
         <v>5</v>
@@ -9523,10 +9523,10 @@
         <v>6</v>
       </c>
       <c r="J49" s="10">
-        <v>1140</v>
+        <v>1094</v>
       </c>
       <c r="K49" s="10">
-        <v>55925546.402918451</v>
+        <v>62385273.714933924</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9534,22 +9534,22 @@
         <v>201</v>
       </c>
       <c r="B50" s="10">
+        <v>444</v>
+      </c>
+      <c r="C50" s="10">
+        <v>1</v>
+      </c>
+      <c r="D50" s="10">
+        <v>1</v>
+      </c>
+      <c r="E50" s="10">
         <v>440</v>
       </c>
-      <c r="C50" s="10">
-        <v>1</v>
-      </c>
-      <c r="D50" s="10">
-        <v>1</v>
-      </c>
-      <c r="E50" s="10">
-        <v>429</v>
-      </c>
       <c r="F50" s="10">
-        <v>8260863.7707575997</v>
+        <v>9368029.2382126935</v>
       </c>
       <c r="G50" s="10">
-        <v>453</v>
+        <v>495</v>
       </c>
       <c r="H50" s="10">
         <v>1</v>
@@ -9558,10 +9558,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="K50" s="10">
-        <v>8658076.1250030715</v>
+        <v>9787519.2750786394</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9569,22 +9569,22 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C51" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" s="10">
         <v>7</v>
       </c>
       <c r="E51" s="10">
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="F51" s="10">
-        <v>24329645.084981102</v>
+        <v>27501290.30900624</v>
       </c>
       <c r="G51" s="10">
-        <v>885</v>
+        <v>938</v>
       </c>
       <c r="H51" s="10">
         <v>2</v>
@@ -9593,10 +9593,10 @@
         <v>5</v>
       </c>
       <c r="J51" s="10">
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="K51" s="10">
-        <v>24008510.265390374</v>
+        <v>27142791.840424143</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9604,22 +9604,22 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="C52" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D52" s="10">
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="F52" s="10">
-        <v>42604532.316107005</v>
+        <v>48007052.156097807</v>
       </c>
       <c r="G52" s="10">
-        <v>1419</v>
+        <v>1495</v>
       </c>
       <c r="H52" s="10">
         <v>3</v>
@@ -9628,10 +9628,10 @@
         <v>11</v>
       </c>
       <c r="J52" s="10">
-        <v>1138</v>
+        <v>1097</v>
       </c>
       <c r="K52" s="10">
-        <v>43979107.294347867</v>
+        <v>49754972.721462965</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9639,7 +9639,7 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C53" s="10">
         <v>1</v>
@@ -9648,13 +9648,13 @@
         <v>6</v>
       </c>
       <c r="E53" s="10">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="F53" s="10">
-        <v>22005709.005341128</v>
+        <v>24801070.576041028</v>
       </c>
       <c r="G53" s="10">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="H53" s="10">
         <v>4</v>
@@ -9663,10 +9663,10 @@
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="K53" s="10">
-        <v>21167858.625659622</v>
+        <v>24039362.163346086</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9674,7 +9674,7 @@
         <v>81</v>
       </c>
       <c r="B54" s="10">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C54" s="10">
         <v>0</v>
@@ -9683,13 +9683,13 @@
         <v>4</v>
       </c>
       <c r="E54" s="10">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="F54" s="10">
-        <v>16006981.240799496</v>
+        <v>18011128.017276742</v>
       </c>
       <c r="G54" s="10">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="H54" s="10">
         <v>2</v>
@@ -9698,10 +9698,10 @@
         <v>3</v>
       </c>
       <c r="J54" s="10">
-        <v>460</v>
+        <v>359</v>
       </c>
       <c r="K54" s="10">
-        <v>17965408.831571799</v>
+        <v>20227997.511374339</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9712,19 +9712,19 @@
         <v>422</v>
       </c>
       <c r="C55" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="10">
         <v>4</v>
       </c>
       <c r="E55" s="10">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="F55" s="10">
-        <v>13856935.277226221</v>
+        <v>15806729.969322076</v>
       </c>
       <c r="G55" s="10">
-        <v>385</v>
+        <v>221</v>
       </c>
       <c r="H55" s="10">
         <v>1</v>
@@ -9733,10 +9733,10 @@
         <v>1</v>
       </c>
       <c r="J55" s="10">
-        <v>10</v>
+        <v>315</v>
       </c>
       <c r="K55" s="10">
-        <v>5873087.196715177</v>
+        <v>6362445.1973371059</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9750,16 +9750,16 @@
         <v>5</v>
       </c>
       <c r="D56" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>872</v>
+        <v>921</v>
       </c>
       <c r="F56" s="10">
-        <v>32922233.232268192</v>
+        <v>37145639.08092615</v>
       </c>
       <c r="G56" s="10">
-        <v>1103</v>
+        <v>972</v>
       </c>
       <c r="H56" s="10">
         <v>3</v>
@@ -9768,10 +9768,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="K56" s="10">
-        <v>34613136.454139821</v>
+        <v>39087199.660863936</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9779,7 +9779,7 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="C57" s="10">
         <v>7</v>
@@ -9788,13 +9788,13 @@
         <v>1</v>
       </c>
       <c r="E57" s="10">
-        <v>1002</v>
+        <v>926</v>
       </c>
       <c r="F57" s="10">
-        <v>32767497.85062144</v>
+        <v>38646435.694154151</v>
       </c>
       <c r="G57" s="10">
-        <v>941</v>
+        <v>1110</v>
       </c>
       <c r="H57" s="10">
         <v>5</v>
@@ -9803,10 +9803,10 @@
         <v>2</v>
       </c>
       <c r="J57" s="10">
-        <v>963</v>
+        <v>883</v>
       </c>
       <c r="K57" s="10">
-        <v>35690534.982378751</v>
+        <v>40674626.262159429</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9814,34 +9814,34 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2048</v>
+        <v>2036</v>
       </c>
       <c r="C58" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D58" s="10">
         <v>8</v>
       </c>
       <c r="E58" s="10">
-        <v>1601</v>
+        <v>1773</v>
       </c>
       <c r="F58" s="10">
-        <v>61113798.319160461</v>
+        <v>69493810.821061969</v>
       </c>
       <c r="G58" s="10">
-        <v>2073</v>
+        <v>1846</v>
       </c>
       <c r="H58" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I58" s="10">
         <v>9</v>
       </c>
       <c r="J58" s="10">
-        <v>1658</v>
+        <v>1501</v>
       </c>
       <c r="K58" s="10">
-        <v>64882425.838394135</v>
+        <v>72374424.098745659</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9849,7 +9849,7 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="C59" s="10">
         <v>4</v>
@@ -9858,13 +9858,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>447</v>
+        <v>498</v>
       </c>
       <c r="F59" s="10">
-        <v>15237386.793200787</v>
+        <v>17384753.173172586</v>
       </c>
       <c r="G59" s="10">
-        <v>662</v>
+        <v>562</v>
       </c>
       <c r="H59" s="10">
         <v>2</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="K59" s="10">
-        <v>16923572.104882669</v>
+        <v>18923708.401292492</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9884,7 +9884,7 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="C60" s="10">
         <v>6</v>
@@ -9893,13 +9893,13 @@
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>715</v>
+        <v>790</v>
       </c>
       <c r="F60" s="10">
-        <v>26569100.705542248</v>
+        <v>30326520.036693711</v>
       </c>
       <c r="G60" s="10">
-        <v>922</v>
+        <v>903</v>
       </c>
       <c r="H60" s="10">
         <v>8</v>
@@ -9908,10 +9908,10 @@
         <v>6</v>
       </c>
       <c r="J60" s="10">
-        <v>738</v>
+        <v>775</v>
       </c>
       <c r="K60" s="10">
-        <v>30353544.458011288</v>
+        <v>34240647.79706008</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9919,7 +9919,7 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="C61" s="10">
         <v>4</v>
@@ -9928,13 +9928,13 @@
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>740</v>
+        <v>658</v>
       </c>
       <c r="F61" s="10">
-        <v>16880304.095586132</v>
+        <v>19194844.171725195</v>
       </c>
       <c r="G61" s="10">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="H61" s="10">
         <v>0</v>
@@ -9943,10 +9943,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="10">
-        <v>613</v>
+        <v>574</v>
       </c>
       <c r="K61" s="10">
-        <v>15435179.114867197</v>
+        <v>17557864.945764679</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9954,22 +9954,22 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C62" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D62" s="10">
         <v>0</v>
       </c>
       <c r="E62" s="10">
-        <v>869</v>
+        <v>938</v>
       </c>
       <c r="F62" s="10">
-        <v>34340368.090365291</v>
+        <v>38667760.821667828</v>
       </c>
       <c r="G62" s="10">
-        <v>1099</v>
+        <v>1156</v>
       </c>
       <c r="H62" s="10">
         <v>6</v>
@@ -9978,10 +9978,10 @@
         <v>1</v>
       </c>
       <c r="J62" s="10">
-        <v>1163</v>
+        <v>1062</v>
       </c>
       <c r="K62" s="10">
-        <v>37729757.422791846</v>
+        <v>42707054.597119845</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9989,34 +9989,34 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1478</v>
+        <v>1497</v>
       </c>
       <c r="C63" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D63" s="10">
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1339</v>
+        <v>1041</v>
       </c>
       <c r="F63" s="10">
-        <v>43422115.586745128</v>
+        <v>47149145.488019548</v>
       </c>
       <c r="G63" s="10">
-        <v>1621</v>
+        <v>1748</v>
       </c>
       <c r="H63" s="10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I63" s="10">
         <v>5</v>
       </c>
       <c r="J63" s="10">
-        <v>1618</v>
+        <v>1603</v>
       </c>
       <c r="K63" s="10">
-        <v>51933160.195166431</v>
+        <v>59553692.350798987</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -10024,7 +10024,7 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C64" s="10">
         <v>2</v>
@@ -10033,13 +10033,13 @@
         <v>4</v>
       </c>
       <c r="E64" s="10">
-        <v>693</v>
+        <v>754</v>
       </c>
       <c r="F64" s="10">
-        <v>23207604.557711422</v>
+        <v>26294359.603784792</v>
       </c>
       <c r="G64" s="10">
-        <v>798</v>
+        <v>875</v>
       </c>
       <c r="H64" s="10">
         <v>4</v>
@@ -10048,10 +10048,10 @@
         <v>5</v>
       </c>
       <c r="J64" s="10">
-        <v>760</v>
+        <v>809</v>
       </c>
       <c r="K64" s="10">
-        <v>21502821.729210172</v>
+        <v>24696556.024657793</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10059,22 +10059,22 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C65" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D65" s="10">
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F65" s="10">
-        <v>25855386.35664548</v>
+        <v>29381517.297919996</v>
       </c>
       <c r="G65" s="10">
-        <v>644</v>
+        <v>567</v>
       </c>
       <c r="H65" s="10">
         <v>5</v>
@@ -10083,10 +10083,10 @@
         <v>7</v>
       </c>
       <c r="J65" s="10">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="K65" s="10">
-        <v>27515605.348086242</v>
+        <v>30966755.450658873</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10094,34 +10094,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>1983</v>
+        <v>1990</v>
       </c>
       <c r="C66" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D66" s="10">
         <v>11</v>
       </c>
       <c r="E66" s="10">
-        <v>1969</v>
+        <v>1567</v>
       </c>
       <c r="F66" s="10">
-        <v>83988262.907164082</v>
+        <v>94637122.61423178</v>
       </c>
       <c r="G66" s="10">
-        <v>1957</v>
+        <v>1973</v>
       </c>
       <c r="H66" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I66" s="10">
         <v>12</v>
       </c>
       <c r="J66" s="10">
-        <v>1637</v>
+        <v>1667</v>
       </c>
       <c r="K66" s="10">
-        <v>87322079.567863107</v>
+        <v>98297860.045866206</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10129,7 +10129,7 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="C67" s="10">
         <v>16</v>
@@ -10138,25 +10138,25 @@
         <v>6</v>
       </c>
       <c r="E67" s="10">
-        <v>1096</v>
+        <v>1356</v>
       </c>
       <c r="F67" s="10">
-        <v>62144411.904331289</v>
+        <v>70773748.576810673</v>
       </c>
       <c r="G67" s="10">
-        <v>1597</v>
+        <v>1671</v>
       </c>
       <c r="H67" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I67" s="10">
         <v>7</v>
       </c>
       <c r="J67" s="10">
-        <v>1318</v>
+        <v>1328</v>
       </c>
       <c r="K67" s="10">
-        <v>63302163.709051661</v>
+        <v>71935440.42983456</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10164,22 +10164,22 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C68" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D68" s="10">
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>720</v>
+        <v>654</v>
       </c>
       <c r="F68" s="10">
-        <v>40291786.850265786</v>
+        <v>45665609.810448475</v>
       </c>
       <c r="G68" s="10">
-        <v>896</v>
+        <v>937</v>
       </c>
       <c r="H68" s="10">
         <v>2</v>
@@ -10188,10 +10188,10 @@
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="K68" s="10">
-        <v>42230040.117961869</v>
+        <v>47462901.347901933</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10199,34 +10199,34 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>2275</v>
+        <v>2204</v>
       </c>
       <c r="C69" s="10">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D69" s="10">
         <v>12</v>
       </c>
       <c r="E69" s="10">
-        <v>1405</v>
+        <v>1245</v>
       </c>
       <c r="F69" s="10">
-        <v>60482844.879700385</v>
+        <v>67656800.451480851</v>
       </c>
       <c r="G69" s="10">
-        <v>2369</v>
+        <v>2091</v>
       </c>
       <c r="H69" s="10">
-        <v>462</v>
+        <v>513</v>
       </c>
       <c r="I69" s="10">
         <v>13</v>
       </c>
       <c r="J69" s="10">
-        <v>1337</v>
+        <v>1327</v>
       </c>
       <c r="K69" s="10">
-        <v>56679542.814377584</v>
+        <v>64152120.69018504</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10234,7 +10234,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C70" s="10">
         <v>0</v>
@@ -10246,10 +10246,10 @@
         <v>246</v>
       </c>
       <c r="F70" s="10">
-        <v>2049584.514477622</v>
+        <v>2633379.3830935382</v>
       </c>
       <c r="G70" s="10">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="H70" s="10">
         <v>2</v>
@@ -10258,10 +10258,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="10">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="K70" s="10">
-        <v>4609199.2052098904</v>
+        <v>5153593.4177207183</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10269,7 +10269,7 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="C71" s="10">
         <v>9</v>
@@ -10278,25 +10278,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="10">
-        <v>1620</v>
+        <v>1571</v>
       </c>
       <c r="F71" s="10">
-        <v>43221691.643919691</v>
+        <v>48997107.208894491</v>
       </c>
       <c r="G71" s="10">
-        <v>1592</v>
+        <v>1715</v>
       </c>
       <c r="H71" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I71" s="10">
         <v>8</v>
       </c>
       <c r="J71" s="10">
-        <v>1580</v>
+        <v>1523</v>
       </c>
       <c r="K71" s="10">
-        <v>42527106.473903023</v>
+        <v>47950631.785390586</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10304,7 +10304,7 @@
         <v>12</v>
       </c>
       <c r="B72" s="10">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C72" s="10">
         <v>3</v>
@@ -10313,25 +10313,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="10">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="F72" s="10">
-        <v>20584123.922306944</v>
+        <v>23101263.016764838</v>
       </c>
       <c r="G72" s="10">
-        <v>791</v>
+        <v>877</v>
       </c>
       <c r="H72" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I72" s="10">
         <v>4</v>
       </c>
       <c r="J72" s="10">
-        <v>647</v>
+        <v>612</v>
       </c>
       <c r="K72" s="10">
-        <v>19382725.801420636</v>
+        <v>22046341.14536155</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10339,22 +10339,22 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1362</v>
+        <v>1391</v>
       </c>
       <c r="C73" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D73" s="10">
         <v>4</v>
       </c>
       <c r="E73" s="10">
-        <v>1057</v>
+        <v>982</v>
       </c>
       <c r="F73" s="10">
-        <v>30147825.724716209</v>
+        <v>34973917.453895658</v>
       </c>
       <c r="G73" s="10">
-        <v>1484</v>
+        <v>1378</v>
       </c>
       <c r="H73" s="10">
         <v>66</v>
@@ -10363,10 +10363,10 @@
         <v>5</v>
       </c>
       <c r="J73" s="10">
-        <v>952</v>
+        <v>1117</v>
       </c>
       <c r="K73" s="10">
-        <v>32338446.233785421</v>
+        <v>36678397.562773459</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10374,34 +10374,34 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1262</v>
+        <v>1253</v>
       </c>
       <c r="C74" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74" s="10">
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="F74" s="10">
-        <v>18961499.08903724</v>
+        <v>22203502.898916803</v>
       </c>
       <c r="G74" s="10">
-        <v>1340</v>
+        <v>1561</v>
       </c>
       <c r="H74" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I74" s="10">
         <v>4</v>
       </c>
       <c r="J74" s="10">
-        <v>1420</v>
+        <v>1377</v>
       </c>
       <c r="K74" s="10">
-        <v>24722694.050578289</v>
+        <v>27770658.560409263</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10409,34 +10409,34 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1752</v>
+        <v>1758</v>
       </c>
       <c r="C75" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D75" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E75" s="10">
-        <v>1165</v>
+        <v>1241</v>
       </c>
       <c r="F75" s="10">
-        <v>53783637.746164359</v>
+        <v>61243048.896313921</v>
       </c>
       <c r="G75" s="10">
-        <v>1798</v>
+        <v>1564</v>
       </c>
       <c r="H75" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I75" s="10">
         <v>7</v>
       </c>
       <c r="J75" s="10">
-        <v>1308</v>
+        <v>1292</v>
       </c>
       <c r="K75" s="10">
-        <v>56895215.540526107</v>
+        <v>63578906.020253301</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10444,7 +10444,7 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C76" s="10">
         <v>2</v>
@@ -10453,13 +10453,13 @@
         <v>1</v>
       </c>
       <c r="E76" s="10">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="F76" s="10">
-        <v>10904494.48472932</v>
+        <v>12389661.65920596</v>
       </c>
       <c r="G76" s="10">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="H76" s="10">
         <v>4</v>
@@ -10468,10 +10468,10 @@
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="K76" s="10">
-        <v>10133380.339113291</v>
+        <v>11379397.772014776</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10479,7 +10479,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C77" s="10">
         <v>3</v>
@@ -10488,13 +10488,13 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>1324</v>
+        <v>791</v>
       </c>
       <c r="F77" s="10">
-        <v>17298035.563470758</v>
+        <v>19944616.410577688</v>
       </c>
       <c r="G77" s="10">
-        <v>888</v>
+        <v>831</v>
       </c>
       <c r="H77" s="10">
         <v>2</v>
@@ -10503,10 +10503,10 @@
         <v>0</v>
       </c>
       <c r="J77" s="10">
-        <v>771</v>
+        <v>835</v>
       </c>
       <c r="K77" s="10">
-        <v>20101925.882868141</v>
+        <v>22860464.684708528</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10517,19 +10517,19 @@
         <v>645</v>
       </c>
       <c r="C78" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" s="10">
         <v>3</v>
       </c>
       <c r="E78" s="10">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="F78" s="10">
-        <v>17062080.811463322</v>
+        <v>19632821.125206627</v>
       </c>
       <c r="G78" s="10">
-        <v>636</v>
+        <v>596</v>
       </c>
       <c r="H78" s="10">
         <v>2</v>
@@ -10538,10 +10538,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="K78" s="10">
-        <v>19008135.274495997</v>
+        <v>21790440.960611559</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10549,7 +10549,7 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C79" s="10">
         <v>6</v>
@@ -10558,25 +10558,25 @@
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>700</v>
+        <v>596</v>
       </c>
       <c r="F79" s="10">
-        <v>13406292.038853647</v>
+        <v>14969353.601374509</v>
       </c>
       <c r="G79" s="10">
-        <v>629</v>
+        <v>934</v>
       </c>
       <c r="H79" s="10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I79" s="10">
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>1099</v>
+        <v>897</v>
       </c>
       <c r="K79" s="10">
-        <v>12587822.709509639</v>
+        <v>14624074.907011259</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10584,7 +10584,7 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C80" s="10">
         <v>1</v>
@@ -10593,25 +10593,25 @@
         <v>7</v>
       </c>
       <c r="E80" s="10">
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="F80" s="10">
-        <v>14534308.575940792</v>
+        <v>16533756.493633192</v>
       </c>
       <c r="G80" s="10">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="H80" s="10">
         <v>3</v>
       </c>
       <c r="I80" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J80" s="10">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="K80" s="10">
-        <v>13056774.364971524</v>
+        <v>14984463.80901321</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10619,34 +10619,34 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="C81" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D81" s="10">
         <v>3</v>
       </c>
       <c r="E81" s="10">
-        <v>502</v>
+        <v>911</v>
       </c>
       <c r="F81" s="10">
-        <v>38552320.650037184</v>
+        <v>43975831.586132079</v>
       </c>
       <c r="G81" s="10">
-        <v>873</v>
+        <v>821</v>
       </c>
       <c r="H81" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I81" s="10">
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>777</v>
+        <v>716</v>
       </c>
       <c r="K81" s="10">
-        <v>31224051.282621074</v>
+        <v>36846421.380385205</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10654,7 +10654,7 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C82" s="10">
         <v>2</v>
@@ -10663,13 +10663,13 @@
         <v>10</v>
       </c>
       <c r="E82" s="10">
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="F82" s="10">
-        <v>22945629.138666265</v>
+        <v>25803193.875584789</v>
       </c>
       <c r="G82" s="10">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="H82" s="10">
         <v>3</v>
@@ -10678,10 +10678,10 @@
         <v>9</v>
       </c>
       <c r="J82" s="10">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="K82" s="10">
-        <v>23789675.00632247</v>
+        <v>26570428.250516757</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10698,25 +10698,25 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>919</v>
+        <v>969</v>
       </c>
       <c r="F83" s="10">
-        <v>18897104.306166232</v>
+        <v>21430456.487673119</v>
       </c>
       <c r="G83" s="10">
-        <v>949</v>
+        <v>1014</v>
       </c>
       <c r="H83" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I83" s="10">
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>771</v>
+        <v>912</v>
       </c>
       <c r="K83" s="10">
-        <v>19078223.4680488</v>
+        <v>21496542.429334331</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10724,7 +10724,7 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C84" s="10">
         <v>2</v>
@@ -10733,13 +10733,13 @@
         <v>5</v>
       </c>
       <c r="E84" s="10">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="F84" s="10">
-        <v>18943363.690892089</v>
+        <v>22212680.787092481</v>
       </c>
       <c r="G84" s="10">
-        <v>969</v>
+        <v>887</v>
       </c>
       <c r="H84" s="10">
         <v>2</v>
@@ -10748,10 +10748,10 @@
         <v>4</v>
       </c>
       <c r="J84" s="10">
-        <v>693</v>
+        <v>829</v>
       </c>
       <c r="K84" s="10">
-        <v>23083990.683582705</v>
+        <v>25862734.284609228</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10759,7 +10759,7 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C85" s="10">
         <v>2</v>
@@ -10768,25 +10768,25 @@
         <v>6</v>
       </c>
       <c r="E85" s="10">
-        <v>791</v>
+        <v>743</v>
       </c>
       <c r="F85" s="10">
-        <v>24876612.513585679</v>
+        <v>28452287.495797113</v>
       </c>
       <c r="G85" s="10">
-        <v>762</v>
+        <v>778</v>
       </c>
       <c r="H85" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I85" s="10">
         <v>7</v>
       </c>
       <c r="J85" s="10">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="K85" s="10">
-        <v>27850529.967314817</v>
+        <v>31363755.234437577</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10794,22 +10794,22 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C86" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" s="10">
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>587</v>
+        <v>522</v>
       </c>
       <c r="F86" s="10">
-        <v>11491400.052304247</v>
+        <v>13050905.489939887</v>
       </c>
       <c r="G86" s="10">
-        <v>540</v>
+        <v>611</v>
       </c>
       <c r="H86" s="10">
         <v>4</v>
@@ -10818,10 +10818,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="K86" s="10">
-        <v>10714929.701390397</v>
+        <v>11988485.977876555</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10829,22 +10829,22 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1770</v>
+        <v>1764</v>
       </c>
       <c r="C87" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D87" s="10">
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1068</v>
+        <v>1312</v>
       </c>
       <c r="F87" s="10">
-        <v>48346216.085946538</v>
+        <v>54521234.381260686</v>
       </c>
       <c r="G87" s="10">
-        <v>1798</v>
+        <v>1639</v>
       </c>
       <c r="H87" s="10">
         <v>2</v>
@@ -10853,10 +10853,10 @@
         <v>9</v>
       </c>
       <c r="J87" s="10">
-        <v>1408</v>
+        <v>1380</v>
       </c>
       <c r="K87" s="10">
-        <v>58448649.984140679</v>
+        <v>66487916.797526561</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10864,7 +10864,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="C88" s="10">
         <v>0</v>
@@ -10873,13 +10873,13 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>606</v>
+        <v>671</v>
       </c>
       <c r="F88" s="10">
-        <v>11404405.748291109</v>
+        <v>12629426.927350204</v>
       </c>
       <c r="G88" s="10">
-        <v>630</v>
+        <v>858</v>
       </c>
       <c r="H88" s="10">
         <v>2</v>
@@ -10888,10 +10888,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>739</v>
+        <v>928</v>
       </c>
       <c r="K88" s="10">
-        <v>12978754.33964923</v>
+        <v>14912277.198876899</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10899,7 +10899,7 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="C89" s="10">
         <v>4</v>
@@ -10908,13 +10908,13 @@
         <v>7</v>
       </c>
       <c r="E89" s="10">
-        <v>569</v>
+        <v>641</v>
       </c>
       <c r="F89" s="10">
-        <v>21469701.985500403</v>
+        <v>24516929.914394263</v>
       </c>
       <c r="G89" s="10">
-        <v>680</v>
+        <v>806</v>
       </c>
       <c r="H89" s="10">
         <v>5</v>
@@ -10923,10 +10923,10 @@
         <v>8</v>
       </c>
       <c r="J89" s="10">
-        <v>741</v>
+        <v>581</v>
       </c>
       <c r="K89" s="10">
-        <v>23423151.156611502</v>
+        <v>26691110.077262778</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10934,7 +10934,7 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C90" s="10">
         <v>2</v>
@@ -10943,13 +10943,13 @@
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>296</v>
+        <v>380</v>
       </c>
       <c r="F90" s="10">
-        <v>5260642.5641915696</v>
+        <v>5910987.391414376</v>
       </c>
       <c r="G90" s="10">
-        <v>374</v>
+        <v>192</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -10958,10 +10958,10 @@
         <v>1</v>
       </c>
       <c r="J90" s="10">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="K90" s="10">
-        <v>4319308.1950398814</v>
+        <v>4445161.1584503073</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.35">
@@ -10969,34 +10969,34 @@
         <v>203</v>
       </c>
       <c r="B91" s="13">
-        <v>84549</v>
+        <v>84407</v>
       </c>
       <c r="C91" s="13">
-        <v>1079</v>
+        <v>1140</v>
       </c>
       <c r="D91" s="13">
         <v>318</v>
       </c>
       <c r="E91" s="13">
-        <v>69895</v>
+        <v>70297</v>
       </c>
       <c r="F91" s="13">
-        <v>2236113285.2862201</v>
+        <v>2541296940.4072208</v>
       </c>
       <c r="G91" s="13">
-        <v>84637</v>
+        <v>83705</v>
       </c>
       <c r="H91" s="13">
-        <v>1539</v>
+        <v>1727</v>
       </c>
       <c r="I91" s="13">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J91" s="13">
-        <v>71296</v>
+        <v>71011</v>
       </c>
       <c r="K91" s="13">
-        <v>2327481078.9661198</v>
+        <v>2629013067.6293702</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -2690,7 +2690,7 @@
         <v>496</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
@@ -3170,7 +3170,7 @@
         <v>494</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
@@ -3570,7 +3570,7 @@
         <v>500</v>
       </c>
       <c r="E21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
@@ -4130,7 +4130,7 @@
         <v>497</v>
       </c>
       <c r="E28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
@@ -5637,6 +5637,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U46"/>
   <conditionalFormatting sqref="U2:U46">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>1</formula>
